--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,28 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -392,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -775,15 +753,16 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -916,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.98</v>
+        <v>26.62</v>
       </c>
       <c r="D2">
-        <v>-0.26</v>
+        <v>-1.33</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -928,46 +907,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.28</v>
+        <v>-27.27</v>
       </c>
       <c r="H2">
-        <v>17.41</v>
+        <v>15.84</v>
       </c>
       <c r="I2">
-        <v>-3.54</v>
+        <v>-4.59</v>
       </c>
       <c r="J2">
-        <v>-2.56</v>
+        <v>-3.24</v>
       </c>
       <c r="K2">
-        <v>-8.390000000000001</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L2">
-        <v>-24.19</v>
+        <v>-26.12</v>
       </c>
       <c r="M2">
-        <v>-11.44</v>
+        <v>-12.04</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P2">
-        <v>27.26</v>
+        <v>27.01</v>
       </c>
       <c r="Q2">
-        <v>27.73</v>
+        <v>27.69</v>
       </c>
       <c r="R2">
-        <v>27.8</v>
+        <v>27.74</v>
       </c>
       <c r="S2">
-        <v>28.46</v>
+        <v>28.43</v>
       </c>
       <c r="T2">
-        <v>-5.2</v>
+        <v>-6.38</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -982,34 +961,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.02</v>
+        <v>33.79</v>
       </c>
       <c r="Z2">
-        <v>-0.15</v>
+        <v>-0.21</v>
       </c>
       <c r="AA2">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="AB2">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AC2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>5.93</v>
+        <v>0.72</v>
       </c>
       <c r="AE2">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="AF2">
-        <v>-19.76</v>
+        <v>-17.43</v>
       </c>
       <c r="AG2">
-        <v>28.56</v>
+        <v>28.65</v>
       </c>
       <c r="AH2">
-        <v>26.9</v>
+        <v>26.72</v>
       </c>
       <c r="AI2">
         <v>29.03</v>
@@ -1018,7 +997,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>32.28</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1029,10 +1008,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D3">
-        <v>0.59</v>
+        <v>-2.74</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1041,46 +1020,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.16</v>
+        <v>-34.02</v>
       </c>
       <c r="H3">
-        <v>15.33</v>
+        <v>12.18</v>
       </c>
       <c r="I3">
-        <v>-2.76</v>
+        <v>-4.14</v>
       </c>
       <c r="J3">
-        <v>-4.57</v>
+        <v>-6.13</v>
       </c>
       <c r="K3">
-        <v>-8.74</v>
+        <v>-10.84</v>
       </c>
       <c r="L3">
-        <v>-30.27</v>
+        <v>-33.09</v>
       </c>
       <c r="M3">
-        <v>-15.31</v>
+        <v>-16.76</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>10.26</v>
+        <v>10.17</v>
       </c>
       <c r="Q3">
-        <v>10.46</v>
+        <v>10.43</v>
       </c>
       <c r="R3">
-        <v>10.73</v>
+        <v>10.71</v>
       </c>
       <c r="S3">
-        <v>11.09</v>
+        <v>11.07</v>
       </c>
       <c r="T3">
-        <v>-7.72</v>
+        <v>-10.12</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1095,43 +1074,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.34</v>
+        <v>31.15</v>
       </c>
       <c r="Z3">
-        <v>-0.14</v>
+        <v>-0.17</v>
       </c>
       <c r="AA3">
         <v>-0.13</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>26.09</v>
+        <v>17.58</v>
       </c>
       <c r="AD3">
-        <v>31.6</v>
+        <v>23.54</v>
       </c>
       <c r="AE3">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>-4.63</v>
+        <v>33.64</v>
       </c>
       <c r="AG3">
-        <v>10.77</v>
+        <v>10.8</v>
       </c>
       <c r="AH3">
-        <v>10.15</v>
+        <v>10.05</v>
       </c>
       <c r="AI3">
-        <v>10.82</v>
+        <v>10.75</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>21.84</v>
+        <v>26.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1142,10 +1121,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>229.9</v>
+        <v>225.6</v>
       </c>
       <c r="D4">
-        <v>-0.15</v>
+        <v>-1.87</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1154,46 +1133,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.56</v>
+        <v>-28.91</v>
       </c>
       <c r="H4">
-        <v>2.59</v>
+        <v>0.67</v>
       </c>
       <c r="I4">
-        <v>-4.01</v>
+        <v>-3.75</v>
       </c>
       <c r="J4">
-        <v>-10.05</v>
+        <v>-9.42</v>
       </c>
       <c r="K4">
-        <v>-4.02</v>
+        <v>-6.76</v>
       </c>
       <c r="L4">
-        <v>-25.35</v>
+        <v>-27.24</v>
       </c>
       <c r="M4">
-        <v>-2.51</v>
+        <v>-3.1</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>231.74</v>
+        <v>229.98</v>
       </c>
       <c r="Q4">
-        <v>238.98</v>
+        <v>237.78</v>
       </c>
       <c r="R4">
-        <v>242.91</v>
+        <v>242.63</v>
       </c>
       <c r="S4">
-        <v>254</v>
+        <v>253.59</v>
       </c>
       <c r="T4">
-        <v>-9.49</v>
+        <v>-11.04</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1208,34 +1187,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.71</v>
+        <v>29.46</v>
       </c>
       <c r="Z4">
-        <v>-4.08</v>
+        <v>-4.56</v>
       </c>
       <c r="AA4">
-        <v>-2.95</v>
+        <v>-3.27</v>
       </c>
       <c r="AB4">
-        <v>-1.13</v>
+        <v>-1.29</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>4.47</v>
+        <v>4.59</v>
       </c>
       <c r="AF4">
-        <v>81.15000000000001</v>
+        <v>21.22</v>
       </c>
       <c r="AG4">
-        <v>249.92</v>
+        <v>249.04</v>
       </c>
       <c r="AH4">
-        <v>228.05</v>
+        <v>226.52</v>
       </c>
       <c r="AI4">
         <v>242.3</v>
@@ -1244,7 +1223,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>42.28</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1255,10 +1234,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>665.55</v>
+        <v>661.85</v>
       </c>
       <c r="D5">
-        <v>-0.48</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1267,46 +1246,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-22.7</v>
+        <v>-23.13</v>
       </c>
       <c r="H5">
-        <v>35.63</v>
+        <v>34.88</v>
       </c>
       <c r="I5">
-        <v>-3.94</v>
+        <v>-5.28</v>
       </c>
       <c r="J5">
-        <v>-1.81</v>
+        <v>-2.81</v>
       </c>
       <c r="K5">
-        <v>23.25</v>
+        <v>21.71</v>
       </c>
       <c r="L5">
-        <v>-20.88</v>
+        <v>-22.58</v>
       </c>
       <c r="M5">
-        <v>-7.63</v>
+        <v>-7.7</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>681.15</v>
+        <v>673.77</v>
       </c>
       <c r="Q5">
-        <v>679.01</v>
+        <v>678.05</v>
       </c>
       <c r="R5">
-        <v>687.65</v>
+        <v>689.9400000000001</v>
       </c>
       <c r="S5">
-        <v>623.91</v>
+        <v>623.5</v>
       </c>
       <c r="T5">
-        <v>6.67</v>
+        <v>6.15</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1321,34 +1300,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>44.02</v>
+        <v>42.82</v>
       </c>
       <c r="Z5">
-        <v>0.49</v>
+        <v>-1.17</v>
       </c>
       <c r="AA5">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="AB5">
-        <v>-2.42</v>
+        <v>-3.26</v>
       </c>
       <c r="AC5">
-        <v>34.4</v>
+        <v>25.94</v>
       </c>
       <c r="AD5">
-        <v>50.28</v>
+        <v>36.75</v>
       </c>
       <c r="AE5">
-        <v>22.6</v>
+        <v>22.64</v>
       </c>
       <c r="AF5">
-        <v>-63.45</v>
+        <v>-43.85</v>
       </c>
       <c r="AG5">
-        <v>720.14</v>
+        <v>719.87</v>
       </c>
       <c r="AH5">
-        <v>637.88</v>
+        <v>636.23</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1357,7 +1336,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>25.15</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1368,58 +1347,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.64</v>
+        <v>25.95</v>
       </c>
       <c r="D6">
-        <v>-0.71</v>
+        <v>-2.59</v>
       </c>
       <c r="E6">
         <v>56.22</v>
       </c>
       <c r="F6">
-        <v>26.64</v>
+        <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-52.61</v>
+        <v>-53.84</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-6.13</v>
+        <v>-6.11</v>
       </c>
       <c r="J6">
-        <v>-8.17</v>
+        <v>-10.55</v>
       </c>
       <c r="K6">
-        <v>-18.13</v>
+        <v>-23.13</v>
       </c>
       <c r="L6">
-        <v>-51.06</v>
+        <v>-52.36</v>
       </c>
       <c r="M6">
-        <v>-12.13</v>
+        <v>-13.08</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>27.07</v>
+        <v>26.73</v>
       </c>
       <c r="Q6">
-        <v>28.44</v>
+        <v>28.29</v>
       </c>
       <c r="R6">
-        <v>29.33</v>
+        <v>29.19</v>
       </c>
       <c r="S6">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="T6">
-        <v>-22.33</v>
+        <v>-24.13</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1434,43 +1413,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.72</v>
+        <v>33.33</v>
       </c>
       <c r="Z6">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
       <c r="AA6">
-        <v>-0.58</v>
+        <v>-0.63</v>
       </c>
       <c r="AB6">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AC6">
-        <v>12.66</v>
+        <v>7.43</v>
       </c>
       <c r="AD6">
-        <v>18.05</v>
+        <v>12.48</v>
       </c>
       <c r="AE6">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="AF6">
-        <v>-46.02</v>
+        <v>-51.77</v>
       </c>
       <c r="AG6">
-        <v>31.08</v>
+        <v>31.14</v>
       </c>
       <c r="AH6">
-        <v>25.81</v>
+        <v>25.45</v>
       </c>
       <c r="AI6">
-        <v>29.41</v>
+        <v>29.4</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>30.69</v>
+        <v>33.58</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1481,37 +1460,37 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="D7">
-        <v>-1.3</v>
+        <v>-1.77</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="G7">
-        <v>-20.66</v>
+        <v>-22.06</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.88</v>
+        <v>-5.67</v>
       </c>
       <c r="J7">
-        <v>-4.52</v>
+        <v>-5.7</v>
       </c>
       <c r="K7">
-        <v>-3.79</v>
+        <v>-7.04</v>
       </c>
       <c r="L7">
-        <v>-8.199999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="M7">
-        <v>3.21</v>
+        <v>2.78</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1520,19 +1499,19 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1282.98</v>
+        <v>1268.14</v>
       </c>
       <c r="Q7">
-        <v>1300.53</v>
+        <v>1296.5</v>
       </c>
       <c r="R7">
-        <v>1301.2</v>
+        <v>1299.48</v>
       </c>
       <c r="S7">
-        <v>1379.69</v>
+        <v>1378.06</v>
       </c>
       <c r="T7">
-        <v>-8.859999999999999</v>
+        <v>-10.36</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1547,43 +1526,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.12</v>
+        <v>32.56</v>
       </c>
       <c r="Z7">
-        <v>-7.47</v>
+        <v>-11.33</v>
       </c>
       <c r="AA7">
-        <v>-2.89</v>
+        <v>-4.58</v>
       </c>
       <c r="AB7">
-        <v>-4.58</v>
+        <v>-6.75</v>
       </c>
       <c r="AC7">
-        <v>7.7</v>
+        <v>2.45</v>
       </c>
       <c r="AD7">
-        <v>24.73</v>
+        <v>10.83</v>
       </c>
       <c r="AE7">
-        <v>21.15</v>
+        <v>21.36</v>
       </c>
       <c r="AF7">
-        <v>-18.05</v>
+        <v>28.29</v>
       </c>
       <c r="AG7">
-        <v>1337.45</v>
+        <v>1342.75</v>
       </c>
       <c r="AH7">
-        <v>1263.62</v>
+        <v>1250.25</v>
       </c>
       <c r="AI7">
-        <v>1323.65</v>
+        <v>1311.43</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>26.58</v>
+        <v>30.95</v>
       </c>
     </row>
   </sheetData>
@@ -1744,47 +1723,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1792,836 +1736,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>61</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-2.56</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.78</v>
+      <c r="D7" s="5">
+        <v>-3.24</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-4.57</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.12</v>
+      <c r="D8" s="5">
+        <v>-6.13</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-10.08</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.05</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.03</v>
+      <c r="D9" s="5">
+        <v>-9.42</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.63</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-1.81</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.91</v>
+      <c r="D10" s="5">
+        <v>-2.81</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-6.55</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-8.17</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.62</v>
+      <c r="D11" s="5">
+        <v>-10.55</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
+        <v>-4.52</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-5.7</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.54</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.59</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.76</v>
+      </c>
+      <c r="D14" s="5">
         <v>-4.14</v>
       </c>
-      <c r="D12" s="6">
-        <v>-4.52</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="E14" s="6">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-3.75</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.94</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-5.28</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-6.13</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-6.11</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.88</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-5.67</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-24.19</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.12</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.88</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.76</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-30.27</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-33.09</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.03</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-25.35</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-27.24</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.1</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.94</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-20.88</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-22.58</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.13</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-51.06</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-52.36</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.19</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.88</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-24.67</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-24.19</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-31.28</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-30.27</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-8.74</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-10.84</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-25.99</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-25.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-4.02</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-18.86</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-20.88</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>23.25</v>
+      </c>
+      <c r="D28" s="5">
+        <v>21.71</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-51.24</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-51.06</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-18.13</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-23.13</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-7.15</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-3.79</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-7.04</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.48</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-7.91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-26.28</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-27.27</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-4.78</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-8.74</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-32.16</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-34.02</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-27.56</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-28.91</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>24.26</v>
-      </c>
-      <c r="D28" s="6">
-        <v>23.25</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-22.7</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-23.13</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-14.85</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-18.13</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.61</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-53.84</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-1.47</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-20.66</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-22.06</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-26.09</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-26.28</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>26.98</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.62</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-32.56</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-32.16</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10.23</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-27.45</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-27.56</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>229.9</v>
+      </c>
+      <c r="D39" s="5">
+        <v>225.6</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-22.32</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-22.7</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>665.55</v>
+      </c>
+      <c r="D40" s="5">
+        <v>661.85</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-52.28</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-52.61</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.64</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.95</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-19.62</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-20.66</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1257.5</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1235.3</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-22.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>27.05</v>
-      </c>
-      <c r="D37" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>38.02</v>
+      </c>
+      <c r="D43" s="5">
+        <v>33.79</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-4.23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>10.17</v>
-      </c>
-      <c r="D38" s="6">
-        <v>10.23</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>38.34</v>
+      </c>
+      <c r="D44" s="5">
+        <v>31.15</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-7.19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>230.25</v>
-      </c>
-      <c r="D39" s="6">
-        <v>229.9</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>33.71</v>
+      </c>
+      <c r="D45" s="5">
+        <v>29.46</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-4.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>668.75</v>
-      </c>
-      <c r="D40" s="6">
-        <v>665.55</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>44.02</v>
+      </c>
+      <c r="D46" s="5">
+        <v>42.82</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>26.83</v>
-      </c>
-      <c r="D41" s="6">
-        <v>26.64</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>36.72</v>
+      </c>
+      <c r="D47" s="5">
+        <v>33.33</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1274</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1257.5</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-16.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>37.12</v>
+      </c>
+      <c r="D48" s="5">
+        <v>32.56</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-4.56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>38.9</v>
-      </c>
-      <c r="D43" s="6">
-        <v>38.02</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-19.76</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-17.43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>35.37</v>
-      </c>
-      <c r="D44" s="6">
-        <v>38.34</v>
-      </c>
-      <c r="E44" s="8">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-4.63</v>
+      </c>
+      <c r="D50" s="5">
+        <v>33.64</v>
+      </c>
+      <c r="E50" s="7">
+        <v>38.27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>34.08</v>
-      </c>
-      <c r="D45" s="6">
-        <v>33.71</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="D51" s="5">
+        <v>21.22</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-59.93</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>45.03</v>
-      </c>
-      <c r="D46" s="6">
-        <v>44.02</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-63.45</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-43.85</v>
+      </c>
+      <c r="E52" s="7">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>37.7</v>
-      </c>
-      <c r="D47" s="6">
-        <v>36.72</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-46.02</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-51.77</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>41.09</v>
-      </c>
-      <c r="D48" s="6">
-        <v>37.12</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.97</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="6">
-        <v>-19.78</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-19.76</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-34.2</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-4.63</v>
-      </c>
-      <c r="E50" s="8">
-        <v>29.57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-27.66</v>
-      </c>
-      <c r="D51" s="6">
-        <v>81.15000000000001</v>
-      </c>
-      <c r="E51" s="8">
-        <v>108.81</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-14.23</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-63.45</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-49.22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-60.44</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-46.02</v>
-      </c>
-      <c r="E53" s="8">
-        <v>14.42</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>-18.05</v>
       </c>
+      <c r="D54" s="5">
+        <v>28.29</v>
+      </c>
       <c r="E54" s="7">
-        <v>-5.35</v>
+        <v>46.34</v>
       </c>
     </row>
   </sheetData>
@@ -2647,60 +2591,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>38</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>33.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-3.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-5.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2802,43 +2746,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0321</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0251</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.07629999999999999</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1144</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1213</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1531</v>
+      <c r="A2" s="13">
+        <v>0.0278</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.031</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.077</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1204</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1308</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1676</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -895,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.62</v>
+        <v>26.42</v>
       </c>
       <c r="D2">
-        <v>-1.33</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -907,46 +907,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.27</v>
+        <v>-27.81</v>
       </c>
       <c r="H2">
-        <v>15.84</v>
+        <v>14.97</v>
       </c>
       <c r="I2">
-        <v>-4.59</v>
+        <v>-2.8</v>
       </c>
       <c r="J2">
-        <v>-3.24</v>
+        <v>-3.96</v>
       </c>
       <c r="K2">
-        <v>-8.050000000000001</v>
+        <v>-8.74</v>
       </c>
       <c r="L2">
-        <v>-26.12</v>
+        <v>-26.57</v>
       </c>
       <c r="M2">
-        <v>-12.04</v>
+        <v>-11.93</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P2">
-        <v>27.01</v>
+        <v>26.86</v>
       </c>
       <c r="Q2">
-        <v>27.69</v>
+        <v>27.64</v>
       </c>
       <c r="R2">
-        <v>27.74</v>
+        <v>27.7</v>
       </c>
       <c r="S2">
-        <v>28.43</v>
+        <v>28.41</v>
       </c>
       <c r="T2">
-        <v>-6.38</v>
+        <v>-6.99</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -961,43 +961,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.79</v>
+        <v>31.68</v>
       </c>
       <c r="Z2">
-        <v>-0.21</v>
+        <v>-0.27</v>
       </c>
       <c r="AA2">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="AB2">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
+        <v>0.36</v>
+      </c>
+      <c r="AE2">
         <v>0.72</v>
       </c>
-      <c r="AE2">
-        <v>0.73</v>
-      </c>
       <c r="AF2">
-        <v>-17.43</v>
+        <v>-27.12</v>
       </c>
       <c r="AG2">
-        <v>28.65</v>
+        <v>28.75</v>
       </c>
       <c r="AH2">
-        <v>26.72</v>
+        <v>26.52</v>
       </c>
       <c r="AI2">
-        <v>29.03</v>
+        <v>28.57</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>33.85</v>
+        <v>36.55</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,10 +1008,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>-2.74</v>
+        <v>0.5</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1020,46 +1020,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-34.02</v>
+        <v>-33.69</v>
       </c>
       <c r="H3">
-        <v>12.18</v>
+        <v>12.74</v>
       </c>
       <c r="I3">
-        <v>-4.14</v>
+        <v>-2.82</v>
       </c>
       <c r="J3">
-        <v>-6.13</v>
+        <v>-5.66</v>
       </c>
       <c r="K3">
-        <v>-10.84</v>
+        <v>-10.87</v>
       </c>
       <c r="L3">
-        <v>-33.09</v>
+        <v>-32.71</v>
       </c>
       <c r="M3">
-        <v>-16.76</v>
+        <v>-16.41</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>10.17</v>
+        <v>10.11</v>
       </c>
       <c r="Q3">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="R3">
-        <v>10.71</v>
+        <v>10.68</v>
       </c>
       <c r="S3">
-        <v>11.07</v>
+        <v>11.05</v>
       </c>
       <c r="T3">
-        <v>-10.12</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1074,43 +1074,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.15</v>
+        <v>33.55</v>
       </c>
       <c r="Z3">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="AA3">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AC3">
-        <v>17.58</v>
+        <v>17.65</v>
       </c>
       <c r="AD3">
-        <v>23.54</v>
+        <v>20.44</v>
       </c>
       <c r="AE3">
         <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>33.64</v>
+        <v>-14.9</v>
       </c>
       <c r="AG3">
-        <v>10.8</v>
+        <v>10.82</v>
       </c>
       <c r="AH3">
-        <v>10.05</v>
+        <v>9.98</v>
       </c>
       <c r="AI3">
-        <v>10.75</v>
+        <v>10.72</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>26.13</v>
+        <v>29.85</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1121,10 +1121,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>225.6</v>
+        <v>224.84</v>
       </c>
       <c r="D4">
-        <v>-1.87</v>
+        <v>-0.34</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1133,46 +1133,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-28.91</v>
+        <v>-29.15</v>
       </c>
       <c r="H4">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I4">
-        <v>-3.75</v>
+        <v>-3.56</v>
       </c>
       <c r="J4">
-        <v>-9.42</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K4">
-        <v>-6.76</v>
+        <v>-7.47</v>
       </c>
       <c r="L4">
-        <v>-27.24</v>
+        <v>-27.63</v>
       </c>
       <c r="M4">
-        <v>-3.1</v>
+        <v>-3.21</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>229.98</v>
+        <v>228.32</v>
       </c>
       <c r="Q4">
-        <v>237.78</v>
+        <v>236.73</v>
       </c>
       <c r="R4">
-        <v>242.63</v>
+        <v>242.26</v>
       </c>
       <c r="S4">
-        <v>253.59</v>
+        <v>253.18</v>
       </c>
       <c r="T4">
-        <v>-11.04</v>
+        <v>-11.19</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1187,16 +1187,16 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.46</v>
+        <v>28.77</v>
       </c>
       <c r="Z4">
-        <v>-4.56</v>
+        <v>-4.94</v>
       </c>
       <c r="AA4">
-        <v>-3.27</v>
+        <v>-3.61</v>
       </c>
       <c r="AB4">
-        <v>-1.29</v>
+        <v>-1.33</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1205,25 +1205,25 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="AF4">
-        <v>21.22</v>
+        <v>10.42</v>
       </c>
       <c r="AG4">
-        <v>249.04</v>
+        <v>248.72</v>
       </c>
       <c r="AH4">
-        <v>226.52</v>
+        <v>224.74</v>
       </c>
       <c r="AI4">
-        <v>242.3</v>
+        <v>240.04</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>45.61</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,10 +1234,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>661.85</v>
+        <v>673.7</v>
       </c>
       <c r="D5">
-        <v>-0.5600000000000001</v>
+        <v>1.79</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1246,46 +1246,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.13</v>
+        <v>-21.75</v>
       </c>
       <c r="H5">
-        <v>34.88</v>
+        <v>37.29</v>
       </c>
       <c r="I5">
-        <v>-5.28</v>
+        <v>-2.96</v>
       </c>
       <c r="J5">
-        <v>-2.81</v>
+        <v>-1.07</v>
       </c>
       <c r="K5">
-        <v>21.71</v>
+        <v>22.21</v>
       </c>
       <c r="L5">
-        <v>-22.58</v>
+        <v>-21.68</v>
       </c>
       <c r="M5">
-        <v>-7.7</v>
+        <v>-7.37</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>673.77</v>
+        <v>669.66</v>
       </c>
       <c r="Q5">
-        <v>678.05</v>
+        <v>678.67</v>
       </c>
       <c r="R5">
-        <v>689.9400000000001</v>
+        <v>692.3200000000001</v>
       </c>
       <c r="S5">
-        <v>623.5</v>
+        <v>623.1900000000001</v>
       </c>
       <c r="T5">
-        <v>6.15</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1300,34 +1300,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>42.82</v>
+        <v>47.72</v>
       </c>
       <c r="Z5">
-        <v>-1.17</v>
+        <v>-1.52</v>
       </c>
       <c r="AA5">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
-        <v>-3.26</v>
+        <v>-2.88</v>
       </c>
       <c r="AC5">
-        <v>25.94</v>
+        <v>30.22</v>
       </c>
       <c r="AD5">
-        <v>36.75</v>
+        <v>30.19</v>
       </c>
       <c r="AE5">
-        <v>22.64</v>
+        <v>23.23</v>
       </c>
       <c r="AF5">
-        <v>-43.85</v>
+        <v>-60.41</v>
       </c>
       <c r="AG5">
-        <v>719.87</v>
+        <v>719.8099999999999</v>
       </c>
       <c r="AH5">
-        <v>636.23</v>
+        <v>637.54</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1336,7 +1336,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>24.44</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1347,10 +1347,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.95</v>
+        <v>26.12</v>
       </c>
       <c r="D6">
-        <v>-2.59</v>
+        <v>0.66</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1359,25 +1359,25 @@
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-53.84</v>
+        <v>-53.54</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.66</v>
       </c>
       <c r="I6">
-        <v>-6.11</v>
+        <v>-4.32</v>
       </c>
       <c r="J6">
-        <v>-10.55</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K6">
-        <v>-23.13</v>
+        <v>-23.63</v>
       </c>
       <c r="L6">
-        <v>-52.36</v>
+        <v>-51.83</v>
       </c>
       <c r="M6">
-        <v>-13.08</v>
+        <v>-12.87</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1386,19 +1386,19 @@
         <v>4</v>
       </c>
       <c r="P6">
-        <v>26.73</v>
+        <v>26.49</v>
       </c>
       <c r="Q6">
-        <v>28.29</v>
+        <v>28.17</v>
       </c>
       <c r="R6">
-        <v>29.19</v>
+        <v>29.08</v>
       </c>
       <c r="S6">
-        <v>34.2</v>
+        <v>34.11</v>
       </c>
       <c r="T6">
-        <v>-24.13</v>
+        <v>-23.42</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1413,43 +1413,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>33.33</v>
+        <v>34.92</v>
       </c>
       <c r="Z6">
-        <v>-0.83</v>
+        <v>-0.87</v>
       </c>
       <c r="AA6">
-        <v>-0.63</v>
+        <v>-0.68</v>
       </c>
       <c r="AB6">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AC6">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="AD6">
-        <v>12.48</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF6">
-        <v>-51.77</v>
+        <v>-34.23</v>
       </c>
       <c r="AG6">
-        <v>31.14</v>
+        <v>31.18</v>
       </c>
       <c r="AH6">
-        <v>25.45</v>
+        <v>25.17</v>
       </c>
       <c r="AI6">
-        <v>29.4</v>
+        <v>28.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>33.58</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1460,10 +1460,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1235.3</v>
+        <v>1240</v>
       </c>
       <c r="D7">
-        <v>-1.77</v>
+        <v>0.38</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1472,25 +1472,25 @@
         <v>1235.3</v>
       </c>
       <c r="G7">
-        <v>-22.06</v>
+        <v>-21.77</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="I7">
-        <v>-5.67</v>
+        <v>-4.24</v>
       </c>
       <c r="J7">
-        <v>-5.7</v>
+        <v>-5.78</v>
       </c>
       <c r="K7">
-        <v>-7.04</v>
+        <v>-6.96</v>
       </c>
       <c r="L7">
-        <v>-9.880000000000001</v>
+        <v>-9.94</v>
       </c>
       <c r="M7">
-        <v>2.78</v>
+        <v>2.43</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1499,19 +1499,19 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1268.14</v>
+        <v>1257.16</v>
       </c>
       <c r="Q7">
-        <v>1296.5</v>
+        <v>1292.4</v>
       </c>
       <c r="R7">
-        <v>1299.48</v>
+        <v>1298.11</v>
       </c>
       <c r="S7">
-        <v>1378.06</v>
+        <v>1376.48</v>
       </c>
       <c r="T7">
-        <v>-10.36</v>
+        <v>-9.91</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1526,43 +1526,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>32.56</v>
+        <v>34.4</v>
       </c>
       <c r="Z7">
-        <v>-11.33</v>
+        <v>-13.85</v>
       </c>
       <c r="AA7">
-        <v>-4.58</v>
+        <v>-6.43</v>
       </c>
       <c r="AB7">
-        <v>-6.75</v>
+        <v>-7.42</v>
       </c>
       <c r="AC7">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="AD7">
-        <v>10.83</v>
+        <v>4.29</v>
       </c>
       <c r="AE7">
-        <v>21.36</v>
+        <v>21.24</v>
       </c>
       <c r="AF7">
-        <v>28.29</v>
+        <v>-7.51</v>
       </c>
       <c r="AG7">
-        <v>1342.75</v>
+        <v>1343.43</v>
       </c>
       <c r="AH7">
-        <v>1250.25</v>
+        <v>1241.37</v>
       </c>
       <c r="AI7">
-        <v>1311.43</v>
+        <v>1311.23</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>30.95</v>
+        <v>34.74</v>
       </c>
     </row>
   </sheetData>
@@ -1760,13 +1760,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.56</v>
+        <v>-3.24</v>
       </c>
       <c r="D7" s="5">
-        <v>-3.24</v>
+        <v>-3.96</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.68</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1777,13 +1777,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.57</v>
+        <v>-6.13</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.13</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-1.56</v>
+        <v>-5.66</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1794,13 +1794,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.05</v>
+        <v>-9.42</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.63</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1811,13 +1811,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-1.81</v>
+        <v>-2.81</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.74</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1828,13 +1828,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-8.17</v>
+        <v>-10.55</v>
       </c>
       <c r="D11" s="5">
-        <v>-10.55</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.38</v>
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1845,13 +1845,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.52</v>
+        <v>-5.7</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.7</v>
+        <v>-5.78</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.18</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1862,13 +1862,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-3.54</v>
+        <v>-4.59</v>
       </c>
       <c r="D13" s="5">
-        <v>-4.59</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.05</v>
+        <v>-2.8</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1879,13 +1879,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.76</v>
+        <v>-4.14</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.38</v>
+        <v>-2.82</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.32</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1896,13 +1896,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.01</v>
+        <v>-3.75</v>
       </c>
       <c r="D15" s="5">
-        <v>-3.75</v>
+        <v>-3.56</v>
       </c>
       <c r="E15" s="7">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1913,13 +1913,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-3.94</v>
+        <v>-5.28</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.28</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.34</v>
+        <v>-2.96</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1930,13 +1930,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-6.13</v>
+        <v>-6.11</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.11</v>
+        <v>-4.32</v>
       </c>
       <c r="E17" s="7">
-        <v>0.02</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1947,13 +1947,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.88</v>
+        <v>-5.67</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.67</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.79</v>
+        <v>-4.24</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1964,13 +1964,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-24.19</v>
+        <v>-26.12</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.12</v>
+        <v>-26.57</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.93</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1981,13 +1981,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-30.27</v>
+        <v>-33.09</v>
       </c>
       <c r="D20" s="5">
-        <v>-33.09</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.82</v>
+        <v>-32.71</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1998,13 +1998,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-25.35</v>
+        <v>-27.24</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.24</v>
+        <v>-27.63</v>
       </c>
       <c r="E21" s="6">
-        <v>-1.89</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2015,13 +2015,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-20.88</v>
+        <v>-22.58</v>
       </c>
       <c r="D22" s="5">
-        <v>-22.58</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.7</v>
+        <v>-21.68</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2032,13 +2032,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-51.06</v>
+        <v>-52.36</v>
       </c>
       <c r="D23" s="5">
-        <v>-52.36</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.3</v>
+        <v>-51.83</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2049,13 +2049,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-8.199999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D24" s="5">
-        <v>-9.880000000000001</v>
+        <v>-9.94</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.68</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2066,13 +2066,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-8.390000000000001</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D25" s="5">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.34</v>
+        <v>-8.74</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2083,13 +2083,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-8.74</v>
+        <v>-10.84</v>
       </c>
       <c r="D26" s="5">
-        <v>-10.84</v>
+        <v>-10.87</v>
       </c>
       <c r="E26" s="6">
-        <v>-2.1</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2100,13 +2100,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-4.02</v>
+        <v>-6.76</v>
       </c>
       <c r="D27" s="5">
-        <v>-6.76</v>
+        <v>-7.47</v>
       </c>
       <c r="E27" s="6">
-        <v>-2.74</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2117,13 +2117,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>23.25</v>
+        <v>21.71</v>
       </c>
       <c r="D28" s="5">
-        <v>21.71</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.54</v>
+        <v>22.21</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2134,13 +2134,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-18.13</v>
+        <v>-23.13</v>
       </c>
       <c r="D29" s="5">
-        <v>-23.13</v>
+        <v>-23.63</v>
       </c>
       <c r="E29" s="6">
-        <v>-5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2151,13 +2151,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-3.79</v>
+        <v>-7.04</v>
       </c>
       <c r="D30" s="5">
-        <v>-7.04</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-3.25</v>
+        <v>-6.96</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2168,13 +2168,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-26.28</v>
+        <v>-27.27</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.27</v>
+        <v>-27.81</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.99</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2185,13 +2185,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-32.16</v>
+        <v>-34.02</v>
       </c>
       <c r="D32" s="5">
-        <v>-34.02</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.86</v>
+        <v>-33.69</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2202,13 +2202,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-27.56</v>
+        <v>-28.91</v>
       </c>
       <c r="D33" s="5">
-        <v>-28.91</v>
+        <v>-29.15</v>
       </c>
       <c r="E33" s="6">
-        <v>-1.35</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2219,13 +2219,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-22.7</v>
+        <v>-23.13</v>
       </c>
       <c r="D34" s="5">
-        <v>-23.13</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-0.43</v>
+        <v>-21.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2236,13 +2236,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-52.61</v>
+        <v>-53.84</v>
       </c>
       <c r="D35" s="5">
-        <v>-53.84</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.23</v>
+        <v>-53.54</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2253,13 +2253,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-20.66</v>
+        <v>-22.06</v>
       </c>
       <c r="D36" s="5">
-        <v>-22.06</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.4</v>
+        <v>-21.77</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2270,13 +2270,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>26.98</v>
+        <v>26.62</v>
       </c>
       <c r="D37" s="5">
-        <v>26.62</v>
+        <v>26.42</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2287,13 +2287,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>10.23</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D38" s="5">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.28</v>
+        <v>10</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.05</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2304,13 +2304,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>229.9</v>
+        <v>225.6</v>
       </c>
       <c r="D39" s="5">
-        <v>225.6</v>
+        <v>224.84</v>
       </c>
       <c r="E39" s="6">
-        <v>-4.3</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2321,13 +2321,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>665.55</v>
+        <v>661.85</v>
       </c>
       <c r="D40" s="5">
-        <v>661.85</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-3.7</v>
+        <v>673.7</v>
+      </c>
+      <c r="E40" s="7">
+        <v>11.85</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2338,13 +2338,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>26.64</v>
+        <v>25.95</v>
       </c>
       <c r="D41" s="5">
-        <v>25.95</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.6899999999999999</v>
+        <v>26.12</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2355,13 +2355,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1257.5</v>
+        <v>1235.3</v>
       </c>
       <c r="D42" s="5">
-        <v>1235.3</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-22.2</v>
+        <v>1240</v>
+      </c>
+      <c r="E42" s="7">
+        <v>4.7</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2372,13 +2372,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>38.02</v>
+        <v>33.79</v>
       </c>
       <c r="D43" s="5">
-        <v>33.79</v>
+        <v>31.68</v>
       </c>
       <c r="E43" s="6">
-        <v>-4.23</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2389,13 +2389,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="5">
-        <v>38.34</v>
+        <v>31.15</v>
       </c>
       <c r="D44" s="5">
-        <v>31.15</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-7.19</v>
+        <v>33.55</v>
+      </c>
+      <c r="E44" s="7">
+        <v>2.4</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2406,13 +2406,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>33.71</v>
+        <v>29.46</v>
       </c>
       <c r="D45" s="5">
-        <v>29.46</v>
+        <v>28.77</v>
       </c>
       <c r="E45" s="6">
-        <v>-4.25</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2423,13 +2423,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>44.02</v>
+        <v>42.82</v>
       </c>
       <c r="D46" s="5">
-        <v>42.82</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-1.2</v>
+        <v>47.72</v>
+      </c>
+      <c r="E46" s="7">
+        <v>4.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2440,13 +2440,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>36.72</v>
+        <v>33.33</v>
       </c>
       <c r="D47" s="5">
-        <v>33.33</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-3.39</v>
+        <v>34.92</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2457,13 +2457,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>37.12</v>
+        <v>32.56</v>
       </c>
       <c r="D48" s="5">
-        <v>32.56</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-4.56</v>
+        <v>34.4</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.84</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2474,13 +2474,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>-19.76</v>
+        <v>-17.43</v>
       </c>
       <c r="D49" s="5">
-        <v>-17.43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.33</v>
+        <v>-27.12</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-9.69</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2491,13 +2491,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>-4.63</v>
+        <v>33.64</v>
       </c>
       <c r="D50" s="5">
-        <v>33.64</v>
-      </c>
-      <c r="E50" s="7">
-        <v>38.27</v>
+        <v>-14.9</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-48.54</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2508,13 +2508,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>81.15000000000001</v>
+        <v>21.22</v>
       </c>
       <c r="D51" s="5">
-        <v>21.22</v>
+        <v>10.42</v>
       </c>
       <c r="E51" s="6">
-        <v>-59.93</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2525,13 +2525,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-63.45</v>
+        <v>-43.85</v>
       </c>
       <c r="D52" s="5">
-        <v>-43.85</v>
-      </c>
-      <c r="E52" s="7">
-        <v>19.6</v>
+        <v>-60.41</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-16.56</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2542,13 +2542,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-46.02</v>
+        <v>-51.77</v>
       </c>
       <c r="D53" s="5">
-        <v>-51.77</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-5.75</v>
+        <v>-34.23</v>
+      </c>
+      <c r="E53" s="7">
+        <v>17.54</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2559,13 +2559,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>-18.05</v>
+        <v>28.29</v>
       </c>
       <c r="D54" s="5">
-        <v>28.29</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46.34</v>
+        <v>-7.51</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-35.8</v>
       </c>
     </row>
   </sheetData>
@@ -2630,16 +2630,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>33.9</v>
+        <v>35.2</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.7</v>
+        <v>-5.9</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0278</v>
+        <v>0.0243</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.031</v>
+        <v>-0.0321</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.077</v>
+        <v>-0.0737</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1204</v>
+        <v>-0.1193</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1308</v>
+        <v>-0.1287</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1676</v>
+        <v>-0.1641</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.8 → 38.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t>38.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -753,9 +781,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -895,10 +921,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.42</v>
+        <v>26.45</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -907,46 +933,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.81</v>
+        <v>-27.73</v>
       </c>
       <c r="H2">
-        <v>14.97</v>
+        <v>15.1</v>
       </c>
       <c r="I2">
-        <v>-2.8</v>
+        <v>-2.79</v>
       </c>
       <c r="J2">
-        <v>-3.96</v>
+        <v>-3.5</v>
       </c>
       <c r="K2">
-        <v>-8.74</v>
+        <v>-15.52</v>
       </c>
       <c r="L2">
-        <v>-26.57</v>
+        <v>-25.81</v>
       </c>
       <c r="M2">
-        <v>-11.93</v>
+        <v>-11.55</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>26.86</v>
+        <v>26.7</v>
       </c>
       <c r="Q2">
-        <v>27.64</v>
+        <v>27.59</v>
       </c>
       <c r="R2">
-        <v>27.7</v>
+        <v>27.66</v>
       </c>
       <c r="S2">
-        <v>28.41</v>
+        <v>28.38</v>
       </c>
       <c r="T2">
-        <v>-6.99</v>
+        <v>-6.8</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -961,43 +987,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.68</v>
+        <v>32.36</v>
       </c>
       <c r="Z2">
-        <v>-0.27</v>
+        <v>-0.31</v>
       </c>
       <c r="AA2">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AB2">
         <v>-0.15</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AD2">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AE2">
         <v>0.72</v>
       </c>
       <c r="AF2">
-        <v>-27.12</v>
+        <v>-5.73</v>
       </c>
       <c r="AG2">
-        <v>28.75</v>
+        <v>28.82</v>
       </c>
       <c r="AH2">
-        <v>26.52</v>
+        <v>26.36</v>
       </c>
       <c r="AI2">
-        <v>28.57</v>
+        <v>28.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>36.55</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,10 +1034,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1020,46 +1046,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.69</v>
+        <v>-33.55</v>
       </c>
       <c r="H3">
-        <v>12.74</v>
+        <v>12.97</v>
       </c>
       <c r="I3">
-        <v>-2.82</v>
+        <v>-1.96</v>
       </c>
       <c r="J3">
-        <v>-5.66</v>
+        <v>-4.66</v>
       </c>
       <c r="K3">
-        <v>-10.87</v>
+        <v>-13.62</v>
       </c>
       <c r="L3">
-        <v>-32.71</v>
+        <v>-32.43</v>
       </c>
       <c r="M3">
-        <v>-16.41</v>
+        <v>-16.17</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P3">
-        <v>10.11</v>
+        <v>10.07</v>
       </c>
       <c r="Q3">
-        <v>10.4</v>
+        <v>10.38</v>
       </c>
       <c r="R3">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
       <c r="S3">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="T3">
-        <v>-9.539999999999999</v>
+        <v>-9.24</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1074,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.55</v>
+        <v>34.53</v>
       </c>
       <c r="Z3">
         <v>-0.18</v>
       </c>
       <c r="AA3">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AB3">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>17.65</v>
+        <v>12.4</v>
       </c>
       <c r="AD3">
-        <v>20.44</v>
+        <v>15.88</v>
       </c>
       <c r="AE3">
         <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>-14.9</v>
+        <v>-3.27</v>
       </c>
       <c r="AG3">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="AH3">
-        <v>9.98</v>
+        <v>9.93</v>
       </c>
       <c r="AI3">
         <v>10.72</v>
@@ -1110,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29.85</v>
+        <v>33.07</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1121,10 +1147,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>224.84</v>
+        <v>229.3</v>
       </c>
       <c r="D4">
-        <v>-0.34</v>
+        <v>1.98</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1133,46 +1159,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-29.15</v>
+        <v>-27.75</v>
       </c>
       <c r="H4">
-        <v>0.33</v>
+        <v>2.32</v>
       </c>
       <c r="I4">
-        <v>-3.56</v>
+        <v>-0.74</v>
       </c>
       <c r="J4">
-        <v>-9.970000000000001</v>
+        <v>-6.71</v>
       </c>
       <c r="K4">
-        <v>-7.47</v>
+        <v>-6.06</v>
       </c>
       <c r="L4">
-        <v>-27.63</v>
+        <v>-26.32</v>
       </c>
       <c r="M4">
-        <v>-3.21</v>
+        <v>-2.58</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>228.32</v>
+        <v>227.98</v>
       </c>
       <c r="Q4">
-        <v>236.73</v>
+        <v>236.04</v>
       </c>
       <c r="R4">
-        <v>242.26</v>
+        <v>242.25</v>
       </c>
       <c r="S4">
-        <v>253.18</v>
+        <v>252.8</v>
       </c>
       <c r="T4">
-        <v>-11.19</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1187,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.77</v>
+        <v>37.95</v>
       </c>
       <c r="Z4">
-        <v>-4.94</v>
+        <v>-4.83</v>
       </c>
       <c r="AA4">
-        <v>-3.61</v>
+        <v>-3.85</v>
       </c>
       <c r="AB4">
-        <v>-1.33</v>
+        <v>-0.98</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>19.58</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="AE4">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="AF4">
-        <v>10.42</v>
+        <v>13.9</v>
       </c>
       <c r="AG4">
-        <v>248.72</v>
+        <v>248.07</v>
       </c>
       <c r="AH4">
-        <v>224.74</v>
+        <v>224.01</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1223,7 +1249,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>48.75</v>
+        <v>47.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>673.7</v>
+        <v>674.05</v>
       </c>
       <c r="D5">
-        <v>1.79</v>
+        <v>0.05</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1246,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.75</v>
+        <v>-21.71</v>
       </c>
       <c r="H5">
-        <v>37.29</v>
+        <v>37.36</v>
       </c>
       <c r="I5">
-        <v>-2.96</v>
+        <v>-0.65</v>
       </c>
       <c r="J5">
-        <v>-1.07</v>
+        <v>1.93</v>
       </c>
       <c r="K5">
-        <v>22.21</v>
+        <v>22.71</v>
       </c>
       <c r="L5">
-        <v>-21.68</v>
+        <v>-21.62</v>
       </c>
       <c r="M5">
-        <v>-7.37</v>
+        <v>-7.29</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>669.66</v>
+        <v>668.78</v>
       </c>
       <c r="Q5">
-        <v>678.67</v>
+        <v>679.35</v>
       </c>
       <c r="R5">
-        <v>692.3200000000001</v>
+        <v>694.99</v>
       </c>
       <c r="S5">
-        <v>623.1900000000001</v>
+        <v>622.87</v>
       </c>
       <c r="T5">
-        <v>8.109999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1300,34 +1326,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.72</v>
+        <v>47.87</v>
       </c>
       <c r="Z5">
-        <v>-1.52</v>
+        <v>-1.74</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>0.75</v>
       </c>
       <c r="AB5">
-        <v>-2.88</v>
+        <v>-2.48</v>
       </c>
       <c r="AC5">
-        <v>30.22</v>
+        <v>31.58</v>
       </c>
       <c r="AD5">
-        <v>30.19</v>
+        <v>29.25</v>
       </c>
       <c r="AE5">
-        <v>23.23</v>
+        <v>22.5</v>
       </c>
       <c r="AF5">
-        <v>-60.41</v>
+        <v>-70.45999999999999</v>
       </c>
       <c r="AG5">
-        <v>719.8099999999999</v>
+        <v>719.66</v>
       </c>
       <c r="AH5">
-        <v>637.54</v>
+        <v>639.04</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1336,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.73</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1347,10 +1373,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.12</v>
+        <v>26.46</v>
       </c>
       <c r="D6">
-        <v>0.66</v>
+        <v>1.3</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1359,46 +1385,46 @@
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-53.54</v>
+        <v>-52.93</v>
       </c>
       <c r="H6">
-        <v>0.66</v>
+        <v>1.97</v>
       </c>
       <c r="I6">
-        <v>-4.32</v>
+        <v>-1.71</v>
       </c>
       <c r="J6">
-        <v>-9.779999999999999</v>
+        <v>-7.19</v>
       </c>
       <c r="K6">
-        <v>-23.63</v>
+        <v>-23.39</v>
       </c>
       <c r="L6">
-        <v>-51.83</v>
+        <v>-51.18</v>
       </c>
       <c r="M6">
-        <v>-12.87</v>
+        <v>-12.23</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>26.49</v>
+        <v>26.4</v>
       </c>
       <c r="Q6">
-        <v>28.17</v>
+        <v>28.09</v>
       </c>
       <c r="R6">
-        <v>29.08</v>
+        <v>28.99</v>
       </c>
       <c r="S6">
-        <v>34.11</v>
+        <v>34.01</v>
       </c>
       <c r="T6">
-        <v>-23.42</v>
+        <v>-22.21</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1413,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.92</v>
+        <v>38.11</v>
       </c>
       <c r="Z6">
-        <v>-0.87</v>
+        <v>-0.86</v>
       </c>
       <c r="AA6">
-        <v>-0.68</v>
+        <v>-0.72</v>
       </c>
       <c r="AB6">
-        <v>-0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>7.25</v>
+        <v>17.3</v>
       </c>
       <c r="AD6">
-        <v>9.109999999999999</v>
+        <v>10.66</v>
       </c>
       <c r="AE6">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AF6">
-        <v>-34.23</v>
+        <v>-45.22</v>
       </c>
       <c r="AG6">
-        <v>31.18</v>
+        <v>31.19</v>
       </c>
       <c r="AH6">
-        <v>25.17</v>
+        <v>24.99</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1449,7 +1475,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>36.43</v>
+        <v>35.55</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1460,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1240</v>
+        <v>1243.9</v>
       </c>
       <c r="D7">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1472,46 +1498,46 @@
         <v>1235.3</v>
       </c>
       <c r="G7">
-        <v>-21.77</v>
+        <v>-21.52</v>
       </c>
       <c r="H7">
-        <v>0.38</v>
+        <v>0.7</v>
       </c>
       <c r="I7">
-        <v>-4.24</v>
+        <v>-2.74</v>
       </c>
       <c r="J7">
-        <v>-5.78</v>
+        <v>-5.91</v>
       </c>
       <c r="K7">
-        <v>-6.96</v>
+        <v>-6.34</v>
       </c>
       <c r="L7">
-        <v>-9.94</v>
+        <v>-10.42</v>
       </c>
       <c r="M7">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>1257.16</v>
+        <v>1250.14</v>
       </c>
       <c r="Q7">
-        <v>1292.4</v>
+        <v>1289.05</v>
       </c>
       <c r="R7">
-        <v>1298.11</v>
+        <v>1297.47</v>
       </c>
       <c r="S7">
-        <v>1376.48</v>
+        <v>1374.89</v>
       </c>
       <c r="T7">
-        <v>-9.91</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1526,43 +1552,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.4</v>
+        <v>35.96</v>
       </c>
       <c r="Z7">
-        <v>-13.85</v>
+        <v>-15.35</v>
       </c>
       <c r="AA7">
-        <v>-6.43</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AB7">
-        <v>-7.42</v>
+        <v>-7.14</v>
       </c>
       <c r="AC7">
-        <v>2.71</v>
+        <v>7.72</v>
       </c>
       <c r="AD7">
         <v>4.29</v>
       </c>
       <c r="AE7">
-        <v>21.24</v>
+        <v>20.79</v>
       </c>
       <c r="AF7">
-        <v>-7.51</v>
+        <v>-27.84</v>
       </c>
       <c r="AG7">
-        <v>1343.43</v>
+        <v>1343.62</v>
       </c>
       <c r="AH7">
-        <v>1241.37</v>
+        <v>1234.47</v>
       </c>
       <c r="AI7">
-        <v>1311.23</v>
+        <v>1308.32</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>34.74</v>
+        <v>38.15</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1723,12 +1749,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1736,836 +1797,870 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-3.24</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-3.96</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.72</v>
+      <c r="D7" s="6">
+        <v>-3.5</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.13</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-5.66</v>
       </c>
+      <c r="D8" s="6">
+        <v>-4.66</v>
+      </c>
       <c r="E8" s="7">
-        <v>0.47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-9.970000000000001</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.55</v>
+      <c r="D9" s="6">
+        <v>-6.71</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.26</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-1.07</v>
       </c>
+      <c r="D10" s="6">
+        <v>1.93</v>
+      </c>
       <c r="E10" s="7">
-        <v>1.74</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-10.55</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-9.779999999999999</v>
       </c>
+      <c r="D11" s="6">
+        <v>-7.19</v>
+      </c>
       <c r="E11" s="7">
-        <v>0.77</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.7</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-5.78</v>
       </c>
-      <c r="E12" s="6">
-        <v>-0.08</v>
+      <c r="D12" s="6">
+        <v>-5.91</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-4.59</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-2.8</v>
       </c>
+      <c r="D13" s="6">
+        <v>-2.79</v>
+      </c>
       <c r="E13" s="7">
-        <v>1.79</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-2.82</v>
       </c>
+      <c r="D14" s="6">
+        <v>-1.96</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.32</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.75</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-3.56</v>
       </c>
+      <c r="D15" s="6">
+        <v>-0.74</v>
+      </c>
       <c r="E15" s="7">
-        <v>0.19</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-5.28</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-2.96</v>
       </c>
+      <c r="D16" s="6">
+        <v>-0.65</v>
+      </c>
       <c r="E16" s="7">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-6.11</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-4.32</v>
       </c>
+      <c r="D17" s="6">
+        <v>-1.71</v>
+      </c>
       <c r="E17" s="7">
-        <v>1.79</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-5.67</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-4.24</v>
       </c>
+      <c r="D18" s="6">
+        <v>-2.74</v>
+      </c>
       <c r="E18" s="7">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-26.12</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-26.57</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.45</v>
+      <c r="D19" s="6">
+        <v>-25.81</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-33.09</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-32.71</v>
       </c>
+      <c r="D20" s="6">
+        <v>-32.43</v>
+      </c>
       <c r="E20" s="7">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-27.24</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-27.63</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.39</v>
+      <c r="D21" s="6">
+        <v>-26.32</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.31</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>-22.58</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-21.68</v>
       </c>
+      <c r="D22" s="6">
+        <v>-21.62</v>
+      </c>
       <c r="E22" s="7">
-        <v>0.9</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-52.36</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>-51.83</v>
       </c>
+      <c r="D23" s="6">
+        <v>-51.18</v>
+      </c>
       <c r="E23" s="7">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-9.94</v>
       </c>
-      <c r="E24" s="6">
-        <v>-0.06</v>
+      <c r="D24" s="6">
+        <v>-10.42</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-8.74</v>
       </c>
-      <c r="E25" s="6">
-        <v>-0.6899999999999999</v>
+      <c r="D25" s="6">
+        <v>-15.52</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-6.78</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-10.84</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>-10.87</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.03</v>
+      <c r="D26" s="6">
+        <v>-13.62</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-7.47</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.71</v>
+      <c r="D27" s="6">
+        <v>-6.06</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.41</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>21.71</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>22.21</v>
+      </c>
+      <c r="D28" s="6">
+        <v>22.71</v>
       </c>
       <c r="E28" s="7">
         <v>0.5</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-23.13</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-23.63</v>
       </c>
-      <c r="E29" s="6">
-        <v>-0.5</v>
+      <c r="D29" s="6">
+        <v>-23.39</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-7.04</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-6.96</v>
       </c>
+      <c r="D30" s="6">
+        <v>-6.34</v>
+      </c>
       <c r="E30" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-27.81</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-27.73</v>
+      </c>
+      <c r="E31" s="7">
         <v>0.08</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-33.69</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-33.55</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-29.15</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-27.75</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-21.75</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-21.71</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-53.54</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-52.93</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-21.77</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-21.52</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-27.27</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-27.81</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>26.42</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.45</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-34.02</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-33.69</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10</v>
+      </c>
+      <c r="D38" s="6">
+        <v>10.02</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-28.91</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-29.15</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>224.84</v>
+      </c>
+      <c r="D39" s="6">
+        <v>229.3</v>
+      </c>
+      <c r="E39" s="7">
+        <v>4.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-23.13</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-21.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>673.7</v>
+      </c>
+      <c r="D40" s="6">
+        <v>674.05</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-53.84</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-53.54</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>26.12</v>
+      </c>
+      <c r="D41" s="6">
+        <v>26.46</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-22.06</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-21.77</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1240</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1243.9</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>26.62</v>
-      </c>
-      <c r="D37" s="5">
-        <v>26.42</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6">
+        <v>66</v>
+      </c>
+      <c r="D43" s="6">
+        <v>50</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6">
+        <v>50</v>
+      </c>
+      <c r="D44" s="6">
+        <v>66</v>
+      </c>
+      <c r="E44" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>31.68</v>
+      </c>
+      <c r="D45" s="6">
+        <v>32.36</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>33.55</v>
+      </c>
+      <c r="D46" s="6">
+        <v>34.53</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>225.6</v>
-      </c>
-      <c r="D39" s="5">
-        <v>224.84</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>28.77</v>
+      </c>
+      <c r="D47" s="6">
+        <v>37.95</v>
+      </c>
+      <c r="E47" s="7">
+        <v>9.18</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>661.85</v>
-      </c>
-      <c r="D40" s="5">
-        <v>673.7</v>
-      </c>
-      <c r="E40" s="7">
-        <v>11.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>47.72</v>
+      </c>
+      <c r="D48" s="6">
+        <v>47.87</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>25.95</v>
-      </c>
-      <c r="D41" s="5">
-        <v>26.12</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>34.92</v>
+      </c>
+      <c r="D49" s="6">
+        <v>38.11</v>
+      </c>
+      <c r="E49" s="7">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1235.3</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1240</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>34.4</v>
+      </c>
+      <c r="D50" s="6">
+        <v>35.96</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>33.79</v>
-      </c>
-      <c r="D43" s="5">
-        <v>31.68</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-27.12</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-5.73</v>
+      </c>
+      <c r="E51" s="7">
+        <v>21.39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>31.15</v>
-      </c>
-      <c r="D44" s="5">
-        <v>33.55</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-14.9</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-3.27</v>
+      </c>
+      <c r="E52" s="7">
+        <v>11.63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>29.46</v>
-      </c>
-      <c r="D45" s="5">
-        <v>28.77</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="D53" s="6">
+        <v>13.9</v>
+      </c>
+      <c r="E53" s="7">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>42.82</v>
-      </c>
-      <c r="D46" s="5">
-        <v>47.72</v>
-      </c>
-      <c r="E46" s="7">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-60.41</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-70.45999999999999</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-10.05</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>33.33</v>
-      </c>
-      <c r="D47" s="5">
-        <v>34.92</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-34.23</v>
+      </c>
+      <c r="D55" s="6">
+        <v>-45.22</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-10.99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>32.56</v>
-      </c>
-      <c r="D48" s="5">
-        <v>34.4</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-17.43</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-27.12</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-9.69</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>33.64</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-14.9</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-48.54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>21.22</v>
-      </c>
-      <c r="D51" s="5">
-        <v>10.42</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-10.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-43.85</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-60.41</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-16.56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-51.77</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-34.23</v>
-      </c>
-      <c r="E53" s="7">
-        <v>17.54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>28.29</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C56" s="6">
         <v>-7.51</v>
       </c>
-      <c r="E54" s="6">
-        <v>-35.8</v>
+      <c r="D56" s="6">
+        <v>-27.84</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-20.33</v>
       </c>
     </row>
   </sheetData>
@@ -2591,60 +2686,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>35.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.8</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-5.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-4.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2746,43 +2841,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0243</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0321</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0737</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1193</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1287</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1641</v>
+      <c r="A2" s="14">
+        <v>0.0281</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0258</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.07290000000000001</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1155</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1223</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1617</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.8 → 38.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>38.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -781,7 +753,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.45</v>
+        <v>26.62</v>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.64</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -933,46 +907,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.73</v>
+        <v>-27.27</v>
       </c>
       <c r="H2">
-        <v>15.1</v>
+        <v>15.84</v>
       </c>
       <c r="I2">
-        <v>-2.79</v>
+        <v>-1.59</v>
       </c>
       <c r="J2">
-        <v>-3.5</v>
+        <v>-2.78</v>
       </c>
       <c r="K2">
-        <v>-15.52</v>
+        <v>-19.53</v>
       </c>
       <c r="L2">
-        <v>-25.81</v>
+        <v>-26.36</v>
       </c>
       <c r="M2">
-        <v>-11.55</v>
+        <v>-11</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="P2">
-        <v>26.7</v>
+        <v>26.62</v>
       </c>
       <c r="Q2">
-        <v>27.59</v>
+        <v>27.54</v>
       </c>
       <c r="R2">
-        <v>27.66</v>
+        <v>27.63</v>
       </c>
       <c r="S2">
-        <v>28.38</v>
+        <v>28.35</v>
       </c>
       <c r="T2">
-        <v>-6.8</v>
+        <v>-6.1</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +961,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.36</v>
+        <v>36.25</v>
       </c>
       <c r="Z2">
-        <v>-0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="AA2">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="AB2">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AC2">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="AD2">
-        <v>0.3</v>
+        <v>2.67</v>
       </c>
       <c r="AE2">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-5.73</v>
+        <v>-77.52</v>
       </c>
       <c r="AG2">
-        <v>28.82</v>
+        <v>28.84</v>
       </c>
       <c r="AH2">
-        <v>26.36</v>
+        <v>26.23</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -1023,7 +997,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>39.23</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1008,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.02</v>
+        <v>9.98</v>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1046,46 +1020,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.55</v>
+        <v>-33.82</v>
       </c>
       <c r="H3">
-        <v>12.97</v>
+        <v>12.51</v>
       </c>
       <c r="I3">
-        <v>-1.96</v>
+        <v>-1.87</v>
       </c>
       <c r="J3">
-        <v>-4.66</v>
+        <v>-4.31</v>
       </c>
       <c r="K3">
-        <v>-13.62</v>
+        <v>-18.06</v>
       </c>
       <c r="L3">
-        <v>-32.43</v>
+        <v>-33.02</v>
       </c>
       <c r="M3">
-        <v>-16.17</v>
+        <v>-16.08</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P3">
-        <v>10.07</v>
+        <v>10.04</v>
       </c>
       <c r="Q3">
-        <v>10.38</v>
+        <v>10.35</v>
       </c>
       <c r="R3">
-        <v>10.67</v>
+        <v>10.65</v>
       </c>
       <c r="S3">
-        <v>11.04</v>
+        <v>11.02</v>
       </c>
       <c r="T3">
-        <v>-9.24</v>
+        <v>-9.48</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,34 +1074,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.53</v>
+        <v>33.46</v>
       </c>
       <c r="Z3">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AA3">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AB3">
         <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>12.4</v>
+        <v>17.37</v>
       </c>
       <c r="AD3">
-        <v>15.88</v>
+        <v>15.81</v>
       </c>
       <c r="AE3">
         <v>0.24</v>
       </c>
       <c r="AF3">
-        <v>-3.27</v>
+        <v>-22.6</v>
       </c>
       <c r="AG3">
         <v>10.83</v>
       </c>
       <c r="AH3">
-        <v>9.93</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AI3">
         <v>10.72</v>
@@ -1136,7 +1110,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>33.07</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1121,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>229.3</v>
+        <v>229.89</v>
       </c>
       <c r="D4">
-        <v>1.98</v>
+        <v>0.26</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1159,46 +1133,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.75</v>
+        <v>-27.56</v>
       </c>
       <c r="H4">
-        <v>2.32</v>
+        <v>2.58</v>
       </c>
       <c r="I4">
-        <v>-0.74</v>
+        <v>-0.16</v>
       </c>
       <c r="J4">
-        <v>-6.71</v>
+        <v>-5.45</v>
       </c>
       <c r="K4">
-        <v>-6.06</v>
+        <v>-5.96</v>
       </c>
       <c r="L4">
-        <v>-26.32</v>
+        <v>-27.1</v>
       </c>
       <c r="M4">
-        <v>-2.58</v>
+        <v>-2.5</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>227.98</v>
+        <v>227.91</v>
       </c>
       <c r="Q4">
-        <v>236.04</v>
+        <v>235.3</v>
       </c>
       <c r="R4">
-        <v>242.25</v>
+        <v>242.18</v>
       </c>
       <c r="S4">
-        <v>252.8</v>
+        <v>252.42</v>
       </c>
       <c r="T4">
-        <v>-9.289999999999999</v>
+        <v>-8.93</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1213,34 +1187,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.95</v>
+        <v>39.07</v>
       </c>
       <c r="Z4">
-        <v>-4.83</v>
+        <v>-4.64</v>
       </c>
       <c r="AA4">
-        <v>-3.85</v>
+        <v>-4.01</v>
       </c>
       <c r="AB4">
-        <v>-0.98</v>
+        <v>-0.63</v>
       </c>
       <c r="AC4">
-        <v>19.58</v>
+        <v>41.55</v>
       </c>
       <c r="AD4">
-        <v>6.53</v>
+        <v>20.38</v>
       </c>
       <c r="AE4">
-        <v>4.58</v>
+        <v>4.44</v>
       </c>
       <c r="AF4">
-        <v>13.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG4">
-        <v>248.07</v>
+        <v>246.92</v>
       </c>
       <c r="AH4">
-        <v>224.01</v>
+        <v>223.68</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1249,7 +1223,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>47.91</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1234,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>674.05</v>
+        <v>669</v>
       </c>
       <c r="D5">
-        <v>0.05</v>
+        <v>-0.75</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1246,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.71</v>
+        <v>-22.3</v>
       </c>
       <c r="H5">
-        <v>37.36</v>
+        <v>36.34</v>
       </c>
       <c r="I5">
-        <v>-0.65</v>
+        <v>0.04</v>
       </c>
       <c r="J5">
-        <v>1.93</v>
+        <v>1.29</v>
       </c>
       <c r="K5">
-        <v>22.71</v>
+        <v>23.91</v>
       </c>
       <c r="L5">
-        <v>-21.62</v>
+        <v>-21.38</v>
       </c>
       <c r="M5">
-        <v>-7.29</v>
+        <v>-7.42</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>668.78</v>
+        <v>668.83</v>
       </c>
       <c r="Q5">
-        <v>679.35</v>
+        <v>678.77</v>
       </c>
       <c r="R5">
-        <v>694.99</v>
+        <v>697.4299999999999</v>
       </c>
       <c r="S5">
-        <v>622.87</v>
+        <v>622.53</v>
       </c>
       <c r="T5">
-        <v>8.220000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1326,34 +1300,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.87</v>
+        <v>45.93</v>
       </c>
       <c r="Z5">
-        <v>-1.74</v>
+        <v>-2.3</v>
       </c>
       <c r="AA5">
-        <v>0.75</v>
+        <v>0.14</v>
       </c>
       <c r="AB5">
-        <v>-2.48</v>
+        <v>-2.43</v>
       </c>
       <c r="AC5">
-        <v>31.58</v>
+        <v>30.96</v>
       </c>
       <c r="AD5">
-        <v>29.25</v>
+        <v>30.92</v>
       </c>
       <c r="AE5">
-        <v>22.5</v>
+        <v>22.62</v>
       </c>
       <c r="AF5">
-        <v>-70.45999999999999</v>
+        <v>-34.14</v>
       </c>
       <c r="AG5">
-        <v>719.66</v>
+        <v>719.34</v>
       </c>
       <c r="AH5">
-        <v>639.04</v>
+        <v>638.2</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1362,7 +1336,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>19.38</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1347,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.46</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>1.3</v>
+        <v>2.04</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1385,46 +1359,46 @@
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-52.93</v>
+        <v>-51.97</v>
       </c>
       <c r="H6">
-        <v>1.97</v>
+        <v>4.05</v>
       </c>
       <c r="I6">
-        <v>-1.71</v>
+        <v>0.63</v>
       </c>
       <c r="J6">
-        <v>-7.19</v>
+        <v>-3.81</v>
       </c>
       <c r="K6">
-        <v>-23.39</v>
+        <v>-20.54</v>
       </c>
       <c r="L6">
-        <v>-51.18</v>
+        <v>-50.06</v>
       </c>
       <c r="M6">
-        <v>-12.23</v>
+        <v>-11.68</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>26.4</v>
+        <v>26.43</v>
       </c>
       <c r="Q6">
-        <v>28.09</v>
+        <v>27.91</v>
       </c>
       <c r="R6">
-        <v>28.99</v>
+        <v>28.91</v>
       </c>
       <c r="S6">
-        <v>34.01</v>
+        <v>33.92</v>
       </c>
       <c r="T6">
-        <v>-22.21</v>
+        <v>-20.41</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,34 +1413,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>38.11</v>
+        <v>42.9</v>
       </c>
       <c r="Z6">
-        <v>-0.86</v>
+        <v>-0.8</v>
       </c>
       <c r="AA6">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC6">
-        <v>17.3</v>
+        <v>43.26</v>
       </c>
       <c r="AD6">
-        <v>10.66</v>
+        <v>22.6</v>
       </c>
       <c r="AE6">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AF6">
-        <v>-45.22</v>
+        <v>-28.47</v>
       </c>
       <c r="AG6">
-        <v>31.19</v>
+        <v>30.81</v>
       </c>
       <c r="AH6">
-        <v>24.99</v>
+        <v>25.01</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1475,7 +1449,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>35.55</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,58 +1460,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1243.9</v>
+        <v>1226.4</v>
       </c>
       <c r="D7">
-        <v>0.31</v>
+        <v>-1.41</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1235.3</v>
+        <v>1226.4</v>
       </c>
       <c r="G7">
-        <v>-21.52</v>
+        <v>-22.62</v>
       </c>
       <c r="H7">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.74</v>
+        <v>-3.74</v>
       </c>
       <c r="J7">
-        <v>-5.91</v>
+        <v>-6.45</v>
       </c>
       <c r="K7">
-        <v>-6.34</v>
+        <v>-6.35</v>
       </c>
       <c r="L7">
-        <v>-10.42</v>
+        <v>-11.95</v>
       </c>
       <c r="M7">
-        <v>2.81</v>
+        <v>2.49</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>1250.14</v>
+        <v>1240.62</v>
       </c>
       <c r="Q7">
-        <v>1289.05</v>
+        <v>1284.71</v>
       </c>
       <c r="R7">
-        <v>1297.47</v>
+        <v>1296.4</v>
       </c>
       <c r="S7">
-        <v>1374.89</v>
+        <v>1373.23</v>
       </c>
       <c r="T7">
-        <v>-9.529999999999999</v>
+        <v>-10.69</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1552,43 +1526,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.96</v>
+        <v>32.26</v>
       </c>
       <c r="Z7">
-        <v>-15.35</v>
+        <v>-17.75</v>
       </c>
       <c r="AA7">
-        <v>-8.210000000000001</v>
+        <v>-10.12</v>
       </c>
       <c r="AB7">
-        <v>-7.14</v>
+        <v>-7.63</v>
       </c>
       <c r="AC7">
         <v>7.72</v>
       </c>
       <c r="AD7">
-        <v>4.29</v>
+        <v>6.05</v>
       </c>
       <c r="AE7">
-        <v>20.79</v>
+        <v>20.8</v>
       </c>
       <c r="AF7">
-        <v>-27.84</v>
+        <v>42.82</v>
       </c>
       <c r="AG7">
-        <v>1343.62</v>
+        <v>1344.73</v>
       </c>
       <c r="AH7">
-        <v>1234.47</v>
+        <v>1224.68</v>
       </c>
       <c r="AI7">
-        <v>1308.32</v>
+        <v>1299.24</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>38.15</v>
+        <v>42.1</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1749,47 +1723,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1797,870 +1736,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-3.96</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-3.5</v>
       </c>
-      <c r="E7" s="7">
+      <c r="D7" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-4.66</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-4.31</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.71</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.45</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.93</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.19</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-3.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-5.91</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-6.45</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.79</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-1.59</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.96</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.87</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-0.74</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-0.16</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.65</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.63</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.74</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.74</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-25.81</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.36</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-32.43</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-33.02</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-26.32</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-27.1</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-21.62</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-21.38</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-51.18</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-50.06</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.42</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.95</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-15.52</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-19.53</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-13.62</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-18.06</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-6.06</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>22.71</v>
+      </c>
+      <c r="D28" s="5">
+        <v>23.91</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-23.39</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-20.54</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.34</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.35</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-27.73</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-27.27</v>
+      </c>
+      <c r="E31" s="6">
         <v>0.46</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-5.66</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-33.55</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-33.82</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.71</v>
-      </c>
-      <c r="E9" s="7">
-        <v>3.26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-27.75</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-27.56</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-21.71</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-22.3</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.93</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-51.97</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-21.52</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-22.62</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>26.45</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.62</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>10.02</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.98</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>229.3</v>
+      </c>
+      <c r="D39" s="5">
+        <v>229.89</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>674.05</v>
+      </c>
+      <c r="D40" s="5">
+        <v>669</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.46</v>
+      </c>
+      <c r="D41" s="5">
+        <v>27</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1243.9</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1226.4</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-17.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>32.36</v>
+      </c>
+      <c r="D43" s="5">
+        <v>36.25</v>
+      </c>
+      <c r="E43" s="6">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>34.53</v>
+      </c>
+      <c r="D44" s="5">
+        <v>33.46</v>
+      </c>
+      <c r="E44" s="7">
         <v>-1.07</v>
       </c>
-      <c r="D10" s="6">
-        <v>1.93</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>37.95</v>
+      </c>
+      <c r="D45" s="5">
+        <v>39.07</v>
+      </c>
+      <c r="E45" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>47.87</v>
+      </c>
+      <c r="D46" s="5">
+        <v>45.93</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.19</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>38.11</v>
+      </c>
+      <c r="D47" s="5">
+        <v>42.9</v>
+      </c>
+      <c r="E47" s="6">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.78</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>35.96</v>
+      </c>
+      <c r="D48" s="5">
+        <v>32.26</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-2.8</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-77.52</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-71.79000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.82</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.96</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-3.27</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-22.6</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-19.33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.56</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.74</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>13.9</v>
+      </c>
+      <c r="D51" s="5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.96</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.65</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-70.45999999999999</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-34.14</v>
+      </c>
+      <c r="E52" s="6">
+        <v>36.32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.32</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.71</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-45.22</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-28.47</v>
+      </c>
+      <c r="E53" s="6">
+        <v>16.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.24</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.74</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.57</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-25.81</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-32.71</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-32.43</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-27.63</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-26.32</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-21.68</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-21.62</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-51.83</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-51.18</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-9.94</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-10.42</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-8.74</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-15.52</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-6.78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-10.87</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-13.62</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>22.21</v>
-      </c>
-      <c r="D28" s="6">
-        <v>22.71</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-23.63</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-23.39</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-27.81</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-27.73</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-33.69</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-33.55</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-29.15</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-27.75</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-21.75</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-21.71</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-53.54</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-52.93</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-21.77</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-21.52</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>26.42</v>
-      </c>
-      <c r="D37" s="6">
-        <v>26.45</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>10</v>
-      </c>
-      <c r="D38" s="6">
-        <v>10.02</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>224.84</v>
-      </c>
-      <c r="D39" s="6">
-        <v>229.3</v>
-      </c>
-      <c r="E39" s="7">
-        <v>4.46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>673.7</v>
-      </c>
-      <c r="D40" s="6">
-        <v>674.05</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>26.12</v>
-      </c>
-      <c r="D41" s="6">
-        <v>26.46</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1240</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1243.9</v>
-      </c>
-      <c r="E42" s="7">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="6">
-        <v>66</v>
-      </c>
-      <c r="D43" s="6">
-        <v>50</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="6">
-        <v>50</v>
-      </c>
-      <c r="D44" s="6">
-        <v>66</v>
-      </c>
-      <c r="E44" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>31.68</v>
-      </c>
-      <c r="D45" s="6">
-        <v>32.36</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>33.55</v>
-      </c>
-      <c r="D46" s="6">
-        <v>34.53</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>28.77</v>
-      </c>
-      <c r="D47" s="6">
-        <v>37.95</v>
-      </c>
-      <c r="E47" s="7">
-        <v>9.18</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>47.72</v>
-      </c>
-      <c r="D48" s="6">
-        <v>47.87</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>34.92</v>
-      </c>
-      <c r="D49" s="6">
-        <v>38.11</v>
-      </c>
-      <c r="E49" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>34.4</v>
-      </c>
-      <c r="D50" s="6">
-        <v>35.96</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="6">
-        <v>-27.12</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-5.73</v>
-      </c>
-      <c r="E51" s="7">
-        <v>21.39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="E52" s="7">
-        <v>11.63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>10.42</v>
-      </c>
-      <c r="D53" s="6">
-        <v>13.9</v>
-      </c>
-      <c r="E53" s="7">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-60.41</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-70.45999999999999</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-10.05</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>-34.23</v>
-      </c>
-      <c r="D55" s="6">
-        <v>-45.22</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-10.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C54" s="5">
         <v>-27.84</v>
       </c>
-      <c r="E56" s="8">
-        <v>-20.33</v>
+      <c r="D54" s="5">
+        <v>42.82</v>
+      </c>
+      <c r="E54" s="6">
+        <v>70.66</v>
       </c>
     </row>
   </sheetData>
@@ -2686,60 +2591,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2841,43 +2746,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0281</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0258</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.07290000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1155</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1223</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1617</v>
+      <c r="A2" s="13">
+        <v>0.0249</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.025</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0742</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.11</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1168</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1608</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.9 → 51.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>51.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,9 +781,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -895,10 +922,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.62</v>
+        <v>26.42</v>
       </c>
       <c r="D2">
-        <v>0.64</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -907,46 +934,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.27</v>
+        <v>-27.81</v>
       </c>
       <c r="H2">
-        <v>15.84</v>
+        <v>14.97</v>
       </c>
       <c r="I2">
-        <v>-1.59</v>
+        <v>-2.08</v>
       </c>
       <c r="J2">
-        <v>-2.78</v>
+        <v>-4.79</v>
       </c>
       <c r="K2">
-        <v>-19.53</v>
+        <v>-19.89</v>
       </c>
       <c r="L2">
-        <v>-26.36</v>
+        <v>-27</v>
       </c>
       <c r="M2">
-        <v>-11</v>
+        <v>-11.16</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P2">
-        <v>26.62</v>
+        <v>26.51</v>
       </c>
       <c r="Q2">
-        <v>27.54</v>
+        <v>27.45</v>
       </c>
       <c r="R2">
-        <v>27.63</v>
+        <v>27.57</v>
       </c>
       <c r="S2">
-        <v>28.35</v>
+        <v>28.32</v>
       </c>
       <c r="T2">
-        <v>-6.1</v>
+        <v>-6.72</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -961,34 +988,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>36.25</v>
+        <v>33.79</v>
       </c>
       <c r="Z2">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AA2">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="AB2">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
       <c r="AC2">
-        <v>7.1</v>
+        <v>10.59</v>
       </c>
       <c r="AD2">
-        <v>2.67</v>
+        <v>6.2</v>
       </c>
       <c r="AE2">
         <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-77.52</v>
+        <v>6.47</v>
       </c>
       <c r="AG2">
-        <v>28.84</v>
+        <v>28.81</v>
       </c>
       <c r="AH2">
-        <v>26.23</v>
+        <v>26.09</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -997,7 +1024,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>40.19</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,10 +1035,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D3">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1020,46 +1047,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.82</v>
+        <v>-33.89</v>
       </c>
       <c r="H3">
-        <v>12.51</v>
+        <v>12.4</v>
       </c>
       <c r="I3">
-        <v>-1.87</v>
+        <v>-2.54</v>
       </c>
       <c r="J3">
-        <v>-4.31</v>
+        <v>-5.41</v>
       </c>
       <c r="K3">
-        <v>-18.06</v>
+        <v>-18.28</v>
       </c>
       <c r="L3">
-        <v>-33.02</v>
+        <v>-33.27</v>
       </c>
       <c r="M3">
-        <v>-16.08</v>
+        <v>-16.01</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P3">
-        <v>10.04</v>
+        <v>9.98</v>
       </c>
       <c r="Q3">
-        <v>10.35</v>
+        <v>10.32</v>
       </c>
       <c r="R3">
-        <v>10.65</v>
+        <v>10.63</v>
       </c>
       <c r="S3">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
       <c r="T3">
-        <v>-9.48</v>
+        <v>-9.44</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1074,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.46</v>
+        <v>33.19</v>
       </c>
       <c r="Z3">
         <v>-0.19</v>
@@ -1086,31 +1113,31 @@
         <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>17.37</v>
+        <v>16.88</v>
       </c>
       <c r="AD3">
-        <v>15.81</v>
+        <v>15.55</v>
       </c>
       <c r="AE3">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AF3">
-        <v>-22.6</v>
+        <v>-41.2</v>
       </c>
       <c r="AG3">
-        <v>10.83</v>
+        <v>10.8</v>
       </c>
       <c r="AH3">
-        <v>9.869999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="AI3">
-        <v>10.72</v>
+        <v>10.67</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>35.86</v>
+        <v>38.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1121,10 +1148,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>229.89</v>
+        <v>229.97</v>
       </c>
       <c r="D4">
-        <v>0.26</v>
+        <v>0.03</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1133,46 +1160,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.56</v>
+        <v>-27.53</v>
       </c>
       <c r="H4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I4">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="J4">
-        <v>-5.45</v>
+        <v>-5.98</v>
       </c>
       <c r="K4">
-        <v>-5.96</v>
+        <v>-5.51</v>
       </c>
       <c r="L4">
         <v>-27.1</v>
       </c>
       <c r="M4">
-        <v>-2.5</v>
+        <v>-2.48</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P4">
-        <v>227.91</v>
+        <v>227.92</v>
       </c>
       <c r="Q4">
-        <v>235.3</v>
+        <v>234.6</v>
       </c>
       <c r="R4">
-        <v>242.18</v>
+        <v>241.94</v>
       </c>
       <c r="S4">
-        <v>252.42</v>
+        <v>252.05</v>
       </c>
       <c r="T4">
-        <v>-8.93</v>
+        <v>-8.76</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1187,34 +1214,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.07</v>
+        <v>39.23</v>
       </c>
       <c r="Z4">
-        <v>-4.64</v>
+        <v>-4.43</v>
       </c>
       <c r="AA4">
-        <v>-4.01</v>
+        <v>-4.09</v>
       </c>
       <c r="AB4">
-        <v>-0.63</v>
+        <v>-0.34</v>
       </c>
       <c r="AC4">
-        <v>41.55</v>
+        <v>63.98</v>
       </c>
       <c r="AD4">
-        <v>20.38</v>
+        <v>41.71</v>
       </c>
       <c r="AE4">
-        <v>4.44</v>
+        <v>4.28</v>
       </c>
       <c r="AF4">
-        <v>8.199999999999999</v>
+        <v>-46.91</v>
       </c>
       <c r="AG4">
-        <v>246.92</v>
+        <v>245.69</v>
       </c>
       <c r="AH4">
-        <v>223.68</v>
+        <v>223.51</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1223,7 +1250,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>44.85</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,10 +1261,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>669</v>
+        <v>682.7</v>
       </c>
       <c r="D5">
-        <v>-0.75</v>
+        <v>2.05</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1246,46 +1273,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-22.3</v>
+        <v>-20.7</v>
       </c>
       <c r="H5">
-        <v>36.34</v>
+        <v>39.13</v>
       </c>
       <c r="I5">
-        <v>0.04</v>
+        <v>2.58</v>
       </c>
       <c r="J5">
-        <v>1.29</v>
+        <v>0.3</v>
       </c>
       <c r="K5">
-        <v>23.91</v>
+        <v>24.33</v>
       </c>
       <c r="L5">
-        <v>-21.38</v>
+        <v>-19.67</v>
       </c>
       <c r="M5">
-        <v>-7.42</v>
+        <v>-6.97</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>668.83</v>
+        <v>672.26</v>
       </c>
       <c r="Q5">
-        <v>678.77</v>
+        <v>679.2</v>
       </c>
       <c r="R5">
-        <v>697.4299999999999</v>
+        <v>699.8099999999999</v>
       </c>
       <c r="S5">
-        <v>622.53</v>
+        <v>622.25</v>
       </c>
       <c r="T5">
-        <v>7.47</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1300,34 +1327,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>45.93</v>
+        <v>51.66</v>
       </c>
       <c r="Z5">
-        <v>-2.3</v>
+        <v>-1.61</v>
       </c>
       <c r="AA5">
-        <v>0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="AB5">
-        <v>-2.43</v>
+        <v>-1.4</v>
       </c>
       <c r="AC5">
-        <v>30.96</v>
+        <v>35.74</v>
       </c>
       <c r="AD5">
-        <v>30.92</v>
+        <v>32.76</v>
       </c>
       <c r="AE5">
-        <v>22.62</v>
+        <v>23.12</v>
       </c>
       <c r="AF5">
-        <v>-34.14</v>
+        <v>-46.11</v>
       </c>
       <c r="AG5">
-        <v>719.34</v>
+        <v>719.74</v>
       </c>
       <c r="AH5">
-        <v>638.2</v>
+        <v>638.66</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1336,7 +1363,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>17.78</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1347,10 +1374,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>26.79</v>
       </c>
       <c r="D6">
-        <v>2.04</v>
+        <v>-0.78</v>
       </c>
       <c r="E6">
         <v>56.22</v>
@@ -1359,46 +1386,46 @@
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-51.97</v>
+        <v>-52.35</v>
       </c>
       <c r="H6">
-        <v>4.05</v>
+        <v>3.24</v>
       </c>
       <c r="I6">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J6">
-        <v>-3.81</v>
+        <v>-12.42</v>
       </c>
       <c r="K6">
-        <v>-20.54</v>
+        <v>-21.48</v>
       </c>
       <c r="L6">
-        <v>-50.06</v>
+        <v>-51.1</v>
       </c>
       <c r="M6">
-        <v>-11.68</v>
+        <v>-12.08</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>26.43</v>
+        <v>26.46</v>
       </c>
       <c r="Q6">
-        <v>27.91</v>
+        <v>27.76</v>
       </c>
       <c r="R6">
-        <v>28.91</v>
+        <v>28.83</v>
       </c>
       <c r="S6">
-        <v>33.92</v>
+        <v>33.83</v>
       </c>
       <c r="T6">
-        <v>-20.41</v>
+        <v>-20.82</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1413,34 +1440,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>42.9</v>
+        <v>41.55</v>
       </c>
       <c r="Z6">
-        <v>-0.8</v>
+        <v>-0.77</v>
       </c>
       <c r="AA6">
-        <v>-0.73</v>
+        <v>-0.74</v>
       </c>
       <c r="AB6">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>43.26</v>
+        <v>61.24</v>
       </c>
       <c r="AD6">
-        <v>22.6</v>
+        <v>40.6</v>
       </c>
       <c r="AE6">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AF6">
-        <v>-28.47</v>
+        <v>-62.37</v>
       </c>
       <c r="AG6">
-        <v>30.81</v>
+        <v>30.55</v>
       </c>
       <c r="AH6">
-        <v>25.01</v>
+        <v>24.97</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1449,7 +1476,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>33.56</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1460,10 +1487,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1226.4</v>
+        <v>1247.4</v>
       </c>
       <c r="D7">
-        <v>-1.41</v>
+        <v>1.71</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1472,46 +1499,46 @@
         <v>1226.4</v>
       </c>
       <c r="G7">
-        <v>-22.62</v>
+        <v>-21.3</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="I7">
-        <v>-3.74</v>
+        <v>-0.8</v>
       </c>
       <c r="J7">
-        <v>-6.45</v>
+        <v>-5.01</v>
       </c>
       <c r="K7">
-        <v>-6.35</v>
+        <v>-5.96</v>
       </c>
       <c r="L7">
-        <v>-11.95</v>
+        <v>-10.83</v>
       </c>
       <c r="M7">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P7">
-        <v>1240.62</v>
+        <v>1238.6</v>
       </c>
       <c r="Q7">
-        <v>1284.71</v>
+        <v>1281.28</v>
       </c>
       <c r="R7">
-        <v>1296.4</v>
+        <v>1295.19</v>
       </c>
       <c r="S7">
-        <v>1373.23</v>
+        <v>1371.77</v>
       </c>
       <c r="T7">
-        <v>-10.69</v>
+        <v>-9.07</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1526,34 +1553,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>32.26</v>
+        <v>40.21</v>
       </c>
       <c r="Z7">
         <v>-17.75</v>
       </c>
       <c r="AA7">
-        <v>-10.12</v>
+        <v>-11.65</v>
       </c>
       <c r="AB7">
-        <v>-7.63</v>
+        <v>-6.11</v>
       </c>
       <c r="AC7">
-        <v>7.72</v>
+        <v>16.6</v>
       </c>
       <c r="AD7">
-        <v>6.05</v>
+        <v>10.68</v>
       </c>
       <c r="AE7">
-        <v>20.8</v>
+        <v>20.93</v>
       </c>
       <c r="AF7">
-        <v>42.82</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="AG7">
-        <v>1344.73</v>
+        <v>1341.61</v>
       </c>
       <c r="AH7">
-        <v>1224.68</v>
+        <v>1220.94</v>
       </c>
       <c r="AI7">
         <v>1299.24</v>
@@ -1562,7 +1589,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>42.1</v>
+        <v>44.83</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1723,12 +1750,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1736,836 +1798,819 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-3.5</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.78</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.72</v>
+      <c r="D7" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-4.66</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.31</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.35</v>
+      <c r="D8" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.71</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-5.45</v>
       </c>
-      <c r="E9" s="6">
-        <v>1.26</v>
+      <c r="D9" s="6">
+        <v>-5.98</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>1.93</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>1.29</v>
       </c>
+      <c r="D10" s="6">
+        <v>0.3</v>
+      </c>
       <c r="E10" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.81</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.42</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-8.609999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.45</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-1.59</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.08</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-1.87</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-0.16</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2.58</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-3.74</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.8</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-26.36</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-27</v>
+      </c>
+      <c r="E19" s="7">
         <v>-0.64</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-33.02</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-33.27</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-21.38</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-19.67</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-7.19</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-3.81</v>
-      </c>
-      <c r="E11" s="6">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-50.06</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-51.1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-5.91</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-6.45</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-11.95</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-10.83</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-19.53</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-19.89</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-18.06</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-18.28</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-5.51</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>23.91</v>
+      </c>
+      <c r="D27" s="6">
+        <v>24.33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-20.54</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-21.48</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-5.96</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-27.27</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-27.81</v>
+      </c>
+      <c r="E30" s="7">
         <v>-0.54</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-33.82</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-33.89</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-27.56</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-27.53</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-22.3</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-20.7</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-51.97</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-52.35</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-22.62</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-21.3</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.59</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>26.62</v>
+      </c>
+      <c r="D36" s="6">
+        <v>26.42</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.96</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.87</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>9.98</v>
+      </c>
+      <c r="D37" s="6">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.74</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-0.16</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>229.89</v>
+      </c>
+      <c r="D38" s="6">
+        <v>229.97</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.65</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>669</v>
+      </c>
+      <c r="D39" s="6">
+        <v>682.7</v>
+      </c>
+      <c r="E39" s="8">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.63</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>27</v>
+      </c>
+      <c r="D40" s="6">
+        <v>26.79</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.74</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.74</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1226.4</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1247.4</v>
+      </c>
+      <c r="E41" s="8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-25.81</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-26.36</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>36.25</v>
+      </c>
+      <c r="D42" s="6">
+        <v>33.79</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-32.43</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-33.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>33.46</v>
+      </c>
+      <c r="D43" s="6">
+        <v>33.19</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-26.32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-27.1</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>39.07</v>
+      </c>
+      <c r="D44" s="6">
+        <v>39.23</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-21.62</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-21.38</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>45.93</v>
+      </c>
+      <c r="D45" s="6">
+        <v>51.66</v>
+      </c>
+      <c r="E45" s="8">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-51.18</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-50.06</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>42.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>41.55</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-10.42</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-11.95</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>32.26</v>
+      </c>
+      <c r="D47" s="6">
+        <v>40.21</v>
+      </c>
+      <c r="E47" s="8">
+        <v>7.95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-15.52</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-19.53</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-77.52</v>
+      </c>
+      <c r="D48" s="6">
+        <v>6.47</v>
+      </c>
+      <c r="E48" s="8">
+        <v>83.98999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-18.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-22.6</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-41.2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-18.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-6.06</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-5.96</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-46.91</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-55.11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>22.71</v>
-      </c>
-      <c r="D28" s="5">
-        <v>23.91</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-34.14</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-46.11</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-11.97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-23.39</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-20.54</v>
-      </c>
-      <c r="E29" s="6">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-28.47</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-62.37</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-33.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-6.34</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-6.35</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-27.73</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-27.27</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-33.55</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-33.82</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-27.75</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-27.56</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-21.71</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-22.3</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-52.93</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.97</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-21.52</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-22.62</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>26.45</v>
-      </c>
-      <c r="D37" s="5">
-        <v>26.62</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>10.02</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.98</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>229.3</v>
-      </c>
-      <c r="D39" s="5">
-        <v>229.89</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>674.05</v>
-      </c>
-      <c r="D40" s="5">
-        <v>669</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>26.46</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1243.9</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1226.4</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>32.36</v>
-      </c>
-      <c r="D43" s="5">
-        <v>36.25</v>
-      </c>
-      <c r="E43" s="6">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>34.53</v>
-      </c>
-      <c r="D44" s="5">
-        <v>33.46</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>37.95</v>
-      </c>
-      <c r="D45" s="5">
-        <v>39.07</v>
-      </c>
-      <c r="E45" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>47.87</v>
-      </c>
-      <c r="D46" s="5">
-        <v>45.93</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>38.11</v>
-      </c>
-      <c r="D47" s="5">
-        <v>42.9</v>
-      </c>
-      <c r="E47" s="6">
-        <v>4.79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>35.96</v>
-      </c>
-      <c r="D48" s="5">
-        <v>32.26</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-77.52</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-71.79000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-3.27</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-22.6</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-19.33</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>13.9</v>
-      </c>
-      <c r="D51" s="5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-70.45999999999999</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-34.14</v>
-      </c>
-      <c r="E52" s="6">
-        <v>36.32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-45.22</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-28.47</v>
-      </c>
-      <c r="E53" s="6">
-        <v>16.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-27.84</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C53" s="6">
         <v>42.82</v>
       </c>
-      <c r="E54" s="6">
-        <v>70.66</v>
+      <c r="D53" s="6">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-51.28</v>
       </c>
     </row>
   </sheetData>
@@ -2591,60 +2636,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.3</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-3.6</v>
-      </c>
-      <c r="G2" s="10">
+      <c r="F2" s="11">
+        <v>-5.6</v>
+      </c>
+      <c r="G2" s="11">
         <v>-7.8</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2746,43 +2791,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0249</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.025</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0742</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.11</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1168</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1608</v>
+      <c r="A2" s="14">
+        <v>0.0275</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0248</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0697</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1116</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1208</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1601</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.9 → 51.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.9</t>
-  </si>
-  <si>
-    <t>51.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,18 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,8 +753,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -922,10 +893,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.42</v>
+        <v>26.26</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-0.61</v>
       </c>
       <c r="E2">
         <v>36.6</v>
@@ -934,25 +905,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.81</v>
+        <v>-28.25</v>
       </c>
       <c r="H2">
-        <v>14.97</v>
+        <v>14.27</v>
       </c>
       <c r="I2">
-        <v>-2.08</v>
+        <v>-1.35</v>
       </c>
       <c r="J2">
-        <v>-4.79</v>
+        <v>-6.78</v>
       </c>
       <c r="K2">
-        <v>-19.89</v>
+        <v>-16.87</v>
       </c>
       <c r="L2">
-        <v>-27</v>
+        <v>-28.17</v>
       </c>
       <c r="M2">
-        <v>-11.16</v>
+        <v>-11.6</v>
       </c>
       <c r="N2">
         <v>50</v>
@@ -961,19 +932,19 @@
         <v>18</v>
       </c>
       <c r="P2">
-        <v>26.51</v>
+        <v>26.43</v>
       </c>
       <c r="Q2">
-        <v>27.45</v>
+        <v>27.35</v>
       </c>
       <c r="R2">
-        <v>27.57</v>
+        <v>27.5</v>
       </c>
       <c r="S2">
-        <v>28.32</v>
+        <v>28.3</v>
       </c>
       <c r="T2">
-        <v>-6.72</v>
+        <v>-7.19</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -988,34 +959,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.79</v>
+        <v>31.92</v>
       </c>
       <c r="Z2">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="AA2">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
       <c r="AB2">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>10.59</v>
+        <v>10.09</v>
       </c>
       <c r="AD2">
-        <v>6.2</v>
+        <v>9.26</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>6.47</v>
+        <v>-36.53</v>
       </c>
       <c r="AG2">
-        <v>28.81</v>
+        <v>28.77</v>
       </c>
       <c r="AH2">
-        <v>26.09</v>
+        <v>25.94</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -1024,7 +995,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>38.95</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1035,10 +1006,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="D3">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1047,46 +1018,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.89</v>
+        <v>-33.75</v>
       </c>
       <c r="H3">
-        <v>12.4</v>
+        <v>12.63</v>
       </c>
       <c r="I3">
-        <v>-2.54</v>
+        <v>0.4</v>
       </c>
       <c r="J3">
-        <v>-5.41</v>
+        <v>-6.46</v>
       </c>
       <c r="K3">
-        <v>-18.28</v>
+        <v>-14.91</v>
       </c>
       <c r="L3">
-        <v>-33.27</v>
+        <v>-33.53</v>
       </c>
       <c r="M3">
-        <v>-16.01</v>
+        <v>-16.76</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P3">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="Q3">
-        <v>10.32</v>
+        <v>10.29</v>
       </c>
       <c r="R3">
-        <v>10.63</v>
+        <v>10.6</v>
       </c>
       <c r="S3">
-        <v>11.01</v>
+        <v>10.99</v>
       </c>
       <c r="T3">
-        <v>-9.44</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1101,34 +1072,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.19</v>
+        <v>34.35</v>
       </c>
       <c r="Z3">
         <v>-0.19</v>
       </c>
       <c r="AA3">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>16.88</v>
+        <v>16.93</v>
       </c>
       <c r="AD3">
-        <v>15.55</v>
+        <v>17.06</v>
       </c>
       <c r="AE3">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="AF3">
-        <v>-41.2</v>
+        <v>-31.05</v>
       </c>
       <c r="AG3">
-        <v>10.8</v>
+        <v>10.77</v>
       </c>
       <c r="AH3">
-        <v>9.83</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AI3">
         <v>10.67</v>
@@ -1137,7 +1108,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>38.28</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1148,10 +1119,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>229.97</v>
+        <v>230.7</v>
       </c>
       <c r="D4">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="E4">
         <v>317.35</v>
@@ -1160,25 +1131,25 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.53</v>
+        <v>-27.3</v>
       </c>
       <c r="H4">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="I4">
-        <v>0.03</v>
+        <v>2.26</v>
       </c>
       <c r="J4">
-        <v>-5.98</v>
+        <v>-5.45</v>
       </c>
       <c r="K4">
-        <v>-5.51</v>
+        <v>-2.99</v>
       </c>
       <c r="L4">
-        <v>-27.1</v>
+        <v>-26.96</v>
       </c>
       <c r="M4">
-        <v>-2.48</v>
+        <v>-2.38</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1187,19 +1158,19 @@
         <v>32</v>
       </c>
       <c r="P4">
-        <v>227.92</v>
+        <v>228.94</v>
       </c>
       <c r="Q4">
-        <v>234.6</v>
+        <v>234.03</v>
       </c>
       <c r="R4">
-        <v>241.94</v>
+        <v>241.72</v>
       </c>
       <c r="S4">
-        <v>252.05</v>
+        <v>251.7</v>
       </c>
       <c r="T4">
-        <v>-8.76</v>
+        <v>-8.34</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1214,34 +1185,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.23</v>
+        <v>40.76</v>
       </c>
       <c r="Z4">
-        <v>-4.43</v>
+        <v>-4.16</v>
       </c>
       <c r="AA4">
-        <v>-4.09</v>
+        <v>-4.11</v>
       </c>
       <c r="AB4">
-        <v>-0.34</v>
+        <v>-0.05</v>
       </c>
       <c r="AC4">
-        <v>63.98</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AD4">
-        <v>41.71</v>
+        <v>58.55</v>
       </c>
       <c r="AE4">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="AF4">
-        <v>-46.91</v>
+        <v>-21.41</v>
       </c>
       <c r="AG4">
-        <v>245.69</v>
+        <v>244.68</v>
       </c>
       <c r="AH4">
-        <v>223.51</v>
+        <v>223.39</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1250,7 +1221,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>42.49</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1261,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>682.7</v>
+        <v>682.6</v>
       </c>
       <c r="D5">
-        <v>2.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1273,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.7</v>
+        <v>-20.72</v>
       </c>
       <c r="H5">
-        <v>39.13</v>
+        <v>39.11</v>
       </c>
       <c r="I5">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="J5">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="K5">
-        <v>24.33</v>
+        <v>25</v>
       </c>
       <c r="L5">
-        <v>-19.67</v>
+        <v>-19.31</v>
       </c>
       <c r="M5">
-        <v>-6.97</v>
+        <v>-7.1</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>672.26</v>
+        <v>676.41</v>
       </c>
       <c r="Q5">
-        <v>679.2</v>
+        <v>680.08</v>
       </c>
       <c r="R5">
-        <v>699.8099999999999</v>
+        <v>699.92</v>
       </c>
       <c r="S5">
-        <v>622.25</v>
+        <v>622.04</v>
       </c>
       <c r="T5">
-        <v>9.710000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1327,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.66</v>
+        <v>51.61</v>
       </c>
       <c r="Z5">
-        <v>-1.61</v>
+        <v>-1.07</v>
       </c>
       <c r="AA5">
-        <v>-0.21</v>
+        <v>-0.38</v>
       </c>
       <c r="AB5">
-        <v>-1.4</v>
+        <v>-0.68</v>
       </c>
       <c r="AC5">
-        <v>35.74</v>
+        <v>48.79</v>
       </c>
       <c r="AD5">
-        <v>32.76</v>
+        <v>38.49</v>
       </c>
       <c r="AE5">
-        <v>23.12</v>
+        <v>22.82</v>
       </c>
       <c r="AF5">
-        <v>-46.11</v>
+        <v>-52.4</v>
       </c>
       <c r="AG5">
-        <v>719.74</v>
+        <v>720.08</v>
       </c>
       <c r="AH5">
-        <v>638.66</v>
+        <v>640.09</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1363,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>18.2</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1374,58 +1345,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.79</v>
+        <v>26.91</v>
       </c>
       <c r="D6">
-        <v>-0.78</v>
+        <v>0.45</v>
       </c>
       <c r="E6">
-        <v>56.22</v>
+        <v>55.71</v>
       </c>
       <c r="F6">
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-52.35</v>
+        <v>-51.7</v>
       </c>
       <c r="H6">
-        <v>3.24</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>0.5600000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="J6">
-        <v>-12.42</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="K6">
-        <v>-21.48</v>
+        <v>-18.65</v>
       </c>
       <c r="L6">
-        <v>-51.1</v>
+        <v>-52.13</v>
       </c>
       <c r="M6">
-        <v>-12.08</v>
+        <v>-12.55</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>26.46</v>
+        <v>26.66</v>
       </c>
       <c r="Q6">
-        <v>27.76</v>
+        <v>27.59</v>
       </c>
       <c r="R6">
-        <v>28.83</v>
+        <v>28.73</v>
       </c>
       <c r="S6">
-        <v>33.83</v>
+        <v>33.75</v>
       </c>
       <c r="T6">
-        <v>-20.82</v>
+        <v>-20.26</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1440,34 +1411,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.55</v>
+        <v>42.66</v>
       </c>
       <c r="Z6">
-        <v>-0.77</v>
+        <v>-0.72</v>
       </c>
       <c r="AA6">
         <v>-0.74</v>
       </c>
       <c r="AB6">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AC6">
-        <v>61.24</v>
+        <v>73.58</v>
       </c>
       <c r="AD6">
-        <v>40.6</v>
+        <v>59.36</v>
       </c>
       <c r="AE6">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="AF6">
-        <v>-62.37</v>
+        <v>-30.42</v>
       </c>
       <c r="AG6">
-        <v>30.55</v>
+        <v>30.12</v>
       </c>
       <c r="AH6">
-        <v>24.97</v>
+        <v>25.06</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1476,7 +1447,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>30.8</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1487,10 +1458,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="D7">
-        <v>1.71</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1499,25 +1470,25 @@
         <v>1226.4</v>
       </c>
       <c r="G7">
-        <v>-21.3</v>
+        <v>-21.74</v>
       </c>
       <c r="H7">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="I7">
-        <v>-0.8</v>
+        <v>0.41</v>
       </c>
       <c r="J7">
-        <v>-5.01</v>
+        <v>-5.74</v>
       </c>
       <c r="K7">
-        <v>-5.96</v>
+        <v>-5.28</v>
       </c>
       <c r="L7">
-        <v>-10.83</v>
+        <v>-11.86</v>
       </c>
       <c r="M7">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1526,19 +1497,19 @@
         <v>44</v>
       </c>
       <c r="P7">
-        <v>1238.6</v>
+        <v>1239.62</v>
       </c>
       <c r="Q7">
-        <v>1281.28</v>
+        <v>1277.81</v>
       </c>
       <c r="R7">
-        <v>1295.19</v>
+        <v>1294.06</v>
       </c>
       <c r="S7">
-        <v>1371.77</v>
+        <v>1370.32</v>
       </c>
       <c r="T7">
-        <v>-9.07</v>
+        <v>-9.48</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1553,34 +1524,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.21</v>
+        <v>38.59</v>
       </c>
       <c r="Z7">
-        <v>-17.75</v>
+        <v>-18.11</v>
       </c>
       <c r="AA7">
-        <v>-11.65</v>
+        <v>-12.94</v>
       </c>
       <c r="AB7">
-        <v>-6.11</v>
+        <v>-5.17</v>
       </c>
       <c r="AC7">
-        <v>16.6</v>
+        <v>20.8</v>
       </c>
       <c r="AD7">
-        <v>10.68</v>
+        <v>15.04</v>
       </c>
       <c r="AE7">
-        <v>20.93</v>
+        <v>20.47</v>
       </c>
       <c r="AF7">
-        <v>-8.460000000000001</v>
+        <v>-4.16</v>
       </c>
       <c r="AG7">
-        <v>1341.61</v>
+        <v>1339.2</v>
       </c>
       <c r="AH7">
-        <v>1220.94</v>
+        <v>1216.41</v>
       </c>
       <c r="AI7">
         <v>1299.24</v>
@@ -1589,7 +1560,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>44.83</v>
+        <v>46.05</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1750,47 +1721,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1798,819 +1734,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.79</v>
       </c>
-      <c r="E7" s="7">
-        <v>-2.01</v>
+      <c r="D7" s="5">
+        <v>-6.78</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-4.31</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.41</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.1</v>
+      <c r="D8" s="5">
+        <v>-6.46</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
+        <v>-5.98</v>
+      </c>
+      <c r="D9" s="5">
         <v>-5.45</v>
       </c>
-      <c r="D9" s="6">
-        <v>-5.98</v>
-      </c>
       <c r="E9" s="7">
-        <v>-0.53</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>0.3</v>
       </c>
+      <c r="D10" s="5">
+        <v>1.27</v>
+      </c>
       <c r="E10" s="7">
-        <v>-0.99</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.81</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-12.42</v>
       </c>
+      <c r="D11" s="5">
+        <v>-9.880000000000001</v>
+      </c>
       <c r="E11" s="7">
-        <v>-8.609999999999999</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-5.01</v>
       </c>
-      <c r="E12" s="8">
-        <v>1.44</v>
+      <c r="D12" s="5">
+        <v>-5.74</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-1.59</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-2.08</v>
       </c>
+      <c r="D13" s="5">
+        <v>-1.35</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.49</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
+        <v>-2.54</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.58</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3.14</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3.7</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.8</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-28.17</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-33.27</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-33.53</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-27.1</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-26.96</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-19.67</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-19.31</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-51.1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-52.13</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.83</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.86</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-19.89</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-16.87</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-18.28</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-14.91</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>24.33</v>
+      </c>
+      <c r="D28" s="5">
+        <v>25</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-21.48</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-18.65</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-5.28</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-27.81</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-28.25</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-33.89</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-33.75</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-27.53</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-27.3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-20.7</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-20.72</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.35</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-51.7</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-21.74</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>26.42</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.26</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>229.97</v>
+      </c>
+      <c r="D39" s="5">
+        <v>230.7</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>682.7</v>
+      </c>
+      <c r="D40" s="5">
+        <v>682.6</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.79</v>
+      </c>
+      <c r="D41" s="5">
+        <v>26.91</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1247.4</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1240.4</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>33.79</v>
+      </c>
+      <c r="D43" s="5">
+        <v>31.92</v>
+      </c>
+      <c r="E43" s="6">
         <v>-1.87</v>
       </c>
-      <c r="D14" s="6">
-        <v>-2.54</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>33.19</v>
+      </c>
+      <c r="D44" s="5">
+        <v>34.35</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.16</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>39.23</v>
+      </c>
+      <c r="D45" s="5">
+        <v>40.76</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.04</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.58</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>51.66</v>
+      </c>
+      <c r="D46" s="5">
+        <v>51.61</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.63</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>41.55</v>
+      </c>
+      <c r="D47" s="5">
+        <v>42.66</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>40.21</v>
+      </c>
+      <c r="D48" s="5">
+        <v>38.59</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.36</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-27</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>6.47</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-36.53</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-33.02</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-33.27</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-41.2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-31.05</v>
+      </c>
+      <c r="E50" s="7">
+        <v>10.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-46.91</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-21.41</v>
+      </c>
+      <c r="E51" s="7">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-21.38</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-19.67</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-46.11</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-52.4</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-6.29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-50.06</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-51.1</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-62.37</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-30.42</v>
+      </c>
+      <c r="E53" s="7">
+        <v>31.95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-11.95</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-10.83</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-19.53</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-19.89</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-18.06</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-18.28</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>23.91</v>
-      </c>
-      <c r="D27" s="6">
-        <v>24.33</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-20.54</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-21.48</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-6.35</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-27.27</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-27.81</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-33.82</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.89</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-27.56</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-27.53</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-22.3</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-20.7</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-51.97</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-52.35</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-22.62</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-21.3</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>26.62</v>
-      </c>
-      <c r="D36" s="6">
-        <v>26.42</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>9.98</v>
-      </c>
-      <c r="D37" s="6">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>229.89</v>
-      </c>
-      <c r="D38" s="6">
-        <v>229.97</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>669</v>
-      </c>
-      <c r="D39" s="6">
-        <v>682.7</v>
-      </c>
-      <c r="E39" s="8">
-        <v>13.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>27</v>
-      </c>
-      <c r="D40" s="6">
-        <v>26.79</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1226.4</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1247.4</v>
-      </c>
-      <c r="E41" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>36.25</v>
-      </c>
-      <c r="D42" s="6">
-        <v>33.79</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>33.46</v>
-      </c>
-      <c r="D43" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>39.07</v>
-      </c>
-      <c r="D44" s="6">
-        <v>39.23</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>45.93</v>
-      </c>
-      <c r="D45" s="6">
-        <v>51.66</v>
-      </c>
-      <c r="E45" s="8">
-        <v>5.73</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>42.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>41.55</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>32.26</v>
-      </c>
-      <c r="D47" s="6">
-        <v>40.21</v>
-      </c>
-      <c r="E47" s="8">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="6">
-        <v>-77.52</v>
-      </c>
-      <c r="D48" s="6">
-        <v>6.47</v>
-      </c>
-      <c r="E48" s="8">
-        <v>83.98999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-22.6</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-41.2</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-18.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-46.91</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-55.11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-34.14</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-46.11</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-11.97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-28.47</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-62.37</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-33.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>42.82</v>
-      </c>
-      <c r="D53" s="6">
+      <c r="C54" s="5">
         <v>-8.460000000000001</v>
       </c>
-      <c r="E53" s="7">
-        <v>-51.28</v>
+      <c r="D54" s="5">
+        <v>-4.16</v>
+      </c>
+      <c r="E54" s="7">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -2636,60 +2589,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
+        <v>-5.5</v>
+      </c>
+      <c r="G2" s="10">
         <v>-5.6</v>
       </c>
-      <c r="G2" s="11">
-        <v>-7.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2791,43 +2744,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0275</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0248</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0697</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1116</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1208</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1601</v>
+      <c r="A2" s="13">
+        <v>0.0242</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0238</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.116</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1255</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1676</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -255,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -893,37 +893,37 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.26</v>
+        <v>26.84</v>
       </c>
       <c r="D2">
-        <v>-0.61</v>
+        <v>2.21</v>
       </c>
       <c r="E2">
-        <v>36.6</v>
+        <v>36.35</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-28.25</v>
+        <v>-26.16</v>
       </c>
       <c r="H2">
-        <v>14.27</v>
+        <v>16.8</v>
       </c>
       <c r="I2">
-        <v>-1.35</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
-        <v>-6.78</v>
+        <v>-4.62</v>
       </c>
       <c r="K2">
-        <v>-16.87</v>
+        <v>-17.52</v>
       </c>
       <c r="L2">
-        <v>-28.17</v>
+        <v>-26.67</v>
       </c>
       <c r="M2">
-        <v>-11.6</v>
+        <v>-11</v>
       </c>
       <c r="N2">
         <v>50</v>
@@ -932,19 +932,19 @@
         <v>18</v>
       </c>
       <c r="P2">
-        <v>26.43</v>
+        <v>26.52</v>
       </c>
       <c r="Q2">
-        <v>27.35</v>
+        <v>27.29</v>
       </c>
       <c r="R2">
-        <v>27.5</v>
+        <v>27.43</v>
       </c>
       <c r="S2">
-        <v>28.3</v>
+        <v>28.27</v>
       </c>
       <c r="T2">
-        <v>-7.19</v>
+        <v>-5.06</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,34 +959,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.92</v>
+        <v>44</v>
       </c>
       <c r="Z2">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="AA2">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="AC2">
-        <v>10.09</v>
+        <v>24.3</v>
       </c>
       <c r="AD2">
-        <v>9.26</v>
+        <v>14.99</v>
       </c>
       <c r="AE2">
         <v>0.71</v>
       </c>
       <c r="AF2">
-        <v>-36.53</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
-        <v>28.77</v>
+        <v>28.67</v>
       </c>
       <c r="AH2">
-        <v>25.94</v>
+        <v>25.9</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -995,7 +995,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>38.22</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1006,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.99</v>
+        <v>10.1</v>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="E3">
         <v>15.08</v>
@@ -1018,25 +1018,25 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.75</v>
+        <v>-33.02</v>
       </c>
       <c r="H3">
-        <v>12.63</v>
+        <v>13.87</v>
       </c>
       <c r="I3">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>-6.46</v>
+        <v>-4.63</v>
       </c>
       <c r="K3">
-        <v>-14.91</v>
+        <v>-14.55</v>
       </c>
       <c r="L3">
-        <v>-33.53</v>
+        <v>-32.67</v>
       </c>
       <c r="M3">
-        <v>-16.76</v>
+        <v>-16.31</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1045,19 +1045,19 @@
         <v>15</v>
       </c>
       <c r="P3">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="Q3">
-        <v>10.29</v>
+        <v>10.26</v>
       </c>
       <c r="R3">
-        <v>10.6</v>
+        <v>10.58</v>
       </c>
       <c r="S3">
-        <v>10.99</v>
+        <v>10.98</v>
       </c>
       <c r="T3">
-        <v>-9.140000000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,34 +1072,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.35</v>
+        <v>40.49</v>
       </c>
       <c r="Z3">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="AA3">
         <v>-0.17</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AC3">
-        <v>16.93</v>
+        <v>33.28</v>
       </c>
       <c r="AD3">
-        <v>17.06</v>
+        <v>22.36</v>
       </c>
       <c r="AE3">
         <v>0.22</v>
       </c>
       <c r="AF3">
-        <v>-31.05</v>
+        <v>6.69</v>
       </c>
       <c r="AG3">
-        <v>10.77</v>
+        <v>10.73</v>
       </c>
       <c r="AH3">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AI3">
         <v>10.67</v>
@@ -1108,7 +1108,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>37.88</v>
+        <v>34.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,37 +1119,37 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>230.7</v>
+        <v>232.15</v>
       </c>
       <c r="D4">
-        <v>0.32</v>
+        <v>0.63</v>
       </c>
       <c r="E4">
-        <v>317.35</v>
+        <v>317</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.3</v>
+        <v>-26.77</v>
       </c>
       <c r="H4">
-        <v>2.95</v>
+        <v>3.59</v>
       </c>
       <c r="I4">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
-        <v>-5.45</v>
+        <v>-4.07</v>
       </c>
       <c r="K4">
-        <v>-2.99</v>
+        <v>-2.81</v>
       </c>
       <c r="L4">
-        <v>-26.96</v>
+        <v>-26.85</v>
       </c>
       <c r="M4">
-        <v>-2.38</v>
+        <v>-2.18</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1158,19 +1158,19 @@
         <v>32</v>
       </c>
       <c r="P4">
-        <v>228.94</v>
+        <v>230.4</v>
       </c>
       <c r="Q4">
-        <v>234.03</v>
+        <v>233.48</v>
       </c>
       <c r="R4">
-        <v>241.72</v>
+        <v>241.65</v>
       </c>
       <c r="S4">
-        <v>251.7</v>
+        <v>251.35</v>
       </c>
       <c r="T4">
-        <v>-8.34</v>
+        <v>-7.64</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,34 +1185,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.76</v>
+        <v>43.79</v>
       </c>
       <c r="Z4">
-        <v>-4.16</v>
+        <v>-3.78</v>
       </c>
       <c r="AA4">
-        <v>-4.11</v>
+        <v>-4.04</v>
       </c>
       <c r="AB4">
-        <v>-0.05</v>
+        <v>0.26</v>
       </c>
       <c r="AC4">
-        <v>70.09999999999999</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="AD4">
-        <v>58.55</v>
+        <v>71.47</v>
       </c>
       <c r="AE4">
-        <v>4.31</v>
+        <v>4.13</v>
       </c>
       <c r="AF4">
-        <v>-21.41</v>
+        <v>-37.1</v>
       </c>
       <c r="AG4">
-        <v>244.68</v>
+        <v>243.25</v>
       </c>
       <c r="AH4">
-        <v>223.39</v>
+        <v>223.72</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1221,7 +1221,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>37.41</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>682.6</v>
+        <v>693.55</v>
       </c>
       <c r="D5">
-        <v>-0.01</v>
+        <v>1.6</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.72</v>
+        <v>-19.44</v>
       </c>
       <c r="H5">
-        <v>39.11</v>
+        <v>41.34</v>
       </c>
       <c r="I5">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="J5">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>25</v>
+        <v>25.89</v>
       </c>
       <c r="L5">
-        <v>-19.31</v>
+        <v>-18.36</v>
       </c>
       <c r="M5">
-        <v>-7.1</v>
+        <v>-6.86</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>676.41</v>
+        <v>680.38</v>
       </c>
       <c r="Q5">
-        <v>680.08</v>
+        <v>681.99</v>
       </c>
       <c r="R5">
-        <v>699.92</v>
+        <v>697.99</v>
       </c>
       <c r="S5">
-        <v>622.04</v>
+        <v>621.85</v>
       </c>
       <c r="T5">
-        <v>9.74</v>
+        <v>11.53</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1298,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.61</v>
+        <v>55.94</v>
       </c>
       <c r="Z5">
-        <v>-1.07</v>
+        <v>0.24</v>
       </c>
       <c r="AA5">
-        <v>-0.38</v>
+        <v>-0.26</v>
       </c>
       <c r="AB5">
-        <v>-0.68</v>
+        <v>0.5</v>
       </c>
       <c r="AC5">
-        <v>48.79</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AD5">
-        <v>38.49</v>
+        <v>53.48</v>
       </c>
       <c r="AE5">
-        <v>22.82</v>
+        <v>22.46</v>
       </c>
       <c r="AF5">
-        <v>-52.4</v>
+        <v>-52.13</v>
       </c>
       <c r="AG5">
-        <v>720.08</v>
+        <v>720.65</v>
       </c>
       <c r="AH5">
-        <v>640.09</v>
+        <v>643.33</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1334,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>18.76</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1345,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.91</v>
+        <v>27.14</v>
       </c>
       <c r="D6">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="E6">
-        <v>55.71</v>
+        <v>55.43</v>
       </c>
       <c r="F6">
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-51.7</v>
+        <v>-51.04</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>4.59</v>
       </c>
       <c r="I6">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="J6">
-        <v>-9.880000000000001</v>
+        <v>-10.55</v>
       </c>
       <c r="K6">
-        <v>-18.65</v>
+        <v>-18.18</v>
       </c>
       <c r="L6">
-        <v>-52.13</v>
+        <v>-51.28</v>
       </c>
       <c r="M6">
-        <v>-12.55</v>
+        <v>-12.2</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1384,19 +1384,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.66</v>
+        <v>26.86</v>
       </c>
       <c r="Q6">
-        <v>27.59</v>
+        <v>27.43</v>
       </c>
       <c r="R6">
-        <v>28.73</v>
+        <v>28.63</v>
       </c>
       <c r="S6">
-        <v>33.75</v>
+        <v>33.66</v>
       </c>
       <c r="T6">
-        <v>-20.26</v>
+        <v>-19.38</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1411,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>42.66</v>
+        <v>44.82</v>
       </c>
       <c r="Z6">
+        <v>-0.66</v>
+      </c>
+      <c r="AA6">
         <v>-0.72</v>
       </c>
-      <c r="AA6">
-        <v>-0.74</v>
-      </c>
       <c r="AB6">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>73.58</v>
+        <v>78.78</v>
       </c>
       <c r="AD6">
-        <v>59.36</v>
+        <v>71.2</v>
       </c>
       <c r="AE6">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AF6">
-        <v>-30.42</v>
+        <v>-47.67</v>
       </c>
       <c r="AG6">
-        <v>30.12</v>
+        <v>29.6</v>
       </c>
       <c r="AH6">
-        <v>25.06</v>
+        <v>25.26</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1447,7 +1447,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.06</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1458,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="D7">
-        <v>-0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,46 +1470,46 @@
         <v>1226.4</v>
       </c>
       <c r="G7">
-        <v>-21.74</v>
+        <v>-21.26</v>
       </c>
       <c r="H7">
-        <v>1.14</v>
+        <v>1.76</v>
       </c>
       <c r="I7">
-        <v>0.41</v>
+        <v>0.65</v>
       </c>
       <c r="J7">
-        <v>-5.74</v>
+        <v>-4.72</v>
       </c>
       <c r="K7">
-        <v>-5.28</v>
+        <v>-4.99</v>
       </c>
       <c r="L7">
-        <v>-11.86</v>
+        <v>-11.39</v>
       </c>
       <c r="M7">
-        <v>2.42</v>
+        <v>2.05</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>1239.62</v>
+        <v>1241.22</v>
       </c>
       <c r="Q7">
-        <v>1277.81</v>
+        <v>1274.36</v>
       </c>
       <c r="R7">
-        <v>1294.06</v>
+        <v>1293.16</v>
       </c>
       <c r="S7">
-        <v>1370.32</v>
+        <v>1368.91</v>
       </c>
       <c r="T7">
-        <v>-9.48</v>
+        <v>-8.83</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,34 +1524,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38.59</v>
+        <v>41.36</v>
       </c>
       <c r="Z7">
-        <v>-18.11</v>
+        <v>-17.58</v>
       </c>
       <c r="AA7">
-        <v>-12.94</v>
+        <v>-13.87</v>
       </c>
       <c r="AB7">
-        <v>-5.17</v>
+        <v>-3.71</v>
       </c>
       <c r="AC7">
-        <v>20.8</v>
+        <v>34.06</v>
       </c>
       <c r="AD7">
-        <v>15.04</v>
+        <v>23.82</v>
       </c>
       <c r="AE7">
-        <v>20.47</v>
+        <v>20</v>
       </c>
       <c r="AF7">
-        <v>-4.16</v>
+        <v>-26.73</v>
       </c>
       <c r="AG7">
-        <v>1339.2</v>
+        <v>1334.22</v>
       </c>
       <c r="AH7">
-        <v>1216.41</v>
+        <v>1214.49</v>
       </c>
       <c r="AI7">
         <v>1299.24</v>
@@ -1560,7 +1560,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>46.05</v>
+        <v>46.71</v>
       </c>
     </row>
   </sheetData>
@@ -1758,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.79</v>
+        <v>-6.78</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.78</v>
+        <v>-4.62</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.99</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1775,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.41</v>
+        <v>-6.46</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.46</v>
+        <v>-4.63</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.05</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1792,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.98</v>
+        <v>-5.45</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.45</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.53</v>
+        <v>-4.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1809,13 +1809,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>0.3</v>
+        <v>1.27</v>
       </c>
       <c r="D10" s="5">
-        <v>1.27</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.97</v>
+        <v>4.3</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1826,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-12.42</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.880000000000001</v>
+        <v>-10.55</v>
       </c>
       <c r="E11" s="7">
-        <v>2.54</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1843,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.01</v>
+        <v>-5.74</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.74</v>
+        <v>-4.72</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.73</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1860,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.08</v>
+        <v>-1.35</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.35</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.73</v>
+        <v>1.59</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.94</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1877,13 +1877,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.54</v>
+        <v>0.4</v>
       </c>
       <c r="D14" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.94</v>
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1894,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>0.03</v>
+        <v>2.26</v>
       </c>
       <c r="D15" s="5">
-        <v>2.26</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.23</v>
+        <v>3.25</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.99</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1911,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="D16" s="5">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="E16" s="7">
-        <v>0.5600000000000001</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1928,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>0.5600000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="D17" s="5">
-        <v>3.7</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.14</v>
+        <v>3.91</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.21</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1945,13 +1945,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.8</v>
+        <v>0.41</v>
       </c>
       <c r="D18" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.21</v>
+        <v>0.65</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1962,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27</v>
+        <v>-28.17</v>
       </c>
       <c r="D19" s="5">
-        <v>-28.17</v>
+        <v>-26.67</v>
       </c>
       <c r="E19" s="6">
-        <v>-1.17</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1979,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-33.27</v>
+        <v>-33.53</v>
       </c>
       <c r="D20" s="5">
-        <v>-33.53</v>
+        <v>-32.67</v>
       </c>
       <c r="E20" s="6">
-        <v>-0.26</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1996,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.1</v>
+        <v>-26.96</v>
       </c>
       <c r="D21" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.14</v>
+        <v>-26.85</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.11</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2013,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-19.67</v>
+        <v>-19.31</v>
       </c>
       <c r="D22" s="5">
-        <v>-19.31</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.36</v>
+        <v>-18.36</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.95</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2030,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-51.1</v>
+        <v>-52.13</v>
       </c>
       <c r="D23" s="5">
-        <v>-52.13</v>
+        <v>-51.28</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.03</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2047,13 +2047,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-10.83</v>
+        <v>-11.86</v>
       </c>
       <c r="D24" s="5">
-        <v>-11.86</v>
+        <v>-11.39</v>
       </c>
       <c r="E24" s="6">
-        <v>-1.03</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2064,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-19.89</v>
+        <v>-16.87</v>
       </c>
       <c r="D25" s="5">
-        <v>-16.87</v>
+        <v>-17.52</v>
       </c>
       <c r="E25" s="7">
-        <v>3.02</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2081,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-18.28</v>
+        <v>-14.91</v>
       </c>
       <c r="D26" s="5">
-        <v>-14.91</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.37</v>
+        <v>-14.55</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.36</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2098,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-5.51</v>
+        <v>-2.99</v>
       </c>
       <c r="D27" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.52</v>
+        <v>-2.81</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.18</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2115,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>24.33</v>
+        <v>25</v>
       </c>
       <c r="D28" s="5">
-        <v>25</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.67</v>
+        <v>25.89</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2132,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-21.48</v>
+        <v>-18.65</v>
       </c>
       <c r="D29" s="5">
-        <v>-18.65</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.83</v>
+        <v>-18.18</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.47</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2149,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-5.96</v>
+        <v>-5.28</v>
       </c>
       <c r="D30" s="5">
-        <v>-5.28</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.68</v>
+        <v>-4.99</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.29</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2166,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.81</v>
+        <v>-28.25</v>
       </c>
       <c r="D31" s="5">
-        <v>-28.25</v>
+        <v>-26.16</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.44</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2183,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-33.89</v>
+        <v>-33.75</v>
       </c>
       <c r="D32" s="5">
-        <v>-33.75</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.14</v>
+        <v>-33.02</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.73</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2200,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-27.53</v>
+        <v>-27.3</v>
       </c>
       <c r="D33" s="5">
-        <v>-27.3</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.23</v>
+        <v>-26.77</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.53</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2217,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-20.7</v>
+        <v>-20.72</v>
       </c>
       <c r="D34" s="5">
-        <v>-20.72</v>
+        <v>-19.44</v>
       </c>
       <c r="E34" s="6">
-        <v>-0.02</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2234,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-52.35</v>
+        <v>-51.7</v>
       </c>
       <c r="D35" s="5">
-        <v>-51.7</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.65</v>
+        <v>-51.04</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.66</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2251,13 +2251,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-21.3</v>
+        <v>-21.74</v>
       </c>
       <c r="D36" s="5">
-        <v>-21.74</v>
+        <v>-21.26</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.44</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2268,13 +2268,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>26.42</v>
+        <v>26.26</v>
       </c>
       <c r="D37" s="5">
-        <v>26.26</v>
+        <v>26.84</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.16</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2285,13 +2285,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.970000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="D38" s="5">
-        <v>9.99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.02</v>
+        <v>10.1</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.11</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2302,13 +2302,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>229.97</v>
+        <v>230.7</v>
       </c>
       <c r="D39" s="5">
-        <v>230.7</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.73</v>
+        <v>232.15</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.45</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2319,13 +2319,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>682.7</v>
+        <v>682.6</v>
       </c>
       <c r="D40" s="5">
-        <v>682.6</v>
+        <v>693.55</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.1</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2336,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>26.79</v>
+        <v>26.91</v>
       </c>
       <c r="D41" s="5">
-        <v>26.91</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.12</v>
+        <v>27.14</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2353,13 +2353,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1247.4</v>
+        <v>1240.4</v>
       </c>
       <c r="D42" s="5">
-        <v>1240.4</v>
+        <v>1248</v>
       </c>
       <c r="E42" s="6">
-        <v>-7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2370,13 +2370,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>33.79</v>
+        <v>31.92</v>
       </c>
       <c r="D43" s="5">
-        <v>31.92</v>
+        <v>44</v>
       </c>
       <c r="E43" s="6">
-        <v>-1.87</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2387,13 +2387,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="5">
-        <v>33.19</v>
+        <v>34.35</v>
       </c>
       <c r="D44" s="5">
-        <v>34.35</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.16</v>
+        <v>40.49</v>
+      </c>
+      <c r="E44" s="6">
+        <v>6.14</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>39.23</v>
+        <v>40.76</v>
       </c>
       <c r="D45" s="5">
-        <v>40.76</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.53</v>
+        <v>43.79</v>
+      </c>
+      <c r="E45" s="6">
+        <v>3.03</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2421,13 +2421,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>51.66</v>
+        <v>51.61</v>
       </c>
       <c r="D46" s="5">
-        <v>51.61</v>
+        <v>55.94</v>
       </c>
       <c r="E46" s="6">
-        <v>-0.05</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2438,13 +2438,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>41.55</v>
+        <v>42.66</v>
       </c>
       <c r="D47" s="5">
-        <v>42.66</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.11</v>
+        <v>44.82</v>
+      </c>
+      <c r="E47" s="6">
+        <v>2.16</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2455,13 +2455,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>40.21</v>
+        <v>38.59</v>
       </c>
       <c r="D48" s="5">
-        <v>38.59</v>
+        <v>41.36</v>
       </c>
       <c r="E48" s="6">
-        <v>-1.62</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2472,13 +2472,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>6.47</v>
+        <v>-36.53</v>
       </c>
       <c r="D49" s="5">
-        <v>-36.53</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E49" s="6">
-        <v>-43</v>
+        <v>45.73</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2489,13 +2489,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>-41.2</v>
+        <v>-31.05</v>
       </c>
       <c r="D50" s="5">
-        <v>-31.05</v>
-      </c>
-      <c r="E50" s="7">
-        <v>10.15</v>
+        <v>6.69</v>
+      </c>
+      <c r="E50" s="6">
+        <v>37.74</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2506,13 +2506,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>-46.91</v>
+        <v>-21.41</v>
       </c>
       <c r="D51" s="5">
-        <v>-21.41</v>
+        <v>-37.1</v>
       </c>
       <c r="E51" s="7">
-        <v>25.5</v>
+        <v>-15.69</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2523,13 +2523,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-46.11</v>
+        <v>-52.4</v>
       </c>
       <c r="D52" s="5">
-        <v>-52.4</v>
+        <v>-52.13</v>
       </c>
       <c r="E52" s="6">
-        <v>-6.29</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2540,13 +2540,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-62.37</v>
+        <v>-30.42</v>
       </c>
       <c r="D53" s="5">
-        <v>-30.42</v>
+        <v>-47.67</v>
       </c>
       <c r="E53" s="7">
-        <v>31.95</v>
+        <v>-17.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2557,13 +2557,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>-8.460000000000001</v>
+        <v>-4.16</v>
       </c>
       <c r="D54" s="5">
-        <v>-4.16</v>
+        <v>-26.73</v>
       </c>
       <c r="E54" s="7">
-        <v>4.3</v>
+        <v>-22.57</v>
       </c>
     </row>
   </sheetData>
@@ -2628,16 +2628,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>40</v>
+        <v>45.1</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.5</v>
+        <v>-4</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2765,22 +2765,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0242</v>
+        <v>0.0205</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0238</v>
+        <v>-0.0218</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07099999999999999</v>
+        <v>-0.06860000000000001</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.116</v>
+        <v>-0.11</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1255</v>
+        <v>-0.122</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1676</v>
+        <v>-0.1631</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>55.9 → 47.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>55.9</t>
+  </si>
+  <si>
+    <t>47.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,58 +921,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.84</v>
+        <v>26.52</v>
       </c>
       <c r="D2">
-        <v>2.21</v>
+        <v>-1.19</v>
       </c>
       <c r="E2">
-        <v>36.35</v>
+        <v>35.97</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.16</v>
+        <v>-26.27</v>
       </c>
       <c r="H2">
-        <v>16.8</v>
+        <v>15.4</v>
       </c>
       <c r="I2">
-        <v>1.59</v>
+        <v>0.26</v>
       </c>
       <c r="J2">
-        <v>-4.62</v>
+        <v>-5.69</v>
       </c>
       <c r="K2">
-        <v>-17.52</v>
+        <v>-15.11</v>
       </c>
       <c r="L2">
-        <v>-26.67</v>
+        <v>-27.04</v>
       </c>
       <c r="M2">
-        <v>-11</v>
+        <v>-11.02</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P2">
-        <v>26.52</v>
+        <v>26.53</v>
       </c>
       <c r="Q2">
-        <v>27.29</v>
+        <v>27.23</v>
       </c>
       <c r="R2">
-        <v>27.43</v>
+        <v>27.38</v>
       </c>
       <c r="S2">
-        <v>28.27</v>
+        <v>28.25</v>
       </c>
       <c r="T2">
-        <v>-5.06</v>
+        <v>-6.12</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>44</v>
+        <v>39.8</v>
       </c>
       <c r="Z2">
         <v>-0.35</v>
       </c>
       <c r="AA2">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="AB2">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>24.3</v>
+        <v>34.25</v>
       </c>
       <c r="AD2">
-        <v>14.99</v>
+        <v>22.88</v>
       </c>
       <c r="AE2">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>9.199999999999999</v>
+        <v>-5.72</v>
       </c>
       <c r="AG2">
-        <v>28.67</v>
+        <v>28.64</v>
       </c>
       <c r="AH2">
-        <v>25.9</v>
+        <v>25.82</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -995,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>35.75</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,58 +1034,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.1</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D3">
-        <v>1.1</v>
+        <v>-1.39</v>
       </c>
       <c r="E3">
-        <v>15.08</v>
+        <v>14.86</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.02</v>
+        <v>-32.97</v>
       </c>
       <c r="H3">
-        <v>13.87</v>
+        <v>12.29</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="J3">
-        <v>-4.63</v>
+        <v>-5.68</v>
       </c>
       <c r="K3">
-        <v>-14.55</v>
+        <v>-15.09</v>
       </c>
       <c r="L3">
-        <v>-32.67</v>
+        <v>-33.95</v>
       </c>
       <c r="M3">
-        <v>-16.31</v>
+        <v>-16.2</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P3">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="Q3">
-        <v>10.26</v>
+        <v>10.23</v>
       </c>
       <c r="R3">
-        <v>10.58</v>
+        <v>10.56</v>
       </c>
       <c r="S3">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
       <c r="T3">
-        <v>-8.02</v>
+        <v>-9.19</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.49</v>
+        <v>35.89</v>
       </c>
       <c r="Z3">
         <v>-0.18</v>
@@ -1081,34 +1109,34 @@
         <v>-0.17</v>
       </c>
       <c r="AB3">
-        <v>-0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>33.28</v>
+        <v>39.45</v>
       </c>
       <c r="AD3">
-        <v>22.36</v>
+        <v>29.88</v>
       </c>
       <c r="AE3">
         <v>0.22</v>
       </c>
       <c r="AF3">
-        <v>6.69</v>
+        <v>34.26</v>
       </c>
       <c r="AG3">
-        <v>10.73</v>
+        <v>10.7</v>
       </c>
       <c r="AH3">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="AI3">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>34.57</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,58 +1147,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>232.15</v>
+        <v>227.2</v>
       </c>
       <c r="D4">
-        <v>0.63</v>
+        <v>-2.13</v>
       </c>
       <c r="E4">
-        <v>317</v>
+        <v>314.9</v>
       </c>
       <c r="F4">
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-26.77</v>
+        <v>-27.85</v>
       </c>
       <c r="H4">
-        <v>3.59</v>
+        <v>1.38</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>-0.92</v>
       </c>
       <c r="J4">
-        <v>-4.07</v>
+        <v>-6.56</v>
       </c>
       <c r="K4">
-        <v>-2.81</v>
+        <v>-5.11</v>
       </c>
       <c r="L4">
-        <v>-26.85</v>
+        <v>-28.33</v>
       </c>
       <c r="M4">
-        <v>-2.18</v>
+        <v>-2.86</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>230.4</v>
+        <v>229.98</v>
       </c>
       <c r="Q4">
-        <v>233.48</v>
+        <v>232.79</v>
       </c>
       <c r="R4">
-        <v>241.65</v>
+        <v>241.46</v>
       </c>
       <c r="S4">
-        <v>251.35</v>
+        <v>250.96</v>
       </c>
       <c r="T4">
-        <v>-7.64</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.79</v>
+        <v>36.86</v>
       </c>
       <c r="Z4">
-        <v>-3.78</v>
+        <v>-3.84</v>
       </c>
       <c r="AA4">
-        <v>-4.04</v>
+        <v>-4</v>
       </c>
       <c r="AB4">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="AC4">
-        <v>80.31999999999999</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="AD4">
-        <v>71.47</v>
+        <v>75.22</v>
       </c>
       <c r="AE4">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="AF4">
-        <v>-37.1</v>
+        <v>3.5</v>
       </c>
       <c r="AG4">
-        <v>243.25</v>
+        <v>242.27</v>
       </c>
       <c r="AH4">
-        <v>223.72</v>
+        <v>223.32</v>
       </c>
       <c r="AI4">
         <v>240.04</v>
@@ -1221,7 +1249,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.01</v>
+        <v>32.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>693.55</v>
+        <v>672.35</v>
       </c>
       <c r="D5">
-        <v>1.6</v>
+        <v>-3.06</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-19.44</v>
+        <v>-21.91</v>
       </c>
       <c r="H5">
-        <v>41.34</v>
+        <v>37.02</v>
       </c>
       <c r="I5">
-        <v>2.95</v>
+        <v>-0.25</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="K5">
-        <v>25.89</v>
+        <v>25.04</v>
       </c>
       <c r="L5">
-        <v>-18.36</v>
+        <v>-19.74</v>
       </c>
       <c r="M5">
-        <v>-6.86</v>
+        <v>-7.44</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>680.38</v>
+        <v>680.04</v>
       </c>
       <c r="Q5">
-        <v>681.99</v>
+        <v>683.22</v>
       </c>
       <c r="R5">
-        <v>697.99</v>
+        <v>695.36</v>
       </c>
       <c r="S5">
-        <v>621.85</v>
+        <v>621.5599999999999</v>
       </c>
       <c r="T5">
-        <v>11.53</v>
+        <v>8.17</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1298,34 +1326,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>55.94</v>
+        <v>47.15</v>
       </c>
       <c r="Z5">
-        <v>0.24</v>
+        <v>-0.42</v>
       </c>
       <c r="AA5">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="AB5">
-        <v>0.5</v>
+        <v>-0.13</v>
       </c>
       <c r="AC5">
-        <v>75.90000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="AD5">
-        <v>53.48</v>
+        <v>64.06</v>
       </c>
       <c r="AE5">
-        <v>22.46</v>
+        <v>23.11</v>
       </c>
       <c r="AF5">
-        <v>-52.13</v>
+        <v>-69.31999999999999</v>
       </c>
       <c r="AG5">
-        <v>720.65</v>
+        <v>718.72</v>
       </c>
       <c r="AH5">
-        <v>643.33</v>
+        <v>647.73</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1334,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>20.09</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1373,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>27.14</v>
+        <v>26.97</v>
       </c>
       <c r="D6">
-        <v>0.85</v>
+        <v>-0.63</v>
       </c>
       <c r="E6">
-        <v>55.43</v>
+        <v>55.05</v>
       </c>
       <c r="F6">
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-51.04</v>
+        <v>-51.01</v>
       </c>
       <c r="H6">
-        <v>4.59</v>
+        <v>3.93</v>
       </c>
       <c r="I6">
-        <v>3.91</v>
+        <v>1.93</v>
       </c>
       <c r="J6">
-        <v>-10.55</v>
+        <v>-11.17</v>
       </c>
       <c r="K6">
-        <v>-18.18</v>
+        <v>-17.35</v>
       </c>
       <c r="L6">
-        <v>-51.28</v>
+        <v>-51.34</v>
       </c>
       <c r="M6">
-        <v>-12.2</v>
+        <v>-12.14</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1384,19 +1412,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.86</v>
+        <v>26.96</v>
       </c>
       <c r="Q6">
-        <v>27.43</v>
+        <v>27.25</v>
       </c>
       <c r="R6">
-        <v>28.63</v>
+        <v>28.54</v>
       </c>
       <c r="S6">
-        <v>33.66</v>
+        <v>33.58</v>
       </c>
       <c r="T6">
-        <v>-19.38</v>
+        <v>-19.69</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>44.82</v>
+        <v>43.52</v>
       </c>
       <c r="Z6">
-        <v>-0.66</v>
+        <v>-0.61</v>
       </c>
       <c r="AA6">
-        <v>-0.72</v>
+        <v>-0.7</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>78.78</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="AD6">
-        <v>71.2</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AF6">
-        <v>-47.67</v>
+        <v>-57.84</v>
       </c>
       <c r="AG6">
-        <v>29.6</v>
+        <v>28.9</v>
       </c>
       <c r="AH6">
-        <v>25.26</v>
+        <v>25.61</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1447,7 +1475,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>25.68</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,58 +1486,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1248</v>
+        <v>1219.2</v>
       </c>
       <c r="D7">
-        <v>0.61</v>
+        <v>-2.31</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1226.4</v>
+        <v>1219.2</v>
       </c>
       <c r="G7">
-        <v>-21.26</v>
+        <v>-23.08</v>
       </c>
       <c r="H7">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.65</v>
+        <v>-1.99</v>
       </c>
       <c r="J7">
-        <v>-4.72</v>
+        <v>-7.43</v>
       </c>
       <c r="K7">
-        <v>-4.99</v>
+        <v>-7.5</v>
       </c>
       <c r="L7">
-        <v>-11.39</v>
+        <v>-12.97</v>
       </c>
       <c r="M7">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>1241.22</v>
+        <v>1236.28</v>
       </c>
       <c r="Q7">
-        <v>1274.36</v>
+        <v>1270.42</v>
       </c>
       <c r="R7">
-        <v>1293.16</v>
+        <v>1291.64</v>
       </c>
       <c r="S7">
-        <v>1368.91</v>
+        <v>1367.34</v>
       </c>
       <c r="T7">
-        <v>-8.83</v>
+        <v>-10.83</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,43 +1552,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>41.36</v>
+        <v>34.92</v>
       </c>
       <c r="Z7">
-        <v>-17.58</v>
+        <v>-19.26</v>
       </c>
       <c r="AA7">
-        <v>-13.87</v>
+        <v>-14.95</v>
       </c>
       <c r="AB7">
-        <v>-3.71</v>
+        <v>-4.31</v>
       </c>
       <c r="AC7">
-        <v>34.06</v>
+        <v>26.35</v>
       </c>
       <c r="AD7">
-        <v>23.82</v>
+        <v>27.07</v>
       </c>
       <c r="AE7">
-        <v>20</v>
+        <v>20.63</v>
       </c>
       <c r="AF7">
-        <v>-26.73</v>
+        <v>21.44</v>
       </c>
       <c r="AG7">
-        <v>1334.22</v>
+        <v>1333.98</v>
       </c>
       <c r="AH7">
-        <v>1214.49</v>
+        <v>1206.85</v>
       </c>
       <c r="AI7">
-        <v>1299.24</v>
+        <v>1292.3</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>46.71</v>
+        <v>49.42</v>
       </c>
     </row>
   </sheetData>
@@ -1721,12 +1749,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1734,836 +1797,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-6.78</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-4.62</v>
       </c>
-      <c r="E7" s="6">
-        <v>2.16</v>
+      <c r="D7" s="6">
+        <v>-5.69</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.46</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.63</v>
       </c>
-      <c r="E8" s="6">
-        <v>1.83</v>
+      <c r="D8" s="6">
+        <v>-5.68</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.45</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-4.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>1.38</v>
+      <c r="D9" s="6">
+        <v>-6.56</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>1.27</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>4.3</v>
       </c>
-      <c r="E10" s="6">
-        <v>3.03</v>
+      <c r="D10" s="6">
+        <v>2.58</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.880000000000001</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-10.55</v>
       </c>
+      <c r="D11" s="6">
+        <v>-11.17</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.67</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-5.74</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-4.72</v>
       </c>
-      <c r="E12" s="6">
-        <v>1.02</v>
+      <c r="D12" s="6">
+        <v>-7.43</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.35</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>1.59</v>
       </c>
-      <c r="E13" s="6">
-        <v>2.94</v>
+      <c r="D13" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>1</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.6</v>
+      <c r="D14" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.26</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>3.25</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.99</v>
+      <c r="D15" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-4.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>3.14</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>2.95</v>
       </c>
+      <c r="D16" s="6">
+        <v>-0.25</v>
+      </c>
       <c r="E16" s="7">
-        <v>-0.19</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>3.7</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>3.91</v>
       </c>
-      <c r="E17" s="6">
-        <v>0.21</v>
+      <c r="D17" s="6">
+        <v>1.93</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.41</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>0.65</v>
       </c>
-      <c r="E18" s="6">
-        <v>0.24</v>
+      <c r="D18" s="6">
+        <v>-1.99</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-28.17</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-26.67</v>
       </c>
-      <c r="E19" s="6">
-        <v>1.5</v>
+      <c r="D19" s="6">
+        <v>-27.04</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-33.53</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-32.67</v>
       </c>
-      <c r="E20" s="6">
-        <v>0.86</v>
+      <c r="D20" s="6">
+        <v>-33.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-26.85</v>
       </c>
-      <c r="E21" s="6">
-        <v>0.11</v>
+      <c r="D21" s="6">
+        <v>-28.33</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.48</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>-19.31</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-18.36</v>
       </c>
-      <c r="E22" s="6">
-        <v>0.95</v>
+      <c r="D22" s="6">
+        <v>-19.74</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
+        <v>-51.28</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-51.34</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-11.39</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-12.97</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-17.52</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-15.11</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-14.55</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-15.09</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-2.81</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-5.11</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>25.89</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25.04</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-18.18</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-17.35</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.5</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-26.16</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-26.27</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-33.02</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-32.97</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-26.77</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-27.85</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-19.44</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-21.91</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-51.04</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-51.01</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-21.26</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-23.08</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>26.84</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.52</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.1</v>
+      </c>
+      <c r="D38" s="6">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>232.15</v>
+      </c>
+      <c r="D39" s="6">
+        <v>227.2</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>693.55</v>
+      </c>
+      <c r="D40" s="6">
+        <v>672.35</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-21.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>27.14</v>
+      </c>
+      <c r="D41" s="6">
+        <v>26.97</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1248</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1219.2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-28.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>44</v>
+      </c>
+      <c r="D43" s="6">
+        <v>39.8</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>40.49</v>
+      </c>
+      <c r="D44" s="6">
+        <v>35.89</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-4.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>43.79</v>
+      </c>
+      <c r="D45" s="6">
+        <v>36.86</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-6.93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>55.94</v>
+      </c>
+      <c r="D46" s="6">
+        <v>47.15</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-8.789999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>44.82</v>
+      </c>
+      <c r="D47" s="6">
+        <v>43.52</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>41.36</v>
+      </c>
+      <c r="D48" s="6">
+        <v>34.92</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-6.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14.92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>6.69</v>
+      </c>
+      <c r="D50" s="6">
+        <v>34.26</v>
+      </c>
+      <c r="E50" s="8">
+        <v>27.57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-37.1</v>
+      </c>
+      <c r="D51" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="E51" s="8">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
         <v>-52.13</v>
       </c>
-      <c r="D23" s="5">
-        <v>-51.28</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D52" s="6">
+        <v>-69.31999999999999</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-17.19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-47.67</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-57.84</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-10.17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-11.86</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-11.39</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-16.87</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-17.52</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-14.91</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-14.55</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-2.81</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>25</v>
-      </c>
-      <c r="D28" s="5">
-        <v>25.89</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-18.65</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-18.18</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-5.28</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-4.99</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-28.25</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.16</v>
-      </c>
-      <c r="E31" s="6">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-33.75</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-33.02</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-27.3</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-26.77</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-20.72</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-19.44</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-51.7</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.04</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-21.74</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-21.26</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>26.26</v>
-      </c>
-      <c r="D37" s="5">
-        <v>26.84</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.58</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.99</v>
-      </c>
-      <c r="D38" s="5">
-        <v>10.1</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>230.7</v>
-      </c>
-      <c r="D39" s="5">
-        <v>232.15</v>
-      </c>
-      <c r="E39" s="6">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>682.6</v>
-      </c>
-      <c r="D40" s="5">
-        <v>693.55</v>
-      </c>
-      <c r="E40" s="6">
-        <v>10.95</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>26.91</v>
-      </c>
-      <c r="D41" s="5">
-        <v>27.14</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1240.4</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1248</v>
-      </c>
-      <c r="E42" s="6">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>31.92</v>
-      </c>
-      <c r="D43" s="5">
-        <v>44</v>
-      </c>
-      <c r="E43" s="6">
-        <v>12.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>34.35</v>
-      </c>
-      <c r="D44" s="5">
-        <v>40.49</v>
-      </c>
-      <c r="E44" s="6">
-        <v>6.14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>40.76</v>
-      </c>
-      <c r="D45" s="5">
-        <v>43.79</v>
-      </c>
-      <c r="E45" s="6">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>51.61</v>
-      </c>
-      <c r="D46" s="5">
-        <v>55.94</v>
-      </c>
-      <c r="E46" s="6">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>42.66</v>
-      </c>
-      <c r="D47" s="5">
-        <v>44.82</v>
-      </c>
-      <c r="E47" s="6">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>38.59</v>
-      </c>
-      <c r="D48" s="5">
-        <v>41.36</v>
-      </c>
-      <c r="E48" s="6">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-36.53</v>
-      </c>
-      <c r="D49" s="5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="E49" s="6">
-        <v>45.73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-31.05</v>
-      </c>
-      <c r="D50" s="5">
-        <v>6.69</v>
-      </c>
-      <c r="E50" s="6">
-        <v>37.74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-21.41</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-37.1</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-15.69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-52.4</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-52.13</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-30.42</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-47.67</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-17.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-4.16</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C54" s="6">
         <v>-26.73</v>
       </c>
-      <c r="E54" s="7">
-        <v>-22.57</v>
+      <c r="D54" s="6">
+        <v>21.44</v>
+      </c>
+      <c r="E54" s="8">
+        <v>48.17</v>
       </c>
     </row>
   </sheetData>
@@ -2589,60 +2652,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>45.1</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>39.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-5.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-5.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2744,43 +2807,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0205</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0218</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.06860000000000001</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.11</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.122</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1631</v>
+      <c r="A2" s="14">
+        <v>0.0163</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0286</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.07440000000000001</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1102</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1214</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.162</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>55.9 → 47.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.9</t>
-  </si>
-  <si>
-    <t>47.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -781,7 +753,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,58 +894,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.52</v>
+        <v>26.38</v>
       </c>
       <c r="D2">
-        <v>-1.19</v>
+        <v>-0.53</v>
       </c>
       <c r="E2">
-        <v>35.97</v>
+        <v>35.58</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.27</v>
+        <v>-25.86</v>
       </c>
       <c r="H2">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="I2">
-        <v>0.26</v>
+        <v>-0.9</v>
       </c>
       <c r="J2">
-        <v>-5.69</v>
+        <v>-4.7</v>
       </c>
       <c r="K2">
-        <v>-15.11</v>
+        <v>-10.09</v>
       </c>
       <c r="L2">
-        <v>-27.04</v>
+        <v>-26.66</v>
       </c>
       <c r="M2">
-        <v>-11.02</v>
+        <v>-10.98</v>
       </c>
       <c r="N2">
         <v>50</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>26.53</v>
+        <v>26.48</v>
       </c>
       <c r="Q2">
-        <v>27.23</v>
+        <v>27.14</v>
       </c>
       <c r="R2">
-        <v>27.38</v>
+        <v>27.34</v>
       </c>
       <c r="S2">
-        <v>28.25</v>
+        <v>28.23</v>
       </c>
       <c r="T2">
-        <v>-6.12</v>
+        <v>-6.54</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +960,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.8</v>
+        <v>38.09</v>
       </c>
       <c r="Z2">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="AA2">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AC2">
-        <v>34.25</v>
+        <v>45.14</v>
       </c>
       <c r="AD2">
-        <v>22.88</v>
+        <v>34.56</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="AF2">
-        <v>-5.72</v>
+        <v>-5.6</v>
       </c>
       <c r="AG2">
-        <v>28.64</v>
+        <v>28.54</v>
       </c>
       <c r="AH2">
-        <v>25.82</v>
+        <v>25.75</v>
       </c>
       <c r="AI2">
         <v>28.47</v>
@@ -1023,7 +996,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>33.26</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,58 +1007,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="D3">
-        <v>-1.39</v>
+        <v>-0.3</v>
       </c>
       <c r="E3">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.97</v>
+        <v>-32.68</v>
       </c>
       <c r="H3">
-        <v>12.29</v>
+        <v>11.95</v>
       </c>
       <c r="I3">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="J3">
-        <v>-5.68</v>
+        <v>-6.05</v>
       </c>
       <c r="K3">
-        <v>-15.09</v>
+        <v>-10.86</v>
       </c>
       <c r="L3">
-        <v>-33.95</v>
+        <v>-33.18</v>
       </c>
       <c r="M3">
-        <v>-16.2</v>
+        <v>-16.16</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P3">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="Q3">
-        <v>10.23</v>
+        <v>10.2</v>
       </c>
       <c r="R3">
-        <v>10.56</v>
+        <v>10.53</v>
       </c>
       <c r="S3">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="T3">
-        <v>-9.19</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.89</v>
+        <v>34.97</v>
       </c>
       <c r="Z3">
         <v>-0.18</v>
@@ -1112,31 +1085,31 @@
         <v>-0</v>
       </c>
       <c r="AC3">
-        <v>39.45</v>
+        <v>44.7</v>
       </c>
       <c r="AD3">
-        <v>29.88</v>
+        <v>39.14</v>
       </c>
       <c r="AE3">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="AF3">
-        <v>34.26</v>
+        <v>-17.76</v>
       </c>
       <c r="AG3">
-        <v>10.7</v>
+        <v>10.66</v>
       </c>
       <c r="AH3">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="AI3">
-        <v>10.66</v>
+        <v>10.55</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>32.58</v>
+        <v>33.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1120,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>227.2</v>
+        <v>227</v>
       </c>
       <c r="D4">
-        <v>-2.13</v>
+        <v>-0.09</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1159,46 +1132,46 @@
         <v>224.1</v>
       </c>
       <c r="G4">
-        <v>-27.85</v>
+        <v>-27.91</v>
       </c>
       <c r="H4">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="I4">
-        <v>-0.92</v>
+        <v>-1.26</v>
       </c>
       <c r="J4">
-        <v>-6.56</v>
+        <v>-5.81</v>
       </c>
       <c r="K4">
-        <v>-5.11</v>
+        <v>-4.1</v>
       </c>
       <c r="L4">
-        <v>-28.33</v>
+        <v>-27.67</v>
       </c>
       <c r="M4">
-        <v>-2.86</v>
+        <v>-2.88</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>229.98</v>
+        <v>229.4</v>
       </c>
       <c r="Q4">
-        <v>232.79</v>
+        <v>232.24</v>
       </c>
       <c r="R4">
-        <v>241.46</v>
+        <v>241.29</v>
       </c>
       <c r="S4">
-        <v>250.96</v>
+        <v>250.61</v>
       </c>
       <c r="T4">
-        <v>-9.470000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1213,43 +1186,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.86</v>
+        <v>36.61</v>
       </c>
       <c r="Z4">
-        <v>-3.84</v>
+        <v>-3.86</v>
       </c>
       <c r="AA4">
-        <v>-4</v>
+        <v>-3.97</v>
       </c>
       <c r="AB4">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AC4">
-        <v>75.23999999999999</v>
+        <v>66.95</v>
       </c>
       <c r="AD4">
-        <v>75.22</v>
+        <v>74.17</v>
       </c>
       <c r="AE4">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
       <c r="AF4">
-        <v>3.5</v>
+        <v>-30.55</v>
       </c>
       <c r="AG4">
-        <v>242.27</v>
+        <v>241.7</v>
       </c>
       <c r="AH4">
-        <v>223.32</v>
+        <v>222.78</v>
       </c>
       <c r="AI4">
-        <v>240.04</v>
+        <v>238.93</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>32.88</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1233,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>672.35</v>
+        <v>672.2</v>
       </c>
       <c r="D5">
-        <v>-3.06</v>
+        <v>-0.02</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1245,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.91</v>
+        <v>-21.92</v>
       </c>
       <c r="H5">
-        <v>37.02</v>
+        <v>36.99</v>
       </c>
       <c r="I5">
-        <v>-0.25</v>
+        <v>0.48</v>
       </c>
       <c r="J5">
-        <v>2.58</v>
+        <v>3.79</v>
       </c>
       <c r="K5">
-        <v>25.04</v>
+        <v>27.89</v>
       </c>
       <c r="L5">
-        <v>-19.74</v>
+        <v>-19.82</v>
       </c>
       <c r="M5">
-        <v>-7.44</v>
+        <v>-7.39</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>680.04</v>
+        <v>680.6799999999999</v>
       </c>
       <c r="Q5">
-        <v>683.22</v>
+        <v>684.8099999999999</v>
       </c>
       <c r="R5">
-        <v>695.36</v>
+        <v>692.9299999999999</v>
       </c>
       <c r="S5">
-        <v>621.5599999999999</v>
+        <v>621.35</v>
       </c>
       <c r="T5">
-        <v>8.17</v>
+        <v>8.18</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1326,34 +1299,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.15</v>
+        <v>47.09</v>
       </c>
       <c r="Z5">
+        <v>-0.95</v>
+      </c>
+      <c r="AA5">
         <v>-0.42</v>
       </c>
-      <c r="AA5">
-        <v>-0.29</v>
-      </c>
       <c r="AB5">
-        <v>-0.13</v>
+        <v>-0.53</v>
       </c>
       <c r="AC5">
-        <v>67.48999999999999</v>
+        <v>55.2</v>
       </c>
       <c r="AD5">
-        <v>64.06</v>
+        <v>66.2</v>
       </c>
       <c r="AE5">
-        <v>23.11</v>
+        <v>22.39</v>
       </c>
       <c r="AF5">
-        <v>-69.31999999999999</v>
+        <v>-73.97</v>
       </c>
       <c r="AG5">
-        <v>718.72</v>
+        <v>714.65</v>
       </c>
       <c r="AH5">
-        <v>647.73</v>
+        <v>654.97</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1362,7 +1335,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>17.88</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,37 +1346,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.97</v>
+        <v>26.75</v>
       </c>
       <c r="D6">
-        <v>-0.63</v>
+        <v>-0.82</v>
       </c>
       <c r="E6">
-        <v>55.05</v>
+        <v>54.44</v>
       </c>
       <c r="F6">
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-51.01</v>
+        <v>-50.86</v>
       </c>
       <c r="H6">
-        <v>3.93</v>
+        <v>3.08</v>
       </c>
       <c r="I6">
-        <v>1.93</v>
+        <v>-0.93</v>
       </c>
       <c r="J6">
-        <v>-11.17</v>
+        <v>-12.15</v>
       </c>
       <c r="K6">
-        <v>-17.35</v>
+        <v>-14.81</v>
       </c>
       <c r="L6">
-        <v>-51.34</v>
+        <v>-51.41</v>
       </c>
       <c r="M6">
-        <v>-12.14</v>
+        <v>-12.17</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1412,19 +1385,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.96</v>
+        <v>26.91</v>
       </c>
       <c r="Q6">
-        <v>27.25</v>
+        <v>27.13</v>
       </c>
       <c r="R6">
-        <v>28.54</v>
+        <v>28.47</v>
       </c>
       <c r="S6">
-        <v>33.58</v>
+        <v>33.51</v>
       </c>
       <c r="T6">
-        <v>-19.69</v>
+        <v>-20.16</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.52</v>
+        <v>41.82</v>
       </c>
       <c r="Z6">
-        <v>-0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="AA6">
-        <v>-0.7</v>
+        <v>-0.68</v>
       </c>
       <c r="AB6">
         <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>84.09999999999999</v>
+        <v>83.42</v>
       </c>
       <c r="AD6">
-        <v>78.81999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="AF6">
-        <v>-57.84</v>
+        <v>-40.87</v>
       </c>
       <c r="AG6">
-        <v>28.9</v>
+        <v>28.53</v>
       </c>
       <c r="AH6">
-        <v>25.61</v>
+        <v>25.74</v>
       </c>
       <c r="AI6">
         <v>28.98</v>
@@ -1475,7 +1448,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>24.97</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1459,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="D7">
-        <v>-2.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,46 +1471,46 @@
         <v>1219.2</v>
       </c>
       <c r="G7">
-        <v>-23.08</v>
+        <v>-22.65</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I7">
-        <v>-1.99</v>
+        <v>-0.03</v>
       </c>
       <c r="J7">
-        <v>-7.43</v>
+        <v>-5.55</v>
       </c>
       <c r="K7">
-        <v>-7.5</v>
+        <v>-5.76</v>
       </c>
       <c r="L7">
-        <v>-12.97</v>
+        <v>-11.43</v>
       </c>
       <c r="M7">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P7">
-        <v>1236.28</v>
+        <v>1236.2</v>
       </c>
       <c r="Q7">
-        <v>1270.42</v>
+        <v>1267.61</v>
       </c>
       <c r="R7">
-        <v>1291.64</v>
+        <v>1290.23</v>
       </c>
       <c r="S7">
-        <v>1367.34</v>
+        <v>1365.79</v>
       </c>
       <c r="T7">
-        <v>-10.83</v>
+        <v>-10.24</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1552,43 +1525,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.92</v>
+        <v>37.4</v>
       </c>
       <c r="Z7">
-        <v>-19.26</v>
+        <v>-19.81</v>
       </c>
       <c r="AA7">
-        <v>-14.95</v>
+        <v>-15.92</v>
       </c>
       <c r="AB7">
-        <v>-4.31</v>
+        <v>-3.89</v>
       </c>
       <c r="AC7">
-        <v>26.35</v>
+        <v>26.27</v>
       </c>
       <c r="AD7">
-        <v>27.07</v>
+        <v>28.89</v>
       </c>
       <c r="AE7">
-        <v>20.63</v>
+        <v>20.37</v>
       </c>
       <c r="AF7">
-        <v>21.44</v>
+        <v>11.37</v>
       </c>
       <c r="AG7">
-        <v>1333.98</v>
+        <v>1333.89</v>
       </c>
       <c r="AH7">
-        <v>1206.85</v>
+        <v>1201.32</v>
       </c>
       <c r="AI7">
-        <v>1292.3</v>
+        <v>1280.05</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>49.42</v>
+        <v>52.39</v>
       </c>
     </row>
   </sheetData>
@@ -1749,47 +1722,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1797,836 +1735,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-5.69</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.07</v>
+      <c r="D7" s="5">
+        <v>-4.7</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-4.63</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.68</v>
       </c>
+      <c r="D8" s="5">
+        <v>-6.05</v>
+      </c>
       <c r="E8" s="7">
-        <v>-1.05</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.07</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-6.56</v>
       </c>
-      <c r="E9" s="7">
-        <v>-2.49</v>
+      <c r="D9" s="5">
+        <v>-5.81</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.75</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>2.58</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.72</v>
+      <c r="D10" s="5">
+        <v>3.79</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-10.55</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-11.17</v>
       </c>
+      <c r="D11" s="5">
+        <v>-12.15</v>
+      </c>
       <c r="E11" s="7">
-        <v>-0.62</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-4.72</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-7.43</v>
       </c>
-      <c r="E12" s="7">
-        <v>-2.71</v>
+      <c r="D12" s="5">
+        <v>-5.55</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1.88</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>1.59</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>0.26</v>
       </c>
+      <c r="D13" s="5">
+        <v>-0.9</v>
+      </c>
       <c r="E13" s="7">
-        <v>-1.33</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-0.6</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.6</v>
+      <c r="D14" s="5">
+        <v>-0.5</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>3.25</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-0.92</v>
       </c>
+      <c r="D15" s="5">
+        <v>-1.26</v>
+      </c>
       <c r="E15" s="7">
-        <v>-4.17</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>2.95</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-0.25</v>
       </c>
-      <c r="E16" s="7">
-        <v>-3.2</v>
+      <c r="D16" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.73</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>3.91</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>1.93</v>
       </c>
+      <c r="D17" s="5">
+        <v>-0.93</v>
+      </c>
       <c r="E17" s="7">
-        <v>-1.98</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-1.99</v>
       </c>
-      <c r="E18" s="7">
-        <v>-2.64</v>
+      <c r="D18" s="5">
+        <v>-0.03</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.96</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="6">
-        <v>-26.67</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-27.04</v>
       </c>
-      <c r="E19" s="7">
-        <v>-0.37</v>
+      <c r="D19" s="5">
+        <v>-26.66</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="6">
-        <v>-32.67</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-33.95</v>
       </c>
-      <c r="E20" s="7">
-        <v>-1.28</v>
+      <c r="D20" s="5">
+        <v>-33.18</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.77</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>-26.85</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>-28.33</v>
       </c>
-      <c r="E21" s="7">
-        <v>-1.48</v>
+      <c r="D21" s="5">
+        <v>-27.67</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.66</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>-18.36</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>-19.74</v>
       </c>
+      <c r="D22" s="5">
+        <v>-19.82</v>
+      </c>
       <c r="E22" s="7">
-        <v>-1.38</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-51.28</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-51.34</v>
       </c>
+      <c r="D23" s="5">
+        <v>-51.41</v>
+      </c>
       <c r="E23" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-12.97</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.43</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-15.11</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-10.09</v>
+      </c>
+      <c r="E25" s="6">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-15.09</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-10.86</v>
+      </c>
+      <c r="E26" s="6">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-5.11</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-4.1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>25.04</v>
+      </c>
+      <c r="D28" s="5">
+        <v>27.89</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-17.35</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-14.81</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-7.5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-5.76</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-26.27</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-25.86</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-32.97</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-32.68</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-27.85</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-27.91</v>
+      </c>
+      <c r="E33" s="7">
         <v>-0.06</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-21.91</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-21.92</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-51.01</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-50.86</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-11.39</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-12.97</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-23.08</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-22.65</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-17.52</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-15.11</v>
-      </c>
-      <c r="E25" s="8">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>26.52</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.38</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-14.55</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-15.09</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.93</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-2.81</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-5.11</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>227.2</v>
+      </c>
+      <c r="D39" s="5">
+        <v>227</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>25.89</v>
-      </c>
-      <c r="D28" s="6">
-        <v>25.04</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>672.35</v>
+      </c>
+      <c r="D40" s="5">
+        <v>672.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-18.18</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-17.35</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.97</v>
+      </c>
+      <c r="D41" s="5">
+        <v>26.75</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-7.5</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1219.2</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1226</v>
+      </c>
+      <c r="E42" s="6">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-26.16</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-26.27</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>39.8</v>
+      </c>
+      <c r="D43" s="5">
+        <v>38.09</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-33.02</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-32.97</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>35.89</v>
+      </c>
+      <c r="D44" s="5">
+        <v>34.97</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-26.77</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-27.85</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>36.86</v>
+      </c>
+      <c r="D45" s="5">
+        <v>36.61</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-19.44</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-21.91</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>47.15</v>
+      </c>
+      <c r="D46" s="5">
+        <v>47.09</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-51.04</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-51.01</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>43.52</v>
+      </c>
+      <c r="D47" s="5">
+        <v>41.82</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-21.26</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-23.08</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>34.92</v>
+      </c>
+      <c r="D48" s="5">
+        <v>37.4</v>
+      </c>
+      <c r="E48" s="6">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>26.84</v>
-      </c>
-      <c r="D37" s="6">
-        <v>26.52</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-5.6</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>10.1</v>
-      </c>
-      <c r="D38" s="6">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>34.26</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-17.76</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-52.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>232.15</v>
-      </c>
-      <c r="D39" s="6">
-        <v>227.2</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-30.55</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-34.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>693.55</v>
-      </c>
-      <c r="D40" s="6">
-        <v>672.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-21.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-69.31999999999999</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-73.97</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>27.14</v>
-      </c>
-      <c r="D41" s="6">
-        <v>26.97</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-57.84</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-40.87</v>
+      </c>
+      <c r="E53" s="6">
+        <v>16.97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1248</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1219.2</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-28.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>44</v>
-      </c>
-      <c r="D43" s="6">
-        <v>39.8</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>40.49</v>
-      </c>
-      <c r="D44" s="6">
-        <v>35.89</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>43.79</v>
-      </c>
-      <c r="D45" s="6">
-        <v>36.86</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-6.93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>55.94</v>
-      </c>
-      <c r="D46" s="6">
-        <v>47.15</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>44.82</v>
-      </c>
-      <c r="D47" s="6">
-        <v>43.52</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>41.36</v>
-      </c>
-      <c r="D48" s="6">
-        <v>34.92</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-6.44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14.92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>6.69</v>
-      </c>
-      <c r="D50" s="6">
-        <v>34.26</v>
-      </c>
-      <c r="E50" s="8">
-        <v>27.57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-37.1</v>
-      </c>
-      <c r="D51" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="E51" s="8">
-        <v>40.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-52.13</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-69.31999999999999</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-17.19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-47.67</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-57.84</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-10.17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-26.73</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>21.44</v>
       </c>
-      <c r="E54" s="8">
-        <v>48.17</v>
+      <c r="D54" s="5">
+        <v>11.37</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-10.07</v>
       </c>
     </row>
   </sheetData>
@@ -2652,60 +2590,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.7</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-5.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-3</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2807,43 +2745,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.0163</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0286</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.07440000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1102</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1214</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.162</v>
+      <c r="A2" s="13">
+        <v>0.0141</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0288</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07389999999999999</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1098</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1217</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1616</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -255,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -753,8 +753,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -894,37 +893,37 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.38</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>-0.53</v>
+        <v>-1.44</v>
       </c>
       <c r="E2">
-        <v>35.58</v>
+        <v>35.23</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.86</v>
+        <v>-26.2</v>
       </c>
       <c r="H2">
-        <v>14.8</v>
+        <v>13.14</v>
       </c>
       <c r="I2">
-        <v>-0.9</v>
+        <v>-1.59</v>
       </c>
       <c r="J2">
-        <v>-4.7</v>
+        <v>-7.54</v>
       </c>
       <c r="K2">
-        <v>-10.09</v>
+        <v>-10.93</v>
       </c>
       <c r="L2">
-        <v>-26.66</v>
+        <v>-26.93</v>
       </c>
       <c r="M2">
-        <v>-10.98</v>
+        <v>-11.26</v>
       </c>
       <c r="N2">
         <v>50</v>
@@ -933,19 +932,19 @@
         <v>26</v>
       </c>
       <c r="P2">
-        <v>26.48</v>
+        <v>26.4</v>
       </c>
       <c r="Q2">
-        <v>27.14</v>
+        <v>27.03</v>
       </c>
       <c r="R2">
-        <v>27.34</v>
+        <v>27.32</v>
       </c>
       <c r="S2">
-        <v>28.23</v>
+        <v>28.2</v>
       </c>
       <c r="T2">
-        <v>-6.54</v>
+        <v>-7.81</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -960,43 +959,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.09</v>
+        <v>33.84</v>
       </c>
       <c r="Z2">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="AA2">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="AB2">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>45.14</v>
+        <v>30.59</v>
       </c>
       <c r="AD2">
-        <v>34.56</v>
+        <v>36.66</v>
       </c>
       <c r="AE2">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>-5.6</v>
+        <v>3.43</v>
       </c>
       <c r="AG2">
-        <v>28.54</v>
+        <v>28.4</v>
       </c>
       <c r="AH2">
-        <v>25.75</v>
+        <v>25.66</v>
       </c>
       <c r="AI2">
-        <v>28.47</v>
+        <v>28.22</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>32.69</v>
+        <v>34.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1007,58 +1006,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.93</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D3">
-        <v>-0.3</v>
+        <v>-5.64</v>
       </c>
       <c r="E3">
-        <v>14.75</v>
+        <v>14.47</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.68</v>
+        <v>-35.25</v>
       </c>
       <c r="H3">
-        <v>11.95</v>
+        <v>5.64</v>
       </c>
       <c r="I3">
-        <v>-0.5</v>
+        <v>-6.02</v>
       </c>
       <c r="J3">
-        <v>-6.05</v>
+        <v>-11.18</v>
       </c>
       <c r="K3">
-        <v>-10.86</v>
+        <v>-15.96</v>
       </c>
       <c r="L3">
-        <v>-33.18</v>
+        <v>-36.47</v>
       </c>
       <c r="M3">
-        <v>-16.16</v>
+        <v>-17.12</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="P3">
-        <v>9.99</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Q3">
-        <v>10.2</v>
+        <v>10.14</v>
       </c>
       <c r="R3">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="S3">
-        <v>10.96</v>
+        <v>10.94</v>
       </c>
       <c r="T3">
-        <v>-9.359999999999999</v>
+        <v>-14.35</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1073,43 +1072,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>34.97</v>
+        <v>23.1</v>
       </c>
       <c r="Z3">
+        <v>-0.22</v>
+      </c>
+      <c r="AA3">
         <v>-0.18</v>
       </c>
-      <c r="AA3">
-        <v>-0.17</v>
-      </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="AC3">
-        <v>44.7</v>
+        <v>23.38</v>
       </c>
       <c r="AD3">
-        <v>39.14</v>
+        <v>35.84</v>
       </c>
       <c r="AE3">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="AF3">
-        <v>-17.76</v>
+        <v>372.33</v>
       </c>
       <c r="AG3">
-        <v>10.66</v>
+        <v>10.7</v>
       </c>
       <c r="AH3">
-        <v>9.74</v>
+        <v>9.58</v>
       </c>
       <c r="AI3">
-        <v>10.55</v>
+        <v>10.33</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>33.06</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1120,58 +1119,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>227</v>
+        <v>220.5</v>
       </c>
       <c r="D4">
-        <v>-0.09</v>
+        <v>-2.86</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>224.1</v>
+        <v>220.5</v>
       </c>
       <c r="G4">
-        <v>-27.91</v>
+        <v>-29.98</v>
       </c>
       <c r="H4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.26</v>
+        <v>-4.12</v>
       </c>
       <c r="J4">
-        <v>-5.81</v>
+        <v>-7.39</v>
       </c>
       <c r="K4">
-        <v>-4.1</v>
+        <v>-6.74</v>
       </c>
       <c r="L4">
-        <v>-27.67</v>
+        <v>-29.45</v>
       </c>
       <c r="M4">
-        <v>-2.88</v>
+        <v>-3.78</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>229.4</v>
+        <v>227.51</v>
       </c>
       <c r="Q4">
-        <v>232.24</v>
+        <v>231.34</v>
       </c>
       <c r="R4">
-        <v>241.29</v>
+        <v>240.84</v>
       </c>
       <c r="S4">
-        <v>250.61</v>
+        <v>250.25</v>
       </c>
       <c r="T4">
-        <v>-9.42</v>
+        <v>-11.89</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1186,43 +1185,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>36.61</v>
+        <v>29.55</v>
       </c>
       <c r="Z4">
-        <v>-3.86</v>
+        <v>-4.35</v>
       </c>
       <c r="AA4">
-        <v>-3.97</v>
+        <v>-4.05</v>
       </c>
       <c r="AB4">
-        <v>0.12</v>
+        <v>-0.3</v>
       </c>
       <c r="AC4">
-        <v>66.95</v>
+        <v>36.49</v>
       </c>
       <c r="AD4">
-        <v>74.17</v>
+        <v>59.56</v>
       </c>
       <c r="AE4">
-        <v>4.1</v>
+        <v>4.39</v>
       </c>
       <c r="AF4">
-        <v>-30.55</v>
+        <v>60.07</v>
       </c>
       <c r="AG4">
         <v>241.7</v>
       </c>
       <c r="AH4">
-        <v>222.78</v>
+        <v>220.99</v>
       </c>
       <c r="AI4">
-        <v>238.93</v>
+        <v>236.07</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.66</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1233,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>672.2</v>
+        <v>658.95</v>
       </c>
       <c r="D5">
-        <v>-0.02</v>
+        <v>-1.97</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1245,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-21.92</v>
+        <v>-23.46</v>
       </c>
       <c r="H5">
-        <v>36.99</v>
+        <v>34.29</v>
       </c>
       <c r="I5">
-        <v>0.48</v>
+        <v>-3.48</v>
       </c>
       <c r="J5">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="K5">
-        <v>27.89</v>
+        <v>25.53</v>
       </c>
       <c r="L5">
-        <v>-19.82</v>
+        <v>-21.01</v>
       </c>
       <c r="M5">
-        <v>-7.39</v>
+        <v>-7.8</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>680.6799999999999</v>
+        <v>675.9299999999999</v>
       </c>
       <c r="Q5">
-        <v>684.8099999999999</v>
+        <v>682.53</v>
       </c>
       <c r="R5">
-        <v>692.9299999999999</v>
+        <v>690.77</v>
       </c>
       <c r="S5">
-        <v>621.35</v>
+        <v>621.08</v>
       </c>
       <c r="T5">
-        <v>8.18</v>
+        <v>6.1</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1299,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.09</v>
+        <v>42.29</v>
       </c>
       <c r="Z5">
-        <v>-0.95</v>
+        <v>-2.41</v>
       </c>
       <c r="AA5">
-        <v>-0.42</v>
+        <v>-0.82</v>
       </c>
       <c r="AB5">
-        <v>-0.53</v>
+        <v>-1.59</v>
       </c>
       <c r="AC5">
-        <v>55.2</v>
+        <v>21.87</v>
       </c>
       <c r="AD5">
-        <v>66.2</v>
+        <v>48.19</v>
       </c>
       <c r="AE5">
-        <v>22.39</v>
+        <v>21.98</v>
       </c>
       <c r="AF5">
-        <v>-73.97</v>
+        <v>-77.12</v>
       </c>
       <c r="AG5">
-        <v>714.65</v>
+        <v>712.98</v>
       </c>
       <c r="AH5">
-        <v>654.97</v>
+        <v>652.08</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1335,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>16.93</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1346,37 +1345,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.75</v>
+        <v>25.98</v>
       </c>
       <c r="D6">
-        <v>-0.82</v>
+        <v>-2.88</v>
       </c>
       <c r="E6">
-        <v>54.44</v>
+        <v>53.87</v>
       </c>
       <c r="F6">
         <v>25.95</v>
       </c>
       <c r="G6">
-        <v>-50.86</v>
+        <v>-51.77</v>
       </c>
       <c r="H6">
-        <v>3.08</v>
+        <v>0.12</v>
       </c>
       <c r="I6">
-        <v>-0.93</v>
+        <v>-3.02</v>
       </c>
       <c r="J6">
-        <v>-12.15</v>
+        <v>-10.84</v>
       </c>
       <c r="K6">
-        <v>-14.81</v>
+        <v>-17.76</v>
       </c>
       <c r="L6">
-        <v>-51.41</v>
+        <v>-52.28</v>
       </c>
       <c r="M6">
-        <v>-12.17</v>
+        <v>-12.69</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1385,19 +1384,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.91</v>
+        <v>26.75</v>
       </c>
       <c r="Q6">
-        <v>27.13</v>
+        <v>26.99</v>
       </c>
       <c r="R6">
-        <v>28.47</v>
+        <v>28.39</v>
       </c>
       <c r="S6">
-        <v>33.51</v>
+        <v>33.42</v>
       </c>
       <c r="T6">
-        <v>-20.16</v>
+        <v>-22.27</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1412,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.82</v>
+        <v>36.47</v>
       </c>
       <c r="Z6">
-        <v>-0.59</v>
+        <v>-0.62</v>
       </c>
       <c r="AA6">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AB6">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
       <c r="AC6">
-        <v>83.42</v>
+        <v>61.37</v>
       </c>
       <c r="AD6">
-        <v>82.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="AE6">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AF6">
-        <v>-40.87</v>
+        <v>-44.98</v>
       </c>
       <c r="AG6">
-        <v>28.53</v>
+        <v>28.24</v>
       </c>
       <c r="AH6">
         <v>25.74</v>
       </c>
       <c r="AI6">
-        <v>28.98</v>
+        <v>28.87</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>25.3</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1459,37 +1458,37 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1226</v>
+        <v>1197.6</v>
       </c>
       <c r="D7">
-        <v>0.5600000000000001</v>
+        <v>-2.32</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1219.2</v>
+        <v>1197.6</v>
       </c>
       <c r="G7">
-        <v>-22.65</v>
+        <v>-24.44</v>
       </c>
       <c r="H7">
-        <v>0.5600000000000001</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-0.03</v>
+        <v>-3.99</v>
       </c>
       <c r="J7">
-        <v>-5.55</v>
+        <v>-6.6</v>
       </c>
       <c r="K7">
-        <v>-5.76</v>
+        <v>-7.44</v>
       </c>
       <c r="L7">
-        <v>-11.43</v>
+        <v>-13.43</v>
       </c>
       <c r="M7">
-        <v>1.41</v>
+        <v>0.74</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1498,19 +1497,19 @@
         <v>43</v>
       </c>
       <c r="P7">
-        <v>1236.2</v>
+        <v>1226.24</v>
       </c>
       <c r="Q7">
-        <v>1267.61</v>
+        <v>1263.14</v>
       </c>
       <c r="R7">
-        <v>1290.23</v>
+        <v>1287.63</v>
       </c>
       <c r="S7">
-        <v>1365.79</v>
+        <v>1364.17</v>
       </c>
       <c r="T7">
-        <v>-10.24</v>
+        <v>-12.21</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1525,43 +1524,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.4</v>
+        <v>31.93</v>
       </c>
       <c r="Z7">
-        <v>-19.81</v>
+        <v>-22.29</v>
       </c>
       <c r="AA7">
-        <v>-15.92</v>
+        <v>-17.19</v>
       </c>
       <c r="AB7">
-        <v>-3.89</v>
+        <v>-5.09</v>
       </c>
       <c r="AC7">
-        <v>26.27</v>
+        <v>13.02</v>
       </c>
       <c r="AD7">
-        <v>28.89</v>
+        <v>21.88</v>
       </c>
       <c r="AE7">
-        <v>20.37</v>
+        <v>20.98</v>
       </c>
       <c r="AF7">
-        <v>11.37</v>
+        <v>12.14</v>
       </c>
       <c r="AG7">
-        <v>1333.89</v>
+        <v>1335.67</v>
       </c>
       <c r="AH7">
-        <v>1201.32</v>
+        <v>1190.6</v>
       </c>
       <c r="AI7">
-        <v>1280.05</v>
+        <v>1271.3</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>52.39</v>
+        <v>55.74</v>
       </c>
     </row>
   </sheetData>
@@ -1759,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-5.69</v>
+        <v>-4.7</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.7</v>
+        <v>-7.54</v>
       </c>
       <c r="E7" s="6">
-        <v>0.99</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1776,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-5.68</v>
+        <v>-6.05</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.05</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.37</v>
+        <v>-11.18</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-5.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1793,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.56</v>
+        <v>-5.81</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.81</v>
+        <v>-7.39</v>
       </c>
       <c r="E9" s="6">
-        <v>0.75</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1810,13 +1809,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>2.58</v>
+        <v>3.79</v>
       </c>
       <c r="D10" s="5">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="E10" s="6">
-        <v>1.21</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1827,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-11.17</v>
+        <v>-12.15</v>
       </c>
       <c r="D11" s="5">
-        <v>-12.15</v>
+        <v>-10.84</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.98</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1844,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-7.43</v>
+        <v>-5.55</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.55</v>
+        <v>-6.6</v>
       </c>
       <c r="E12" s="6">
-        <v>1.88</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1861,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>0.26</v>
+        <v>-0.9</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.16</v>
+        <v>-1.59</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1878,13 +1877,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.5</v>
+        <v>-6.02</v>
       </c>
       <c r="E14" s="6">
-        <v>0.1</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1895,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-0.92</v>
+        <v>-1.26</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.26</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.34</v>
+        <v>-4.12</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1912,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.25</v>
+        <v>0.48</v>
       </c>
       <c r="D16" s="5">
-        <v>0.48</v>
+        <v>-3.48</v>
       </c>
       <c r="E16" s="6">
-        <v>0.73</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1929,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>1.93</v>
+        <v>-0.93</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.86</v>
+        <v>-3.02</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1946,13 +1945,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-1.99</v>
+        <v>-0.03</v>
       </c>
       <c r="D18" s="5">
-        <v>-0.03</v>
+        <v>-3.99</v>
       </c>
       <c r="E18" s="6">
-        <v>1.96</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1963,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-27.04</v>
+        <v>-26.66</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.66</v>
+        <v>-26.93</v>
       </c>
       <c r="E19" s="6">
-        <v>0.38</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1980,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-33.95</v>
+        <v>-33.18</v>
       </c>
       <c r="D20" s="5">
-        <v>-33.18</v>
+        <v>-36.47</v>
       </c>
       <c r="E20" s="6">
-        <v>0.77</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1997,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-28.33</v>
+        <v>-27.67</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.67</v>
+        <v>-29.45</v>
       </c>
       <c r="E21" s="6">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2014,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-19.74</v>
+        <v>-19.82</v>
       </c>
       <c r="D22" s="5">
-        <v>-19.82</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.08</v>
+        <v>-21.01</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2031,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-51.34</v>
+        <v>-51.41</v>
       </c>
       <c r="D23" s="5">
-        <v>-51.41</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-52.28</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2048,13 +2047,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-12.97</v>
+        <v>-11.43</v>
       </c>
       <c r="D24" s="5">
-        <v>-11.43</v>
+        <v>-13.43</v>
       </c>
       <c r="E24" s="6">
-        <v>1.54</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2065,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-15.11</v>
+        <v>-10.09</v>
       </c>
       <c r="D25" s="5">
-        <v>-10.09</v>
+        <v>-10.93</v>
       </c>
       <c r="E25" s="6">
-        <v>5.02</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2082,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-15.09</v>
+        <v>-10.86</v>
       </c>
       <c r="D26" s="5">
-        <v>-10.86</v>
+        <v>-15.96</v>
       </c>
       <c r="E26" s="6">
-        <v>4.23</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2099,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-5.11</v>
+        <v>-4.1</v>
       </c>
       <c r="D27" s="5">
-        <v>-4.1</v>
+        <v>-6.74</v>
       </c>
       <c r="E27" s="6">
-        <v>1.01</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2116,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>25.04</v>
+        <v>27.89</v>
       </c>
       <c r="D28" s="5">
-        <v>27.89</v>
+        <v>25.53</v>
       </c>
       <c r="E28" s="6">
-        <v>2.85</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2133,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-17.35</v>
+        <v>-14.81</v>
       </c>
       <c r="D29" s="5">
-        <v>-14.81</v>
+        <v>-17.76</v>
       </c>
       <c r="E29" s="6">
-        <v>2.54</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2150,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-7.5</v>
+        <v>-5.76</v>
       </c>
       <c r="D30" s="5">
-        <v>-5.76</v>
+        <v>-7.44</v>
       </c>
       <c r="E30" s="6">
-        <v>1.74</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2167,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-26.27</v>
+        <v>-25.86</v>
       </c>
       <c r="D31" s="5">
-        <v>-25.86</v>
+        <v>-26.2</v>
       </c>
       <c r="E31" s="6">
-        <v>0.41</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2184,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-32.97</v>
+        <v>-32.68</v>
       </c>
       <c r="D32" s="5">
-        <v>-32.68</v>
+        <v>-35.25</v>
       </c>
       <c r="E32" s="6">
-        <v>0.29</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2201,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-27.85</v>
+        <v>-27.91</v>
       </c>
       <c r="D33" s="5">
-        <v>-27.91</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.06</v>
+        <v>-29.98</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2218,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-21.91</v>
+        <v>-21.92</v>
       </c>
       <c r="D34" s="5">
-        <v>-21.92</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.01</v>
+        <v>-23.46</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.54</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2235,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-51.01</v>
+        <v>-50.86</v>
       </c>
       <c r="D35" s="5">
-        <v>-50.86</v>
+        <v>-51.77</v>
       </c>
       <c r="E35" s="6">
-        <v>0.15</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2252,13 +2251,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-23.08</v>
+        <v>-22.65</v>
       </c>
       <c r="D36" s="5">
-        <v>-22.65</v>
+        <v>-24.44</v>
       </c>
       <c r="E36" s="6">
-        <v>0.43</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2269,13 +2268,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>26.52</v>
+        <v>26.38</v>
       </c>
       <c r="D37" s="5">
-        <v>26.38</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.14</v>
+        <v>26</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2286,13 +2285,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.960000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="D38" s="5">
-        <v>9.93</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.03</v>
+        <v>9.369999999999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2303,13 +2302,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>227.2</v>
+        <v>227</v>
       </c>
       <c r="D39" s="5">
-        <v>227</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.2</v>
+        <v>220.5</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-6.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2320,13 +2319,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>672.35</v>
+        <v>672.2</v>
       </c>
       <c r="D40" s="5">
-        <v>672.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.15</v>
+        <v>658.95</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-13.25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2337,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>26.97</v>
+        <v>26.75</v>
       </c>
       <c r="D41" s="5">
-        <v>26.75</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.22</v>
+        <v>25.98</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2354,13 +2353,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1219.2</v>
+        <v>1226</v>
       </c>
       <c r="D42" s="5">
-        <v>1226</v>
+        <v>1197.6</v>
       </c>
       <c r="E42" s="6">
-        <v>6.8</v>
+        <v>-28.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2371,13 +2370,13 @@
         <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>39.8</v>
+        <v>38.09</v>
       </c>
       <c r="D43" s="5">
-        <v>38.09</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.71</v>
+        <v>33.84</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-4.25</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2388,13 +2387,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="5">
-        <v>35.89</v>
+        <v>34.97</v>
       </c>
       <c r="D44" s="5">
-        <v>34.97</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.92</v>
+        <v>23.1</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-11.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2405,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>36.86</v>
+        <v>36.61</v>
       </c>
       <c r="D45" s="5">
-        <v>36.61</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.25</v>
+        <v>29.55</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-7.06</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2422,13 +2421,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>47.15</v>
+        <v>47.09</v>
       </c>
       <c r="D46" s="5">
-        <v>47.09</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.06</v>
+        <v>42.29</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2439,13 +2438,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>43.52</v>
+        <v>41.82</v>
       </c>
       <c r="D47" s="5">
-        <v>41.82</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.7</v>
+        <v>36.47</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-5.35</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2456,13 +2455,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>34.92</v>
+        <v>37.4</v>
       </c>
       <c r="D48" s="5">
-        <v>37.4</v>
+        <v>31.93</v>
       </c>
       <c r="E48" s="6">
-        <v>2.48</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2473,13 +2472,13 @@
         <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>-5.72</v>
+        <v>-5.6</v>
       </c>
       <c r="D49" s="5">
-        <v>-5.6</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.12</v>
+        <v>3.43</v>
+      </c>
+      <c r="E49" s="7">
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2490,13 +2489,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>34.26</v>
+        <v>-17.76</v>
       </c>
       <c r="D50" s="5">
-        <v>-17.76</v>
+        <v>372.33</v>
       </c>
       <c r="E50" s="7">
-        <v>-52.02</v>
+        <v>390.09</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2507,13 +2506,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>3.5</v>
+        <v>-30.55</v>
       </c>
       <c r="D51" s="5">
-        <v>-30.55</v>
+        <v>60.07</v>
       </c>
       <c r="E51" s="7">
-        <v>-34.05</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2524,13 +2523,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-69.31999999999999</v>
+        <v>-73.97</v>
       </c>
       <c r="D52" s="5">
-        <v>-73.97</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-4.65</v>
+        <v>-77.12</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-3.15</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2541,13 +2540,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-57.84</v>
+        <v>-40.87</v>
       </c>
       <c r="D53" s="5">
-        <v>-40.87</v>
+        <v>-44.98</v>
       </c>
       <c r="E53" s="6">
-        <v>16.97</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2558,13 +2557,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>21.44</v>
+        <v>11.37</v>
       </c>
       <c r="D54" s="5">
-        <v>11.37</v>
+        <v>12.14</v>
       </c>
       <c r="E54" s="7">
-        <v>-10.07</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -2629,16 +2628,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>39.3</v>
+        <v>32.9</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.1</v>
+        <v>-6.8</v>
       </c>
       <c r="G2" s="10">
-        <v>-3</v>
+        <v>-5.6</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2766,22 +2765,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0141</v>
+        <v>0.0074</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0288</v>
+        <v>-0.0378</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.07389999999999999</v>
+        <v>-0.078</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1098</v>
+        <v>-0.1126</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1217</v>
+        <v>-0.1269</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1616</v>
+        <v>-0.1712</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -893,10 +893,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26</v>
+        <v>25.91</v>
       </c>
       <c r="D2">
-        <v>-1.44</v>
+        <v>-0.35</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -905,46 +905,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.2</v>
+        <v>-26.45</v>
       </c>
       <c r="H2">
-        <v>13.14</v>
+        <v>12.75</v>
       </c>
       <c r="I2">
-        <v>-1.59</v>
+        <v>-1.33</v>
       </c>
       <c r="J2">
-        <v>-7.54</v>
+        <v>-8.48</v>
       </c>
       <c r="K2">
-        <v>-10.93</v>
+        <v>-11.96</v>
       </c>
       <c r="L2">
-        <v>-26.93</v>
+        <v>-25.37</v>
       </c>
       <c r="M2">
-        <v>-11.26</v>
+        <v>-11.88</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P2">
-        <v>26.4</v>
+        <v>26.33</v>
       </c>
       <c r="Q2">
-        <v>27.03</v>
+        <v>26.91</v>
       </c>
       <c r="R2">
-        <v>27.32</v>
+        <v>27.29</v>
       </c>
       <c r="S2">
-        <v>28.2</v>
+        <v>28.18</v>
       </c>
       <c r="T2">
-        <v>-7.81</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,43 +959,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.84</v>
+        <v>32.9</v>
       </c>
       <c r="Z2">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AA2">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AC2">
-        <v>30.59</v>
+        <v>20.45</v>
       </c>
       <c r="AD2">
-        <v>36.66</v>
+        <v>32.06</v>
       </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>3.43</v>
+        <v>-26.47</v>
       </c>
       <c r="AG2">
-        <v>28.4</v>
+        <v>28.24</v>
       </c>
       <c r="AH2">
-        <v>25.66</v>
+        <v>25.58</v>
       </c>
       <c r="AI2">
-        <v>28.22</v>
+        <v>28.06</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>34.56</v>
+        <v>37.36</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,58 +1006,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.369999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="D3">
-        <v>-5.64</v>
+        <v>1.28</v>
       </c>
       <c r="E3">
-        <v>14.47</v>
+        <v>14.32</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-35.25</v>
+        <v>-33.73</v>
       </c>
       <c r="H3">
-        <v>5.64</v>
+        <v>6.99</v>
       </c>
       <c r="I3">
-        <v>-6.02</v>
+        <v>-5.01</v>
       </c>
       <c r="J3">
-        <v>-11.18</v>
+        <v>-10.22</v>
       </c>
       <c r="K3">
-        <v>-15.96</v>
+        <v>-16.39</v>
       </c>
       <c r="L3">
-        <v>-36.47</v>
+        <v>-34.42</v>
       </c>
       <c r="M3">
-        <v>-17.12</v>
+        <v>-16.97</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P3">
-        <v>9.869999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="Q3">
-        <v>10.14</v>
+        <v>10.08</v>
       </c>
       <c r="R3">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="S3">
-        <v>10.94</v>
+        <v>10.92</v>
       </c>
       <c r="T3">
-        <v>-14.35</v>
+        <v>-13.12</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,34 +1072,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.1</v>
+        <v>28.69</v>
       </c>
       <c r="Z3">
-        <v>-0.22</v>
+        <v>-0.24</v>
       </c>
       <c r="AA3">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AB3">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>23.38</v>
+        <v>23.27</v>
       </c>
       <c r="AD3">
-        <v>35.84</v>
+        <v>30.45</v>
       </c>
       <c r="AE3">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AF3">
-        <v>372.33</v>
+        <v>82.69</v>
       </c>
       <c r="AG3">
-        <v>10.7</v>
+        <v>10.66</v>
       </c>
       <c r="AH3">
-        <v>9.58</v>
+        <v>9.5</v>
       </c>
       <c r="AI3">
         <v>10.33</v>
@@ -1108,7 +1108,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>38.66</v>
+        <v>35.83</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,58 +1119,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>220.5</v>
+        <v>217.56</v>
       </c>
       <c r="D4">
-        <v>-2.86</v>
+        <v>-1.33</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>220.5</v>
+        <v>217.56</v>
       </c>
       <c r="G4">
-        <v>-29.98</v>
+        <v>-30.91</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-4.12</v>
+        <v>-5.7</v>
       </c>
       <c r="J4">
-        <v>-7.39</v>
+        <v>-8.74</v>
       </c>
       <c r="K4">
-        <v>-6.74</v>
+        <v>-9.35</v>
       </c>
       <c r="L4">
-        <v>-29.45</v>
+        <v>-29.08</v>
       </c>
       <c r="M4">
-        <v>-3.78</v>
+        <v>-4.19</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>227.51</v>
+        <v>224.88</v>
       </c>
       <c r="Q4">
-        <v>231.34</v>
+        <v>230.16</v>
       </c>
       <c r="R4">
-        <v>240.84</v>
+        <v>240.41</v>
       </c>
       <c r="S4">
-        <v>250.25</v>
+        <v>249.88</v>
       </c>
       <c r="T4">
-        <v>-11.89</v>
+        <v>-12.93</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,43 +1185,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.55</v>
+        <v>27.01</v>
       </c>
       <c r="Z4">
-        <v>-4.35</v>
+        <v>-4.91</v>
       </c>
       <c r="AA4">
-        <v>-4.05</v>
+        <v>-4.22</v>
       </c>
       <c r="AB4">
-        <v>-0.3</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AC4">
-        <v>36.49</v>
+        <v>19.14</v>
       </c>
       <c r="AD4">
-        <v>59.56</v>
+        <v>40.86</v>
       </c>
       <c r="AE4">
-        <v>4.39</v>
+        <v>4.44</v>
       </c>
       <c r="AF4">
-        <v>60.07</v>
+        <v>46.59</v>
       </c>
       <c r="AG4">
-        <v>241.7</v>
+        <v>241.12</v>
       </c>
       <c r="AH4">
-        <v>220.99</v>
+        <v>219.19</v>
       </c>
       <c r="AI4">
-        <v>236.07</v>
+        <v>231.26</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>37.4</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>658.95</v>
+        <v>656.5</v>
       </c>
       <c r="D5">
-        <v>-1.97</v>
+        <v>-0.37</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.46</v>
+        <v>-23.75</v>
       </c>
       <c r="H5">
-        <v>34.29</v>
+        <v>33.79</v>
       </c>
       <c r="I5">
-        <v>-3.48</v>
+        <v>-3.82</v>
       </c>
       <c r="J5">
-        <v>2.88</v>
+        <v>-6.82</v>
       </c>
       <c r="K5">
-        <v>25.53</v>
+        <v>19.66</v>
       </c>
       <c r="L5">
-        <v>-21.01</v>
+        <v>-20.34</v>
       </c>
       <c r="M5">
-        <v>-7.8</v>
+        <v>-7.88</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>675.9299999999999</v>
+        <v>670.71</v>
       </c>
       <c r="Q5">
-        <v>682.53</v>
+        <v>679.84</v>
       </c>
       <c r="R5">
-        <v>690.77</v>
+        <v>688.95</v>
       </c>
       <c r="S5">
-        <v>621.08</v>
+        <v>620.8200000000001</v>
       </c>
       <c r="T5">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1298,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>42.29</v>
+        <v>41.44</v>
       </c>
       <c r="Z5">
-        <v>-2.41</v>
+        <v>-3.72</v>
       </c>
       <c r="AA5">
-        <v>-0.82</v>
+        <v>-1.4</v>
       </c>
       <c r="AB5">
-        <v>-1.59</v>
+        <v>-2.32</v>
       </c>
       <c r="AC5">
-        <v>21.87</v>
+        <v>10.86</v>
       </c>
       <c r="AD5">
-        <v>48.19</v>
+        <v>29.31</v>
       </c>
       <c r="AE5">
-        <v>21.98</v>
+        <v>22.03</v>
       </c>
       <c r="AF5">
-        <v>-77.12</v>
+        <v>-62.43</v>
       </c>
       <c r="AG5">
-        <v>712.98</v>
+        <v>709.48</v>
       </c>
       <c r="AH5">
-        <v>652.08</v>
+        <v>650.21</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1334,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>17.57</v>
+        <v>20.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1345,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.98</v>
+        <v>25.88</v>
       </c>
       <c r="D6">
-        <v>-2.88</v>
+        <v>-0.38</v>
       </c>
       <c r="E6">
-        <v>53.87</v>
+        <v>53.24</v>
       </c>
       <c r="F6">
-        <v>25.95</v>
+        <v>25.88</v>
       </c>
       <c r="G6">
-        <v>-51.77</v>
+        <v>-51.39</v>
       </c>
       <c r="H6">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-3.02</v>
+        <v>-3.83</v>
       </c>
       <c r="J6">
-        <v>-10.84</v>
+        <v>-10.14</v>
       </c>
       <c r="K6">
-        <v>-17.76</v>
+        <v>-20.86</v>
       </c>
       <c r="L6">
-        <v>-52.28</v>
+        <v>-51.96</v>
       </c>
       <c r="M6">
-        <v>-12.69</v>
+        <v>-13.26</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1384,19 +1384,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.75</v>
+        <v>26.54</v>
       </c>
       <c r="Q6">
-        <v>26.99</v>
+        <v>26.92</v>
       </c>
       <c r="R6">
-        <v>28.39</v>
+        <v>28.3</v>
       </c>
       <c r="S6">
-        <v>33.42</v>
+        <v>33.34</v>
       </c>
       <c r="T6">
-        <v>-22.27</v>
+        <v>-22.37</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.47</v>
+        <v>35.83</v>
       </c>
       <c r="Z6">
-        <v>-0.62</v>
+        <v>-0.65</v>
       </c>
       <c r="AA6">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AB6">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>61.37</v>
+        <v>40.98</v>
       </c>
       <c r="AD6">
-        <v>76.3</v>
+        <v>61.92</v>
       </c>
       <c r="AE6">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="AF6">
-        <v>-44.98</v>
+        <v>-42.88</v>
       </c>
       <c r="AG6">
-        <v>28.24</v>
+        <v>28.26</v>
       </c>
       <c r="AH6">
-        <v>25.74</v>
+        <v>25.59</v>
       </c>
       <c r="AI6">
-        <v>28.87</v>
+        <v>28.17</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.45</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,58 +1458,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1197.6</v>
+        <v>1182</v>
       </c>
       <c r="D7">
-        <v>-2.32</v>
+        <v>-1.3</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1197.6</v>
+        <v>1182</v>
       </c>
       <c r="G7">
-        <v>-24.44</v>
+        <v>-25.42</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-3.99</v>
+        <v>-4.71</v>
       </c>
       <c r="J7">
-        <v>-6.6</v>
+        <v>-8.16</v>
       </c>
       <c r="K7">
-        <v>-7.44</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="L7">
-        <v>-13.43</v>
+        <v>-14.14</v>
       </c>
       <c r="M7">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>1226.24</v>
+        <v>1214.56</v>
       </c>
       <c r="Q7">
-        <v>1263.14</v>
+        <v>1258.39</v>
       </c>
       <c r="R7">
-        <v>1287.63</v>
+        <v>1284.81</v>
       </c>
       <c r="S7">
-        <v>1364.17</v>
+        <v>1362.43</v>
       </c>
       <c r="T7">
-        <v>-12.21</v>
+        <v>-13.24</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,43 +1524,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.93</v>
+        <v>29.39</v>
       </c>
       <c r="Z7">
-        <v>-22.29</v>
+        <v>-25.22</v>
       </c>
       <c r="AA7">
-        <v>-17.19</v>
+        <v>-18.8</v>
       </c>
       <c r="AB7">
-        <v>-5.09</v>
+        <v>-6.42</v>
       </c>
       <c r="AC7">
-        <v>13.02</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AD7">
-        <v>21.88</v>
+        <v>16.14</v>
       </c>
       <c r="AE7">
-        <v>20.98</v>
+        <v>20.66</v>
       </c>
       <c r="AF7">
-        <v>12.14</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AG7">
-        <v>1335.67</v>
+        <v>1339.08</v>
       </c>
       <c r="AH7">
-        <v>1190.6</v>
+        <v>1177.69</v>
       </c>
       <c r="AI7">
-        <v>1271.3</v>
+        <v>1252.04</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>55.74</v>
+        <v>59.27</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1758,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.7</v>
+        <v>-7.54</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.54</v>
+        <v>-8.48</v>
       </c>
       <c r="E7" s="6">
-        <v>-2.84</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1775,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.05</v>
+        <v>-11.18</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.18</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-5.13</v>
+        <v>-10.22</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1792,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.81</v>
+        <v>-7.39</v>
       </c>
       <c r="D9" s="5">
-        <v>-7.39</v>
+        <v>-8.74</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.58</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1809,13 +1809,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>3.79</v>
+        <v>2.88</v>
       </c>
       <c r="D10" s="5">
-        <v>2.88</v>
+        <v>-6.82</v>
       </c>
       <c r="E10" s="6">
-        <v>-0.91</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1826,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-12.15</v>
+        <v>-10.84</v>
       </c>
       <c r="D11" s="5">
-        <v>-10.84</v>
+        <v>-10.14</v>
       </c>
       <c r="E11" s="7">
-        <v>1.31</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1843,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.55</v>
+        <v>-6.6</v>
       </c>
       <c r="D12" s="5">
-        <v>-6.6</v>
+        <v>-8.16</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.05</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1860,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.9</v>
+        <v>-1.59</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.59</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-1.33</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1877,13 +1877,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.5</v>
+        <v>-6.02</v>
       </c>
       <c r="D14" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-5.52</v>
+        <v>-5.01</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.01</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1894,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.26</v>
+        <v>-4.12</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.12</v>
+        <v>-5.7</v>
       </c>
       <c r="E15" s="6">
-        <v>-2.86</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1911,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>0.48</v>
+        <v>-3.48</v>
       </c>
       <c r="D16" s="5">
-        <v>-3.48</v>
+        <v>-3.82</v>
       </c>
       <c r="E16" s="6">
-        <v>-3.96</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1928,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-0.93</v>
+        <v>-3.02</v>
       </c>
       <c r="D17" s="5">
-        <v>-3.02</v>
+        <v>-3.83</v>
       </c>
       <c r="E17" s="6">
-        <v>-2.09</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1945,13 +1945,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.03</v>
+        <v>-3.99</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.99</v>
+        <v>-4.71</v>
       </c>
       <c r="E18" s="6">
-        <v>-3.96</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1962,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.66</v>
+        <v>-26.93</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.93</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.27</v>
+        <v>-25.37</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1979,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-33.18</v>
+        <v>-36.47</v>
       </c>
       <c r="D20" s="5">
-        <v>-36.47</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-3.29</v>
+        <v>-34.42</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.05</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1996,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-27.67</v>
+        <v>-29.45</v>
       </c>
       <c r="D21" s="5">
-        <v>-29.45</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.78</v>
+        <v>-29.08</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2013,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-19.82</v>
+        <v>-21.01</v>
       </c>
       <c r="D22" s="5">
-        <v>-21.01</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.19</v>
+        <v>-20.34</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2030,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-51.41</v>
+        <v>-52.28</v>
       </c>
       <c r="D23" s="5">
-        <v>-52.28</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-0.87</v>
+        <v>-51.96</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2047,13 +2047,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-11.43</v>
+        <v>-13.43</v>
       </c>
       <c r="D24" s="5">
-        <v>-13.43</v>
+        <v>-14.14</v>
       </c>
       <c r="E24" s="6">
-        <v>-2</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2064,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.09</v>
+        <v>-10.93</v>
       </c>
       <c r="D25" s="5">
-        <v>-10.93</v>
+        <v>-11.96</v>
       </c>
       <c r="E25" s="6">
-        <v>-0.84</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2081,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-10.86</v>
+        <v>-15.96</v>
       </c>
       <c r="D26" s="5">
-        <v>-15.96</v>
+        <v>-16.39</v>
       </c>
       <c r="E26" s="6">
-        <v>-5.1</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2098,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-4.1</v>
+        <v>-6.74</v>
       </c>
       <c r="D27" s="5">
-        <v>-6.74</v>
+        <v>-9.35</v>
       </c>
       <c r="E27" s="6">
-        <v>-2.64</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2115,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>27.89</v>
+        <v>25.53</v>
       </c>
       <c r="D28" s="5">
-        <v>25.53</v>
+        <v>19.66</v>
       </c>
       <c r="E28" s="6">
-        <v>-2.36</v>
+        <v>-5.87</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2132,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-14.81</v>
+        <v>-17.76</v>
       </c>
       <c r="D29" s="5">
-        <v>-17.76</v>
+        <v>-20.86</v>
       </c>
       <c r="E29" s="6">
-        <v>-2.95</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2149,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-5.76</v>
+        <v>-7.44</v>
       </c>
       <c r="D30" s="5">
-        <v>-7.44</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="E30" s="6">
-        <v>-1.68</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2166,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-25.86</v>
+        <v>-26.2</v>
       </c>
       <c r="D31" s="5">
-        <v>-26.2</v>
+        <v>-26.45</v>
       </c>
       <c r="E31" s="6">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2183,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-32.68</v>
+        <v>-35.25</v>
       </c>
       <c r="D32" s="5">
-        <v>-35.25</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.57</v>
+        <v>-33.73</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2200,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-27.91</v>
+        <v>-29.98</v>
       </c>
       <c r="D33" s="5">
-        <v>-29.98</v>
+        <v>-30.91</v>
       </c>
       <c r="E33" s="6">
-        <v>-2.07</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2217,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-21.92</v>
+        <v>-23.46</v>
       </c>
       <c r="D34" s="5">
-        <v>-23.46</v>
+        <v>-23.75</v>
       </c>
       <c r="E34" s="6">
-        <v>-1.54</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2234,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-50.86</v>
+        <v>-51.77</v>
       </c>
       <c r="D35" s="5">
-        <v>-51.77</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.91</v>
+        <v>-51.39</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.38</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2251,13 +2251,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-22.65</v>
+        <v>-24.44</v>
       </c>
       <c r="D36" s="5">
-        <v>-24.44</v>
+        <v>-25.42</v>
       </c>
       <c r="E36" s="6">
-        <v>-1.79</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2268,13 +2268,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>26.38</v>
+        <v>26</v>
       </c>
       <c r="D37" s="5">
-        <v>26</v>
+        <v>25.91</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.38</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2285,13 +2285,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.93</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D38" s="5">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.5600000000000001</v>
+        <v>9.49</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2302,13 +2302,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>227</v>
+        <v>220.5</v>
       </c>
       <c r="D39" s="5">
-        <v>220.5</v>
+        <v>217.56</v>
       </c>
       <c r="E39" s="6">
-        <v>-6.5</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2319,13 +2319,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>672.2</v>
+        <v>658.95</v>
       </c>
       <c r="D40" s="5">
-        <v>658.95</v>
+        <v>656.5</v>
       </c>
       <c r="E40" s="6">
-        <v>-13.25</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2336,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>26.75</v>
+        <v>25.98</v>
       </c>
       <c r="D41" s="5">
-        <v>25.98</v>
+        <v>25.88</v>
       </c>
       <c r="E41" s="6">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2353,13 +2353,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1226</v>
+        <v>1197.6</v>
       </c>
       <c r="D42" s="5">
-        <v>1197.6</v>
+        <v>1182</v>
       </c>
       <c r="E42" s="6">
-        <v>-28.4</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2367,203 +2367,237 @@
         <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C43" s="5">
-        <v>38.09</v>
+        <v>50</v>
       </c>
       <c r="D43" s="5">
-        <v>33.84</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-4.25</v>
+        <v>66</v>
+      </c>
+      <c r="E43" s="7">
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C44" s="5">
-        <v>34.97</v>
+        <v>66</v>
       </c>
       <c r="D44" s="5">
-        <v>23.1</v>
+        <v>50</v>
       </c>
       <c r="E44" s="6">
-        <v>-11.87</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>36.61</v>
+        <v>33.84</v>
       </c>
       <c r="D45" s="5">
-        <v>29.55</v>
+        <v>32.9</v>
       </c>
       <c r="E45" s="6">
-        <v>-7.06</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>47.09</v>
+        <v>23.1</v>
       </c>
       <c r="D46" s="5">
-        <v>42.29</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-4.8</v>
+        <v>28.69</v>
+      </c>
+      <c r="E46" s="7">
+        <v>5.59</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>41.82</v>
+        <v>29.55</v>
       </c>
       <c r="D47" s="5">
-        <v>36.47</v>
+        <v>27.01</v>
       </c>
       <c r="E47" s="6">
-        <v>-5.35</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>37.4</v>
+        <v>42.29</v>
       </c>
       <c r="D48" s="5">
-        <v>31.93</v>
+        <v>41.44</v>
       </c>
       <c r="E48" s="6">
-        <v>-5.47</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>-5.6</v>
+        <v>36.47</v>
       </c>
       <c r="D49" s="5">
-        <v>3.43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>9.029999999999999</v>
+        <v>35.83</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>-17.76</v>
+        <v>31.93</v>
       </c>
       <c r="D50" s="5">
-        <v>372.33</v>
-      </c>
-      <c r="E50" s="7">
-        <v>390.09</v>
+        <v>29.39</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>-30.55</v>
+        <v>3.43</v>
       </c>
       <c r="D51" s="5">
-        <v>60.07</v>
-      </c>
-      <c r="E51" s="7">
-        <v>90.62</v>
+        <v>-26.47</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-29.9</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-73.97</v>
+        <v>372.33</v>
       </c>
       <c r="D52" s="5">
-        <v>-77.12</v>
+        <v>82.69</v>
       </c>
       <c r="E52" s="6">
-        <v>-3.15</v>
+        <v>-289.64</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-40.87</v>
+        <v>60.07</v>
       </c>
       <c r="D53" s="5">
-        <v>-44.98</v>
+        <v>46.59</v>
       </c>
       <c r="E53" s="6">
-        <v>-4.11</v>
+        <v>-13.48</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>11.37</v>
+        <v>-77.12</v>
       </c>
       <c r="D54" s="5">
+        <v>-62.43</v>
+      </c>
+      <c r="E54" s="7">
+        <v>14.69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-44.98</v>
+      </c>
+      <c r="D55" s="5">
+        <v>-42.88</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
         <v>12.14</v>
       </c>
-      <c r="E54" s="7">
-        <v>0.77</v>
+      <c r="D56" s="5">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="E56" s="7">
+        <v>84.76000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2628,16 +2662,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.8</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="G2" s="10">
-        <v>-5.6</v>
+        <v>-8.1</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2765,22 +2799,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0074</v>
+        <v>0.0064</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0378</v>
+        <v>-0.04190000000000001</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.078</v>
+        <v>-0.0788</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1126</v>
+        <v>-0.1188</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1269</v>
+        <v>-0.1326</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1712</v>
+        <v>-0.1697</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.4 → 31.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>31.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,10 +921,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.91</v>
+        <v>25.93</v>
       </c>
       <c r="D2">
-        <v>-0.35</v>
+        <v>0.08</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -905,25 +933,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.45</v>
+        <v>-26.4</v>
       </c>
       <c r="H2">
-        <v>12.75</v>
+        <v>12.84</v>
       </c>
       <c r="I2">
-        <v>-1.33</v>
+        <v>-3.39</v>
       </c>
       <c r="J2">
-        <v>-8.48</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K2">
-        <v>-11.96</v>
+        <v>-13.04</v>
       </c>
       <c r="L2">
-        <v>-25.37</v>
+        <v>-24.45</v>
       </c>
       <c r="M2">
-        <v>-11.88</v>
+        <v>-11.59</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -932,19 +960,19 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>26.33</v>
+        <v>26.15</v>
       </c>
       <c r="Q2">
-        <v>26.91</v>
+        <v>26.82</v>
       </c>
       <c r="R2">
-        <v>27.29</v>
+        <v>27.27</v>
       </c>
       <c r="S2">
-        <v>28.18</v>
+        <v>28.15</v>
       </c>
       <c r="T2">
-        <v>-8.050000000000001</v>
+        <v>-7.9</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,34 +987,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>32.9</v>
+        <v>33.34</v>
       </c>
       <c r="Z2">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="AA2">
-        <v>-0.34</v>
+        <v>-0.36</v>
       </c>
       <c r="AB2">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>20.45</v>
+        <v>13.67</v>
       </c>
       <c r="AD2">
-        <v>32.06</v>
+        <v>21.57</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF2">
-        <v>-26.47</v>
+        <v>-3.74</v>
       </c>
       <c r="AG2">
-        <v>28.24</v>
+        <v>28.15</v>
       </c>
       <c r="AH2">
-        <v>25.58</v>
+        <v>25.49</v>
       </c>
       <c r="AI2">
         <v>28.06</v>
@@ -995,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>37.36</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,37 +1034,37 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.49</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D3">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="E3">
-        <v>14.32</v>
+        <v>14.24</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.73</v>
+        <v>-33.64</v>
       </c>
       <c r="H3">
-        <v>6.99</v>
+        <v>6.54</v>
       </c>
       <c r="I3">
-        <v>-5.01</v>
+        <v>-6.44</v>
       </c>
       <c r="J3">
-        <v>-10.22</v>
+        <v>-11.18</v>
       </c>
       <c r="K3">
-        <v>-16.39</v>
+        <v>-17.18</v>
       </c>
       <c r="L3">
-        <v>-34.42</v>
+        <v>-34.01</v>
       </c>
       <c r="M3">
-        <v>-16.97</v>
+        <v>-17.01</v>
       </c>
       <c r="N3">
         <v>34</v>
@@ -1045,19 +1073,19 @@
         <v>14</v>
       </c>
       <c r="P3">
-        <v>9.77</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q3">
-        <v>10.08</v>
+        <v>10.03</v>
       </c>
       <c r="R3">
-        <v>10.47</v>
+        <v>10.44</v>
       </c>
       <c r="S3">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
       <c r="T3">
-        <v>-13.12</v>
+        <v>-13.36</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,34 +1100,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.69</v>
+        <v>27.96</v>
       </c>
       <c r="Z3">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="AA3">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="AB3">
         <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>23.27</v>
+        <v>20.01</v>
       </c>
       <c r="AD3">
-        <v>30.45</v>
+        <v>22.22</v>
       </c>
       <c r="AE3">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AF3">
-        <v>82.69</v>
+        <v>3.2</v>
       </c>
       <c r="AG3">
-        <v>10.66</v>
+        <v>10.64</v>
       </c>
       <c r="AH3">
-        <v>9.5</v>
+        <v>9.42</v>
       </c>
       <c r="AI3">
         <v>10.33</v>
@@ -1108,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>35.83</v>
+        <v>33.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,37 +1147,37 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>217.56</v>
+        <v>216.88</v>
       </c>
       <c r="D4">
-        <v>-1.33</v>
+        <v>-0.31</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>217.56</v>
+        <v>216.88</v>
       </c>
       <c r="G4">
-        <v>-30.91</v>
+        <v>-31.13</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-5.7</v>
+        <v>-6.58</v>
       </c>
       <c r="J4">
-        <v>-8.74</v>
+        <v>-10.14</v>
       </c>
       <c r="K4">
-        <v>-9.35</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L4">
-        <v>-29.08</v>
+        <v>-28.09</v>
       </c>
       <c r="M4">
-        <v>-4.19</v>
+        <v>-4.28</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1158,19 +1186,19 @@
         <v>27</v>
       </c>
       <c r="P4">
-        <v>224.88</v>
+        <v>221.83</v>
       </c>
       <c r="Q4">
-        <v>230.16</v>
+        <v>229.21</v>
       </c>
       <c r="R4">
-        <v>240.41</v>
+        <v>239.95</v>
       </c>
       <c r="S4">
-        <v>249.88</v>
+        <v>249.47</v>
       </c>
       <c r="T4">
-        <v>-12.93</v>
+        <v>-13.06</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>27.01</v>
+        <v>26.44</v>
       </c>
       <c r="Z4">
-        <v>-4.91</v>
+        <v>-5.36</v>
       </c>
       <c r="AA4">
-        <v>-4.22</v>
+        <v>-4.45</v>
       </c>
       <c r="AB4">
-        <v>-0.6899999999999999</v>
+        <v>-0.91</v>
       </c>
       <c r="AC4">
-        <v>19.14</v>
+        <v>1.73</v>
       </c>
       <c r="AD4">
-        <v>40.86</v>
+        <v>19.12</v>
       </c>
       <c r="AE4">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="AF4">
-        <v>46.59</v>
+        <v>17.67</v>
       </c>
       <c r="AG4">
-        <v>241.12</v>
+        <v>241.32</v>
       </c>
       <c r="AH4">
-        <v>219.19</v>
+        <v>217.1</v>
       </c>
       <c r="AI4">
         <v>231.26</v>
@@ -1221,7 +1249,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>41.57</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1260,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>656.5</v>
+        <v>666.15</v>
       </c>
       <c r="D5">
-        <v>-0.37</v>
+        <v>1.47</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1272,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.75</v>
+        <v>-22.63</v>
       </c>
       <c r="H5">
-        <v>33.79</v>
+        <v>35.76</v>
       </c>
       <c r="I5">
-        <v>-3.82</v>
+        <v>-3.95</v>
       </c>
       <c r="J5">
-        <v>-6.82</v>
+        <v>-6.2</v>
       </c>
       <c r="K5">
-        <v>19.66</v>
+        <v>19.93</v>
       </c>
       <c r="L5">
-        <v>-20.34</v>
+        <v>-18.78</v>
       </c>
       <c r="M5">
-        <v>-7.88</v>
+        <v>-7.6</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>670.71</v>
+        <v>665.23</v>
       </c>
       <c r="Q5">
-        <v>679.84</v>
+        <v>677.87</v>
       </c>
       <c r="R5">
-        <v>688.95</v>
+        <v>687.4</v>
       </c>
       <c r="S5">
-        <v>620.8200000000001</v>
+        <v>620.59</v>
       </c>
       <c r="T5">
-        <v>5.75</v>
+        <v>7.34</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1298,34 +1326,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.44</v>
+        <v>46.01</v>
       </c>
       <c r="Z5">
-        <v>-3.72</v>
+        <v>-3.94</v>
       </c>
       <c r="AA5">
-        <v>-1.4</v>
+        <v>-1.91</v>
       </c>
       <c r="AB5">
-        <v>-2.32</v>
+        <v>-2.03</v>
       </c>
       <c r="AC5">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>29.31</v>
+        <v>14.41</v>
       </c>
       <c r="AE5">
-        <v>22.03</v>
+        <v>21.91</v>
       </c>
       <c r="AF5">
-        <v>-62.43</v>
+        <v>-42.89</v>
       </c>
       <c r="AG5">
-        <v>709.48</v>
+        <v>705.46</v>
       </c>
       <c r="AH5">
-        <v>650.21</v>
+        <v>650.28</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1334,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>20.45</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1373,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="D6">
-        <v>-0.38</v>
+        <v>-0.04</v>
       </c>
       <c r="E6">
-        <v>53.24</v>
+        <v>52.4</v>
       </c>
       <c r="F6">
-        <v>25.88</v>
+        <v>25.87</v>
       </c>
       <c r="G6">
-        <v>-51.39</v>
+        <v>-50.63</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-3.83</v>
+        <v>-4.68</v>
       </c>
       <c r="J6">
-        <v>-10.14</v>
+        <v>-4.99</v>
       </c>
       <c r="K6">
-        <v>-20.86</v>
+        <v>-21.87</v>
       </c>
       <c r="L6">
-        <v>-51.96</v>
+        <v>-51.41</v>
       </c>
       <c r="M6">
-        <v>-13.26</v>
+        <v>-13.02</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1384,19 +1412,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.54</v>
+        <v>26.29</v>
       </c>
       <c r="Q6">
-        <v>26.92</v>
+        <v>26.82</v>
       </c>
       <c r="R6">
-        <v>28.3</v>
+        <v>28.23</v>
       </c>
       <c r="S6">
-        <v>33.34</v>
+        <v>33.25</v>
       </c>
       <c r="T6">
-        <v>-22.37</v>
+        <v>-22.2</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1439,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.83</v>
+        <v>35.76</v>
       </c>
       <c r="Z6">
-        <v>-0.65</v>
+        <v>-0.67</v>
       </c>
       <c r="AA6">
         <v>-0.66</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>40.98</v>
+        <v>23.39</v>
       </c>
       <c r="AD6">
-        <v>61.92</v>
+        <v>41.91</v>
       </c>
       <c r="AE6">
         <v>0.84</v>
       </c>
       <c r="AF6">
-        <v>-42.88</v>
+        <v>-51.21</v>
       </c>
       <c r="AG6">
-        <v>28.26</v>
+        <v>28.12</v>
       </c>
       <c r="AH6">
-        <v>25.59</v>
+        <v>25.51</v>
       </c>
       <c r="AI6">
         <v>28.17</v>
@@ -1447,7 +1475,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.84</v>
+        <v>32.44</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D7">
-        <v>-1.3</v>
+        <v>0.42</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,46 +1498,46 @@
         <v>1182</v>
       </c>
       <c r="G7">
-        <v>-25.42</v>
+        <v>-25.11</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="I7">
-        <v>-4.71</v>
+        <v>-4.89</v>
       </c>
       <c r="J7">
-        <v>-8.16</v>
+        <v>-7.05</v>
       </c>
       <c r="K7">
-        <v>-9.630000000000001</v>
+        <v>-8.94</v>
       </c>
       <c r="L7">
-        <v>-14.14</v>
+        <v>-13.11</v>
       </c>
       <c r="M7">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P7">
-        <v>1214.56</v>
+        <v>1202.36</v>
       </c>
       <c r="Q7">
-        <v>1258.39</v>
+        <v>1252.29</v>
       </c>
       <c r="R7">
-        <v>1284.81</v>
+        <v>1282.48</v>
       </c>
       <c r="S7">
-        <v>1362.43</v>
+        <v>1360.67</v>
       </c>
       <c r="T7">
-        <v>-13.24</v>
+        <v>-12.76</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,43 +1552,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>29.39</v>
+        <v>31.28</v>
       </c>
       <c r="Z7">
-        <v>-25.22</v>
+        <v>-26.83</v>
       </c>
       <c r="AA7">
-        <v>-18.8</v>
+        <v>-20.4</v>
       </c>
       <c r="AB7">
         <v>-6.42</v>
       </c>
       <c r="AC7">
+        <v>5.26</v>
+      </c>
+      <c r="AD7">
         <v>9.140000000000001</v>
       </c>
-      <c r="AD7">
-        <v>16.14</v>
-      </c>
       <c r="AE7">
-        <v>20.66</v>
+        <v>20.24</v>
       </c>
       <c r="AF7">
-        <v>96.90000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="AG7">
-        <v>1339.08</v>
+        <v>1335.29</v>
       </c>
       <c r="AH7">
-        <v>1177.69</v>
+        <v>1169.28</v>
       </c>
       <c r="AI7">
-        <v>1252.04</v>
+        <v>1249.83</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>59.27</v>
+        <v>62.33</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1721,12 +1749,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1734,870 +1797,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.54</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-8.48</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.9399999999999999</v>
+      <c r="D7" s="6">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
+        <v>-10.22</v>
+      </c>
+      <c r="D8" s="6">
         <v>-11.18</v>
       </c>
-      <c r="D8" s="5">
-        <v>-10.22</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.96</v>
+      <c r="E8" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.39</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8.74</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.35</v>
+      <c r="D9" s="6">
+        <v>-10.14</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>2.88</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-6.82</v>
       </c>
-      <c r="E10" s="6">
-        <v>-9.699999999999999</v>
+      <c r="D10" s="6">
+        <v>-6.2</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-10.84</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-10.14</v>
       </c>
+      <c r="D11" s="6">
+        <v>-4.99</v>
+      </c>
       <c r="E11" s="7">
-        <v>0.7</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-6.6</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-8.16</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.56</v>
+      <c r="D12" s="6">
+        <v>-7.05</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.59</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-1.33</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.26</v>
+      <c r="D13" s="6">
+        <v>-3.39</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-6.02</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-5.01</v>
       </c>
-      <c r="E14" s="7">
-        <v>1.01</v>
+      <c r="D14" s="6">
+        <v>-6.44</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-4.12</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-5.7</v>
       </c>
-      <c r="E15" s="6">
-        <v>-1.58</v>
+      <c r="D15" s="6">
+        <v>-6.58</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-3.48</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-3.82</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.34</v>
+      <c r="D16" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-3.02</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-3.83</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.8100000000000001</v>
+      <c r="D17" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-3.99</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-4.71</v>
       </c>
-      <c r="E18" s="6">
-        <v>-0.72</v>
+      <c r="D18" s="6">
+        <v>-4.89</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-26.93</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-25.37</v>
       </c>
+      <c r="D19" s="6">
+        <v>-24.45</v>
+      </c>
       <c r="E19" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-34.42</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-34.01</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-29.08</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-28.09</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-20.34</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E22" s="7">
         <v>1.56</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-51.96</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-51.41</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-14.14</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-13.11</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-11.96</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-13.04</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-36.47</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-34.42</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-16.39</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-17.18</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-29.45</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-29.08</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-9.35</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-21.01</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-20.34</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>19.66</v>
+      </c>
+      <c r="D28" s="6">
+        <v>19.93</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-52.28</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-51.96</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-20.86</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-21.87</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-14.14</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-8.94</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-10.93</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-11.96</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-26.45</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-26.4</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-15.96</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-16.39</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-33.73</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-33.64</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-6.74</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-30.91</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-31.13</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>25.53</v>
-      </c>
-      <c r="D28" s="5">
-        <v>19.66</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-23.75</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-22.63</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-17.76</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-20.86</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-51.39</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-50.63</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-7.44</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-25.42</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-25.11</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-26.2</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.45</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>25.91</v>
+      </c>
+      <c r="D37" s="6">
+        <v>25.93</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-35.25</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-33.73</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>9.49</v>
+      </c>
+      <c r="D38" s="6">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-29.98</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-30.91</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>217.56</v>
+      </c>
+      <c r="D39" s="6">
+        <v>216.88</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-23.46</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-23.75</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>656.5</v>
+      </c>
+      <c r="D40" s="6">
+        <v>666.15</v>
+      </c>
+      <c r="E40" s="7">
+        <v>9.65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-51.77</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.39</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>25.88</v>
+      </c>
+      <c r="D41" s="6">
+        <v>25.87</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-24.44</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-25.42</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1182</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1187</v>
+      </c>
+      <c r="E42" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>26</v>
-      </c>
-      <c r="D37" s="5">
-        <v>25.91</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>32.9</v>
+      </c>
+      <c r="D43" s="6">
+        <v>33.34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.49</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>28.69</v>
+      </c>
+      <c r="D44" s="6">
+        <v>27.96</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>220.5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>217.56</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>27.01</v>
+      </c>
+      <c r="D45" s="6">
+        <v>26.44</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>658.95</v>
-      </c>
-      <c r="D40" s="5">
-        <v>656.5</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>41.44</v>
+      </c>
+      <c r="D46" s="6">
+        <v>46.01</v>
+      </c>
+      <c r="E46" s="7">
+        <v>4.57</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>25.98</v>
-      </c>
-      <c r="D41" s="5">
-        <v>25.88</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>35.83</v>
+      </c>
+      <c r="D47" s="6">
+        <v>35.76</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1197.6</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1182</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-15.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>29.39</v>
+      </c>
+      <c r="D48" s="6">
+        <v>31.28</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="5">
-        <v>50</v>
-      </c>
-      <c r="D43" s="5">
-        <v>66</v>
-      </c>
-      <c r="E43" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-26.47</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-3.74</v>
+      </c>
+      <c r="E49" s="7">
+        <v>22.73</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>82.69</v>
+      </c>
+      <c r="D50" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-79.48999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="5">
-        <v>66</v>
-      </c>
-      <c r="D44" s="5">
-        <v>50</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>33.84</v>
-      </c>
-      <c r="D45" s="5">
-        <v>32.9</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>23.1</v>
-      </c>
-      <c r="D46" s="5">
-        <v>28.69</v>
-      </c>
-      <c r="E46" s="7">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>29.55</v>
-      </c>
-      <c r="D47" s="5">
-        <v>27.01</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>46.59</v>
+      </c>
+      <c r="D51" s="6">
+        <v>17.67</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-28.92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>42.29</v>
-      </c>
-      <c r="D48" s="5">
-        <v>41.44</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-62.43</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-42.89</v>
+      </c>
+      <c r="E52" s="7">
+        <v>19.54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>36.47</v>
-      </c>
-      <c r="D49" s="5">
-        <v>35.83</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-42.88</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-51.21</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-8.33</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>31.93</v>
-      </c>
-      <c r="D50" s="5">
-        <v>29.39</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="5">
-        <v>3.43</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-26.47</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-29.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>372.33</v>
-      </c>
-      <c r="D52" s="5">
-        <v>82.69</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-289.64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>60.07</v>
-      </c>
-      <c r="D53" s="5">
-        <v>46.59</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-13.48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-77.12</v>
-      </c>
-      <c r="D54" s="5">
-        <v>-62.43</v>
-      </c>
-      <c r="E54" s="7">
-        <v>14.69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-44.98</v>
-      </c>
-      <c r="D55" s="5">
-        <v>-42.88</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>12.14</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C54" s="6">
         <v>96.90000000000001</v>
       </c>
-      <c r="E56" s="7">
-        <v>84.76000000000001</v>
+      <c r="D54" s="6">
+        <v>25.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-71.5</v>
       </c>
     </row>
   </sheetData>
@@ -2623,60 +2652,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>32.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>33.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2778,43 +2807,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0064</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.04190000000000001</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0788</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1188</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1326</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1697</v>
+      <c r="A2" s="14">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0428</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.076</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1159</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1302</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1701</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.4 → 31.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.4</t>
-  </si>
-  <si>
-    <t>31.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -282,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -921,10 +893,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.93</v>
+        <v>25.41</v>
       </c>
       <c r="D2">
-        <v>0.08</v>
+        <v>-2.01</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -933,25 +905,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.4</v>
+        <v>-27.87</v>
       </c>
       <c r="H2">
-        <v>12.84</v>
+        <v>10.57</v>
       </c>
       <c r="I2">
-        <v>-3.39</v>
+        <v>-4.19</v>
       </c>
       <c r="J2">
-        <v>-8.279999999999999</v>
+        <v>-8.5</v>
       </c>
       <c r="K2">
-        <v>-13.04</v>
+        <v>-14.56</v>
       </c>
       <c r="L2">
-        <v>-24.45</v>
+        <v>-24.22</v>
       </c>
       <c r="M2">
-        <v>-11.59</v>
+        <v>-12.11</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -960,19 +932,19 @@
         <v>27</v>
       </c>
       <c r="P2">
-        <v>26.15</v>
+        <v>25.93</v>
       </c>
       <c r="Q2">
-        <v>26.82</v>
+        <v>26.7</v>
       </c>
       <c r="R2">
-        <v>27.27</v>
+        <v>27.23</v>
       </c>
       <c r="S2">
-        <v>28.15</v>
+        <v>28.13</v>
       </c>
       <c r="T2">
-        <v>-7.9</v>
+        <v>-9.67</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,43 +959,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.34</v>
+        <v>28.15</v>
       </c>
       <c r="Z2">
-        <v>-0.43</v>
+        <v>-0.48</v>
       </c>
       <c r="AA2">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="AB2">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="AC2">
-        <v>13.67</v>
+        <v>7.82</v>
       </c>
       <c r="AD2">
-        <v>21.57</v>
+        <v>13.98</v>
       </c>
       <c r="AE2">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>-3.74</v>
+        <v>8.92</v>
       </c>
       <c r="AG2">
-        <v>28.15</v>
+        <v>28.08</v>
       </c>
       <c r="AH2">
-        <v>25.49</v>
+        <v>25.32</v>
       </c>
       <c r="AI2">
-        <v>28.06</v>
+        <v>27.67</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>39.79</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1006,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.449999999999999</v>
+        <v>9.32</v>
       </c>
       <c r="D3">
-        <v>-0.42</v>
+        <v>-1.38</v>
       </c>
       <c r="E3">
         <v>14.24</v>
@@ -1046,46 +1018,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.64</v>
+        <v>-34.55</v>
       </c>
       <c r="H3">
-        <v>6.54</v>
+        <v>5.07</v>
       </c>
       <c r="I3">
-        <v>-6.44</v>
+        <v>-6.43</v>
       </c>
       <c r="J3">
-        <v>-11.18</v>
+        <v>-11.24</v>
       </c>
       <c r="K3">
-        <v>-17.18</v>
+        <v>-17.52</v>
       </c>
       <c r="L3">
-        <v>-34.01</v>
+        <v>-34.32</v>
       </c>
       <c r="M3">
-        <v>-17.01</v>
+        <v>-17.94</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P3">
-        <v>9.640000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="Q3">
-        <v>10.03</v>
+        <v>9.98</v>
       </c>
       <c r="R3">
-        <v>10.44</v>
+        <v>10.41</v>
       </c>
       <c r="S3">
-        <v>10.91</v>
+        <v>10.89</v>
       </c>
       <c r="T3">
-        <v>-13.36</v>
+        <v>-14.42</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,43 +1072,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>27.96</v>
+        <v>25.68</v>
       </c>
       <c r="Z3">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="AA3">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AC3">
-        <v>20.01</v>
+        <v>24.95</v>
       </c>
       <c r="AD3">
-        <v>22.22</v>
+        <v>22.74</v>
       </c>
       <c r="AE3">
         <v>0.34</v>
       </c>
       <c r="AF3">
-        <v>3.2</v>
+        <v>-1.66</v>
       </c>
       <c r="AG3">
-        <v>10.64</v>
+        <v>10.65</v>
       </c>
       <c r="AH3">
-        <v>9.42</v>
+        <v>9.31</v>
       </c>
       <c r="AI3">
-        <v>10.33</v>
+        <v>10.28</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>33.38</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,58 +1119,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>216.88</v>
+        <v>212.5</v>
       </c>
       <c r="D4">
-        <v>-0.31</v>
+        <v>-2.02</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>216.88</v>
+        <v>212.5</v>
       </c>
       <c r="G4">
-        <v>-31.13</v>
+        <v>-32.52</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-6.58</v>
+        <v>-6.47</v>
       </c>
       <c r="J4">
-        <v>-10.14</v>
+        <v>-9.9</v>
       </c>
       <c r="K4">
-        <v>-9.529999999999999</v>
+        <v>-11.22</v>
       </c>
       <c r="L4">
-        <v>-28.09</v>
+        <v>-28.17</v>
       </c>
       <c r="M4">
-        <v>-4.28</v>
+        <v>-4.9</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>221.83</v>
+        <v>218.89</v>
       </c>
       <c r="Q4">
-        <v>229.21</v>
+        <v>227.99</v>
       </c>
       <c r="R4">
-        <v>239.95</v>
+        <v>239.5</v>
       </c>
       <c r="S4">
-        <v>249.47</v>
+        <v>249.03</v>
       </c>
       <c r="T4">
-        <v>-13.06</v>
+        <v>-14.67</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1213,43 +1185,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>26.44</v>
+        <v>23.09</v>
       </c>
       <c r="Z4">
-        <v>-5.36</v>
+        <v>-5.99</v>
       </c>
       <c r="AA4">
-        <v>-4.45</v>
+        <v>-4.76</v>
       </c>
       <c r="AB4">
-        <v>-0.91</v>
+        <v>-1.23</v>
       </c>
       <c r="AC4">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>19.12</v>
+        <v>6.96</v>
       </c>
       <c r="AE4">
-        <v>4.46</v>
+        <v>4.74</v>
       </c>
       <c r="AF4">
-        <v>17.67</v>
+        <v>138.04</v>
       </c>
       <c r="AG4">
-        <v>241.32</v>
+        <v>241.65</v>
       </c>
       <c r="AH4">
-        <v>217.1</v>
+        <v>214.32</v>
       </c>
       <c r="AI4">
-        <v>231.26</v>
+        <v>226.58</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>45.19</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>666.15</v>
+        <v>653.15</v>
       </c>
       <c r="D5">
-        <v>1.47</v>
+        <v>-1.95</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1272,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-22.63</v>
+        <v>-24.14</v>
       </c>
       <c r="H5">
-        <v>35.76</v>
+        <v>33.11</v>
       </c>
       <c r="I5">
-        <v>-3.95</v>
+        <v>-2.86</v>
       </c>
       <c r="J5">
-        <v>-6.2</v>
+        <v>-7.44</v>
       </c>
       <c r="K5">
-        <v>19.93</v>
+        <v>18.79</v>
       </c>
       <c r="L5">
-        <v>-18.78</v>
+        <v>-20.17</v>
       </c>
       <c r="M5">
-        <v>-7.6</v>
+        <v>-7.98</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>665.23</v>
+        <v>661.39</v>
       </c>
       <c r="Q5">
-        <v>677.87</v>
+        <v>675.63</v>
       </c>
       <c r="R5">
-        <v>687.4</v>
+        <v>686.01</v>
       </c>
       <c r="S5">
-        <v>620.59</v>
+        <v>620.3</v>
       </c>
       <c r="T5">
-        <v>7.34</v>
+        <v>5.3</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1326,34 +1298,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>46.01</v>
+        <v>41.33</v>
       </c>
       <c r="Z5">
-        <v>-3.94</v>
+        <v>-5.1</v>
       </c>
       <c r="AA5">
-        <v>-1.91</v>
+        <v>-2.55</v>
       </c>
       <c r="AB5">
-        <v>-2.03</v>
+        <v>-2.55</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>14.41</v>
+        <v>10.62</v>
       </c>
       <c r="AE5">
-        <v>21.91</v>
+        <v>21.76</v>
       </c>
       <c r="AF5">
-        <v>-42.89</v>
+        <v>-14.16</v>
       </c>
       <c r="AG5">
-        <v>705.46</v>
+        <v>703.65</v>
       </c>
       <c r="AH5">
-        <v>650.28</v>
+        <v>647.62</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1362,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>20.7</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,37 +1345,37 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.87</v>
+        <v>25.43</v>
       </c>
       <c r="D6">
-        <v>-0.04</v>
+        <v>-1.7</v>
       </c>
       <c r="E6">
         <v>52.4</v>
       </c>
       <c r="F6">
-        <v>25.87</v>
+        <v>25.43</v>
       </c>
       <c r="G6">
-        <v>-50.63</v>
+        <v>-51.47</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-4.68</v>
+        <v>-5.71</v>
       </c>
       <c r="J6">
-        <v>-4.99</v>
+        <v>-9.34</v>
       </c>
       <c r="K6">
-        <v>-21.87</v>
+        <v>-22.85</v>
       </c>
       <c r="L6">
-        <v>-51.41</v>
+        <v>-50.79</v>
       </c>
       <c r="M6">
-        <v>-13.02</v>
+        <v>-14.08</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1412,19 +1384,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>26.29</v>
+        <v>25.98</v>
       </c>
       <c r="Q6">
-        <v>26.82</v>
+        <v>26.73</v>
       </c>
       <c r="R6">
-        <v>28.23</v>
+        <v>28.16</v>
       </c>
       <c r="S6">
-        <v>33.25</v>
+        <v>33.16</v>
       </c>
       <c r="T6">
-        <v>-22.2</v>
+        <v>-23.32</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.76</v>
+        <v>32.82</v>
       </c>
       <c r="Z6">
+        <v>-0.71</v>
+      </c>
+      <c r="AA6">
         <v>-0.67</v>
       </c>
-      <c r="AA6">
-        <v>-0.66</v>
-      </c>
       <c r="AB6">
-        <v>-0</v>
+        <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>23.39</v>
+        <v>14.29</v>
       </c>
       <c r="AD6">
-        <v>41.91</v>
+        <v>26.22</v>
       </c>
       <c r="AE6">
         <v>0.84</v>
       </c>
       <c r="AF6">
-        <v>-51.21</v>
+        <v>-14.08</v>
       </c>
       <c r="AG6">
-        <v>28.12</v>
+        <v>28.15</v>
       </c>
       <c r="AH6">
-        <v>25.51</v>
+        <v>25.3</v>
       </c>
       <c r="AI6">
-        <v>28.17</v>
+        <v>28.03</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.44</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,58 +1458,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1187</v>
+        <v>1167.7</v>
       </c>
       <c r="D7">
-        <v>0.42</v>
+        <v>-1.63</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1182</v>
+        <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-25.11</v>
+        <v>-26.33</v>
       </c>
       <c r="H7">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.89</v>
+        <v>-4.22</v>
       </c>
       <c r="J7">
-        <v>-7.05</v>
+        <v>-10.79</v>
       </c>
       <c r="K7">
-        <v>-8.94</v>
+        <v>-10.45</v>
       </c>
       <c r="L7">
-        <v>-13.11</v>
+        <v>-14.84</v>
       </c>
       <c r="M7">
-        <v>0.79</v>
+        <v>0.43</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P7">
-        <v>1202.36</v>
+        <v>1192.06</v>
       </c>
       <c r="Q7">
-        <v>1252.29</v>
+        <v>1245.02</v>
       </c>
       <c r="R7">
-        <v>1282.48</v>
+        <v>1280.06</v>
       </c>
       <c r="S7">
-        <v>1360.67</v>
+        <v>1358.77</v>
       </c>
       <c r="T7">
-        <v>-12.76</v>
+        <v>-14.06</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1552,43 +1524,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.28</v>
+        <v>28.15</v>
       </c>
       <c r="Z7">
-        <v>-26.83</v>
+        <v>-29.32</v>
       </c>
       <c r="AA7">
-        <v>-20.4</v>
+        <v>-22.19</v>
       </c>
       <c r="AB7">
-        <v>-6.42</v>
+        <v>-7.13</v>
       </c>
       <c r="AC7">
         <v>5.26</v>
       </c>
       <c r="AD7">
-        <v>9.140000000000001</v>
+        <v>6.55</v>
       </c>
       <c r="AE7">
-        <v>20.24</v>
+        <v>20.67</v>
       </c>
       <c r="AF7">
-        <v>25.4</v>
+        <v>36.89</v>
       </c>
       <c r="AG7">
-        <v>1335.29</v>
+        <v>1331</v>
       </c>
       <c r="AH7">
-        <v>1169.28</v>
+        <v>1159.03</v>
       </c>
       <c r="AI7">
-        <v>1249.83</v>
+        <v>1234.36</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>62.33</v>
+        <v>65.64</v>
       </c>
     </row>
   </sheetData>
@@ -1749,47 +1721,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1797,836 +1734,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-8.48</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-8.279999999999999</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.2</v>
+      <c r="D7" s="5">
+        <v>-8.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-10.22</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-11.18</v>
       </c>
-      <c r="E8" s="8">
-        <v>-0.96</v>
+      <c r="D8" s="5">
+        <v>-11.24</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-8.74</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.14</v>
       </c>
-      <c r="E9" s="8">
-        <v>-1.4</v>
+      <c r="D9" s="5">
+        <v>-9.9</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.82</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-6.2</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D10" s="5">
+        <v>-7.44</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-4.99</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.34</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.05</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-10.79</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.19</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-6.44</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-6.43</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.58</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.95</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.86</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-5.71</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.89</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-24.45</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-24.22</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-34.01</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-34.32</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-28.09</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-28.17</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-18.78</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-20.17</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-51.41</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-50.79</v>
+      </c>
+      <c r="E23" s="7">
         <v>0.62</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-14.84</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-13.04</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-14.56</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-17.18</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-17.52</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-11.22</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>19.93</v>
+      </c>
+      <c r="D28" s="5">
+        <v>18.79</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="E11" s="7">
-        <v>5.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-21.87</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-22.85</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-8.16</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-8.94</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.45</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.39</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-26.4</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-27.87</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-6.44</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-33.64</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-34.55</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.58</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-31.13</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-32.52</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.95</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-22.63</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-24.14</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-50.63</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-51.47</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-25.11</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-26.33</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>25.93</v>
+      </c>
+      <c r="D37" s="5">
+        <v>25.41</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.32</v>
+      </c>
+      <c r="E38" s="6">
         <v>-0.13</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>216.88</v>
+      </c>
+      <c r="D39" s="5">
+        <v>212.5</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>666.15</v>
+      </c>
+      <c r="D40" s="5">
+        <v>653.15</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>25.87</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.43</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1187</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1167.7</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-19.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>33.34</v>
+      </c>
+      <c r="D43" s="5">
+        <v>28.15</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-5.19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>27.96</v>
+      </c>
+      <c r="D44" s="5">
+        <v>25.68</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>26.44</v>
+      </c>
+      <c r="D45" s="5">
+        <v>23.09</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-3.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46.01</v>
+      </c>
+      <c r="D46" s="5">
+        <v>41.33</v>
+      </c>
+      <c r="E46" s="6">
         <v>-4.68</v>
       </c>
-      <c r="E17" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>35.76</v>
+      </c>
+      <c r="D47" s="5">
+        <v>32.82</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.89</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>31.28</v>
+      </c>
+      <c r="D48" s="5">
+        <v>28.15</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-25.37</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-24.45</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-3.74</v>
+      </c>
+      <c r="D49" s="5">
+        <v>8.92</v>
+      </c>
+      <c r="E49" s="7">
+        <v>12.66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-34.42</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-34.01</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>3.2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-1.66</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-4.86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-29.08</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-28.09</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>17.67</v>
+      </c>
+      <c r="D51" s="5">
+        <v>138.04</v>
+      </c>
+      <c r="E51" s="7">
+        <v>120.37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-20.34</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-42.89</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-14.16</v>
+      </c>
+      <c r="E52" s="7">
+        <v>28.73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-51.96</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-51.41</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-51.21</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-14.08</v>
+      </c>
+      <c r="E53" s="7">
+        <v>37.13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.14</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-13.11</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-11.96</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-13.04</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-16.39</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-17.18</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-9.35</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>19.66</v>
-      </c>
-      <c r="D28" s="6">
-        <v>19.93</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-20.86</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-21.87</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-8.94</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-26.45</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-26.4</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-33.73</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-33.64</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-30.91</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-31.13</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-23.75</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-22.63</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-51.39</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-50.63</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-25.42</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-25.11</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>25.91</v>
-      </c>
-      <c r="D37" s="6">
-        <v>25.93</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>9.49</v>
-      </c>
-      <c r="D38" s="6">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>217.56</v>
-      </c>
-      <c r="D39" s="6">
-        <v>216.88</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>656.5</v>
-      </c>
-      <c r="D40" s="6">
-        <v>666.15</v>
-      </c>
-      <c r="E40" s="7">
-        <v>9.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>25.88</v>
-      </c>
-      <c r="D41" s="6">
-        <v>25.87</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1182</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1187</v>
-      </c>
-      <c r="E42" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>32.9</v>
-      </c>
-      <c r="D43" s="6">
-        <v>33.34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>28.69</v>
-      </c>
-      <c r="D44" s="6">
-        <v>27.96</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>27.01</v>
-      </c>
-      <c r="D45" s="6">
-        <v>26.44</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>41.44</v>
-      </c>
-      <c r="D46" s="6">
-        <v>46.01</v>
-      </c>
-      <c r="E46" s="7">
-        <v>4.57</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>35.83</v>
-      </c>
-      <c r="D47" s="6">
-        <v>35.76</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>29.39</v>
-      </c>
-      <c r="D48" s="6">
-        <v>31.28</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="6">
-        <v>-26.47</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="E49" s="7">
-        <v>22.73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>82.69</v>
-      </c>
-      <c r="D50" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-79.48999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>46.59</v>
-      </c>
-      <c r="D51" s="6">
-        <v>17.67</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-28.92</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-62.43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-42.89</v>
-      </c>
-      <c r="E52" s="7">
-        <v>19.54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-42.88</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-51.21</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-8.33</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>25.4</v>
       </c>
-      <c r="E54" s="8">
-        <v>-71.5</v>
+      <c r="D54" s="5">
+        <v>36.89</v>
+      </c>
+      <c r="E54" s="7">
+        <v>11.49</v>
       </c>
     </row>
   </sheetData>
@@ -2652,60 +2589,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>33.5</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>29.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-9.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-9.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2807,43 +2744,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0428</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.076</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1159</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1302</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1701</v>
+      <c r="A2" s="13">
+        <v>0.0043</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.049</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.07980000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1211</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1408</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1794</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.1 → 34.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>34.5</t>
+  </si>
+  <si>
+    <t>28.1 → 34.9</t>
+  </si>
+  <si>
+    <t>34.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,14 +404,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,10 +927,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.41</v>
+        <v>25.71</v>
       </c>
       <c r="D2">
-        <v>-2.01</v>
+        <v>1.18</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -905,46 +939,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.87</v>
+        <v>-27.02</v>
       </c>
       <c r="H2">
-        <v>10.57</v>
+        <v>11.88</v>
       </c>
       <c r="I2">
-        <v>-4.19</v>
+        <v>-2.54</v>
       </c>
       <c r="J2">
-        <v>-8.5</v>
+        <v>-7.68</v>
       </c>
       <c r="K2">
-        <v>-14.56</v>
+        <v>-12.1</v>
       </c>
       <c r="L2">
-        <v>-24.22</v>
+        <v>-22.04</v>
       </c>
       <c r="M2">
-        <v>-12.11</v>
+        <v>-12.77</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="P2">
-        <v>25.93</v>
+        <v>25.79</v>
       </c>
       <c r="Q2">
-        <v>26.7</v>
+        <v>26.59</v>
       </c>
       <c r="R2">
-        <v>27.23</v>
+        <v>27.2</v>
       </c>
       <c r="S2">
-        <v>28.13</v>
+        <v>28.1</v>
       </c>
       <c r="T2">
-        <v>-9.67</v>
+        <v>-8.5</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,34 +993,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.15</v>
+        <v>34.49</v>
       </c>
       <c r="Z2">
-        <v>-0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="AA2">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="AB2">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AC2">
-        <v>7.82</v>
+        <v>17.84</v>
       </c>
       <c r="AD2">
-        <v>13.98</v>
+        <v>13.11</v>
       </c>
       <c r="AE2">
         <v>0.7</v>
       </c>
       <c r="AF2">
-        <v>8.92</v>
+        <v>24.09</v>
       </c>
       <c r="AG2">
-        <v>28.08</v>
+        <v>27.92</v>
       </c>
       <c r="AH2">
-        <v>25.32</v>
+        <v>25.26</v>
       </c>
       <c r="AI2">
         <v>27.67</v>
@@ -995,7 +1029,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>43.92</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1040,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.32</v>
+        <v>9.4</v>
       </c>
       <c r="D3">
-        <v>-1.38</v>
+        <v>0.86</v>
       </c>
       <c r="E3">
         <v>14.24</v>
@@ -1018,46 +1052,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-34.55</v>
+        <v>-33.99</v>
       </c>
       <c r="H3">
-        <v>5.07</v>
+        <v>5.98</v>
       </c>
       <c r="I3">
-        <v>-6.43</v>
+        <v>-5.34</v>
       </c>
       <c r="J3">
-        <v>-11.24</v>
+        <v>-9.09</v>
       </c>
       <c r="K3">
-        <v>-17.52</v>
+        <v>-15.7</v>
       </c>
       <c r="L3">
-        <v>-34.32</v>
+        <v>-31.39</v>
       </c>
       <c r="M3">
-        <v>-17.94</v>
+        <v>-18.72</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>9.51</v>
+        <v>9.41</v>
       </c>
       <c r="Q3">
-        <v>9.98</v>
+        <v>9.94</v>
       </c>
       <c r="R3">
-        <v>10.41</v>
+        <v>10.38</v>
       </c>
       <c r="S3">
-        <v>10.89</v>
+        <v>10.87</v>
       </c>
       <c r="T3">
-        <v>-14.42</v>
+        <v>-13.54</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.68</v>
+        <v>29.49</v>
       </c>
       <c r="Z3">
-        <v>-0.28</v>
+        <v>-0.29</v>
       </c>
       <c r="AA3">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="AB3">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>24.95</v>
+        <v>26.49</v>
       </c>
       <c r="AD3">
-        <v>22.74</v>
+        <v>23.82</v>
       </c>
       <c r="AE3">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="AF3">
-        <v>-1.66</v>
+        <v>-8.5</v>
       </c>
       <c r="AG3">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
       <c r="AH3">
-        <v>9.31</v>
+        <v>9.23</v>
       </c>
       <c r="AI3">
         <v>10.28</v>
@@ -1108,7 +1142,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29.55</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,37 +1153,37 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="D4">
-        <v>-2.02</v>
+        <v>-0.24</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="G4">
-        <v>-32.52</v>
+        <v>-32.68</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-6.47</v>
+        <v>-6.61</v>
       </c>
       <c r="J4">
-        <v>-9.9</v>
+        <v>-10.51</v>
       </c>
       <c r="K4">
-        <v>-11.22</v>
+        <v>-11.67</v>
       </c>
       <c r="L4">
-        <v>-28.17</v>
+        <v>-27.94</v>
       </c>
       <c r="M4">
-        <v>-4.9</v>
+        <v>-4.96</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1158,19 +1192,19 @@
         <v>26</v>
       </c>
       <c r="P4">
-        <v>218.89</v>
+        <v>215.89</v>
       </c>
       <c r="Q4">
-        <v>227.99</v>
+        <v>226.71</v>
       </c>
       <c r="R4">
-        <v>239.5</v>
+        <v>239.08</v>
       </c>
       <c r="S4">
-        <v>249.03</v>
+        <v>248.59</v>
       </c>
       <c r="T4">
-        <v>-14.67</v>
+        <v>-14.72</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,43 +1219,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>23.09</v>
+        <v>22.73</v>
       </c>
       <c r="Z4">
-        <v>-5.99</v>
+        <v>-6.46</v>
       </c>
       <c r="AA4">
-        <v>-4.76</v>
+        <v>-5.1</v>
       </c>
       <c r="AB4">
-        <v>-1.23</v>
+        <v>-1.36</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>6.96</v>
+        <v>0.58</v>
       </c>
       <c r="AE4">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="AF4">
-        <v>138.04</v>
+        <v>27.5</v>
       </c>
       <c r="AG4">
-        <v>241.65</v>
+        <v>241.37</v>
       </c>
       <c r="AH4">
-        <v>214.32</v>
+        <v>212.06</v>
       </c>
       <c r="AI4">
-        <v>226.58</v>
+        <v>226.22</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>49.72</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1266,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>653.15</v>
+        <v>651.35</v>
       </c>
       <c r="D5">
-        <v>-1.95</v>
+        <v>-0.28</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1244,46 +1278,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-24.14</v>
+        <v>-24.35</v>
       </c>
       <c r="H5">
-        <v>33.11</v>
+        <v>32.74</v>
       </c>
       <c r="I5">
-        <v>-2.86</v>
+        <v>-3.1</v>
       </c>
       <c r="J5">
-        <v>-7.44</v>
+        <v>-6.66</v>
       </c>
       <c r="K5">
-        <v>18.79</v>
+        <v>18.99</v>
       </c>
       <c r="L5">
-        <v>-20.17</v>
+        <v>-21.6</v>
       </c>
       <c r="M5">
-        <v>-7.98</v>
+        <v>-7.89</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P5">
-        <v>661.39</v>
+        <v>657.22</v>
       </c>
       <c r="Q5">
-        <v>675.63</v>
+        <v>673.33</v>
       </c>
       <c r="R5">
-        <v>686.01</v>
+        <v>684.55</v>
       </c>
       <c r="S5">
-        <v>620.3</v>
+        <v>619.97</v>
       </c>
       <c r="T5">
-        <v>5.3</v>
+        <v>5.06</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1298,34 +1332,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>41.33</v>
+        <v>40.72</v>
       </c>
       <c r="Z5">
-        <v>-5.1</v>
+        <v>-6.09</v>
       </c>
       <c r="AA5">
-        <v>-2.55</v>
+        <v>-3.26</v>
       </c>
       <c r="AB5">
-        <v>-2.55</v>
+        <v>-2.84</v>
       </c>
       <c r="AC5">
         <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>10.62</v>
+        <v>10.5</v>
       </c>
       <c r="AE5">
-        <v>21.76</v>
+        <v>21.5</v>
       </c>
       <c r="AF5">
-        <v>-14.16</v>
+        <v>-45.06</v>
       </c>
       <c r="AG5">
-        <v>703.65</v>
+        <v>701.4</v>
       </c>
       <c r="AH5">
-        <v>647.62</v>
+        <v>645.27</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1334,7 +1368,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.92</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1379,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.43</v>
+        <v>25.44</v>
       </c>
       <c r="D6">
-        <v>-1.7</v>
+        <v>0.04</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1357,46 +1391,46 @@
         <v>25.43</v>
       </c>
       <c r="G6">
-        <v>-51.47</v>
+        <v>-51.45</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I6">
-        <v>-5.71</v>
+        <v>-4.9</v>
       </c>
       <c r="J6">
-        <v>-9.34</v>
+        <v>-6.61</v>
       </c>
       <c r="K6">
-        <v>-22.85</v>
+        <v>-21.63</v>
       </c>
       <c r="L6">
-        <v>-50.79</v>
+        <v>-50.69</v>
       </c>
       <c r="M6">
-        <v>-14.08</v>
+        <v>-16.35</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>25.98</v>
+        <v>25.72</v>
       </c>
       <c r="Q6">
-        <v>26.73</v>
+        <v>26.62</v>
       </c>
       <c r="R6">
-        <v>28.16</v>
+        <v>28.11</v>
       </c>
       <c r="S6">
-        <v>33.16</v>
+        <v>33.07</v>
       </c>
       <c r="T6">
-        <v>-23.32</v>
+        <v>-23.08</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1445,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>32.82</v>
+        <v>32.95</v>
       </c>
       <c r="Z6">
-        <v>-0.71</v>
+        <v>-0.73</v>
       </c>
       <c r="AA6">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="AB6">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="AC6">
-        <v>14.29</v>
+        <v>7.42</v>
       </c>
       <c r="AD6">
-        <v>26.22</v>
+        <v>15.04</v>
       </c>
       <c r="AE6">
         <v>0.84</v>
       </c>
       <c r="AF6">
-        <v>-14.08</v>
+        <v>-39.28</v>
       </c>
       <c r="AG6">
-        <v>28.15</v>
+        <v>28.1</v>
       </c>
       <c r="AH6">
-        <v>25.3</v>
+        <v>25.14</v>
       </c>
       <c r="AI6">
         <v>28.03</v>
@@ -1447,7 +1481,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>34.41</v>
+        <v>35.81</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1492,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1167.7</v>
+        <v>1186.4</v>
       </c>
       <c r="D7">
-        <v>-1.63</v>
+        <v>1.6</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,46 +1504,46 @@
         <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-26.33</v>
+        <v>-25.15</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I7">
-        <v>-4.22</v>
+        <v>-3.23</v>
       </c>
       <c r="J7">
-        <v>-10.79</v>
+        <v>-9.65</v>
       </c>
       <c r="K7">
-        <v>-10.45</v>
+        <v>-10.21</v>
       </c>
       <c r="L7">
-        <v>-14.84</v>
+        <v>-13.18</v>
       </c>
       <c r="M7">
-        <v>0.43</v>
+        <v>0.08</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>1192.06</v>
+        <v>1184.14</v>
       </c>
       <c r="Q7">
-        <v>1245.02</v>
+        <v>1239.21</v>
       </c>
       <c r="R7">
-        <v>1280.06</v>
+        <v>1278.34</v>
       </c>
       <c r="S7">
-        <v>1358.77</v>
+        <v>1356.95</v>
       </c>
       <c r="T7">
-        <v>-14.06</v>
+        <v>-12.57</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,34 +1558,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>28.15</v>
+        <v>34.94</v>
       </c>
       <c r="Z7">
-        <v>-29.32</v>
+        <v>-29.45</v>
       </c>
       <c r="AA7">
-        <v>-22.19</v>
+        <v>-23.64</v>
       </c>
       <c r="AB7">
-        <v>-7.13</v>
+        <v>-5.81</v>
       </c>
       <c r="AC7">
-        <v>5.26</v>
+        <v>22.39</v>
       </c>
       <c r="AD7">
-        <v>6.55</v>
+        <v>10.97</v>
       </c>
       <c r="AE7">
-        <v>20.67</v>
+        <v>21</v>
       </c>
       <c r="AF7">
-        <v>36.89</v>
+        <v>15.22</v>
       </c>
       <c r="AG7">
-        <v>1331</v>
+        <v>1324.53</v>
       </c>
       <c r="AH7">
-        <v>1159.03</v>
+        <v>1153.89</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1560,7 +1594,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>65.64</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +1735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1721,855 +1755,910 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-8.5</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-7.68</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-11.18</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-11.24</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-9.09</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.14</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-9.9</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D10" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-7.44</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.66</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-9.34</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-6.61</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.79</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-4.19</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-6.43</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.47</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-6.61</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.9</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-4.22</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-24.22</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-22.04</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-34.32</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-31.39</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-28.17</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-27.94</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-20.17</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-21.6</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-50.79</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-50.69</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-14.84</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-13.18</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-14.56</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-12.1</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-17.52</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-15.7</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-11.22</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-11.67</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>18.79</v>
+      </c>
+      <c r="D29" s="6">
+        <v>18.99</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-22.85</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-21.63</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-10.45</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E31" s="7">
         <v>0.24</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-27.87</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-27.02</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-34.55</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-33.99</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-32.52</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-32.68</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-6.2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-7.44</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-24.14</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-24.35</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-4.99</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-9.34</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-51.47</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-51.45</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-7.05</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-10.79</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-3.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-26.33</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-25.15</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-4.19</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>25.41</v>
+      </c>
+      <c r="D38" s="6">
+        <v>25.71</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-6.44</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-6.43</v>
-      </c>
-      <c r="E14" s="7">
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>9.32</v>
+      </c>
+      <c r="D39" s="6">
+        <v>9.4</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>212.5</v>
+      </c>
+      <c r="D40" s="6">
+        <v>212</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>653.15</v>
+      </c>
+      <c r="D41" s="6">
+        <v>651.35</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>25.43</v>
+      </c>
+      <c r="D42" s="6">
+        <v>25.44</v>
+      </c>
+      <c r="E42" s="7">
         <v>0.01</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1167.7</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1186.4</v>
+      </c>
+      <c r="E43" s="7">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="6">
+        <v>28.15</v>
+      </c>
+      <c r="D44" s="6">
+        <v>34.49</v>
+      </c>
+      <c r="E44" s="7">
+        <v>6.34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6">
+        <v>25.68</v>
+      </c>
+      <c r="D45" s="6">
+        <v>29.49</v>
+      </c>
+      <c r="E45" s="7">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.58</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-6.47</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>23.09</v>
+      </c>
+      <c r="D46" s="6">
+        <v>22.73</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-3.95</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.86</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>41.33</v>
+      </c>
+      <c r="D47" s="6">
+        <v>40.72</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-4.68</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-5.71</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>32.82</v>
+      </c>
+      <c r="D48" s="6">
+        <v>32.95</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-4.89</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-4.22</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>28.15</v>
+      </c>
+      <c r="D49" s="6">
+        <v>34.94</v>
+      </c>
+      <c r="E49" s="7">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-24.45</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-24.22</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="6">
+        <v>8.92</v>
+      </c>
+      <c r="D50" s="6">
+        <v>24.09</v>
+      </c>
+      <c r="E50" s="7">
+        <v>15.17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-34.01</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-34.32</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-1.66</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-8.5</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-6.84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-28.09</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-28.17</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>138.04</v>
+      </c>
+      <c r="D52" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-110.54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-18.78</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-20.17</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-14.16</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-45.06</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-30.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-51.41</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-50.79</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-14.08</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-39.28</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-13.11</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-13.04</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-14.56</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-17.18</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-17.52</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-11.22</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>19.93</v>
-      </c>
-      <c r="D28" s="5">
-        <v>18.79</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-21.87</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-22.85</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-8.94</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.45</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-26.4</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-27.87</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-33.64</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-34.55</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-31.13</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-32.52</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-22.63</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-24.14</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-50.63</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-51.47</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-25.11</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-26.33</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>25.93</v>
-      </c>
-      <c r="D37" s="5">
-        <v>25.41</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.32</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>216.88</v>
-      </c>
-      <c r="D39" s="5">
-        <v>212.5</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-4.38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>666.15</v>
-      </c>
-      <c r="D40" s="5">
-        <v>653.15</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>25.87</v>
-      </c>
-      <c r="D41" s="5">
-        <v>25.43</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1187</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1167.7</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-19.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>33.34</v>
-      </c>
-      <c r="D43" s="5">
-        <v>28.15</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-5.19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>27.96</v>
-      </c>
-      <c r="D44" s="5">
-        <v>25.68</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>26.44</v>
-      </c>
-      <c r="D45" s="5">
-        <v>23.09</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46.01</v>
-      </c>
-      <c r="D46" s="5">
-        <v>41.33</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-4.68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>35.76</v>
-      </c>
-      <c r="D47" s="5">
-        <v>32.82</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-2.94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>31.28</v>
-      </c>
-      <c r="D48" s="5">
-        <v>28.15</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B55" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>-3.74</v>
-      </c>
-      <c r="D49" s="5">
-        <v>8.92</v>
-      </c>
-      <c r="E49" s="7">
-        <v>12.66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>3.2</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-1.66</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-4.86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>17.67</v>
-      </c>
-      <c r="D51" s="5">
-        <v>138.04</v>
-      </c>
-      <c r="E51" s="7">
-        <v>120.37</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-42.89</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-14.16</v>
-      </c>
-      <c r="E52" s="7">
-        <v>28.73</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-51.21</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-14.08</v>
-      </c>
-      <c r="E53" s="7">
-        <v>37.13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>25.4</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C55" s="6">
         <v>36.89</v>
       </c>
-      <c r="E54" s="7">
-        <v>11.49</v>
+      <c r="D55" s="6">
+        <v>15.22</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-21.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2589,60 +2678,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>29.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2744,43 +2833,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>0.0043</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.049</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.07980000000000001</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1211</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1408</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1794</v>
+      <c r="A2" s="14">
+        <v>0.0008</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0496</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.0789</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1277</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1635</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1872</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,22 +187,25 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.1 → 34.5</t>
+    <t>29.5 → 44.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>28.1</t>
-  </si>
-  <si>
-    <t>34.5</t>
-  </si>
-  <si>
-    <t>28.1 → 34.9</t>
-  </si>
-  <si>
-    <t>34.9</t>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>22.7 → 35.4</t>
+  </si>
+  <si>
+    <t>22.7</t>
+  </si>
+  <si>
+    <t>35.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -927,10 +930,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.71</v>
+        <v>25.78</v>
       </c>
       <c r="D2">
-        <v>1.18</v>
+        <v>0.27</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -939,25 +942,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.02</v>
+        <v>-26.82</v>
       </c>
       <c r="H2">
-        <v>11.88</v>
+        <v>12.18</v>
       </c>
       <c r="I2">
-        <v>-2.54</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>-7.68</v>
+        <v>-7.5</v>
       </c>
       <c r="K2">
-        <v>-12.1</v>
+        <v>-10.55</v>
       </c>
       <c r="L2">
-        <v>-22.04</v>
+        <v>-21.93</v>
       </c>
       <c r="M2">
-        <v>-12.77</v>
+        <v>-12.32</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -966,19 +969,19 @@
         <v>32</v>
       </c>
       <c r="P2">
-        <v>25.79</v>
+        <v>25.75</v>
       </c>
       <c r="Q2">
-        <v>26.59</v>
+        <v>26.48</v>
       </c>
       <c r="R2">
-        <v>27.2</v>
+        <v>27.18</v>
       </c>
       <c r="S2">
-        <v>28.1</v>
+        <v>28.07</v>
       </c>
       <c r="T2">
-        <v>-8.5</v>
+        <v>-8.16</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -993,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.49</v>
+        <v>35.91</v>
       </c>
       <c r="Z2">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="AA2">
-        <v>-0.4</v>
+        <v>-0.42</v>
       </c>
       <c r="AB2">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>17.84</v>
+        <v>29.64</v>
       </c>
       <c r="AD2">
-        <v>13.11</v>
+        <v>18.43</v>
       </c>
       <c r="AE2">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="AF2">
-        <v>24.09</v>
+        <v>64</v>
       </c>
       <c r="AG2">
-        <v>27.92</v>
+        <v>27.69</v>
       </c>
       <c r="AH2">
-        <v>25.26</v>
+        <v>25.27</v>
       </c>
       <c r="AI2">
-        <v>27.67</v>
+        <v>27.51</v>
       </c>
       <c r="AJ2" t="s">
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>46.7</v>
+        <v>51.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1043,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D3">
-        <v>0.86</v>
+        <v>4.26</v>
       </c>
       <c r="E3">
         <v>14.24</v>
@@ -1052,46 +1055,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.99</v>
+        <v>-31.18</v>
       </c>
       <c r="H3">
-        <v>5.98</v>
+        <v>10.48</v>
       </c>
       <c r="I3">
-        <v>-5.34</v>
+        <v>4.59</v>
       </c>
       <c r="J3">
-        <v>-9.09</v>
+        <v>-4.48</v>
       </c>
       <c r="K3">
-        <v>-15.7</v>
+        <v>-11.63</v>
       </c>
       <c r="L3">
-        <v>-31.39</v>
+        <v>-29.95</v>
       </c>
       <c r="M3">
-        <v>-18.72</v>
+        <v>-17.38</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="P3">
-        <v>9.41</v>
+        <v>9.49</v>
       </c>
       <c r="Q3">
-        <v>9.94</v>
+        <v>9.9</v>
       </c>
       <c r="R3">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="S3">
-        <v>10.87</v>
+        <v>10.86</v>
       </c>
       <c r="T3">
-        <v>-13.54</v>
+        <v>-9.75</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1106,34 +1109,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.49</v>
+        <v>44.76</v>
       </c>
       <c r="Z3">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
       <c r="AA3">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>26.49</v>
+        <v>50.51</v>
       </c>
       <c r="AD3">
-        <v>23.82</v>
+        <v>33.98</v>
       </c>
       <c r="AE3">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="AF3">
-        <v>-8.5</v>
+        <v>55.89</v>
       </c>
       <c r="AG3">
-        <v>10.64</v>
+        <v>10.55</v>
       </c>
       <c r="AH3">
-        <v>9.23</v>
+        <v>9.25</v>
       </c>
       <c r="AI3">
         <v>10.28</v>
@@ -1142,7 +1145,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>25.67</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1156,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>212</v>
+        <v>217.9</v>
       </c>
       <c r="D4">
-        <v>-0.24</v>
+        <v>2.78</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1165,25 +1168,25 @@
         <v>212</v>
       </c>
       <c r="G4">
-        <v>-32.68</v>
+        <v>-30.8</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="I4">
-        <v>-6.61</v>
+        <v>-1.18</v>
       </c>
       <c r="J4">
-        <v>-10.51</v>
+        <v>-8.23</v>
       </c>
       <c r="K4">
-        <v>-11.67</v>
+        <v>-10.36</v>
       </c>
       <c r="L4">
-        <v>-27.94</v>
+        <v>-25.68</v>
       </c>
       <c r="M4">
-        <v>-4.96</v>
+        <v>-4.12</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1192,19 +1195,19 @@
         <v>26</v>
       </c>
       <c r="P4">
-        <v>215.89</v>
+        <v>215.37</v>
       </c>
       <c r="Q4">
-        <v>226.71</v>
+        <v>225.63</v>
       </c>
       <c r="R4">
-        <v>239.08</v>
+        <v>238.74</v>
       </c>
       <c r="S4">
-        <v>248.59</v>
+        <v>248.21</v>
       </c>
       <c r="T4">
-        <v>-14.72</v>
+        <v>-12.21</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1219,34 +1222,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>22.73</v>
+        <v>35.35</v>
       </c>
       <c r="Z4">
-        <v>-6.46</v>
+        <v>-6.28</v>
       </c>
       <c r="AA4">
-        <v>-5.1</v>
+        <v>-5.33</v>
       </c>
       <c r="AB4">
-        <v>-1.36</v>
+        <v>-0.95</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>19.98</v>
       </c>
       <c r="AD4">
-        <v>0.58</v>
+        <v>6.66</v>
       </c>
       <c r="AE4">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="AF4">
-        <v>27.5</v>
+        <v>32.1</v>
       </c>
       <c r="AG4">
-        <v>241.37</v>
+        <v>239.49</v>
       </c>
       <c r="AH4">
-        <v>212.06</v>
+        <v>211.78</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1255,7 +1258,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>53.65</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1269,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>651.35</v>
+        <v>658.95</v>
       </c>
       <c r="D5">
-        <v>-0.28</v>
+        <v>1.17</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1278,46 +1281,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-24.35</v>
+        <v>-23.46</v>
       </c>
       <c r="H5">
-        <v>32.74</v>
+        <v>34.29</v>
       </c>
       <c r="I5">
-        <v>-3.1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-6.66</v>
+        <v>-5.51</v>
       </c>
       <c r="K5">
-        <v>18.99</v>
+        <v>18.74</v>
       </c>
       <c r="L5">
-        <v>-21.6</v>
+        <v>-20.53</v>
       </c>
       <c r="M5">
-        <v>-7.89</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P5">
         <v>657.22</v>
       </c>
       <c r="Q5">
-        <v>673.33</v>
+        <v>671.64</v>
       </c>
       <c r="R5">
-        <v>684.55</v>
+        <v>683.15</v>
       </c>
       <c r="S5">
-        <v>619.97</v>
+        <v>619.72</v>
       </c>
       <c r="T5">
-        <v>5.06</v>
+        <v>6.33</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1332,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>40.72</v>
+        <v>44.48</v>
       </c>
       <c r="Z5">
-        <v>-6.09</v>
+        <v>-6.2</v>
       </c>
       <c r="AA5">
-        <v>-3.26</v>
+        <v>-3.84</v>
       </c>
       <c r="AB5">
-        <v>-2.84</v>
+        <v>-2.35</v>
       </c>
       <c r="AC5">
-        <v>10.5</v>
+        <v>8.25</v>
       </c>
       <c r="AD5">
-        <v>10.5</v>
+        <v>9.75</v>
       </c>
       <c r="AE5">
-        <v>21.5</v>
+        <v>20.82</v>
       </c>
       <c r="AF5">
-        <v>-45.06</v>
+        <v>-57.52</v>
       </c>
       <c r="AG5">
-        <v>701.4</v>
+        <v>698.8200000000001</v>
       </c>
       <c r="AH5">
-        <v>645.27</v>
+        <v>644.46</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1368,7 +1371,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>22.98</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1382,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.44</v>
+        <v>26.22</v>
       </c>
       <c r="D6">
-        <v>0.04</v>
+        <v>3.07</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1391,46 +1394,46 @@
         <v>25.43</v>
       </c>
       <c r="G6">
-        <v>-51.45</v>
+        <v>-49.96</v>
       </c>
       <c r="H6">
-        <v>0.04</v>
+        <v>3.11</v>
       </c>
       <c r="I6">
-        <v>-4.9</v>
+        <v>0.92</v>
       </c>
       <c r="J6">
-        <v>-6.61</v>
+        <v>-4.83</v>
       </c>
       <c r="K6">
-        <v>-21.63</v>
+        <v>-17.83</v>
       </c>
       <c r="L6">
-        <v>-50.69</v>
+        <v>-49.04</v>
       </c>
       <c r="M6">
-        <v>-16.35</v>
+        <v>-15.22</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>25.72</v>
+        <v>25.77</v>
       </c>
       <c r="Q6">
-        <v>26.62</v>
+        <v>26.51</v>
       </c>
       <c r="R6">
-        <v>28.11</v>
+        <v>28.06</v>
       </c>
       <c r="S6">
-        <v>33.07</v>
+        <v>32.99</v>
       </c>
       <c r="T6">
-        <v>-23.08</v>
+        <v>-20.53</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1445,34 +1448,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>32.95</v>
+        <v>42.63</v>
       </c>
       <c r="Z6">
-        <v>-0.73</v>
+        <v>-0.68</v>
       </c>
       <c r="AA6">
         <v>-0.68</v>
       </c>
       <c r="AB6">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>7.42</v>
+        <v>27.63</v>
       </c>
       <c r="AD6">
-        <v>15.04</v>
+        <v>16.45</v>
       </c>
       <c r="AE6">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="AF6">
-        <v>-39.28</v>
+        <v>-27.28</v>
       </c>
       <c r="AG6">
-        <v>28.1</v>
+        <v>27.75</v>
       </c>
       <c r="AH6">
-        <v>25.14</v>
+        <v>25.27</v>
       </c>
       <c r="AI6">
         <v>28.03</v>
@@ -1481,7 +1484,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>35.81</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1495,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1186.4</v>
+        <v>1218</v>
       </c>
       <c r="D7">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1504,46 +1507,46 @@
         <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-25.15</v>
+        <v>-23.15</v>
       </c>
       <c r="H7">
-        <v>1.6</v>
+        <v>4.31</v>
       </c>
       <c r="I7">
-        <v>-3.23</v>
+        <v>1.7</v>
       </c>
       <c r="J7">
-        <v>-9.65</v>
+        <v>-6.49</v>
       </c>
       <c r="K7">
-        <v>-10.21</v>
+        <v>-6.91</v>
       </c>
       <c r="L7">
-        <v>-13.18</v>
+        <v>-10.29</v>
       </c>
       <c r="M7">
-        <v>0.08</v>
+        <v>0.99</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>1184.14</v>
+        <v>1188.22</v>
       </c>
       <c r="Q7">
-        <v>1239.21</v>
+        <v>1234.01</v>
       </c>
       <c r="R7">
-        <v>1278.34</v>
+        <v>1277.14</v>
       </c>
       <c r="S7">
-        <v>1356.95</v>
+        <v>1355.37</v>
       </c>
       <c r="T7">
-        <v>-12.57</v>
+        <v>-10.14</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1558,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.94</v>
+        <v>44.49</v>
       </c>
       <c r="Z7">
-        <v>-29.45</v>
+        <v>-26.69</v>
       </c>
       <c r="AA7">
-        <v>-23.64</v>
+        <v>-24.25</v>
       </c>
       <c r="AB7">
-        <v>-5.81</v>
+        <v>-2.44</v>
       </c>
       <c r="AC7">
-        <v>22.39</v>
+        <v>50.47</v>
       </c>
       <c r="AD7">
-        <v>10.97</v>
+        <v>26.04</v>
       </c>
       <c r="AE7">
-        <v>21</v>
+        <v>21.84</v>
       </c>
       <c r="AF7">
-        <v>15.22</v>
+        <v>45.06</v>
       </c>
       <c r="AG7">
-        <v>1324.53</v>
+        <v>1310.28</v>
       </c>
       <c r="AH7">
-        <v>1153.89</v>
+        <v>1157.74</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1594,7 +1597,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>65.45999999999999</v>
+        <v>59.01</v>
       </c>
     </row>
   </sheetData>
@@ -1775,7 +1778,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1795,7 +1798,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>54</v>
@@ -1807,15 +1810,15 @@
         <v>56</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1827,16 +1830,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1847,13 +1850,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-8.5</v>
+        <v>-7.68</v>
       </c>
       <c r="D8" s="6">
-        <v>-7.68</v>
+        <v>-7.5</v>
       </c>
       <c r="E8" s="7">
-        <v>0.82</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1864,13 +1867,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.24</v>
+        <v>-9.09</v>
       </c>
       <c r="D9" s="6">
-        <v>-9.09</v>
+        <v>-4.48</v>
       </c>
       <c r="E9" s="7">
-        <v>2.15</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1881,13 +1884,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-9.9</v>
+        <v>-10.51</v>
       </c>
       <c r="D10" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.61</v>
+        <v>-8.23</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1898,13 +1901,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-7.44</v>
+        <v>-6.66</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.66</v>
+        <v>-5.51</v>
       </c>
       <c r="E11" s="7">
-        <v>0.78</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1915,13 +1918,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.34</v>
+        <v>-6.61</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.61</v>
+        <v>-4.83</v>
       </c>
       <c r="E12" s="7">
-        <v>2.73</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1932,13 +1935,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.79</v>
+        <v>-9.65</v>
       </c>
       <c r="D13" s="6">
-        <v>-9.65</v>
+        <v>-6.49</v>
       </c>
       <c r="E13" s="7">
-        <v>1.14</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1949,13 +1952,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.19</v>
+        <v>-2.54</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.54</v>
+        <v>-0.85</v>
       </c>
       <c r="E14" s="7">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1966,13 +1969,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.43</v>
+        <v>-5.34</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.34</v>
+        <v>4.59</v>
       </c>
       <c r="E15" s="7">
-        <v>1.09</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1983,13 +1986,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.47</v>
+        <v>-6.61</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.14</v>
+        <v>-1.18</v>
+      </c>
+      <c r="E16" s="7">
+        <v>5.43</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2000,13 +2003,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.86</v>
+        <v>-3.1</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.24</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2017,13 +2020,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.71</v>
+        <v>-4.9</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.9</v>
+        <v>0.92</v>
       </c>
       <c r="E18" s="7">
-        <v>0.8100000000000001</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2034,13 +2037,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.22</v>
+        <v>-3.23</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.23</v>
+        <v>1.7</v>
       </c>
       <c r="E19" s="7">
-        <v>0.99</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2051,13 +2054,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-24.22</v>
+        <v>-22.04</v>
       </c>
       <c r="D20" s="6">
-        <v>-22.04</v>
+        <v>-21.93</v>
       </c>
       <c r="E20" s="7">
-        <v>2.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2068,13 +2071,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-34.32</v>
+        <v>-31.39</v>
       </c>
       <c r="D21" s="6">
-        <v>-31.39</v>
+        <v>-29.95</v>
       </c>
       <c r="E21" s="7">
-        <v>2.93</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2085,13 +2088,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-28.17</v>
+        <v>-27.94</v>
       </c>
       <c r="D22" s="6">
-        <v>-27.94</v>
+        <v>-25.68</v>
       </c>
       <c r="E22" s="7">
-        <v>0.23</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2102,13 +2105,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-20.17</v>
+        <v>-21.6</v>
       </c>
       <c r="D23" s="6">
-        <v>-21.6</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.43</v>
+        <v>-20.53</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2119,13 +2122,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-50.79</v>
+        <v>-50.69</v>
       </c>
       <c r="D24" s="6">
-        <v>-50.69</v>
+        <v>-49.04</v>
       </c>
       <c r="E24" s="7">
-        <v>0.1</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2136,13 +2139,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-14.84</v>
+        <v>-13.18</v>
       </c>
       <c r="D25" s="6">
-        <v>-13.18</v>
+        <v>-10.29</v>
       </c>
       <c r="E25" s="7">
-        <v>1.66</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2153,13 +2156,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-14.56</v>
+        <v>-12.1</v>
       </c>
       <c r="D26" s="6">
-        <v>-12.1</v>
+        <v>-10.55</v>
       </c>
       <c r="E26" s="7">
-        <v>2.46</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2170,13 +2173,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-17.52</v>
+        <v>-15.7</v>
       </c>
       <c r="D27" s="6">
-        <v>-15.7</v>
+        <v>-11.63</v>
       </c>
       <c r="E27" s="7">
-        <v>1.82</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2187,13 +2190,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-11.22</v>
+        <v>-11.67</v>
       </c>
       <c r="D28" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.45</v>
+        <v>-10.36</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.31</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2204,13 +2207,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>18.79</v>
+        <v>18.99</v>
       </c>
       <c r="D29" s="6">
-        <v>18.99</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.2</v>
+        <v>18.74</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2221,13 +2224,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-22.85</v>
+        <v>-21.63</v>
       </c>
       <c r="D30" s="6">
-        <v>-21.63</v>
+        <v>-17.83</v>
       </c>
       <c r="E30" s="7">
-        <v>1.22</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2238,13 +2241,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-10.45</v>
+        <v>-10.21</v>
       </c>
       <c r="D31" s="6">
-        <v>-10.21</v>
+        <v>-6.91</v>
       </c>
       <c r="E31" s="7">
-        <v>0.24</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2255,13 +2258,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-27.87</v>
+        <v>-27.02</v>
       </c>
       <c r="D32" s="6">
-        <v>-27.02</v>
+        <v>-26.82</v>
       </c>
       <c r="E32" s="7">
-        <v>0.85</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2272,13 +2275,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-34.55</v>
+        <v>-33.99</v>
       </c>
       <c r="D33" s="6">
-        <v>-33.99</v>
+        <v>-31.18</v>
       </c>
       <c r="E33" s="7">
-        <v>0.5600000000000001</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2289,13 +2292,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-32.52</v>
+        <v>-32.68</v>
       </c>
       <c r="D34" s="6">
-        <v>-32.68</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.16</v>
+        <v>-30.8</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2306,13 +2309,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-24.14</v>
+        <v>-24.35</v>
       </c>
       <c r="D35" s="6">
-        <v>-24.35</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.21</v>
+        <v>-23.46</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2323,13 +2326,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-51.47</v>
+        <v>-51.45</v>
       </c>
       <c r="D36" s="6">
-        <v>-51.45</v>
+        <v>-49.96</v>
       </c>
       <c r="E36" s="7">
-        <v>0.02</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2340,13 +2343,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-26.33</v>
+        <v>-25.15</v>
       </c>
       <c r="D37" s="6">
-        <v>-25.15</v>
+        <v>-23.15</v>
       </c>
       <c r="E37" s="7">
-        <v>1.18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2357,13 +2360,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>25.41</v>
+        <v>25.71</v>
       </c>
       <c r="D38" s="6">
-        <v>25.71</v>
+        <v>25.78</v>
       </c>
       <c r="E38" s="7">
-        <v>0.3</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2374,13 +2377,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>9.32</v>
+        <v>9.4</v>
       </c>
       <c r="D39" s="6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E39" s="7">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2391,13 +2394,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>212.5</v>
+        <v>212</v>
       </c>
       <c r="D40" s="6">
-        <v>212</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.5</v>
+        <v>217.9</v>
+      </c>
+      <c r="E40" s="7">
+        <v>5.9</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2408,13 +2411,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>653.15</v>
+        <v>651.35</v>
       </c>
       <c r="D41" s="6">
-        <v>651.35</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.8</v>
+        <v>658.95</v>
+      </c>
+      <c r="E41" s="7">
+        <v>7.6</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2425,13 +2428,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>25.43</v>
+        <v>25.44</v>
       </c>
       <c r="D42" s="6">
-        <v>25.44</v>
+        <v>26.22</v>
       </c>
       <c r="E42" s="7">
-        <v>0.01</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2442,13 +2445,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>1167.7</v>
+        <v>1186.4</v>
       </c>
       <c r="D43" s="6">
-        <v>1186.4</v>
+        <v>1218</v>
       </c>
       <c r="E43" s="7">
-        <v>18.7</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2459,13 +2462,13 @@
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>28.15</v>
+        <v>34.49</v>
       </c>
       <c r="D44" s="6">
-        <v>34.49</v>
+        <v>35.91</v>
       </c>
       <c r="E44" s="7">
-        <v>6.34</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2476,13 +2479,13 @@
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>25.68</v>
+        <v>29.49</v>
       </c>
       <c r="D45" s="6">
-        <v>29.49</v>
+        <v>44.76</v>
       </c>
       <c r="E45" s="7">
-        <v>3.81</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2493,13 +2496,13 @@
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>23.09</v>
+        <v>22.73</v>
       </c>
       <c r="D46" s="6">
-        <v>22.73</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.36</v>
+        <v>35.35</v>
+      </c>
+      <c r="E46" s="7">
+        <v>12.62</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2510,13 +2513,13 @@
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>41.33</v>
+        <v>40.72</v>
       </c>
       <c r="D47" s="6">
-        <v>40.72</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.61</v>
+        <v>44.48</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.76</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2527,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>32.82</v>
+        <v>32.95</v>
       </c>
       <c r="D48" s="6">
-        <v>32.95</v>
+        <v>42.63</v>
       </c>
       <c r="E48" s="7">
-        <v>0.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2544,13 +2547,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>28.15</v>
+        <v>34.94</v>
       </c>
       <c r="D49" s="6">
-        <v>34.94</v>
+        <v>44.49</v>
       </c>
       <c r="E49" s="7">
-        <v>6.79</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2561,13 +2564,13 @@
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>8.92</v>
+        <v>24.09</v>
       </c>
       <c r="D50" s="6">
-        <v>24.09</v>
+        <v>64</v>
       </c>
       <c r="E50" s="7">
-        <v>15.17</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2578,13 +2581,13 @@
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-1.66</v>
+        <v>-8.5</v>
       </c>
       <c r="D51" s="6">
-        <v>-8.5</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-6.84</v>
+        <v>55.89</v>
+      </c>
+      <c r="E51" s="7">
+        <v>64.39</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2595,13 +2598,13 @@
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>138.04</v>
+        <v>27.5</v>
       </c>
       <c r="D52" s="6">
-        <v>27.5</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-110.54</v>
+        <v>32.1</v>
+      </c>
+      <c r="E52" s="7">
+        <v>4.6</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2612,13 +2615,13 @@
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-14.16</v>
+        <v>-45.06</v>
       </c>
       <c r="D53" s="6">
-        <v>-45.06</v>
+        <v>-57.52</v>
       </c>
       <c r="E53" s="8">
-        <v>-30.9</v>
+        <v>-12.46</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2629,13 +2632,13 @@
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-14.08</v>
+        <v>-39.28</v>
       </c>
       <c r="D54" s="6">
-        <v>-39.28</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-25.2</v>
+        <v>-27.28</v>
+      </c>
+      <c r="E54" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2646,13 +2649,13 @@
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>36.89</v>
+        <v>15.22</v>
       </c>
       <c r="D55" s="6">
-        <v>15.22</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-21.67</v>
+        <v>45.06</v>
+      </c>
+      <c r="E55" s="7">
+        <v>29.84</v>
       </c>
     </row>
   </sheetData>
@@ -2682,28 +2685,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2717,16 +2720,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>32.6</v>
+        <v>41.3</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.4</v>
+        <v>-6.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.699999999999999</v>
+        <v>-6.4</v>
       </c>
       <c r="H2" s="11">
         <v>58.2</v>
@@ -2854,22 +2857,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0008</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0496</v>
+        <v>-0.0412</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0789</v>
+        <v>-0.08220000000000001</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1277</v>
+        <v>-0.1232</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1635</v>
+        <v>-0.1522</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.1872</v>
+        <v>-0.1738</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,43 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.5 → 44.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>44.8</t>
-  </si>
-  <si>
-    <t>22.7 → 35.4</t>
-  </si>
-  <si>
-    <t>22.7</t>
-  </si>
-  <si>
-    <t>35.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -790,7 +753,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -930,10 +895,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.78</v>
+        <v>26.1</v>
       </c>
       <c r="D2">
-        <v>0.27</v>
+        <v>1.24</v>
       </c>
       <c r="E2">
         <v>35.23</v>
@@ -942,46 +907,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.82</v>
+        <v>-25.92</v>
       </c>
       <c r="H2">
-        <v>12.18</v>
+        <v>13.58</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>0.73</v>
       </c>
       <c r="J2">
-        <v>-7.5</v>
+        <v>-6.69</v>
       </c>
       <c r="K2">
-        <v>-10.55</v>
+        <v>-6.75</v>
       </c>
       <c r="L2">
-        <v>-21.93</v>
+        <v>-23.24</v>
       </c>
       <c r="M2">
-        <v>-12.32</v>
+        <v>-12.18</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P2">
-        <v>25.75</v>
+        <v>25.79</v>
       </c>
       <c r="Q2">
-        <v>26.48</v>
+        <v>26.39</v>
       </c>
       <c r="R2">
-        <v>27.18</v>
+        <v>27.15</v>
       </c>
       <c r="S2">
-        <v>28.07</v>
+        <v>28.05</v>
       </c>
       <c r="T2">
-        <v>-8.16</v>
+        <v>-6.94</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -996,34 +961,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>35.91</v>
+        <v>42.09</v>
       </c>
       <c r="Z2">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="AA2">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AC2">
-        <v>29.64</v>
+        <v>58.96</v>
       </c>
       <c r="AD2">
-        <v>18.43</v>
+        <v>35.48</v>
       </c>
       <c r="AE2">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="AF2">
-        <v>64</v>
+        <v>-25.98</v>
       </c>
       <c r="AG2">
-        <v>27.69</v>
+        <v>27.41</v>
       </c>
       <c r="AH2">
-        <v>25.27</v>
+        <v>25.37</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1032,7 +997,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>51.01</v>
+        <v>52.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1008,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D3">
-        <v>4.26</v>
+        <v>-1.63</v>
       </c>
       <c r="E3">
         <v>14.24</v>
@@ -1055,46 +1020,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.18</v>
+        <v>-32.3</v>
       </c>
       <c r="H3">
-        <v>10.48</v>
+        <v>8.68</v>
       </c>
       <c r="I3">
-        <v>4.59</v>
+        <v>1.58</v>
       </c>
       <c r="J3">
-        <v>-4.48</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="K3">
-        <v>-11.63</v>
+        <v>-10.66</v>
       </c>
       <c r="L3">
-        <v>-29.95</v>
+        <v>-31.29</v>
       </c>
       <c r="M3">
-        <v>-17.38</v>
+        <v>-17.97</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P3">
-        <v>9.49</v>
+        <v>9.52</v>
       </c>
       <c r="Q3">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R3">
-        <v>10.36</v>
+        <v>10.34</v>
       </c>
       <c r="S3">
-        <v>10.86</v>
+        <v>10.84</v>
       </c>
       <c r="T3">
-        <v>-9.75</v>
+        <v>-11.11</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1109,31 +1074,31 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>44.76</v>
+        <v>40.94</v>
       </c>
       <c r="Z3">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AA3">
         <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AC3">
-        <v>50.51</v>
+        <v>73.03</v>
       </c>
       <c r="AD3">
-        <v>33.98</v>
+        <v>50.01</v>
       </c>
       <c r="AE3">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="AF3">
-        <v>55.89</v>
+        <v>7.27</v>
       </c>
       <c r="AG3">
-        <v>10.55</v>
+        <v>10.48</v>
       </c>
       <c r="AH3">
         <v>9.25</v>
@@ -1145,7 +1110,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>26.09</v>
+        <v>26.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1121,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>217.9</v>
+        <v>216.44</v>
       </c>
       <c r="D4">
-        <v>2.78</v>
+        <v>-0.67</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1168,46 +1133,46 @@
         <v>212</v>
       </c>
       <c r="G4">
-        <v>-30.8</v>
+        <v>-31.27</v>
       </c>
       <c r="H4">
-        <v>2.78</v>
+        <v>2.09</v>
       </c>
       <c r="I4">
-        <v>-1.18</v>
+        <v>-0.51</v>
       </c>
       <c r="J4">
-        <v>-8.23</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K4">
-        <v>-10.36</v>
+        <v>-5.89</v>
       </c>
       <c r="L4">
-        <v>-25.68</v>
+        <v>-27.87</v>
       </c>
       <c r="M4">
-        <v>-4.12</v>
+        <v>-4.32</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>215.37</v>
+        <v>215.14</v>
       </c>
       <c r="Q4">
-        <v>225.63</v>
+        <v>224.74</v>
       </c>
       <c r="R4">
-        <v>238.74</v>
+        <v>238.35</v>
       </c>
       <c r="S4">
-        <v>248.21</v>
+        <v>247.82</v>
       </c>
       <c r="T4">
-        <v>-12.21</v>
+        <v>-12.66</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1222,34 +1187,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.35</v>
+        <v>33.88</v>
       </c>
       <c r="Z4">
-        <v>-6.28</v>
+        <v>-6.19</v>
       </c>
       <c r="AA4">
-        <v>-5.33</v>
+        <v>-5.51</v>
       </c>
       <c r="AB4">
-        <v>-0.95</v>
+        <v>-0.68</v>
       </c>
       <c r="AC4">
-        <v>19.98</v>
+        <v>37.62</v>
       </c>
       <c r="AD4">
-        <v>6.66</v>
+        <v>19.2</v>
       </c>
       <c r="AE4">
-        <v>4.87</v>
+        <v>4.75</v>
       </c>
       <c r="AF4">
-        <v>32.1</v>
+        <v>-21.45</v>
       </c>
       <c r="AG4">
-        <v>239.49</v>
+        <v>238.52</v>
       </c>
       <c r="AH4">
-        <v>211.78</v>
+        <v>210.95</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1258,7 +1223,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>51.03</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1234,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>658.95</v>
+        <v>657.4</v>
       </c>
       <c r="D5">
-        <v>1.17</v>
+        <v>-0.24</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1281,46 +1246,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.46</v>
+        <v>-23.64</v>
       </c>
       <c r="H5">
-        <v>34.29</v>
+        <v>33.97</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="J5">
-        <v>-5.51</v>
+        <v>-5.12</v>
       </c>
       <c r="K5">
-        <v>18.74</v>
+        <v>21.63</v>
       </c>
       <c r="L5">
-        <v>-20.53</v>
+        <v>-21.12</v>
       </c>
       <c r="M5">
-        <v>-8.220000000000001</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P5">
-        <v>657.22</v>
+        <v>657.4</v>
       </c>
       <c r="Q5">
-        <v>671.64</v>
+        <v>669.5700000000001</v>
       </c>
       <c r="R5">
-        <v>683.15</v>
+        <v>681.92</v>
       </c>
       <c r="S5">
-        <v>619.72</v>
+        <v>619.47</v>
       </c>
       <c r="T5">
-        <v>6.33</v>
+        <v>6.12</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1335,34 +1300,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>44.48</v>
+        <v>43.87</v>
       </c>
       <c r="Z5">
-        <v>-6.2</v>
+        <v>-6.33</v>
       </c>
       <c r="AA5">
-        <v>-3.84</v>
+        <v>-4.34</v>
       </c>
       <c r="AB5">
-        <v>-2.35</v>
+        <v>-1.99</v>
       </c>
       <c r="AC5">
-        <v>8.25</v>
+        <v>15.16</v>
       </c>
       <c r="AD5">
-        <v>9.75</v>
+        <v>11.3</v>
       </c>
       <c r="AE5">
-        <v>20.82</v>
+        <v>20.15</v>
       </c>
       <c r="AF5">
-        <v>-57.52</v>
+        <v>-56.62</v>
       </c>
       <c r="AG5">
-        <v>698.8200000000001</v>
+        <v>694.25</v>
       </c>
       <c r="AH5">
-        <v>644.46</v>
+        <v>644.9</v>
       </c>
       <c r="AI5">
         <v>634.86</v>
@@ -1371,7 +1336,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>23.89</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1347,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.22</v>
+        <v>25.7</v>
       </c>
       <c r="D6">
-        <v>3.07</v>
+        <v>-1.98</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1394,46 +1359,46 @@
         <v>25.43</v>
       </c>
       <c r="G6">
-        <v>-49.96</v>
+        <v>-50.95</v>
       </c>
       <c r="H6">
-        <v>3.11</v>
+        <v>1.06</v>
       </c>
       <c r="I6">
-        <v>0.92</v>
+        <v>-0.7</v>
       </c>
       <c r="J6">
-        <v>-4.83</v>
+        <v>-9.44</v>
       </c>
       <c r="K6">
-        <v>-17.83</v>
+        <v>-16.99</v>
       </c>
       <c r="L6">
-        <v>-49.04</v>
+        <v>-50.67</v>
       </c>
       <c r="M6">
-        <v>-15.22</v>
+        <v>-16.25</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>25.77</v>
+        <v>25.73</v>
       </c>
       <c r="Q6">
-        <v>26.51</v>
+        <v>26.41</v>
       </c>
       <c r="R6">
-        <v>28.06</v>
+        <v>28</v>
       </c>
       <c r="S6">
-        <v>32.99</v>
+        <v>32.91</v>
       </c>
       <c r="T6">
-        <v>-20.53</v>
+        <v>-21.91</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1448,34 +1413,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>42.63</v>
+        <v>38.63</v>
       </c>
       <c r="Z6">
-        <v>-0.68</v>
+        <v>-0.67</v>
       </c>
       <c r="AA6">
         <v>-0.68</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>27.63</v>
+        <v>43.77</v>
       </c>
       <c r="AD6">
-        <v>16.45</v>
+        <v>26.27</v>
       </c>
       <c r="AE6">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="AF6">
-        <v>-27.28</v>
+        <v>-51.91</v>
       </c>
       <c r="AG6">
-        <v>27.75</v>
+        <v>27.58</v>
       </c>
       <c r="AH6">
-        <v>25.27</v>
+        <v>25.25</v>
       </c>
       <c r="AI6">
         <v>28.03</v>
@@ -1484,7 +1449,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>34.17</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1460,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1218</v>
+        <v>1207.7</v>
       </c>
       <c r="D7">
-        <v>2.66</v>
+        <v>-0.85</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1507,25 +1472,25 @@
         <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-23.15</v>
+        <v>-23.8</v>
       </c>
       <c r="H7">
-        <v>4.31</v>
+        <v>3.43</v>
       </c>
       <c r="I7">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="J7">
-        <v>-6.49</v>
+        <v>-8.65</v>
       </c>
       <c r="K7">
-        <v>-6.91</v>
+        <v>-5.35</v>
       </c>
       <c r="L7">
-        <v>-10.29</v>
+        <v>-11.35</v>
       </c>
       <c r="M7">
-        <v>0.99</v>
+        <v>0.72</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1534,19 +1499,19 @@
         <v>46</v>
       </c>
       <c r="P7">
-        <v>1188.22</v>
+        <v>1193.36</v>
       </c>
       <c r="Q7">
-        <v>1234.01</v>
+        <v>1228.92</v>
       </c>
       <c r="R7">
-        <v>1277.14</v>
+        <v>1275.7</v>
       </c>
       <c r="S7">
-        <v>1355.37</v>
+        <v>1353.72</v>
       </c>
       <c r="T7">
-        <v>-10.14</v>
+        <v>-10.79</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1561,34 +1526,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>44.49</v>
+        <v>42.31</v>
       </c>
       <c r="Z7">
-        <v>-26.69</v>
+        <v>-25.05</v>
       </c>
       <c r="AA7">
-        <v>-24.25</v>
+        <v>-24.41</v>
       </c>
       <c r="AB7">
-        <v>-2.44</v>
+        <v>-0.64</v>
       </c>
       <c r="AC7">
-        <v>50.47</v>
+        <v>79.36</v>
       </c>
       <c r="AD7">
-        <v>26.04</v>
+        <v>50.74</v>
       </c>
       <c r="AE7">
-        <v>21.84</v>
+        <v>21.51</v>
       </c>
       <c r="AF7">
-        <v>45.06</v>
+        <v>-7.19</v>
       </c>
       <c r="AG7">
-        <v>1310.28</v>
+        <v>1297.15</v>
       </c>
       <c r="AH7">
-        <v>1157.74</v>
+        <v>1160.69</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1597,7 +1562,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>59.01</v>
+        <v>53.08</v>
       </c>
     </row>
   </sheetData>
@@ -1738,7 +1703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1758,910 +1723,855 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.5</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-6.69</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-4.48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-8.369999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.23</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-5.12</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-4.83</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.44</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-6.49</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-8.65</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-0.85</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>4.59</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.58</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.01</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D16" s="5">
+        <v>0.14</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.92</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.7</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.7</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2.17</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-21.93</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-23.24</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-29.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-31.29</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-25.68</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-27.87</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-20.53</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-21.12</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-49.04</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-50.67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-10.29</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.35</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-10.55</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-6.75</v>
+      </c>
+      <c r="E25" s="6">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-11.63</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-10.66</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-10.36</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-5.89</v>
+      </c>
+      <c r="E27" s="6">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>18.74</v>
+      </c>
+      <c r="D28" s="5">
+        <v>21.63</v>
+      </c>
+      <c r="E28" s="6">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-17.83</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-16.99</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.91</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-5.35</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-26.82</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-25.92</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-31.18</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-32.3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-30.8</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-31.27</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-23.46</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-23.64</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-49.96</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-50.95</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-23.15</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-23.8</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>25.78</v>
+      </c>
+      <c r="D37" s="5">
+        <v>26.1</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>217.9</v>
+      </c>
+      <c r="D39" s="5">
+        <v>216.44</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>658.95</v>
+      </c>
+      <c r="D40" s="5">
+        <v>657.4</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>26.22</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.7</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1218</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1207.7</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-10.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>35.91</v>
+      </c>
+      <c r="D43" s="5">
+        <v>42.09</v>
+      </c>
+      <c r="E43" s="6">
+        <v>6.18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>44.76</v>
+      </c>
+      <c r="D44" s="5">
+        <v>40.94</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>35.35</v>
+      </c>
+      <c r="D45" s="5">
+        <v>33.88</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>44.48</v>
+      </c>
+      <c r="D46" s="5">
+        <v>43.87</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>42.63</v>
+      </c>
+      <c r="D47" s="5">
+        <v>38.63</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>44.49</v>
+      </c>
+      <c r="D48" s="5">
+        <v>42.31</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
         <v>64</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.68</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-7.5</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D49" s="5">
+        <v>-25.98</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-89.98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-9.09</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="E9" s="7">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>55.89</v>
+      </c>
+      <c r="D50" s="5">
+        <v>7.27</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-48.62</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.23</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>32.1</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-21.45</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-53.55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-5.51</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-57.52</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-56.62</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.83</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>-27.28</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-51.91</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-24.63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-6.49</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.54</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.85</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4.59</v>
-      </c>
-      <c r="E15" s="7">
-        <v>9.93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E16" s="7">
-        <v>5.43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.9</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="E18" s="7">
-        <v>5.82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="E19" s="7">
-        <v>4.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-21.93</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-31.39</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-29.95</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-27.94</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-25.68</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-21.6</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-20.53</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-50.69</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-49.04</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-13.18</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-10.29</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-12.1</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-10.55</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-15.7</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-11.63</v>
-      </c>
-      <c r="E27" s="7">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-11.67</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-10.36</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>18.99</v>
-      </c>
-      <c r="D29" s="6">
-        <v>18.74</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-21.63</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-17.83</v>
-      </c>
-      <c r="E30" s="7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-27.02</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-26.82</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-33.99</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-31.18</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-32.68</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-30.8</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-24.35</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-23.46</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-51.45</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-49.96</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-25.15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-23.15</v>
-      </c>
-      <c r="E37" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>25.71</v>
-      </c>
-      <c r="D38" s="6">
-        <v>25.78</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>9.4</v>
-      </c>
-      <c r="D39" s="6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>212</v>
-      </c>
-      <c r="D40" s="6">
-        <v>217.9</v>
-      </c>
-      <c r="E40" s="7">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>651.35</v>
-      </c>
-      <c r="D41" s="6">
-        <v>658.95</v>
-      </c>
-      <c r="E41" s="7">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>25.44</v>
-      </c>
-      <c r="D42" s="6">
-        <v>26.22</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1186.4</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1218</v>
-      </c>
-      <c r="E43" s="7">
-        <v>31.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>34.49</v>
-      </c>
-      <c r="D44" s="6">
-        <v>35.91</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>29.49</v>
-      </c>
-      <c r="D45" s="6">
-        <v>44.76</v>
-      </c>
-      <c r="E45" s="7">
-        <v>15.27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>22.73</v>
-      </c>
-      <c r="D46" s="6">
-        <v>35.35</v>
-      </c>
-      <c r="E46" s="7">
-        <v>12.62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>40.72</v>
-      </c>
-      <c r="D47" s="6">
-        <v>44.48</v>
-      </c>
-      <c r="E47" s="7">
-        <v>3.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>32.95</v>
-      </c>
-      <c r="D48" s="6">
-        <v>42.63</v>
-      </c>
-      <c r="E48" s="7">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>34.94</v>
-      </c>
-      <c r="D49" s="6">
-        <v>44.49</v>
-      </c>
-      <c r="E49" s="7">
-        <v>9.550000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="6">
-        <v>24.09</v>
-      </c>
-      <c r="D50" s="6">
-        <v>64</v>
-      </c>
-      <c r="E50" s="7">
-        <v>39.91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-8.5</v>
-      </c>
-      <c r="D51" s="6">
-        <v>55.89</v>
-      </c>
-      <c r="E51" s="7">
-        <v>64.39</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>27.5</v>
-      </c>
-      <c r="D52" s="6">
-        <v>32.1</v>
-      </c>
-      <c r="E52" s="7">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-45.06</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-57.52</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-12.46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-39.28</v>
-      </c>
-      <c r="D54" s="6">
-        <v>-27.28</v>
+      <c r="C54" s="5">
+        <v>45.06</v>
+      </c>
+      <c r="D54" s="5">
+        <v>-7.19</v>
       </c>
       <c r="E54" s="7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>15.22</v>
-      </c>
-      <c r="D55" s="6">
-        <v>45.06</v>
-      </c>
-      <c r="E55" s="7">
-        <v>29.84</v>
+        <v>-52.25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2681,60 +2591,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-6.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2836,43 +2746,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0412</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.08220000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1232</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1522</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1738</v>
+      <c r="A2" s="13">
+        <v>0.0072</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0432</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0803</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1218</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1625</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1797</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>DOWN</t>
-  </si>
-  <si>
-    <t>UP</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -255,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,58 +892,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.1</v>
+        <v>25.1</v>
       </c>
       <c r="D2">
-        <v>1.24</v>
+        <v>-3.83</v>
       </c>
       <c r="E2">
-        <v>35.23</v>
+        <v>34.64</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.92</v>
+        <v>-27.54</v>
       </c>
       <c r="H2">
-        <v>13.58</v>
+        <v>9.23</v>
       </c>
       <c r="I2">
-        <v>0.73</v>
+        <v>-3.2</v>
       </c>
       <c r="J2">
-        <v>-6.69</v>
+        <v>-10.04</v>
       </c>
       <c r="K2">
-        <v>-6.75</v>
+        <v>-11.65</v>
       </c>
       <c r="L2">
-        <v>-23.24</v>
+        <v>-28.75</v>
       </c>
       <c r="M2">
-        <v>-12.18</v>
+        <v>-12.86</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P2">
-        <v>25.79</v>
+        <v>25.62</v>
       </c>
       <c r="Q2">
-        <v>26.39</v>
+        <v>26.29</v>
       </c>
       <c r="R2">
-        <v>27.15</v>
+        <v>27.11</v>
       </c>
       <c r="S2">
-        <v>28.05</v>
+        <v>28.02</v>
       </c>
       <c r="T2">
-        <v>-6.94</v>
+        <v>-10.41</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -961,34 +958,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.09</v>
+        <v>31.78</v>
       </c>
       <c r="Z2">
-        <v>-0.45</v>
+        <v>-0.5</v>
       </c>
       <c r="AA2">
-        <v>-0.43</v>
+        <v>-0.44</v>
       </c>
       <c r="AB2">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="AC2">
-        <v>58.96</v>
+        <v>53.25</v>
       </c>
       <c r="AD2">
-        <v>35.48</v>
+        <v>47.28</v>
       </c>
       <c r="AE2">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AF2">
-        <v>-25.98</v>
+        <v>21.97</v>
       </c>
       <c r="AG2">
-        <v>27.41</v>
+        <v>27.38</v>
       </c>
       <c r="AH2">
-        <v>25.37</v>
+        <v>25.19</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -997,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>52.18</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1008,58 +1005,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.640000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D3">
-        <v>-1.63</v>
+        <v>-4.46</v>
       </c>
       <c r="E3">
-        <v>14.24</v>
+        <v>14.2</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.3</v>
+        <v>-35.14</v>
       </c>
       <c r="H3">
-        <v>8.68</v>
+        <v>3.83</v>
       </c>
       <c r="I3">
-        <v>1.58</v>
+        <v>-2.54</v>
       </c>
       <c r="J3">
-        <v>-8.369999999999999</v>
+        <v>-11.27</v>
       </c>
       <c r="K3">
-        <v>-10.66</v>
+        <v>-15.43</v>
       </c>
       <c r="L3">
-        <v>-31.29</v>
+        <v>-35.32</v>
       </c>
       <c r="M3">
-        <v>-17.97</v>
+        <v>-18.9</v>
       </c>
       <c r="N3">
         <v>34</v>
       </c>
       <c r="O3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P3">
-        <v>9.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q3">
-        <v>9.859999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="R3">
-        <v>10.34</v>
+        <v>10.3</v>
       </c>
       <c r="S3">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
       <c r="T3">
-        <v>-11.11</v>
+        <v>-14.96</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1074,34 +1071,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.94</v>
+        <v>32.83</v>
       </c>
       <c r="Z3">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="AA3">
         <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>73.03</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AD3">
-        <v>50.01</v>
+        <v>66.44</v>
       </c>
       <c r="AE3">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="AF3">
-        <v>7.27</v>
+        <v>31.06</v>
       </c>
       <c r="AG3">
-        <v>10.48</v>
+        <v>10.46</v>
       </c>
       <c r="AH3">
-        <v>9.25</v>
+        <v>9.16</v>
       </c>
       <c r="AI3">
         <v>10.28</v>
@@ -1110,7 +1107,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>26.46</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1121,58 +1118,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>216.44</v>
+        <v>211</v>
       </c>
       <c r="D4">
-        <v>-0.67</v>
+        <v>-2.51</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G4">
-        <v>-31.27</v>
+        <v>-32.99</v>
       </c>
       <c r="H4">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.51</v>
+        <v>-2.71</v>
       </c>
       <c r="J4">
-        <v>-9.630000000000001</v>
+        <v>-9.98</v>
       </c>
       <c r="K4">
-        <v>-5.89</v>
+        <v>-9.59</v>
       </c>
       <c r="L4">
-        <v>-27.87</v>
+        <v>-30.06</v>
       </c>
       <c r="M4">
-        <v>-4.32</v>
+        <v>-5.09</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>215.14</v>
+        <v>213.97</v>
       </c>
       <c r="Q4">
-        <v>224.74</v>
+        <v>223.63</v>
       </c>
       <c r="R4">
-        <v>238.35</v>
+        <v>237.83</v>
       </c>
       <c r="S4">
-        <v>247.82</v>
+        <v>247.42</v>
       </c>
       <c r="T4">
-        <v>-12.66</v>
+        <v>-14.72</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1187,34 +1184,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.88</v>
+        <v>29.02</v>
       </c>
       <c r="Z4">
-        <v>-6.19</v>
+        <v>-6.48</v>
       </c>
       <c r="AA4">
-        <v>-5.51</v>
+        <v>-5.7</v>
       </c>
       <c r="AB4">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="AC4">
-        <v>37.62</v>
+        <v>47.58</v>
       </c>
       <c r="AD4">
-        <v>19.2</v>
+        <v>35.06</v>
       </c>
       <c r="AE4">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AF4">
-        <v>-21.45</v>
+        <v>-17.83</v>
       </c>
       <c r="AG4">
-        <v>238.52</v>
+        <v>238.11</v>
       </c>
       <c r="AH4">
-        <v>210.95</v>
+        <v>209.15</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1223,7 +1220,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>48.76</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1234,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>657.4</v>
+        <v>631.65</v>
       </c>
       <c r="D5">
-        <v>-0.24</v>
+        <v>-3.92</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1246,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.64</v>
+        <v>-26.63</v>
       </c>
       <c r="H5">
-        <v>33.97</v>
+        <v>28.72</v>
       </c>
       <c r="I5">
-        <v>0.14</v>
+        <v>-5.18</v>
       </c>
       <c r="J5">
-        <v>-5.12</v>
+        <v>-9.6</v>
       </c>
       <c r="K5">
-        <v>21.63</v>
+        <v>15.56</v>
       </c>
       <c r="L5">
-        <v>-21.12</v>
+        <v>-24.09</v>
       </c>
       <c r="M5">
-        <v>-8.029999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="P5">
-        <v>657.4</v>
+        <v>650.5</v>
       </c>
       <c r="Q5">
-        <v>669.5700000000001</v>
+        <v>666.4400000000001</v>
       </c>
       <c r="R5">
-        <v>681.92</v>
+        <v>679.99</v>
       </c>
       <c r="S5">
-        <v>619.47</v>
+        <v>619.1</v>
       </c>
       <c r="T5">
-        <v>6.12</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1300,43 +1297,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>43.87</v>
+        <v>35.2</v>
       </c>
       <c r="Z5">
-        <v>-6.33</v>
+        <v>-8.42</v>
       </c>
       <c r="AA5">
-        <v>-4.34</v>
+        <v>-5.16</v>
       </c>
       <c r="AB5">
-        <v>-1.99</v>
+        <v>-3.26</v>
       </c>
       <c r="AC5">
         <v>15.16</v>
       </c>
       <c r="AD5">
-        <v>11.3</v>
+        <v>12.86</v>
       </c>
       <c r="AE5">
-        <v>20.15</v>
+        <v>21.36</v>
       </c>
       <c r="AF5">
-        <v>-56.62</v>
+        <v>-39.12</v>
       </c>
       <c r="AG5">
-        <v>694.25</v>
+        <v>693.6799999999999</v>
       </c>
       <c r="AH5">
-        <v>644.9</v>
+        <v>639.2</v>
       </c>
       <c r="AI5">
-        <v>634.86</v>
+        <v>707.99</v>
       </c>
       <c r="AJ5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AK5">
-        <v>23.57</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1347,58 +1344,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.7</v>
+        <v>24.39</v>
       </c>
       <c r="D6">
-        <v>-1.98</v>
+        <v>-5.1</v>
       </c>
       <c r="E6">
         <v>52.4</v>
       </c>
       <c r="F6">
-        <v>25.43</v>
+        <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-50.95</v>
+        <v>-53.45</v>
       </c>
       <c r="H6">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.7</v>
+        <v>-5.72</v>
       </c>
       <c r="J6">
-        <v>-9.44</v>
+        <v>-11.76</v>
       </c>
       <c r="K6">
-        <v>-16.99</v>
+        <v>-20.68</v>
       </c>
       <c r="L6">
-        <v>-50.67</v>
+        <v>-53.37</v>
       </c>
       <c r="M6">
-        <v>-16.25</v>
+        <v>-16.81</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>25.73</v>
+        <v>25.44</v>
       </c>
       <c r="Q6">
-        <v>26.41</v>
+        <v>26.27</v>
       </c>
       <c r="R6">
-        <v>28</v>
+        <v>27.91</v>
       </c>
       <c r="S6">
-        <v>32.91</v>
+        <v>32.83</v>
       </c>
       <c r="T6">
-        <v>-21.91</v>
+        <v>-25.7</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1413,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>38.63</v>
+        <v>30.78</v>
       </c>
       <c r="Z6">
-        <v>-0.67</v>
+        <v>-0.76</v>
       </c>
       <c r="AA6">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AC6">
-        <v>43.77</v>
+        <v>43.39</v>
       </c>
       <c r="AD6">
-        <v>26.27</v>
+        <v>38.26</v>
       </c>
       <c r="AE6">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="AF6">
-        <v>-51.91</v>
+        <v>43.6</v>
       </c>
       <c r="AG6">
-        <v>27.58</v>
+        <v>27.67</v>
       </c>
       <c r="AH6">
-        <v>25.25</v>
+        <v>24.86</v>
       </c>
       <c r="AI6">
-        <v>28.03</v>
+        <v>27.59</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.75</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1460,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1207.7</v>
+        <v>1178</v>
       </c>
       <c r="D7">
-        <v>-0.85</v>
+        <v>-2.46</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1472,46 +1469,46 @@
         <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-23.8</v>
+        <v>-25.68</v>
       </c>
       <c r="H7">
-        <v>3.43</v>
+        <v>0.88</v>
       </c>
       <c r="I7">
-        <v>2.17</v>
+        <v>-0.76</v>
       </c>
       <c r="J7">
-        <v>-8.65</v>
+        <v>-10.04</v>
       </c>
       <c r="K7">
-        <v>-5.35</v>
+        <v>-7.95</v>
       </c>
       <c r="L7">
-        <v>-11.35</v>
+        <v>-13.2</v>
       </c>
       <c r="M7">
-        <v>0.72</v>
+        <v>-0.53</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1193.36</v>
+        <v>1191.56</v>
       </c>
       <c r="Q7">
-        <v>1228.92</v>
+        <v>1223.08</v>
       </c>
       <c r="R7">
-        <v>1275.7</v>
+        <v>1273.9</v>
       </c>
       <c r="S7">
-        <v>1353.72</v>
+        <v>1351.92</v>
       </c>
       <c r="T7">
-        <v>-10.79</v>
+        <v>-12.86</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1526,34 +1523,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.31</v>
+        <v>36.72</v>
       </c>
       <c r="Z7">
-        <v>-25.05</v>
+        <v>-25.85</v>
       </c>
       <c r="AA7">
-        <v>-24.41</v>
+        <v>-24.7</v>
       </c>
       <c r="AB7">
-        <v>-0.64</v>
+        <v>-1.15</v>
       </c>
       <c r="AC7">
-        <v>79.36</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="AD7">
-        <v>50.74</v>
+        <v>69.84</v>
       </c>
       <c r="AE7">
-        <v>21.51</v>
+        <v>22.48</v>
       </c>
       <c r="AF7">
-        <v>-7.19</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AG7">
-        <v>1297.15</v>
+        <v>1287.42</v>
       </c>
       <c r="AH7">
-        <v>1160.69</v>
+        <v>1158.73</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1562,7 +1559,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>53.08</v>
+        <v>51.42</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1713,7 +1710,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1723,12 +1720,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1740,16 +1737,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1760,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.5</v>
+        <v>-6.69</v>
       </c>
       <c r="D7" s="5">
-        <v>-6.69</v>
+        <v>-10.04</v>
       </c>
       <c r="E7" s="6">
-        <v>0.8100000000000001</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1777,13 +1774,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-4.48</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D8" s="5">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-3.89</v>
+        <v>-11.27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1794,13 +1791,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.23</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.4</v>
+        <v>-9.98</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1811,13 +1808,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-5.51</v>
+        <v>-5.12</v>
       </c>
       <c r="D10" s="5">
-        <v>-5.12</v>
+        <v>-9.6</v>
       </c>
       <c r="E10" s="6">
-        <v>0.39</v>
+        <v>-4.48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1828,13 +1825,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-4.83</v>
+        <v>-9.44</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.44</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-4.61</v>
+        <v>-11.76</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1845,13 +1842,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-6.49</v>
+        <v>-8.65</v>
       </c>
       <c r="D12" s="5">
-        <v>-8.65</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.16</v>
+        <v>-10.04</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1862,13 +1859,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.85</v>
+        <v>0.73</v>
       </c>
       <c r="D13" s="5">
-        <v>0.73</v>
+        <v>-3.2</v>
       </c>
       <c r="E13" s="6">
-        <v>1.58</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1879,13 +1876,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>4.59</v>
+        <v>1.58</v>
       </c>
       <c r="D14" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.01</v>
+        <v>-2.54</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-4.12</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1896,13 +1893,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.18</v>
+        <v>-0.51</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.51</v>
+        <v>-2.71</v>
       </c>
       <c r="E15" s="6">
-        <v>0.67</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1913,13 +1910,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="D16" s="5">
-        <v>0.14</v>
+        <v>-5.18</v>
       </c>
       <c r="E16" s="6">
-        <v>0.14</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1930,13 +1927,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>0.92</v>
+        <v>-0.7</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.7</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.62</v>
+        <v>-5.72</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-5.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1947,13 +1944,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="D18" s="5">
-        <v>2.17</v>
+        <v>-0.76</v>
       </c>
       <c r="E18" s="6">
-        <v>0.47</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1964,13 +1961,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-21.93</v>
+        <v>-23.24</v>
       </c>
       <c r="D19" s="5">
-        <v>-23.24</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.31</v>
+        <v>-28.75</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-5.51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1981,13 +1978,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-29.95</v>
+        <v>-31.29</v>
       </c>
       <c r="D20" s="5">
-        <v>-31.29</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.34</v>
+        <v>-35.32</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-4.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1998,12 +1995,12 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-25.68</v>
+        <v>-27.87</v>
       </c>
       <c r="D21" s="5">
-        <v>-27.87</v>
-      </c>
-      <c r="E21" s="7">
+        <v>-30.06</v>
+      </c>
+      <c r="E21" s="6">
         <v>-2.19</v>
       </c>
     </row>
@@ -2015,13 +2012,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-20.53</v>
+        <v>-21.12</v>
       </c>
       <c r="D22" s="5">
-        <v>-21.12</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.59</v>
+        <v>-24.09</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.97</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2032,13 +2029,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-49.04</v>
+        <v>-50.67</v>
       </c>
       <c r="D23" s="5">
-        <v>-50.67</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.63</v>
+        <v>-53.37</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2049,13 +2046,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-10.29</v>
+        <v>-11.35</v>
       </c>
       <c r="D24" s="5">
-        <v>-11.35</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.06</v>
+        <v>-13.2</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2066,13 +2063,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.55</v>
+        <v>-6.75</v>
       </c>
       <c r="D25" s="5">
-        <v>-6.75</v>
+        <v>-11.65</v>
       </c>
       <c r="E25" s="6">
-        <v>3.8</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2083,13 +2080,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-11.63</v>
+        <v>-10.66</v>
       </c>
       <c r="D26" s="5">
-        <v>-10.66</v>
+        <v>-15.43</v>
       </c>
       <c r="E26" s="6">
-        <v>0.97</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2100,13 +2097,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-10.36</v>
+        <v>-5.89</v>
       </c>
       <c r="D27" s="5">
-        <v>-5.89</v>
+        <v>-9.59</v>
       </c>
       <c r="E27" s="6">
-        <v>4.47</v>
+        <v>-3.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2117,13 +2114,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>18.74</v>
+        <v>21.63</v>
       </c>
       <c r="D28" s="5">
-        <v>21.63</v>
+        <v>15.56</v>
       </c>
       <c r="E28" s="6">
-        <v>2.89</v>
+        <v>-6.07</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2134,13 +2131,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-17.83</v>
+        <v>-16.99</v>
       </c>
       <c r="D29" s="5">
-        <v>-16.99</v>
+        <v>-20.68</v>
       </c>
       <c r="E29" s="6">
-        <v>0.84</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2151,13 +2148,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.91</v>
+        <v>-5.35</v>
       </c>
       <c r="D30" s="5">
-        <v>-5.35</v>
+        <v>-7.95</v>
       </c>
       <c r="E30" s="6">
-        <v>1.56</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2168,13 +2165,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-26.82</v>
+        <v>-25.92</v>
       </c>
       <c r="D31" s="5">
-        <v>-25.92</v>
+        <v>-27.54</v>
       </c>
       <c r="E31" s="6">
-        <v>0.9</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2185,13 +2182,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-31.18</v>
+        <v>-32.3</v>
       </c>
       <c r="D32" s="5">
-        <v>-32.3</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.12</v>
+        <v>-35.14</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2202,13 +2199,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-30.8</v>
+        <v>-31.27</v>
       </c>
       <c r="D33" s="5">
-        <v>-31.27</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.47</v>
+        <v>-32.99</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.72</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2219,13 +2216,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-23.46</v>
+        <v>-23.64</v>
       </c>
       <c r="D34" s="5">
-        <v>-23.64</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.18</v>
+        <v>-26.63</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2236,13 +2233,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-49.96</v>
+        <v>-50.95</v>
       </c>
       <c r="D35" s="5">
-        <v>-50.95</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.99</v>
+        <v>-53.45</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2253,13 +2250,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-23.15</v>
+        <v>-23.8</v>
       </c>
       <c r="D36" s="5">
-        <v>-23.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.65</v>
+        <v>-25.68</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2270,13 +2267,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>25.78</v>
+        <v>26.1</v>
       </c>
       <c r="D37" s="5">
-        <v>26.1</v>
+        <v>25.1</v>
       </c>
       <c r="E37" s="6">
-        <v>0.32</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2287,13 +2284,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D38" s="5">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.16</v>
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2304,13 +2301,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>217.9</v>
+        <v>216.44</v>
       </c>
       <c r="D39" s="5">
-        <v>216.44</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.46</v>
+        <v>211</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-5.44</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2321,13 +2318,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>658.95</v>
+        <v>657.4</v>
       </c>
       <c r="D40" s="5">
-        <v>657.4</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.55</v>
+        <v>631.65</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-25.75</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2338,13 +2335,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>26.22</v>
+        <v>25.7</v>
       </c>
       <c r="D41" s="5">
-        <v>25.7</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.52</v>
+        <v>24.39</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2355,13 +2352,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1218</v>
+        <v>1207.7</v>
       </c>
       <c r="D42" s="5">
-        <v>1207.7</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-10.3</v>
+        <v>1178</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-29.7</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2369,203 +2366,237 @@
         <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C43" s="5">
-        <v>35.91</v>
+        <v>66</v>
       </c>
       <c r="D43" s="5">
-        <v>42.09</v>
+        <v>50</v>
       </c>
       <c r="E43" s="6">
-        <v>6.18</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C44" s="5">
-        <v>44.76</v>
+        <v>50</v>
       </c>
       <c r="D44" s="5">
-        <v>40.94</v>
+        <v>66</v>
       </c>
       <c r="E44" s="7">
-        <v>-3.82</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>35.35</v>
+        <v>42.09</v>
       </c>
       <c r="D45" s="5">
-        <v>33.88</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.47</v>
+        <v>31.78</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-10.31</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>44.48</v>
+        <v>40.94</v>
       </c>
       <c r="D46" s="5">
-        <v>43.87</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.61</v>
+        <v>32.83</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>42.63</v>
+        <v>33.88</v>
       </c>
       <c r="D47" s="5">
-        <v>38.63</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-4</v>
+        <v>29.02</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-4.86</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>44.49</v>
+        <v>43.87</v>
       </c>
       <c r="D48" s="5">
-        <v>42.31</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.18</v>
+        <v>35.2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-8.67</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>64</v>
+        <v>38.63</v>
       </c>
       <c r="D49" s="5">
-        <v>-25.98</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-89.98</v>
+        <v>30.78</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>55.89</v>
+        <v>42.31</v>
       </c>
       <c r="D50" s="5">
-        <v>7.27</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-48.62</v>
+        <v>36.72</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>32.1</v>
+        <v>-25.98</v>
       </c>
       <c r="D51" s="5">
-        <v>-21.45</v>
+        <v>21.97</v>
       </c>
       <c r="E51" s="7">
-        <v>-53.55</v>
+        <v>47.95</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-57.52</v>
+        <v>7.27</v>
       </c>
       <c r="D52" s="5">
-        <v>-56.62</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.9</v>
+        <v>31.06</v>
+      </c>
+      <c r="E52" s="7">
+        <v>23.79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-27.28</v>
+        <v>-21.45</v>
       </c>
       <c r="D53" s="5">
-        <v>-51.91</v>
+        <v>-17.83</v>
       </c>
       <c r="E53" s="7">
-        <v>-24.63</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>45.06</v>
+        <v>-56.62</v>
       </c>
       <c r="D54" s="5">
+        <v>-39.12</v>
+      </c>
+      <c r="E54" s="7">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-51.91</v>
+      </c>
+      <c r="D55" s="5">
+        <v>43.6</v>
+      </c>
+      <c r="E55" s="7">
+        <v>95.51000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
         <v>-7.19</v>
       </c>
-      <c r="E54" s="7">
-        <v>-52.25</v>
+      <c r="D56" s="5">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="E56" s="7">
+        <v>16.64</v>
       </c>
     </row>
   </sheetData>
@@ -2595,28 +2626,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2630,16 +2661,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>40.3</v>
+        <v>32.7</v>
       </c>
       <c r="E2" s="10">
         <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-8</v>
+        <v>-10.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-4</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H2" s="10">
         <v>58.2</v>
@@ -2767,22 +2798,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0072</v>
+        <v>-0.0053</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0432</v>
+        <v>-0.0509</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0803</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1218</v>
+        <v>-0.1286</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1625</v>
+        <v>-0.1681</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.1797</v>
+        <v>-0.189</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="59">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,16 +172,7 @@
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -212,13 +203,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,22 +239,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,24 +256,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,33 +325,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1700,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1733,870 +1684,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-6.69</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-10.04</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-11.27</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-9.98</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-5.12</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-9.6</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-4.48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-9.44</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-11.76</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-8.65</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-10.04</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0.73</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.2</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.58</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-4.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-2.71</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-5.18</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-5.32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.7</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-5.72</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2.17</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.76</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-23.24</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-28.75</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-5.51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-31.29</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-35.32</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-27.87</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-30.06</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-21.12</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-24.09</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-50.67</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-53.37</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-11.35</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-13.2</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-6.75</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-11.65</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-10.66</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-15.43</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-4.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-5.89</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-9.59</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>21.63</v>
-      </c>
-      <c r="D28" s="5">
-        <v>15.56</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-6.07</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-16.99</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-20.68</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-5.35</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-25.92</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-27.54</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-32.3</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-35.14</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-31.27</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-32.99</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-23.64</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-26.63</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-50.95</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-53.45</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-23.8</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-25.68</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>26.1</v>
-      </c>
-      <c r="D37" s="5">
-        <v>25.1</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>216.44</v>
-      </c>
-      <c r="D39" s="5">
-        <v>211</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-5.44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>657.4</v>
-      </c>
-      <c r="D40" s="5">
-        <v>631.65</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-25.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>25.7</v>
-      </c>
-      <c r="D41" s="5">
-        <v>24.39</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1207.7</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1178</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-29.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="5">
-        <v>66</v>
-      </c>
-      <c r="D43" s="5">
-        <v>50</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="5">
-        <v>50</v>
-      </c>
-      <c r="D44" s="5">
-        <v>66</v>
-      </c>
-      <c r="E44" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>42.09</v>
-      </c>
-      <c r="D45" s="5">
-        <v>31.78</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-10.31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>40.94</v>
-      </c>
-      <c r="D46" s="5">
-        <v>32.83</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>33.88</v>
-      </c>
-      <c r="D47" s="5">
-        <v>29.02</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-4.86</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>43.87</v>
-      </c>
-      <c r="D48" s="5">
-        <v>35.2</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-8.67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>38.63</v>
-      </c>
-      <c r="D49" s="5">
-        <v>30.78</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-7.85</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>42.31</v>
-      </c>
-      <c r="D50" s="5">
-        <v>36.72</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-5.59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-25.98</v>
-      </c>
-      <c r="D51" s="5">
-        <v>21.97</v>
-      </c>
-      <c r="E51" s="7">
-        <v>47.95</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>7.27</v>
-      </c>
-      <c r="D52" s="5">
-        <v>31.06</v>
-      </c>
-      <c r="E52" s="7">
-        <v>23.79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-21.45</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-17.83</v>
-      </c>
-      <c r="E53" s="7">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>-56.62</v>
-      </c>
-      <c r="D54" s="5">
-        <v>-39.12</v>
-      </c>
-      <c r="E54" s="7">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-51.91</v>
-      </c>
-      <c r="D55" s="5">
-        <v>43.6</v>
-      </c>
-      <c r="E55" s="7">
-        <v>95.51000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-7.19</v>
-      </c>
-      <c r="D56" s="5">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="E56" s="7">
-        <v>16.64</v>
       </c>
     </row>
   </sheetData>
@@ -2622,60 +1711,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="6">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="6">
         <v>32.7</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="6">
         <v>-10.4</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="6">
         <v>-8.300000000000001</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2777,42 +1866,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>-0.0053</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="9">
         <v>-0.0509</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="9">
         <v>-0.08779999999999999</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="9">
         <v>-0.1286</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="9">
         <v>-0.1681</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="9">
         <v>-0.189</v>
       </c>
     </row>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,13 +166,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.0 → 35.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>35.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -203,11 +239,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -239,8 +277,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +308,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -325,27 +395,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -701,9 +778,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -843,10 +918,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.1</v>
+        <v>25.85</v>
       </c>
       <c r="D2">
-        <v>-3.83</v>
+        <v>2.99</v>
       </c>
       <c r="E2">
         <v>34.64</v>
@@ -855,46 +930,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.54</v>
+        <v>-25.38</v>
       </c>
       <c r="H2">
-        <v>9.23</v>
+        <v>12.49</v>
       </c>
       <c r="I2">
-        <v>-3.2</v>
+        <v>1.73</v>
       </c>
       <c r="J2">
-        <v>-10.04</v>
+        <v>-4.89</v>
       </c>
       <c r="K2">
-        <v>-11.65</v>
+        <v>-11.44</v>
       </c>
       <c r="L2">
-        <v>-28.75</v>
+        <v>-24.9</v>
       </c>
       <c r="M2">
-        <v>-12.86</v>
+        <v>-12.34</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O2">
         <v>28</v>
       </c>
       <c r="P2">
-        <v>25.62</v>
+        <v>25.71</v>
       </c>
       <c r="Q2">
-        <v>26.29</v>
+        <v>26.22</v>
       </c>
       <c r="R2">
-        <v>27.11</v>
+        <v>27.07</v>
       </c>
       <c r="S2">
-        <v>28.02</v>
+        <v>27.99</v>
       </c>
       <c r="T2">
-        <v>-10.41</v>
+        <v>-7.65</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -909,34 +984,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.78</v>
+        <v>43.05</v>
       </c>
       <c r="Z2">
-        <v>-0.5</v>
+        <v>-0.47</v>
       </c>
       <c r="AA2">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="AB2">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="AC2">
-        <v>53.25</v>
+        <v>68.27</v>
       </c>
       <c r="AD2">
-        <v>47.28</v>
+        <v>60.16</v>
       </c>
       <c r="AE2">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AF2">
-        <v>21.97</v>
+        <v>38.73</v>
       </c>
       <c r="AG2">
-        <v>27.38</v>
+        <v>27.24</v>
       </c>
       <c r="AH2">
-        <v>25.19</v>
+        <v>25.2</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -945,7 +1020,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>54.64</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -956,10 +1031,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.210000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="D3">
-        <v>-4.46</v>
+        <v>5.86</v>
       </c>
       <c r="E3">
         <v>14.2</v>
@@ -968,46 +1043,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-35.14</v>
+        <v>-31.34</v>
       </c>
       <c r="H3">
-        <v>3.83</v>
+        <v>9.92</v>
       </c>
       <c r="I3">
-        <v>-2.54</v>
+        <v>4.61</v>
       </c>
       <c r="J3">
-        <v>-11.27</v>
+        <v>-5.25</v>
       </c>
       <c r="K3">
-        <v>-15.43</v>
+        <v>-11.6</v>
       </c>
       <c r="L3">
-        <v>-35.32</v>
+        <v>-30.95</v>
       </c>
       <c r="M3">
-        <v>-18.9</v>
+        <v>-17.83</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O3">
         <v>18</v>
       </c>
       <c r="P3">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="Q3">
-        <v>9.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="R3">
-        <v>10.3</v>
+        <v>10.28</v>
       </c>
       <c r="S3">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="T3">
-        <v>-14.96</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1022,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.83</v>
+        <v>47.03</v>
       </c>
       <c r="Z3">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="AA3">
         <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
         <v>75.76000000000001</v>
       </c>
       <c r="AD3">
-        <v>66.44</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AE3">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="AF3">
-        <v>31.06</v>
+        <v>48.86</v>
       </c>
       <c r="AG3">
-        <v>10.46</v>
+        <v>10.41</v>
       </c>
       <c r="AH3">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="AI3">
         <v>10.28</v>
@@ -1058,7 +1133,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>24.33</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1069,10 +1144,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>211</v>
+        <v>214.62</v>
       </c>
       <c r="D4">
-        <v>-2.51</v>
+        <v>1.72</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1081,46 +1156,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-32.99</v>
+        <v>-31.85</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="I4">
-        <v>-2.71</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>-9.98</v>
+        <v>-7.95</v>
       </c>
       <c r="K4">
-        <v>-9.59</v>
+        <v>-11.3</v>
       </c>
       <c r="L4">
-        <v>-30.06</v>
+        <v>-29.92</v>
       </c>
       <c r="M4">
-        <v>-5.09</v>
+        <v>-4.57</v>
       </c>
       <c r="N4">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="O4">
         <v>28</v>
       </c>
       <c r="P4">
-        <v>213.97</v>
+        <v>214.39</v>
       </c>
       <c r="Q4">
-        <v>223.63</v>
+        <v>222.81</v>
       </c>
       <c r="R4">
-        <v>237.83</v>
+        <v>237.13</v>
       </c>
       <c r="S4">
-        <v>247.42</v>
+        <v>247.01</v>
       </c>
       <c r="T4">
-        <v>-14.72</v>
+        <v>-13.11</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1135,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.02</v>
+        <v>35.63</v>
       </c>
       <c r="Z4">
-        <v>-6.48</v>
+        <v>-6.34</v>
       </c>
       <c r="AA4">
-        <v>-5.7</v>
+        <v>-5.83</v>
       </c>
       <c r="AB4">
-        <v>-0.78</v>
+        <v>-0.52</v>
       </c>
       <c r="AC4">
-        <v>47.58</v>
+        <v>48.02</v>
       </c>
       <c r="AD4">
-        <v>35.06</v>
+        <v>44.41</v>
       </c>
       <c r="AE4">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="AF4">
-        <v>-17.83</v>
+        <v>4.75</v>
       </c>
       <c r="AG4">
-        <v>238.11</v>
+        <v>237.39</v>
       </c>
       <c r="AH4">
-        <v>209.15</v>
+        <v>208.23</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1171,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>48.96</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1182,10 +1257,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>631.65</v>
+        <v>648.05</v>
       </c>
       <c r="D5">
-        <v>-3.92</v>
+        <v>2.6</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1194,25 +1269,25 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-26.63</v>
+        <v>-24.73</v>
       </c>
       <c r="H5">
-        <v>28.72</v>
+        <v>32.07</v>
       </c>
       <c r="I5">
-        <v>-5.18</v>
+        <v>-0.78</v>
       </c>
       <c r="J5">
-        <v>-9.6</v>
+        <v>-6.65</v>
       </c>
       <c r="K5">
-        <v>15.56</v>
+        <v>14.89</v>
       </c>
       <c r="L5">
-        <v>-24.09</v>
+        <v>-21.82</v>
       </c>
       <c r="M5">
-        <v>-8.779999999999999</v>
+        <v>-7.98</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1221,19 +1296,19 @@
         <v>58</v>
       </c>
       <c r="P5">
-        <v>650.5</v>
+        <v>649.48</v>
       </c>
       <c r="Q5">
-        <v>666.4400000000001</v>
+        <v>664.92</v>
       </c>
       <c r="R5">
-        <v>679.99</v>
+        <v>677.88</v>
       </c>
       <c r="S5">
-        <v>619.1</v>
+        <v>618.6900000000001</v>
       </c>
       <c r="T5">
-        <v>2.03</v>
+        <v>4.75</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1248,43 +1323,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>35.2</v>
+        <v>42.94</v>
       </c>
       <c r="Z5">
-        <v>-8.42</v>
+        <v>-8.65</v>
       </c>
       <c r="AA5">
-        <v>-5.16</v>
+        <v>-5.86</v>
       </c>
       <c r="AB5">
-        <v>-3.26</v>
+        <v>-2.8</v>
       </c>
       <c r="AC5">
-        <v>15.16</v>
+        <v>19.34</v>
       </c>
       <c r="AD5">
-        <v>12.86</v>
+        <v>16.55</v>
       </c>
       <c r="AE5">
-        <v>21.36</v>
+        <v>21.4</v>
       </c>
       <c r="AF5">
-        <v>-39.12</v>
+        <v>13.73</v>
       </c>
       <c r="AG5">
-        <v>693.6799999999999</v>
+        <v>692.73</v>
       </c>
       <c r="AH5">
-        <v>639.2</v>
+        <v>637.12</v>
       </c>
       <c r="AI5">
-        <v>707.99</v>
+        <v>705.24</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>28.01</v>
+        <v>31.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1295,10 +1370,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.39</v>
+        <v>24.69</v>
       </c>
       <c r="D6">
-        <v>-5.1</v>
+        <v>1.23</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1307,25 +1382,25 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-53.45</v>
+        <v>-52.88</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="I6">
-        <v>-5.72</v>
+        <v>-2.91</v>
       </c>
       <c r="J6">
-        <v>-11.76</v>
+        <v>-9.56</v>
       </c>
       <c r="K6">
-        <v>-20.68</v>
+        <v>-20.79</v>
       </c>
       <c r="L6">
-        <v>-53.37</v>
+        <v>-52.51</v>
       </c>
       <c r="M6">
-        <v>-16.81</v>
+        <v>-16.58</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1334,19 +1409,19 @@
         <v>5</v>
       </c>
       <c r="P6">
-        <v>25.44</v>
+        <v>25.29</v>
       </c>
       <c r="Q6">
-        <v>26.27</v>
+        <v>26.16</v>
       </c>
       <c r="R6">
-        <v>27.91</v>
+        <v>27.82</v>
       </c>
       <c r="S6">
-        <v>32.83</v>
+        <v>32.74</v>
       </c>
       <c r="T6">
-        <v>-25.7</v>
+        <v>-24.59</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1361,43 +1436,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>30.78</v>
+        <v>34.09</v>
       </c>
       <c r="Z6">
-        <v>-0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="AA6">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="AB6">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AC6">
-        <v>43.39</v>
+        <v>23.98</v>
       </c>
       <c r="AD6">
-        <v>38.26</v>
+        <v>37.05</v>
       </c>
       <c r="AE6">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="AF6">
-        <v>43.6</v>
+        <v>-12.02</v>
       </c>
       <c r="AG6">
-        <v>27.67</v>
+        <v>27.69</v>
       </c>
       <c r="AH6">
-        <v>24.86</v>
+        <v>24.62</v>
       </c>
       <c r="AI6">
-        <v>27.59</v>
+        <v>27.21</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>35.67</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1408,10 +1483,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1178</v>
+        <v>1170.3</v>
       </c>
       <c r="D7">
-        <v>-2.46</v>
+        <v>-0.65</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1420,25 +1495,25 @@
         <v>1167.7</v>
       </c>
       <c r="G7">
-        <v>-25.68</v>
+        <v>-26.16</v>
       </c>
       <c r="H7">
-        <v>0.88</v>
+        <v>0.22</v>
       </c>
       <c r="I7">
-        <v>-0.76</v>
+        <v>0.22</v>
       </c>
       <c r="J7">
-        <v>-10.04</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="K7">
-        <v>-7.95</v>
+        <v>-10.51</v>
       </c>
       <c r="L7">
-        <v>-13.2</v>
+        <v>-14.49</v>
       </c>
       <c r="M7">
-        <v>-0.53</v>
+        <v>-0.52</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1447,19 +1522,19 @@
         <v>47</v>
       </c>
       <c r="P7">
-        <v>1191.56</v>
+        <v>1192.08</v>
       </c>
       <c r="Q7">
-        <v>1223.08</v>
+        <v>1217.64</v>
       </c>
       <c r="R7">
-        <v>1273.9</v>
+        <v>1271.79</v>
       </c>
       <c r="S7">
-        <v>1351.92</v>
+        <v>1349.98</v>
       </c>
       <c r="T7">
-        <v>-12.86</v>
+        <v>-13.31</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1474,34 +1549,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.72</v>
+        <v>35.42</v>
       </c>
       <c r="Z7">
-        <v>-25.85</v>
+        <v>-26.79</v>
       </c>
       <c r="AA7">
-        <v>-24.7</v>
+        <v>-25.12</v>
       </c>
       <c r="AB7">
-        <v>-1.15</v>
+        <v>-1.68</v>
       </c>
       <c r="AC7">
-        <v>79.70999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="AD7">
-        <v>69.84</v>
+        <v>73.42</v>
       </c>
       <c r="AE7">
-        <v>22.48</v>
+        <v>22.21</v>
       </c>
       <c r="AF7">
-        <v>9.449999999999999</v>
+        <v>-6.51</v>
       </c>
       <c r="AG7">
-        <v>1287.42</v>
+        <v>1280.44</v>
       </c>
       <c r="AH7">
-        <v>1158.73</v>
+        <v>1154.84</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1510,7 +1585,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>51.42</v>
+        <v>50.99</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1671,12 +1746,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1685,7 +1795,886 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-10.04</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.89</v>
+      </c>
+      <c r="E7" s="7">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-11.27</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-5.25</v>
+      </c>
+      <c r="E8" s="7">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-9.98</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.95</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-9.6</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-11.76</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-9.56</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-10.04</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.2</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.73</v>
+      </c>
+      <c r="E13" s="7">
+        <v>4.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4.61</v>
+      </c>
+      <c r="E14" s="7">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.71</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.18</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.76</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-28.75</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-24.9</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-35.32</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-30.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-30.06</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-29.92</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-24.09</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-21.82</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-53.37</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-52.51</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-14.49</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-11.65</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-11.44</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-15.43</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-11.6</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-9.59</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-11.3</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15.56</v>
+      </c>
+      <c r="D28" s="6">
+        <v>14.89</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-20.68</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-20.79</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-7.95</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-27.54</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-25.38</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-35.14</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-31.34</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-32.99</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-31.85</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-26.63</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-24.73</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-53.45</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-52.88</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-25.68</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-26.16</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>25.1</v>
+      </c>
+      <c r="D37" s="6">
+        <v>25.85</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="D38" s="6">
+        <v>9.75</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>211</v>
+      </c>
+      <c r="D39" s="6">
+        <v>214.62</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>631.65</v>
+      </c>
+      <c r="D40" s="6">
+        <v>648.05</v>
+      </c>
+      <c r="E40" s="7">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>24.39</v>
+      </c>
+      <c r="D41" s="6">
+        <v>24.69</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1178</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1170.3</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-7.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6">
         <v>50</v>
+      </c>
+      <c r="D43" s="6">
+        <v>66</v>
+      </c>
+      <c r="E43" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6">
+        <v>34</v>
+      </c>
+      <c r="D44" s="6">
+        <v>50</v>
+      </c>
+      <c r="E44" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="6">
+        <v>66</v>
+      </c>
+      <c r="D45" s="6">
+        <v>34</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6">
+        <v>31.78</v>
+      </c>
+      <c r="D46" s="6">
+        <v>43.05</v>
+      </c>
+      <c r="E46" s="7">
+        <v>11.27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>32.83</v>
+      </c>
+      <c r="D47" s="6">
+        <v>47.03</v>
+      </c>
+      <c r="E47" s="7">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>29.02</v>
+      </c>
+      <c r="D48" s="6">
+        <v>35.63</v>
+      </c>
+      <c r="E48" s="7">
+        <v>6.61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>35.2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>42.94</v>
+      </c>
+      <c r="E49" s="7">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>30.78</v>
+      </c>
+      <c r="D50" s="6">
+        <v>34.09</v>
+      </c>
+      <c r="E50" s="7">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>36.72</v>
+      </c>
+      <c r="D51" s="6">
+        <v>35.42</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="6">
+        <v>21.97</v>
+      </c>
+      <c r="D52" s="6">
+        <v>38.73</v>
+      </c>
+      <c r="E52" s="7">
+        <v>16.76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>31.06</v>
+      </c>
+      <c r="D53" s="6">
+        <v>48.86</v>
+      </c>
+      <c r="E53" s="7">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-17.83</v>
+      </c>
+      <c r="D54" s="6">
+        <v>4.75</v>
+      </c>
+      <c r="E54" s="7">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-39.12</v>
+      </c>
+      <c r="D55" s="6">
+        <v>13.73</v>
+      </c>
+      <c r="E55" s="7">
+        <v>52.85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>43.6</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-12.02</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-55.62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-6.51</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-15.96</v>
       </c>
     </row>
   </sheetData>
@@ -1711,60 +2700,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>58</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
-        <v>32.7</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>39.7</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="6">
-        <v>-10.4</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-7.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1866,43 +2855,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="9">
-        <v>-0.0053</v>
-      </c>
-      <c r="B2" s="9">
-        <v>-0.0509</v>
-      </c>
-      <c r="C2" s="9">
-        <v>-0.08779999999999999</v>
-      </c>
-      <c r="D2" s="9">
-        <v>-0.1286</v>
-      </c>
-      <c r="E2" s="9">
-        <v>-0.1681</v>
-      </c>
-      <c r="F2" s="9">
-        <v>-0.189</v>
+      <c r="A2" s="14">
+        <v>-0.0052</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0457</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.07980000000000001</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1234</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1658</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.1783</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -954,7 +954,7 @@
         <v>66</v>
       </c>
       <c r="O2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P2">
         <v>25.71</v>
@@ -1067,7 +1067,7 @@
         <v>50</v>
       </c>
       <c r="O3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="P3">
         <v>9.56</v>
@@ -1180,7 +1180,7 @@
         <v>34</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P4">
         <v>214.39</v>
@@ -1293,7 +1293,7 @@
         <v>99</v>
       </c>
       <c r="O5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P5">
         <v>649.48</v>
@@ -1406,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="O6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P6">
         <v>25.29</v>
@@ -1519,7 +1519,7 @@
         <v>83</v>
       </c>
       <c r="O7">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="P7">
         <v>1192.08</v>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.0 → 35.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>35.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -918,10 +890,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.85</v>
+        <v>25.34</v>
       </c>
       <c r="D2">
-        <v>2.99</v>
+        <v>-1.97</v>
       </c>
       <c r="E2">
         <v>34.64</v>
@@ -930,46 +902,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.38</v>
+        <v>-26.85</v>
       </c>
       <c r="H2">
-        <v>12.49</v>
+        <v>10.27</v>
       </c>
       <c r="I2">
-        <v>1.73</v>
+        <v>-1.44</v>
       </c>
       <c r="J2">
-        <v>-4.89</v>
+        <v>-6.87</v>
       </c>
       <c r="K2">
-        <v>-11.44</v>
+        <v>-15.81</v>
       </c>
       <c r="L2">
-        <v>-24.9</v>
+        <v>-26.47</v>
       </c>
       <c r="M2">
-        <v>-12.34</v>
+        <v>-13.71</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>25.71</v>
+        <v>25.63</v>
       </c>
       <c r="Q2">
-        <v>26.22</v>
+        <v>26.13</v>
       </c>
       <c r="R2">
-        <v>27.07</v>
+        <v>27.03</v>
       </c>
       <c r="S2">
-        <v>27.99</v>
+        <v>27.96</v>
       </c>
       <c r="T2">
-        <v>-7.65</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -984,34 +956,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.05</v>
+        <v>38.4</v>
       </c>
       <c r="Z2">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="AA2">
         <v>-0.45</v>
       </c>
       <c r="AB2">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AC2">
-        <v>68.27</v>
+        <v>60.51</v>
       </c>
       <c r="AD2">
-        <v>60.16</v>
+        <v>60.68</v>
       </c>
       <c r="AE2">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="AF2">
-        <v>38.73</v>
+        <v>114.27</v>
       </c>
       <c r="AG2">
-        <v>27.24</v>
+        <v>27.15</v>
       </c>
       <c r="AH2">
-        <v>25.2</v>
+        <v>25.12</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1020,7 +992,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>55.47</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1003,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.75</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D3">
-        <v>5.86</v>
+        <v>-0.51</v>
       </c>
       <c r="E3">
         <v>14.2</v>
@@ -1043,46 +1015,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.34</v>
+        <v>-31.69</v>
       </c>
       <c r="H3">
-        <v>9.92</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I3">
-        <v>4.61</v>
+        <v>3.19</v>
       </c>
       <c r="J3">
-        <v>-5.25</v>
+        <v>-5.09</v>
       </c>
       <c r="K3">
-        <v>-11.6</v>
+        <v>-13.7</v>
       </c>
       <c r="L3">
-        <v>-30.95</v>
+        <v>-30.86</v>
       </c>
       <c r="M3">
-        <v>-17.83</v>
+        <v>-18.24</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>9.56</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q3">
-        <v>9.789999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="R3">
-        <v>10.28</v>
+        <v>10.26</v>
       </c>
       <c r="S3">
-        <v>10.82</v>
+        <v>10.8</v>
       </c>
       <c r="T3">
-        <v>-9.859999999999999</v>
+        <v>-10.2</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1097,31 +1069,31 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>47.03</v>
+        <v>46.06</v>
       </c>
       <c r="Z3">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AA3">
         <v>-0.24</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AC3">
-        <v>75.76000000000001</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="AD3">
-        <v>74.84999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="AE3">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="AF3">
-        <v>48.86</v>
+        <v>-10.24</v>
       </c>
       <c r="AG3">
-        <v>10.41</v>
+        <v>10.36</v>
       </c>
       <c r="AH3">
         <v>9.17</v>
@@ -1133,7 +1105,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>21.44</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1116,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>214.62</v>
+        <v>213.45</v>
       </c>
       <c r="D4">
-        <v>1.72</v>
+        <v>-0.55</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1156,46 +1128,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-31.85</v>
+        <v>-32.22</v>
       </c>
       <c r="H4">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="J4">
-        <v>-7.95</v>
+        <v>-7.6</v>
       </c>
       <c r="K4">
-        <v>-11.3</v>
+        <v>-11.58</v>
       </c>
       <c r="L4">
-        <v>-29.92</v>
+        <v>-31.12</v>
       </c>
       <c r="M4">
-        <v>-4.57</v>
+        <v>-4.72</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>214.39</v>
+        <v>214.68</v>
       </c>
       <c r="Q4">
-        <v>222.81</v>
+        <v>221.97</v>
       </c>
       <c r="R4">
-        <v>237.13</v>
+        <v>236.46</v>
       </c>
       <c r="S4">
-        <v>247.01</v>
+        <v>246.58</v>
       </c>
       <c r="T4">
-        <v>-13.11</v>
+        <v>-13.44</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.63</v>
+        <v>34.51</v>
       </c>
       <c r="Z4">
-        <v>-6.34</v>
+        <v>-6.26</v>
       </c>
       <c r="AA4">
-        <v>-5.83</v>
+        <v>-5.92</v>
       </c>
       <c r="AB4">
-        <v>-0.52</v>
+        <v>-0.34</v>
       </c>
       <c r="AC4">
-        <v>48.02</v>
+        <v>49.03</v>
       </c>
       <c r="AD4">
-        <v>44.41</v>
+        <v>48.21</v>
       </c>
       <c r="AE4">
-        <v>4.86</v>
+        <v>4.9</v>
       </c>
       <c r="AF4">
-        <v>4.75</v>
+        <v>-41.91</v>
       </c>
       <c r="AG4">
-        <v>237.39</v>
+        <v>236.68</v>
       </c>
       <c r="AH4">
-        <v>208.23</v>
+        <v>207.26</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1246,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>49.13</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1229,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>648.05</v>
+        <v>654.95</v>
       </c>
       <c r="D5">
-        <v>2.6</v>
+        <v>1.06</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1269,46 +1241,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-24.73</v>
+        <v>-23.93</v>
       </c>
       <c r="H5">
-        <v>32.07</v>
+        <v>33.47</v>
       </c>
       <c r="I5">
-        <v>-0.78</v>
+        <v>0.55</v>
       </c>
       <c r="J5">
-        <v>-6.65</v>
+        <v>-3.46</v>
       </c>
       <c r="K5">
-        <v>14.89</v>
+        <v>-3.24</v>
       </c>
       <c r="L5">
-        <v>-21.82</v>
+        <v>-20.4</v>
       </c>
       <c r="M5">
-        <v>-7.98</v>
+        <v>-7.26</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>649.48</v>
+        <v>650.2</v>
       </c>
       <c r="Q5">
-        <v>664.92</v>
+        <v>664.23</v>
       </c>
       <c r="R5">
-        <v>677.88</v>
+        <v>676.14</v>
       </c>
       <c r="S5">
-        <v>618.6900000000001</v>
+        <v>618.28</v>
       </c>
       <c r="T5">
-        <v>4.75</v>
+        <v>5.93</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1323,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>42.94</v>
+        <v>45.86</v>
       </c>
       <c r="Z5">
-        <v>-8.65</v>
+        <v>-8.18</v>
       </c>
       <c r="AA5">
-        <v>-5.86</v>
+        <v>-6.32</v>
       </c>
       <c r="AB5">
-        <v>-2.8</v>
+        <v>-1.86</v>
       </c>
       <c r="AC5">
-        <v>19.34</v>
+        <v>29.57</v>
       </c>
       <c r="AD5">
-        <v>16.55</v>
+        <v>21.36</v>
       </c>
       <c r="AE5">
-        <v>21.4</v>
+        <v>20.95</v>
       </c>
       <c r="AF5">
-        <v>13.73</v>
+        <v>-18.09</v>
       </c>
       <c r="AG5">
-        <v>692.73</v>
+        <v>692.3200000000001</v>
       </c>
       <c r="AH5">
-        <v>637.12</v>
+        <v>636.14</v>
       </c>
       <c r="AI5">
         <v>705.24</v>
@@ -1359,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>31.87</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1342,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.69</v>
+        <v>25.02</v>
       </c>
       <c r="D6">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1382,25 +1354,25 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-52.88</v>
+        <v>-52.25</v>
       </c>
       <c r="H6">
-        <v>1.23</v>
+        <v>2.58</v>
       </c>
       <c r="I6">
-        <v>-2.91</v>
+        <v>-1.65</v>
       </c>
       <c r="J6">
-        <v>-9.56</v>
+        <v>-7.06</v>
       </c>
       <c r="K6">
-        <v>-20.79</v>
+        <v>-21.3</v>
       </c>
       <c r="L6">
-        <v>-52.51</v>
+        <v>-51.84</v>
       </c>
       <c r="M6">
-        <v>-16.58</v>
+        <v>-19.34</v>
       </c>
       <c r="N6">
         <v>17</v>
@@ -1409,19 +1381,19 @@
         <v>6</v>
       </c>
       <c r="P6">
-        <v>25.29</v>
+        <v>25.2</v>
       </c>
       <c r="Q6">
-        <v>26.16</v>
+        <v>26.07</v>
       </c>
       <c r="R6">
-        <v>27.82</v>
+        <v>27.73</v>
       </c>
       <c r="S6">
-        <v>32.74</v>
+        <v>32.65</v>
       </c>
       <c r="T6">
-        <v>-24.59</v>
+        <v>-23.38</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1436,34 +1408,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.09</v>
+        <v>37.61</v>
       </c>
       <c r="Z6">
         <v>-0.8</v>
       </c>
       <c r="AA6">
-        <v>-0.72</v>
+        <v>-0.73</v>
       </c>
       <c r="AB6">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="AC6">
-        <v>23.98</v>
+        <v>24.05</v>
       </c>
       <c r="AD6">
-        <v>37.05</v>
+        <v>30.47</v>
       </c>
       <c r="AE6">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AF6">
-        <v>-12.02</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="AG6">
-        <v>27.69</v>
+        <v>27.65</v>
       </c>
       <c r="AH6">
-        <v>24.62</v>
+        <v>24.49</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1472,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>38.2</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1483,58 +1455,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1170.3</v>
+        <v>1158.9</v>
       </c>
       <c r="D7">
-        <v>-0.65</v>
+        <v>-0.97</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1167.7</v>
+        <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-26.16</v>
+        <v>-26.88</v>
       </c>
       <c r="H7">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.22</v>
+        <v>-2.32</v>
       </c>
       <c r="J7">
-        <v>-9.619999999999999</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="K7">
-        <v>-10.51</v>
+        <v>-10.64</v>
       </c>
       <c r="L7">
-        <v>-14.49</v>
+        <v>-15.93</v>
       </c>
       <c r="M7">
-        <v>-0.52</v>
+        <v>-0.83</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P7">
-        <v>1192.08</v>
+        <v>1186.58</v>
       </c>
       <c r="Q7">
-        <v>1217.64</v>
+        <v>1211.89</v>
       </c>
       <c r="R7">
-        <v>1271.79</v>
+        <v>1269.11</v>
       </c>
       <c r="S7">
-        <v>1349.98</v>
+        <v>1347.94</v>
       </c>
       <c r="T7">
-        <v>-13.31</v>
+        <v>-14.02</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1549,34 +1521,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.42</v>
+        <v>33.52</v>
       </c>
       <c r="Z7">
-        <v>-26.79</v>
+        <v>-28.14</v>
       </c>
       <c r="AA7">
-        <v>-25.12</v>
+        <v>-25.72</v>
       </c>
       <c r="AB7">
-        <v>-1.68</v>
+        <v>-2.42</v>
       </c>
       <c r="AC7">
-        <v>61.2</v>
+        <v>43.26</v>
       </c>
       <c r="AD7">
-        <v>73.42</v>
+        <v>61.39</v>
       </c>
       <c r="AE7">
-        <v>22.21</v>
+        <v>22.93</v>
       </c>
       <c r="AF7">
-        <v>-6.51</v>
+        <v>-13.11</v>
       </c>
       <c r="AG7">
-        <v>1280.44</v>
+        <v>1274.03</v>
       </c>
       <c r="AH7">
-        <v>1154.84</v>
+        <v>1149.74</v>
       </c>
       <c r="AI7">
         <v>1234.36</v>
@@ -1585,7 +1557,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>50.99</v>
+        <v>51.14</v>
       </c>
     </row>
   </sheetData>
@@ -1726,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1746,47 +1718,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1794,662 +1731,662 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.04</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.89</v>
       </c>
-      <c r="E7" s="7">
-        <v>5.15</v>
+      <c r="D7" s="5">
+        <v>-6.87</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-11.27</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.25</v>
       </c>
+      <c r="D8" s="5">
+        <v>-5.09</v>
+      </c>
       <c r="E8" s="7">
-        <v>6.02</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-9.98</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-7.95</v>
       </c>
+      <c r="D9" s="5">
+        <v>-7.6</v>
+      </c>
       <c r="E9" s="7">
-        <v>2.03</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-9.6</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-6.65</v>
       </c>
+      <c r="D10" s="5">
+        <v>-3.46</v>
+      </c>
       <c r="E10" s="7">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-9.56</v>
       </c>
+      <c r="D11" s="5">
+        <v>-7.06</v>
+      </c>
       <c r="E11" s="7">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-10.04</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-9.619999999999999</v>
       </c>
+      <c r="D12" s="5">
+        <v>-9.390000000000001</v>
+      </c>
       <c r="E12" s="7">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
-        <v>-3.2</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>1.73</v>
       </c>
-      <c r="E13" s="7">
-        <v>4.93</v>
+      <c r="D13" s="5">
+        <v>-1.44</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
+        <v>4.61</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3.19</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.68</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.78</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.55</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-2.91</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.65</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.32</v>
+      </c>
+      <c r="E18" s="6">
         <v>-2.54</v>
       </c>
-      <c r="D14" s="6">
-        <v>4.61</v>
-      </c>
-      <c r="E14" s="7">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-24.9</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.47</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-30.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-30.86</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.71</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-29.92</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-31.12</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.18</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E16" s="7">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-21.82</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-20.4</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-52.51</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-51.84</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-14.49</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-15.93</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-28.75</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-24.9</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-11.44</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-15.81</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-35.32</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-30.95</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4.37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-11.6</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-13.7</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-30.06</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-29.92</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-11.3</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-11.58</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-24.09</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-21.82</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>14.89</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-3.24</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-18.13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-53.37</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-52.51</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-20.79</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-21.3</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-13.2</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-14.49</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-10.51</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.64</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-11.65</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-11.44</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-25.38</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-26.85</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-15.43</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-11.6</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-31.34</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-31.69</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-9.59</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-31.85</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-32.22</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>15.56</v>
-      </c>
-      <c r="D28" s="6">
-        <v>14.89</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-24.73</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-23.93</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-20.68</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.88</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-52.25</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-7.95</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-10.51</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.56</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-26.16</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-26.88</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-27.54</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-25.38</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>25.85</v>
+      </c>
+      <c r="D37" s="5">
+        <v>25.34</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-31.34</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.75</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-32.99</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-31.85</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>214.62</v>
+      </c>
+      <c r="D39" s="5">
+        <v>213.45</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-26.63</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-24.73</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>648.05</v>
+      </c>
+      <c r="D40" s="5">
+        <v>654.95</v>
+      </c>
+      <c r="E40" s="7">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-53.45</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-52.88</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>24.69</v>
+      </c>
+      <c r="D41" s="5">
+        <v>25.02</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-25.68</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-26.16</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
+      <c r="B42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="6">
-        <v>25.1</v>
-      </c>
-      <c r="D37" s="6">
-        <v>25.85</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="C42" s="5">
+        <v>1170.3</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1158.9</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-11.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="D38" s="6">
-        <v>9.75</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="5">
+        <v>50</v>
+      </c>
+      <c r="D43" s="5">
+        <v>34</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>211</v>
-      </c>
-      <c r="D39" s="6">
-        <v>214.62</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>631.65</v>
-      </c>
-      <c r="D40" s="6">
-        <v>648.05</v>
-      </c>
-      <c r="E40" s="7">
-        <v>16.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>24.39</v>
-      </c>
-      <c r="D41" s="6">
-        <v>24.69</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1178</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1170.3</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-7.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="B44" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C43" s="6">
-        <v>50</v>
-      </c>
-      <c r="D43" s="6">
-        <v>66</v>
-      </c>
-      <c r="E43" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>34</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>50</v>
       </c>
       <c r="E44" s="7">
@@ -2457,224 +2394,207 @@
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>43.05</v>
+      </c>
+      <c r="D45" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-4.65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>47.03</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46.06</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="6">
-        <v>66</v>
-      </c>
-      <c r="D45" s="6">
-        <v>34</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>35.63</v>
+      </c>
+      <c r="D47" s="5">
+        <v>34.51</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>42.94</v>
+      </c>
+      <c r="D48" s="5">
+        <v>45.86</v>
+      </c>
+      <c r="E48" s="7">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>34.09</v>
+      </c>
+      <c r="D49" s="5">
+        <v>37.61</v>
+      </c>
+      <c r="E49" s="7">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>35.42</v>
+      </c>
+      <c r="D50" s="5">
+        <v>33.52</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>31.78</v>
-      </c>
-      <c r="D46" s="6">
-        <v>43.05</v>
-      </c>
-      <c r="E46" s="7">
-        <v>11.27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>38.73</v>
+      </c>
+      <c r="D51" s="5">
+        <v>114.27</v>
+      </c>
+      <c r="E51" s="7">
+        <v>75.54000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>32.83</v>
-      </c>
-      <c r="D47" s="6">
-        <v>47.03</v>
-      </c>
-      <c r="E47" s="7">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>48.86</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-10.24</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-59.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>29.02</v>
-      </c>
-      <c r="D48" s="6">
-        <v>35.63</v>
-      </c>
-      <c r="E48" s="7">
-        <v>6.61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4.75</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-41.91</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-46.66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>35.2</v>
-      </c>
-      <c r="D49" s="6">
-        <v>42.94</v>
-      </c>
-      <c r="E49" s="7">
-        <v>7.74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="5">
+        <v>13.73</v>
+      </c>
+      <c r="D54" s="5">
+        <v>-18.09</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-31.82</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>30.78</v>
-      </c>
-      <c r="D50" s="6">
-        <v>34.09</v>
-      </c>
-      <c r="E50" s="7">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-12.02</v>
+      </c>
+      <c r="D55" s="5">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="E55" s="7">
+        <v>95.76000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>36.72</v>
-      </c>
-      <c r="D51" s="6">
-        <v>35.42</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="6">
-        <v>21.97</v>
-      </c>
-      <c r="D52" s="6">
-        <v>38.73</v>
-      </c>
-      <c r="E52" s="7">
-        <v>16.76</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>31.06</v>
-      </c>
-      <c r="D53" s="6">
-        <v>48.86</v>
-      </c>
-      <c r="E53" s="7">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>-17.83</v>
-      </c>
-      <c r="D54" s="6">
-        <v>4.75</v>
-      </c>
-      <c r="E54" s="7">
-        <v>22.58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>-39.12</v>
-      </c>
-      <c r="D55" s="6">
-        <v>13.73</v>
-      </c>
-      <c r="E55" s="7">
-        <v>52.85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>43.6</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-12.02</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-55.62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C56" s="5">
         <v>-6.51</v>
       </c>
-      <c r="E57" s="8">
-        <v>-15.96</v>
+      <c r="D56" s="5">
+        <v>-13.11</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-6.6</v>
       </c>
     </row>
   </sheetData>
@@ -2700,60 +2620,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>41.28</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2855,43 +2775,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>-0.0052</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0457</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.07980000000000001</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1234</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1658</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.1783</v>
+      <c r="A2" s="13">
+        <v>-0.0083</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0472</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0726</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1371</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1824</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.1934</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,10 +163,52 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.5 → 50.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>50.4</t>
+  </si>
+  <si>
+    <t>57.8 → 49.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>49.6</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,17 +410,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -750,7 +794,10 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -890,10 +937,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.34</v>
+        <v>26.37</v>
       </c>
       <c r="D2">
-        <v>-1.97</v>
+        <v>-3.62</v>
       </c>
       <c r="E2">
         <v>34.64</v>
@@ -902,46 +949,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.85</v>
+        <v>-23.87</v>
       </c>
       <c r="H2">
-        <v>10.27</v>
+        <v>14.75</v>
       </c>
       <c r="I2">
-        <v>-1.44</v>
+        <v>1.03</v>
       </c>
       <c r="J2">
-        <v>-6.87</v>
+        <v>-2.26</v>
       </c>
       <c r="K2">
-        <v>-15.81</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L2">
-        <v>-26.47</v>
+        <v>-22.46</v>
       </c>
       <c r="M2">
-        <v>-13.71</v>
+        <v>-13.13</v>
       </c>
       <c r="N2">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="O2">
+        <v>35</v>
+      </c>
+      <c r="P2">
         <v>26</v>
       </c>
-      <c r="P2">
-        <v>25.63</v>
-      </c>
       <c r="Q2">
-        <v>26.13</v>
+        <v>26.14</v>
       </c>
       <c r="R2">
-        <v>27.03</v>
+        <v>27</v>
       </c>
       <c r="S2">
-        <v>27.96</v>
+        <v>27.91</v>
       </c>
       <c r="T2">
-        <v>-9.359999999999999</v>
+        <v>-5.51</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -956,34 +1003,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.4</v>
+        <v>49.57</v>
       </c>
       <c r="Z2">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="AA2">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="AB2">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="AC2">
-        <v>60.51</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="AD2">
-        <v>60.68</v>
+        <v>75.23</v>
       </c>
       <c r="AE2">
-        <v>0.87</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
-        <v>114.27</v>
+        <v>37.33</v>
       </c>
       <c r="AG2">
-        <v>27.15</v>
+        <v>27.21</v>
       </c>
       <c r="AH2">
-        <v>25.12</v>
+        <v>25.06</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -992,7 +1039,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>56.99</v>
+        <v>43.46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1050,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.699999999999999</v>
+        <v>10.84</v>
       </c>
       <c r="D3">
-        <v>-0.51</v>
+        <v>-2.78</v>
       </c>
       <c r="E3">
         <v>14.2</v>
@@ -1015,46 +1062,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-31.69</v>
+        <v>-23.66</v>
       </c>
       <c r="H3">
-        <v>9.359999999999999</v>
+        <v>22.21</v>
       </c>
       <c r="I3">
-        <v>3.19</v>
+        <v>12.45</v>
       </c>
       <c r="J3">
-        <v>-5.09</v>
+        <v>5.96</v>
       </c>
       <c r="K3">
-        <v>-13.7</v>
+        <v>-3.3</v>
       </c>
       <c r="L3">
-        <v>-30.86</v>
+        <v>-22.35</v>
       </c>
       <c r="M3">
-        <v>-18.24</v>
+        <v>-16.59</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="P3">
-        <v>9.619999999999999</v>
+        <v>10.13</v>
       </c>
       <c r="Q3">
-        <v>9.76</v>
+        <v>9.85</v>
       </c>
       <c r="R3">
-        <v>10.26</v>
+        <v>10.27</v>
       </c>
       <c r="S3">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="T3">
-        <v>-10.2</v>
+        <v>0.51</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1066,46 +1113,46 @@
         <v>44</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>46.06</v>
+        <v>61.63</v>
       </c>
       <c r="Z3">
-        <v>-0.21</v>
+        <v>0.01</v>
       </c>
       <c r="AA3">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="AB3">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="AC3">
-        <v>80.29000000000001</v>
+        <v>94.44</v>
       </c>
       <c r="AD3">
-        <v>77.27</v>
+        <v>91.13</v>
       </c>
       <c r="AE3">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="AF3">
-        <v>-10.24</v>
+        <v>207.26</v>
       </c>
       <c r="AG3">
-        <v>10.36</v>
+        <v>10.81</v>
       </c>
       <c r="AH3">
-        <v>9.17</v>
+        <v>8.9</v>
       </c>
       <c r="AI3">
-        <v>10.28</v>
+        <v>9.4</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>19.52</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1163,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>213.45</v>
+        <v>219</v>
       </c>
       <c r="D4">
-        <v>-0.55</v>
+        <v>0.55</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1128,46 +1175,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-32.22</v>
+        <v>-30.45</v>
       </c>
       <c r="H4">
-        <v>1.16</v>
+        <v>3.79</v>
       </c>
       <c r="I4">
-        <v>0.68</v>
+        <v>1.18</v>
       </c>
       <c r="J4">
-        <v>-7.6</v>
+        <v>-4.74</v>
       </c>
       <c r="K4">
-        <v>-11.58</v>
+        <v>-7.43</v>
       </c>
       <c r="L4">
-        <v>-31.12</v>
+        <v>-28.75</v>
       </c>
       <c r="M4">
-        <v>-4.72</v>
+        <v>-3.94</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>214.68</v>
+        <v>215.17</v>
       </c>
       <c r="Q4">
-        <v>221.97</v>
+        <v>221.03</v>
       </c>
       <c r="R4">
-        <v>236.46</v>
+        <v>234.81</v>
       </c>
       <c r="S4">
-        <v>246.58</v>
+        <v>245.78</v>
       </c>
       <c r="T4">
-        <v>-13.44</v>
+        <v>-10.89</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,34 +1229,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.51</v>
+        <v>43.7</v>
       </c>
       <c r="Z4">
-        <v>-6.26</v>
+        <v>-5.23</v>
       </c>
       <c r="AA4">
-        <v>-5.92</v>
+        <v>-5.76</v>
       </c>
       <c r="AB4">
-        <v>-0.34</v>
+        <v>0.52</v>
       </c>
       <c r="AC4">
-        <v>49.03</v>
+        <v>82.22</v>
       </c>
       <c r="AD4">
-        <v>48.21</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AE4">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="AF4">
-        <v>-41.91</v>
+        <v>-5.76</v>
       </c>
       <c r="AG4">
-        <v>236.68</v>
+        <v>235.26</v>
       </c>
       <c r="AH4">
-        <v>207.26</v>
+        <v>206.81</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1218,7 +1265,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>47.05</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1276,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>654.95</v>
+        <v>682.75</v>
       </c>
       <c r="D5">
-        <v>1.06</v>
+        <v>1.47</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1241,46 +1288,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-23.93</v>
+        <v>-20.7</v>
       </c>
       <c r="H5">
-        <v>33.47</v>
+        <v>39.14</v>
       </c>
       <c r="I5">
-        <v>0.55</v>
+        <v>3.86</v>
       </c>
       <c r="J5">
-        <v>-3.46</v>
+        <v>2.58</v>
       </c>
       <c r="K5">
-        <v>-3.24</v>
+        <v>-15.09</v>
       </c>
       <c r="L5">
-        <v>-20.4</v>
+        <v>-17.02</v>
       </c>
       <c r="M5">
-        <v>-7.26</v>
+        <v>-6.1</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="O5">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>650.2</v>
+        <v>658.05</v>
       </c>
       <c r="Q5">
-        <v>664.23</v>
+        <v>665.64</v>
       </c>
       <c r="R5">
-        <v>676.14</v>
+        <v>674.71</v>
       </c>
       <c r="S5">
-        <v>618.28</v>
+        <v>617.72</v>
       </c>
       <c r="T5">
-        <v>5.93</v>
+        <v>10.53</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,34 +1342,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>45.86</v>
+        <v>55.94</v>
       </c>
       <c r="Z5">
-        <v>-8.18</v>
+        <v>-3.95</v>
       </c>
       <c r="AA5">
-        <v>-6.32</v>
+        <v>-5.84</v>
       </c>
       <c r="AB5">
-        <v>-1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AC5">
-        <v>29.57</v>
+        <v>78.52</v>
       </c>
       <c r="AD5">
-        <v>21.36</v>
+        <v>55.24</v>
       </c>
       <c r="AE5">
-        <v>20.95</v>
+        <v>21.16</v>
       </c>
       <c r="AF5">
-        <v>-18.09</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="AG5">
-        <v>692.3200000000001</v>
+        <v>695.09</v>
       </c>
       <c r="AH5">
-        <v>636.14</v>
+        <v>636.2</v>
       </c>
       <c r="AI5">
         <v>705.24</v>
@@ -1331,7 +1378,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>32.4</v>
+        <v>27.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1389,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.02</v>
+        <v>26.48</v>
       </c>
       <c r="D6">
-        <v>1.34</v>
+        <v>0.95</v>
       </c>
       <c r="E6">
         <v>52.4</v>
@@ -1354,46 +1401,46 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-52.25</v>
+        <v>-49.47</v>
       </c>
       <c r="H6">
-        <v>2.58</v>
+        <v>8.57</v>
       </c>
       <c r="I6">
-        <v>-1.65</v>
+        <v>3.04</v>
       </c>
       <c r="J6">
-        <v>-7.06</v>
+        <v>-0.6</v>
       </c>
       <c r="K6">
-        <v>-21.3</v>
+        <v>-16.62</v>
       </c>
       <c r="L6">
-        <v>-51.84</v>
+        <v>-49.38</v>
       </c>
       <c r="M6">
-        <v>-19.34</v>
+        <v>-19.59</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>25.2</v>
+        <v>25.36</v>
       </c>
       <c r="Q6">
         <v>26.07</v>
       </c>
       <c r="R6">
-        <v>27.73</v>
+        <v>27.61</v>
       </c>
       <c r="S6">
-        <v>32.65</v>
+        <v>32.48</v>
       </c>
       <c r="T6">
-        <v>-23.38</v>
+        <v>-18.47</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1408,34 +1455,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.61</v>
+        <v>50.41</v>
       </c>
       <c r="Z6">
-        <v>-0.8</v>
+        <v>-0.57</v>
       </c>
       <c r="AA6">
-        <v>-0.73</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AB6">
-        <v>-0.06</v>
+        <v>0.12</v>
       </c>
       <c r="AC6">
-        <v>24.05</v>
+        <v>82.88</v>
       </c>
       <c r="AD6">
-        <v>30.47</v>
+        <v>54.77</v>
       </c>
       <c r="AE6">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="AF6">
-        <v>83.73999999999999</v>
+        <v>60.09</v>
       </c>
       <c r="AG6">
         <v>27.65</v>
       </c>
       <c r="AH6">
-        <v>24.49</v>
+        <v>24.5</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1444,7 +1491,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>35.69</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1455,10 +1502,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1158.9</v>
+        <v>1174.6</v>
       </c>
       <c r="D7">
-        <v>-0.97</v>
+        <v>0.68</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1467,25 +1514,25 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-26.88</v>
+        <v>-25.89</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="I7">
-        <v>-2.32</v>
+        <v>-2.74</v>
       </c>
       <c r="J7">
-        <v>-9.390000000000001</v>
+        <v>-6.59</v>
       </c>
       <c r="K7">
-        <v>-10.64</v>
+        <v>-9.33</v>
       </c>
       <c r="L7">
-        <v>-15.93</v>
+        <v>-14.35</v>
       </c>
       <c r="M7">
-        <v>-0.83</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1494,19 +1541,19 @@
         <v>41</v>
       </c>
       <c r="P7">
-        <v>1186.58</v>
+        <v>1169.7</v>
       </c>
       <c r="Q7">
-        <v>1211.89</v>
+        <v>1204.31</v>
       </c>
       <c r="R7">
-        <v>1269.11</v>
+        <v>1263.4</v>
       </c>
       <c r="S7">
-        <v>1347.94</v>
+        <v>1344.07</v>
       </c>
       <c r="T7">
-        <v>-14.02</v>
+        <v>-12.61</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1521,43 +1568,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.52</v>
+        <v>38.59</v>
       </c>
       <c r="Z7">
-        <v>-28.14</v>
+        <v>-27.38</v>
       </c>
       <c r="AA7">
-        <v>-25.72</v>
+        <v>-26.46</v>
       </c>
       <c r="AB7">
-        <v>-2.42</v>
+        <v>-0.92</v>
       </c>
       <c r="AC7">
-        <v>43.26</v>
+        <v>48.36</v>
       </c>
       <c r="AD7">
-        <v>61.39</v>
+        <v>44.5</v>
       </c>
       <c r="AE7">
-        <v>22.93</v>
+        <v>22.65</v>
       </c>
       <c r="AF7">
-        <v>-13.11</v>
+        <v>-16.36</v>
       </c>
       <c r="AG7">
-        <v>1274.03</v>
+        <v>1265.87</v>
       </c>
       <c r="AH7">
-        <v>1149.74</v>
+        <v>1142.75</v>
       </c>
       <c r="AI7">
-        <v>1234.36</v>
+        <v>1227.59</v>
       </c>
       <c r="AJ7" t="s">
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>51.14</v>
+        <v>47.1</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1708,7 +1755,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1718,889 +1765,944 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.89</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-6.87</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-2.26</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.25</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-5.09</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="7">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5.96</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-7.6</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="7">
+        <v>-5.41</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-4.74</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.65</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-3.46</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="C11" s="7">
+        <v>0.61</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2.58</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.56</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-7.06</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="7">
+        <v>-2.24</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="C13" s="7">
+        <v>-8.42</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.59</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-1.44</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-3.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="7">
+        <v>6.13</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.03</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>4.61</v>
-      </c>
-      <c r="D14" s="5">
-        <v>3.19</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="C15" s="7">
+        <v>13.78</v>
+      </c>
+      <c r="D15" s="7">
+        <v>12.45</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.68</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1.18</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.78</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="C17" s="7">
+        <v>2.11</v>
+      </c>
+      <c r="D17" s="7">
+        <v>3.86</v>
+      </c>
+      <c r="E17" s="9">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-2.91</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-1.65</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="C18" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="D18" s="7">
+        <v>3.04</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="C19" s="7">
+        <v>-4.21</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-2.74</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-24.9</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-26.47</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="C20" s="7">
+        <v>-20.05</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-22.46</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-30.95</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-30.86</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="C21" s="7">
+        <v>-20.24</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-22.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-29.92</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-31.12</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="C22" s="7">
+        <v>-28.51</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-28.75</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>-21.82</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-20.4</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="C23" s="7">
+        <v>-17.85</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-17.02</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-52.51</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-51.84</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="C24" s="7">
+        <v>-49.8</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-49.38</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-14.49</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-15.93</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="C25" s="7">
+        <v>-14.28</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-14.35</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-11.44</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-15.81</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="C26" s="7">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-11.6</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-13.7</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="C27" s="7">
+        <v>-1.15</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-3.3</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="5">
-        <v>-11.3</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-11.58</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="C28" s="7">
+        <v>-7.7</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-7.43</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>14.89</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-3.24</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-18.13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="C29" s="7">
+        <v>-14.85</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-15.09</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-20.79</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-21.3</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="C30" s="7">
+        <v>-17.93</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-16.62</v>
+      </c>
+      <c r="E30" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-10.51</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.64</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="C31" s="7">
+        <v>-9.77</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-9.33</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-25.38</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.85</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="C32" s="7">
+        <v>-21.02</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-23.87</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="5">
-        <v>-31.34</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-31.69</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="C33" s="7">
+        <v>-21.48</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-23.66</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="5">
-        <v>-31.85</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-32.22</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="C34" s="7">
+        <v>-30.84</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-30.45</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="5">
-        <v>-24.73</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-23.93</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="C35" s="7">
+        <v>-21.85</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-20.7</v>
+      </c>
+      <c r="E35" s="9">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="5">
-        <v>-52.88</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-52.25</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="C36" s="7">
+        <v>-49.94</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-49.47</v>
+      </c>
+      <c r="E36" s="9">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="5">
-        <v>-26.16</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-26.88</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="C37" s="7">
+        <v>-26.39</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-25.89</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="5">
-        <v>25.85</v>
-      </c>
-      <c r="D37" s="5">
-        <v>25.34</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="C38" s="7">
+        <v>27.36</v>
+      </c>
+      <c r="D38" s="7">
+        <v>26.37</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="5">
-        <v>9.75</v>
-      </c>
-      <c r="D38" s="5">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="C39" s="7">
+        <v>11.15</v>
+      </c>
+      <c r="D39" s="7">
+        <v>10.84</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="5">
-        <v>214.62</v>
-      </c>
-      <c r="D39" s="5">
-        <v>213.45</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="C40" s="7">
+        <v>217.8</v>
+      </c>
+      <c r="D40" s="7">
+        <v>219</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="5">
-        <v>648.05</v>
-      </c>
-      <c r="D40" s="5">
-        <v>654.95</v>
-      </c>
-      <c r="E40" s="7">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="C41" s="7">
+        <v>672.85</v>
+      </c>
+      <c r="D41" s="7">
+        <v>682.75</v>
+      </c>
+      <c r="E41" s="9">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="5">
-        <v>24.69</v>
-      </c>
-      <c r="D41" s="5">
-        <v>25.02</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="C42" s="7">
+        <v>26.23</v>
+      </c>
+      <c r="D42" s="7">
+        <v>26.48</v>
+      </c>
+      <c r="E42" s="9">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="5">
-        <v>1170.3</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1158.9</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-11.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="C43" s="7">
+        <v>1166.7</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1174.6</v>
+      </c>
+      <c r="E43" s="9">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="7">
+        <v>66</v>
+      </c>
+      <c r="D44" s="7">
+        <v>50</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="7">
+        <v>50</v>
+      </c>
+      <c r="D45" s="7">
+        <v>66</v>
+      </c>
+      <c r="E45" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>57.82</v>
+      </c>
+      <c r="D46" s="7">
+        <v>49.57</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-8.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="5">
-        <v>50</v>
-      </c>
-      <c r="D43" s="5">
-        <v>34</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>67.19</v>
+      </c>
+      <c r="D47" s="7">
+        <v>61.63</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-5.56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="5">
-        <v>34</v>
-      </c>
-      <c r="D44" s="5">
-        <v>50</v>
-      </c>
-      <c r="E44" s="7">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>41.83</v>
+      </c>
+      <c r="D48" s="7">
+        <v>43.7</v>
+      </c>
+      <c r="E48" s="9">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="7">
+        <v>52.65</v>
+      </c>
+      <c r="D49" s="7">
+        <v>55.94</v>
+      </c>
+      <c r="E49" s="9">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="7">
+        <v>48.49</v>
+      </c>
+      <c r="D50" s="7">
+        <v>50.41</v>
+      </c>
+      <c r="E50" s="9">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>36.04</v>
+      </c>
+      <c r="D51" s="7">
+        <v>38.59</v>
+      </c>
+      <c r="E51" s="9">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>43.05</v>
-      </c>
-      <c r="D45" s="5">
-        <v>38.4</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>419.92</v>
+      </c>
+      <c r="D52" s="7">
+        <v>37.33</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-382.59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>47.03</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46.06</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>2925.66</v>
+      </c>
+      <c r="D53" s="7">
+        <v>207.26</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2718.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>35.63</v>
-      </c>
-      <c r="D47" s="5">
-        <v>34.51</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7">
+        <v>30.62</v>
+      </c>
+      <c r="D54" s="7">
+        <v>-5.76</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-36.38</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>42.94</v>
-      </c>
-      <c r="D48" s="5">
-        <v>45.86</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="7">
+        <v>-5.41</v>
+      </c>
+      <c r="D55" s="7">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="E55" s="9">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>34.09</v>
-      </c>
-      <c r="D49" s="5">
-        <v>37.61</v>
-      </c>
-      <c r="E49" s="7">
-        <v>3.52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="7">
+        <v>82.45</v>
+      </c>
+      <c r="D56" s="7">
+        <v>60.09</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-22.36</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>35.42</v>
-      </c>
-      <c r="D50" s="5">
-        <v>33.52</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="B57" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C51" s="5">
-        <v>38.73</v>
-      </c>
-      <c r="D51" s="5">
-        <v>114.27</v>
-      </c>
-      <c r="E51" s="7">
-        <v>75.54000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>48.86</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-10.24</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-59.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4.75</v>
-      </c>
-      <c r="D53" s="5">
-        <v>-41.91</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-46.66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>13.73</v>
-      </c>
-      <c r="D54" s="5">
-        <v>-18.09</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-31.82</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-12.02</v>
-      </c>
-      <c r="D55" s="5">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="E55" s="7">
-        <v>95.76000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-6.51</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-13.11</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-6.6</v>
+      <c r="C57" s="7">
+        <v>-15.46</v>
+      </c>
+      <c r="D57" s="7">
+        <v>-16.36</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2620,60 +2722,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
-        <v>41.28</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>45.28</v>
+      </c>
+      <c r="C2" s="13">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>39.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>20</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-6.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-12.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>50</v>
+      </c>
+      <c r="E2" s="12">
+        <v>30</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-0.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-10.1</v>
+      </c>
+      <c r="H2" s="12">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -2775,43 +2877,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>-0.0083</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0472</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0726</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1371</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1824</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.1934</v>
+      <c r="A2" s="15">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0394</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.061</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.1313</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1659</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.1959</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,46 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.5 → 50.4</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>50.4</t>
-  </si>
-  <si>
-    <t>57.8 → 49.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>57.8</t>
-  </si>
-  <si>
-    <t>49.6</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -410,19 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -795,9 +754,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -937,58 +894,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.37</v>
+        <v>26.06</v>
       </c>
       <c r="D2">
-        <v>-3.62</v>
+        <v>-1.18</v>
       </c>
       <c r="E2">
-        <v>34.64</v>
+        <v>34.42</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.87</v>
+        <v>-24.29</v>
       </c>
       <c r="H2">
-        <v>14.75</v>
+        <v>13.4</v>
       </c>
       <c r="I2">
-        <v>1.03</v>
+        <v>3.82</v>
       </c>
       <c r="J2">
-        <v>-2.26</v>
+        <v>-2.1</v>
       </c>
       <c r="K2">
-        <v>-8.880000000000001</v>
+        <v>-7.62</v>
       </c>
       <c r="L2">
-        <v>-22.46</v>
+        <v>-24.77</v>
       </c>
       <c r="M2">
-        <v>-13.13</v>
+        <v>-13.44</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="O2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P2">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q2">
-        <v>26.14</v>
+        <v>26.12</v>
       </c>
       <c r="R2">
-        <v>27</v>
+        <v>26.98</v>
       </c>
       <c r="S2">
-        <v>27.91</v>
+        <v>27.88</v>
       </c>
       <c r="T2">
-        <v>-5.51</v>
+        <v>-6.52</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1003,34 +960,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>49.57</v>
+        <v>47.3</v>
       </c>
       <c r="Z2">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="AA2">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="AB2">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AC2">
-        <v>78.95999999999999</v>
+        <v>78.91</v>
       </c>
       <c r="AD2">
-        <v>75.23</v>
+        <v>81.36</v>
       </c>
       <c r="AE2">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>37.33</v>
+        <v>3.16</v>
       </c>
       <c r="AG2">
-        <v>27.21</v>
+        <v>27.19</v>
       </c>
       <c r="AH2">
-        <v>25.06</v>
+        <v>25.05</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1039,7 +996,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>43.46</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1050,58 +1007,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.84</v>
+        <v>10.07</v>
       </c>
       <c r="D3">
-        <v>-2.78</v>
+        <v>-7.1</v>
       </c>
       <c r="E3">
-        <v>14.2</v>
+        <v>14.02</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-23.66</v>
+        <v>-28.17</v>
       </c>
       <c r="H3">
-        <v>22.21</v>
+        <v>13.53</v>
       </c>
       <c r="I3">
-        <v>12.45</v>
+        <v>9.34</v>
       </c>
       <c r="J3">
-        <v>5.96</v>
+        <v>1.21</v>
       </c>
       <c r="K3">
-        <v>-3.3</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L3">
-        <v>-22.35</v>
+        <v>-29.08</v>
       </c>
       <c r="M3">
-        <v>-16.59</v>
+        <v>-17.62</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="P3">
-        <v>10.13</v>
+        <v>10.3</v>
       </c>
       <c r="Q3">
-        <v>9.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R3">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="S3">
-        <v>10.79</v>
+        <v>10.77</v>
       </c>
       <c r="T3">
-        <v>0.51</v>
+        <v>-6.52</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1113,34 +1070,34 @@
         <v>44</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y3">
-        <v>61.63</v>
+        <v>50.46</v>
       </c>
       <c r="Z3">
         <v>0.01</v>
       </c>
       <c r="AA3">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="AB3">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AC3">
-        <v>94.44</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="AD3">
-        <v>91.13</v>
+        <v>92.08</v>
       </c>
       <c r="AE3">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="AF3">
-        <v>207.26</v>
+        <v>105.16</v>
       </c>
       <c r="AG3">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="AH3">
         <v>8.9</v>
@@ -1152,7 +1109,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>27.51</v>
+        <v>26.97</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1163,10 +1120,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>219</v>
+        <v>219.01</v>
       </c>
       <c r="D4">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1178,43 +1135,43 @@
         <v>-30.45</v>
       </c>
       <c r="H4">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
-        <v>1.18</v>
+        <v>3.8</v>
       </c>
       <c r="J4">
-        <v>-4.74</v>
+        <v>-2.92</v>
       </c>
       <c r="K4">
-        <v>-7.43</v>
+        <v>-7.06</v>
       </c>
       <c r="L4">
-        <v>-28.75</v>
+        <v>-28.93</v>
       </c>
       <c r="M4">
-        <v>-3.94</v>
+        <v>-3.93</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P4">
-        <v>215.17</v>
+        <v>216.78</v>
       </c>
       <c r="Q4">
-        <v>221.03</v>
+        <v>220.74</v>
       </c>
       <c r="R4">
-        <v>234.81</v>
+        <v>233.89</v>
       </c>
       <c r="S4">
-        <v>245.78</v>
+        <v>245.39</v>
       </c>
       <c r="T4">
-        <v>-10.89</v>
+        <v>-10.75</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1229,34 +1186,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.7</v>
+        <v>43.72</v>
       </c>
       <c r="Z4">
-        <v>-5.23</v>
+        <v>-4.75</v>
       </c>
       <c r="AA4">
-        <v>-5.76</v>
+        <v>-5.55</v>
       </c>
       <c r="AB4">
-        <v>0.52</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AC4">
-        <v>82.22</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD4">
-        <v>66.84999999999999</v>
+        <v>82.81</v>
       </c>
       <c r="AE4">
-        <v>4.97</v>
+        <v>4.9</v>
       </c>
       <c r="AF4">
-        <v>-5.76</v>
+        <v>11.47</v>
       </c>
       <c r="AG4">
-        <v>235.26</v>
+        <v>234.87</v>
       </c>
       <c r="AH4">
-        <v>206.81</v>
+        <v>206.61</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1265,7 +1222,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>39.91</v>
+        <v>35.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1276,10 +1233,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>682.75</v>
+        <v>680.7</v>
       </c>
       <c r="D5">
-        <v>1.47</v>
+        <v>-0.3</v>
       </c>
       <c r="E5">
         <v>860.95</v>
@@ -1288,46 +1245,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.7</v>
+        <v>-20.94</v>
       </c>
       <c r="H5">
-        <v>39.14</v>
+        <v>38.72</v>
       </c>
       <c r="I5">
-        <v>3.86</v>
+        <v>7.77</v>
       </c>
       <c r="J5">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="K5">
-        <v>-15.09</v>
+        <v>-14.2</v>
       </c>
       <c r="L5">
-        <v>-17.02</v>
+        <v>-18.23</v>
       </c>
       <c r="M5">
-        <v>-6.1</v>
+        <v>-5.69</v>
       </c>
       <c r="N5">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P5">
-        <v>658.05</v>
+        <v>667.86</v>
       </c>
       <c r="Q5">
-        <v>665.64</v>
+        <v>665.99</v>
       </c>
       <c r="R5">
-        <v>674.71</v>
+        <v>674.24</v>
       </c>
       <c r="S5">
-        <v>617.72</v>
+        <v>617.51</v>
       </c>
       <c r="T5">
-        <v>10.53</v>
+        <v>10.23</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1342,34 +1299,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>55.94</v>
+        <v>55.09</v>
       </c>
       <c r="Z5">
-        <v>-3.95</v>
+        <v>-2.24</v>
       </c>
       <c r="AA5">
-        <v>-5.84</v>
+        <v>-5.12</v>
       </c>
       <c r="AB5">
-        <v>1.89</v>
+        <v>2.88</v>
       </c>
       <c r="AC5">
-        <v>78.52</v>
+        <v>93.34</v>
       </c>
       <c r="AD5">
-        <v>55.24</v>
+        <v>76.5</v>
       </c>
       <c r="AE5">
-        <v>21.16</v>
+        <v>21</v>
       </c>
       <c r="AF5">
-        <v>79.79000000000001</v>
+        <v>-5.34</v>
       </c>
       <c r="AG5">
-        <v>695.09</v>
+        <v>696</v>
       </c>
       <c r="AH5">
-        <v>636.2</v>
+        <v>635.98</v>
       </c>
       <c r="AI5">
         <v>705.24</v>
@@ -1378,7 +1335,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>27.12</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1389,58 +1346,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.48</v>
+        <v>26.68</v>
       </c>
       <c r="D6">
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
       <c r="E6">
-        <v>52.4</v>
+        <v>51.66</v>
       </c>
       <c r="F6">
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-49.47</v>
+        <v>-48.35</v>
       </c>
       <c r="H6">
-        <v>8.57</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I6">
-        <v>3.04</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J6">
-        <v>-0.6</v>
+        <v>2.81</v>
       </c>
       <c r="K6">
-        <v>-16.62</v>
+        <v>-11.98</v>
       </c>
       <c r="L6">
-        <v>-49.38</v>
+        <v>-49.08</v>
       </c>
       <c r="M6">
-        <v>-19.59</v>
+        <v>-20.48</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P6">
-        <v>25.36</v>
+        <v>25.82</v>
       </c>
       <c r="Q6">
-        <v>26.07</v>
+        <v>26.1</v>
       </c>
       <c r="R6">
-        <v>27.61</v>
+        <v>27.54</v>
       </c>
       <c r="S6">
-        <v>32.48</v>
+        <v>32.39</v>
       </c>
       <c r="T6">
-        <v>-18.47</v>
+        <v>-17.63</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1455,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>50.41</v>
+        <v>51.96</v>
       </c>
       <c r="Z6">
-        <v>-0.57</v>
+        <v>-0.46</v>
       </c>
       <c r="AA6">
-        <v>-0.6899999999999999</v>
+        <v>-0.65</v>
       </c>
       <c r="AB6">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="AC6">
-        <v>82.88</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>54.77</v>
+        <v>80.09</v>
       </c>
       <c r="AE6">
-        <v>0.96</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>60.09</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AG6">
-        <v>27.65</v>
+        <v>27.7</v>
       </c>
       <c r="AH6">
-        <v>24.5</v>
+        <v>24.51</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1491,7 +1448,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.1</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1502,10 +1459,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1174.6</v>
+        <v>1215</v>
       </c>
       <c r="D7">
-        <v>0.68</v>
+        <v>3.44</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1514,46 +1471,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-25.89</v>
+        <v>-23.34</v>
       </c>
       <c r="H7">
-        <v>1.35</v>
+        <v>4.84</v>
       </c>
       <c r="I7">
-        <v>-2.74</v>
+        <v>3.14</v>
       </c>
       <c r="J7">
-        <v>-6.59</v>
+        <v>-1.64</v>
       </c>
       <c r="K7">
-        <v>-9.33</v>
+        <v>-6.29</v>
       </c>
       <c r="L7">
-        <v>-14.35</v>
+        <v>-11.66</v>
       </c>
       <c r="M7">
-        <v>-0.8100000000000001</v>
+        <v>-0.19</v>
       </c>
       <c r="N7">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O7">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="P7">
-        <v>1169.7</v>
+        <v>1177.1</v>
       </c>
       <c r="Q7">
-        <v>1204.31</v>
+        <v>1203.06</v>
       </c>
       <c r="R7">
-        <v>1263.4</v>
+        <v>1261.88</v>
       </c>
       <c r="S7">
-        <v>1344.07</v>
+        <v>1342.39</v>
       </c>
       <c r="T7">
-        <v>-12.61</v>
+        <v>-9.49</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1568,34 +1525,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38.59</v>
+        <v>49.64</v>
       </c>
       <c r="Z7">
-        <v>-27.38</v>
+        <v>-23.17</v>
       </c>
       <c r="AA7">
-        <v>-26.46</v>
+        <v>-25.8</v>
       </c>
       <c r="AB7">
-        <v>-0.92</v>
+        <v>2.63</v>
       </c>
       <c r="AC7">
-        <v>48.36</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AD7">
-        <v>44.5</v>
+        <v>53.66</v>
       </c>
       <c r="AE7">
-        <v>22.65</v>
+        <v>24.19</v>
       </c>
       <c r="AF7">
-        <v>-16.36</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="AG7">
-        <v>1265.87</v>
+        <v>1262.55</v>
       </c>
       <c r="AH7">
-        <v>1142.75</v>
+        <v>1143.57</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1604,7 +1561,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>47.1</v>
+        <v>42.71</v>
       </c>
     </row>
   </sheetData>
@@ -1745,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1765,944 +1722,923 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-2.26</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5.96</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-4.74</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-2.92</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.58</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-0.6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2.81</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-6.59</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.64</v>
+      </c>
+      <c r="E12" s="6">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3.82</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="D14" s="5">
+        <v>9.34</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1.18</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="E15" s="6">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3.86</v>
+      </c>
+      <c r="D16" s="5">
+        <v>7.77</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3.04</v>
+      </c>
+      <c r="D17" s="5">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E17" s="6">
+        <v>6.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.74</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.14</v>
+      </c>
+      <c r="E18" s="6">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-22.46</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-24.77</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-22.35</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-29.08</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-6.73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-28.75</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-28.93</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-17.02</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-18.23</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-49.38</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-49.08</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-14.35</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-11.66</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-7.62</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-3.3</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-7.43</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-7.06</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-15.09</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-14.2</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-11.98</v>
+      </c>
+      <c r="E29" s="6">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.33</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.29</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-23.87</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-24.29</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-23.66</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-28.17</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-4.51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-20.7</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-20.94</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-49.47</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-48.35</v>
+      </c>
+      <c r="E34" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-25.89</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-23.34</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>26.37</v>
+      </c>
+      <c r="D36" s="5">
+        <v>26.06</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>10.84</v>
+      </c>
+      <c r="D37" s="5">
+        <v>10.07</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>219</v>
+      </c>
+      <c r="D38" s="5">
+        <v>219.01</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>682.75</v>
+      </c>
+      <c r="D39" s="5">
+        <v>680.7</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>26.48</v>
+      </c>
+      <c r="D40" s="5">
+        <v>26.68</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1174.6</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1215</v>
+      </c>
+      <c r="E41" s="6">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="5">
+        <v>50</v>
+      </c>
+      <c r="D42" s="5">
         <v>66</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="E42" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="5">
+        <v>99</v>
+      </c>
+      <c r="D43" s="5">
+        <v>34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="5">
+        <v>34</v>
+      </c>
+      <c r="D44" s="5">
+        <v>50</v>
+      </c>
+      <c r="E44" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="5">
+        <v>66</v>
+      </c>
+      <c r="D45" s="5">
+        <v>83</v>
+      </c>
+      <c r="E45" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="5">
+        <v>83</v>
+      </c>
+      <c r="D46" s="5">
+        <v>99</v>
+      </c>
+      <c r="E46" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>49.57</v>
+      </c>
+      <c r="D47" s="5">
+        <v>47.3</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="D9" s="7">
-        <v>5.96</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>61.63</v>
+      </c>
+      <c r="D48" s="5">
+        <v>50.46</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-11.17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.41</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-4.74</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>43.7</v>
+      </c>
+      <c r="D49" s="5">
+        <v>43.72</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.61</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2.58</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>55.94</v>
+      </c>
+      <c r="D50" s="5">
+        <v>55.09</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.24</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>50.41</v>
+      </c>
+      <c r="D51" s="5">
+        <v>51.96</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-8.42</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-6.59</v>
-      </c>
-      <c r="E13" s="9">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>38.59</v>
+      </c>
+      <c r="D52" s="5">
+        <v>49.64</v>
+      </c>
+      <c r="E52" s="6">
+        <v>11.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>6.13</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.03</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>37.33</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3.16</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-34.17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>13.78</v>
-      </c>
-      <c r="D15" s="7">
-        <v>12.45</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="5">
+        <v>207.26</v>
+      </c>
+      <c r="D54" s="5">
+        <v>105.16</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-102.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.05</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1.18</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-5.76</v>
+      </c>
+      <c r="D55" s="5">
+        <v>11.47</v>
+      </c>
+      <c r="E55" s="6">
+        <v>17.23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>2.11</v>
-      </c>
-      <c r="D17" s="7">
-        <v>3.86</v>
-      </c>
-      <c r="E17" s="9">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>79.79000000000001</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-85.13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="D18" s="7">
-        <v>3.04</v>
-      </c>
-      <c r="E18" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>60.09</v>
+      </c>
+      <c r="D57" s="5">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="E57" s="6">
+        <v>39.01</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.21</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-2.74</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-20.05</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-22.46</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-20.24</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-22.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-28.51</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-28.75</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-17.85</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-17.02</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-49.8</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-49.38</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-14.28</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-14.35</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-1.15</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-3.3</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-7.7</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-7.43</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-14.85</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-15.09</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-17.93</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-16.62</v>
-      </c>
-      <c r="E30" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-9.77</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-9.33</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-21.02</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-23.87</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-21.48</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-23.66</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-30.84</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-30.45</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-21.85</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-20.7</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-49.94</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-49.47</v>
-      </c>
-      <c r="E36" s="9">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-26.39</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-25.89</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>27.36</v>
-      </c>
-      <c r="D38" s="7">
-        <v>26.37</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>11.15</v>
-      </c>
-      <c r="D39" s="7">
-        <v>10.84</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>217.8</v>
-      </c>
-      <c r="D40" s="7">
-        <v>219</v>
-      </c>
-      <c r="E40" s="9">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>672.85</v>
-      </c>
-      <c r="D41" s="7">
-        <v>682.75</v>
-      </c>
-      <c r="E41" s="9">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>26.23</v>
-      </c>
-      <c r="D42" s="7">
-        <v>26.48</v>
-      </c>
-      <c r="E42" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1166.7</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1174.6</v>
-      </c>
-      <c r="E43" s="9">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="7">
-        <v>66</v>
-      </c>
-      <c r="D44" s="7">
-        <v>50</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="7">
-        <v>50</v>
-      </c>
-      <c r="D45" s="7">
-        <v>66</v>
-      </c>
-      <c r="E45" s="9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>57.82</v>
-      </c>
-      <c r="D46" s="7">
-        <v>49.57</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-8.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>67.19</v>
-      </c>
-      <c r="D47" s="7">
-        <v>61.63</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-5.56</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>41.83</v>
-      </c>
-      <c r="D48" s="7">
-        <v>43.7</v>
-      </c>
-      <c r="E48" s="9">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="7">
-        <v>52.65</v>
-      </c>
-      <c r="D49" s="7">
-        <v>55.94</v>
-      </c>
-      <c r="E49" s="9">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7">
-        <v>48.49</v>
-      </c>
-      <c r="D50" s="7">
-        <v>50.41</v>
-      </c>
-      <c r="E50" s="9">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="7">
-        <v>36.04</v>
-      </c>
-      <c r="D51" s="7">
-        <v>38.59</v>
-      </c>
-      <c r="E51" s="9">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C52" s="7">
-        <v>419.92</v>
-      </c>
-      <c r="D52" s="7">
-        <v>37.33</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-382.59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>2925.66</v>
-      </c>
-      <c r="D53" s="7">
-        <v>207.26</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2718.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>30.62</v>
-      </c>
-      <c r="D54" s="7">
-        <v>-5.76</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-36.38</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-5.41</v>
-      </c>
-      <c r="D55" s="7">
-        <v>79.79000000000001</v>
-      </c>
-      <c r="E55" s="9">
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="7">
-        <v>82.45</v>
-      </c>
-      <c r="D56" s="7">
-        <v>60.09</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-22.36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="7">
-        <v>-15.46</v>
-      </c>
-      <c r="D57" s="7">
+      <c r="C58" s="5">
         <v>-16.36</v>
       </c>
-      <c r="E57" s="8">
-        <v>-0.9</v>
+      <c r="D58" s="5">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="E58" s="6">
+        <v>93.15000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2722,60 +2658,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
-        <v>45.28</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="10">
+        <v>41.28</v>
+      </c>
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>50</v>
-      </c>
-      <c r="E2" s="12">
-        <v>30</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-0.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-10.1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="10">
+        <v>49.7</v>
+      </c>
+      <c r="E2" s="10">
+        <v>20</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-9.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>58.2</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2877,43 +2813,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
-        <v>-0.008100000000000001</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0394</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.061</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.1313</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1659</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.1959</v>
+      <c r="A2" s="13">
+        <v>-0.0019</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0393</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.05690000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1344</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1762</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.2048</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.5 → 49.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -753,8 +781,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -894,58 +921,58 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.06</v>
+        <v>26.15</v>
       </c>
       <c r="D2">
-        <v>-1.18</v>
+        <v>0.35</v>
       </c>
       <c r="E2">
-        <v>34.42</v>
+        <v>33.65</v>
       </c>
       <c r="F2">
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-24.29</v>
+        <v>-22.29</v>
       </c>
       <c r="H2">
-        <v>13.4</v>
+        <v>13.79</v>
       </c>
       <c r="I2">
-        <v>3.82</v>
+        <v>1.16</v>
       </c>
       <c r="J2">
-        <v>-2.1</v>
+        <v>-1.02</v>
       </c>
       <c r="K2">
-        <v>-7.62</v>
+        <v>-4.28</v>
       </c>
       <c r="L2">
-        <v>-24.77</v>
+        <v>-24.03</v>
       </c>
       <c r="M2">
-        <v>-13.44</v>
+        <v>-13.37</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>26.2</v>
+        <v>26.26</v>
       </c>
       <c r="Q2">
-        <v>26.12</v>
+        <v>26.11</v>
       </c>
       <c r="R2">
-        <v>26.98</v>
+        <v>26.95</v>
       </c>
       <c r="S2">
-        <v>27.88</v>
+        <v>27.85</v>
       </c>
       <c r="T2">
-        <v>-6.52</v>
+        <v>-6.12</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -960,31 +987,31 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>47.3</v>
+        <v>48.04</v>
       </c>
       <c r="Z2">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="AA2">
-        <v>-0.37</v>
+        <v>-0.34</v>
       </c>
       <c r="AB2">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AC2">
-        <v>78.91</v>
+        <v>67.92</v>
       </c>
       <c r="AD2">
-        <v>81.36</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>3.16</v>
+        <v>44.88</v>
       </c>
       <c r="AG2">
-        <v>27.19</v>
+        <v>27.16</v>
       </c>
       <c r="AH2">
         <v>25.05</v>
@@ -996,7 +1023,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>38.02</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1007,58 +1034,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>10.07</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D3">
-        <v>-7.1</v>
+        <v>-1.19</v>
       </c>
       <c r="E3">
-        <v>14.02</v>
+        <v>13.96</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-28.17</v>
+        <v>-28.72</v>
       </c>
       <c r="H3">
-        <v>13.53</v>
+        <v>12.18</v>
       </c>
       <c r="I3">
-        <v>9.34</v>
+        <v>2.05</v>
       </c>
       <c r="J3">
-        <v>1.21</v>
+        <v>-0.5</v>
       </c>
       <c r="K3">
-        <v>-9.119999999999999</v>
+        <v>-10.04</v>
       </c>
       <c r="L3">
-        <v>-29.08</v>
+        <v>-29.03</v>
       </c>
       <c r="M3">
-        <v>-17.62</v>
+        <v>-17.81</v>
       </c>
       <c r="N3">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="O3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>10.3</v>
+        <v>10.34</v>
       </c>
       <c r="Q3">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
       <c r="R3">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="S3">
-        <v>10.77</v>
+        <v>10.76</v>
       </c>
       <c r="T3">
-        <v>-6.52</v>
+        <v>-7.53</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1073,31 +1100,31 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>50.46</v>
+        <v>48.97</v>
       </c>
       <c r="Z3">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AB3">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AC3">
-        <v>83.15000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="AD3">
-        <v>92.08</v>
+        <v>82.31999999999999</v>
       </c>
       <c r="AE3">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AF3">
-        <v>105.16</v>
+        <v>-53.55</v>
       </c>
       <c r="AG3">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
       <c r="AH3">
         <v>8.9</v>
@@ -1109,7 +1136,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>26.97</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1120,10 +1147,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>219.01</v>
+        <v>216.25</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1132,46 +1159,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-30.45</v>
+        <v>-31.33</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>2.49</v>
       </c>
       <c r="I4">
-        <v>3.8</v>
+        <v>0.76</v>
       </c>
       <c r="J4">
-        <v>-2.92</v>
+        <v>-3.82</v>
       </c>
       <c r="K4">
-        <v>-7.06</v>
+        <v>-11</v>
       </c>
       <c r="L4">
-        <v>-28.93</v>
+        <v>-29.89</v>
       </c>
       <c r="M4">
-        <v>-3.93</v>
+        <v>-4.31</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="O4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>216.78</v>
+        <v>217.1</v>
       </c>
       <c r="Q4">
-        <v>220.74</v>
+        <v>220.09</v>
       </c>
       <c r="R4">
-        <v>233.89</v>
+        <v>232.97</v>
       </c>
       <c r="S4">
-        <v>245.39</v>
+        <v>245</v>
       </c>
       <c r="T4">
-        <v>-10.75</v>
+        <v>-11.73</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1186,34 +1213,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>43.72</v>
+        <v>40.27</v>
       </c>
       <c r="Z4">
-        <v>-4.75</v>
+        <v>-4.54</v>
       </c>
       <c r="AA4">
-        <v>-5.55</v>
+        <v>-5.35</v>
       </c>
       <c r="AB4">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="AC4">
-        <v>96.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="AD4">
-        <v>82.81</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="AE4">
-        <v>4.9</v>
+        <v>4.98</v>
       </c>
       <c r="AF4">
-        <v>11.47</v>
+        <v>34.2</v>
       </c>
       <c r="AG4">
-        <v>234.87</v>
+        <v>233.76</v>
       </c>
       <c r="AH4">
-        <v>206.61</v>
+        <v>206.43</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1222,7 +1249,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>35.27</v>
+        <v>34.42</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1233,58 +1260,58 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>680.7</v>
+        <v>713.25</v>
       </c>
       <c r="D5">
-        <v>-0.3</v>
+        <v>4.78</v>
       </c>
       <c r="E5">
-        <v>860.95</v>
+        <v>819.5</v>
       </c>
       <c r="F5">
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-20.94</v>
+        <v>-12.97</v>
       </c>
       <c r="H5">
-        <v>38.72</v>
+        <v>45.35</v>
       </c>
       <c r="I5">
-        <v>7.77</v>
+        <v>10.06</v>
       </c>
       <c r="J5">
-        <v>2.85</v>
+        <v>5.87</v>
       </c>
       <c r="K5">
-        <v>-14.2</v>
+        <v>-7.04</v>
       </c>
       <c r="L5">
-        <v>-18.23</v>
+        <v>-17.16</v>
       </c>
       <c r="M5">
-        <v>-5.69</v>
+        <v>-4.8</v>
       </c>
       <c r="N5">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P5">
-        <v>667.86</v>
+        <v>680.9</v>
       </c>
       <c r="Q5">
-        <v>665.99</v>
+        <v>667.95</v>
       </c>
       <c r="R5">
-        <v>674.24</v>
+        <v>674.85</v>
       </c>
       <c r="S5">
-        <v>617.51</v>
+        <v>617.45</v>
       </c>
       <c r="T5">
-        <v>10.23</v>
+        <v>15.51</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1299,43 +1326,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>55.09</v>
+        <v>64.38</v>
       </c>
       <c r="Z5">
-        <v>-2.24</v>
+        <v>1.73</v>
       </c>
       <c r="AA5">
-        <v>-5.12</v>
+        <v>-3.75</v>
       </c>
       <c r="AB5">
-        <v>2.88</v>
+        <v>5.48</v>
       </c>
       <c r="AC5">
-        <v>93.34</v>
+        <v>98.63</v>
       </c>
       <c r="AD5">
-        <v>76.5</v>
+        <v>90.16</v>
       </c>
       <c r="AE5">
-        <v>21</v>
+        <v>22.29</v>
       </c>
       <c r="AF5">
-        <v>-5.34</v>
+        <v>390.31</v>
       </c>
       <c r="AG5">
-        <v>696</v>
+        <v>704.5700000000001</v>
       </c>
       <c r="AH5">
-        <v>635.98</v>
+        <v>631.34</v>
       </c>
       <c r="AI5">
-        <v>705.24</v>
+        <v>633.34</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>25.87</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1346,10 +1373,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.68</v>
+        <v>26.46</v>
       </c>
       <c r="D6">
-        <v>0.76</v>
+        <v>-0.82</v>
       </c>
       <c r="E6">
         <v>51.66</v>
@@ -1358,46 +1385,46 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-48.35</v>
+        <v>-48.78</v>
       </c>
       <c r="H6">
-        <v>9.390000000000001</v>
+        <v>8.49</v>
       </c>
       <c r="I6">
-        <v>9.390000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="J6">
-        <v>2.81</v>
+        <v>1.3</v>
       </c>
       <c r="K6">
-        <v>-11.98</v>
+        <v>-11.8</v>
       </c>
       <c r="L6">
-        <v>-49.08</v>
+        <v>-48.74</v>
       </c>
       <c r="M6">
-        <v>-20.48</v>
+        <v>-20.6</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P6">
-        <v>25.82</v>
+        <v>26.17</v>
       </c>
       <c r="Q6">
         <v>26.1</v>
       </c>
       <c r="R6">
-        <v>27.54</v>
+        <v>27.48</v>
       </c>
       <c r="S6">
-        <v>32.39</v>
+        <v>32.31</v>
       </c>
       <c r="T6">
-        <v>-17.63</v>
+        <v>-18.11</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1412,28 +1439,28 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>51.96</v>
+        <v>50.11</v>
       </c>
       <c r="Z6">
-        <v>-0.46</v>
+        <v>-0.39</v>
       </c>
       <c r="AA6">
-        <v>-0.65</v>
+        <v>-0.59</v>
       </c>
       <c r="AB6">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>97.09</v>
       </c>
       <c r="AD6">
-        <v>80.09</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="AF6">
-        <v>99.09999999999999</v>
+        <v>-55.42</v>
       </c>
       <c r="AG6">
         <v>27.7</v>
@@ -1448,7 +1475,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.38</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1459,10 +1486,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1215</v>
+        <v>1211.2</v>
       </c>
       <c r="D7">
-        <v>3.44</v>
+        <v>-0.31</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1471,46 +1498,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-23.34</v>
+        <v>-23.58</v>
       </c>
       <c r="H7">
-        <v>4.84</v>
+        <v>4.51</v>
       </c>
       <c r="I7">
-        <v>3.14</v>
+        <v>3.49</v>
       </c>
       <c r="J7">
-        <v>-1.64</v>
+        <v>-2.32</v>
       </c>
       <c r="K7">
-        <v>-6.29</v>
+        <v>-8.74</v>
       </c>
       <c r="L7">
-        <v>-11.66</v>
+        <v>-11.51</v>
       </c>
       <c r="M7">
-        <v>-0.19</v>
+        <v>-0.25</v>
       </c>
       <c r="N7">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="O7">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="P7">
-        <v>1177.1</v>
+        <v>1185.28</v>
       </c>
       <c r="Q7">
-        <v>1203.06</v>
+        <v>1201.42</v>
       </c>
       <c r="R7">
-        <v>1261.88</v>
+        <v>1260.51</v>
       </c>
       <c r="S7">
-        <v>1342.39</v>
+        <v>1340.75</v>
       </c>
       <c r="T7">
-        <v>-9.49</v>
+        <v>-9.66</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1525,34 +1552,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>49.64</v>
+        <v>48.75</v>
       </c>
       <c r="Z7">
-        <v>-23.17</v>
+        <v>-19.91</v>
       </c>
       <c r="AA7">
-        <v>-25.8</v>
+        <v>-24.62</v>
       </c>
       <c r="AB7">
-        <v>2.63</v>
+        <v>4.71</v>
       </c>
       <c r="AC7">
-        <v>70.73999999999999</v>
+        <v>86.59</v>
       </c>
       <c r="AD7">
-        <v>53.66</v>
+        <v>68.56</v>
       </c>
       <c r="AE7">
-        <v>24.19</v>
+        <v>24.06</v>
       </c>
       <c r="AF7">
-        <v>76.79000000000001</v>
+        <v>26.33</v>
       </c>
       <c r="AG7">
-        <v>1262.55</v>
+        <v>1257.91</v>
       </c>
       <c r="AH7">
-        <v>1143.57</v>
+        <v>1144.94</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1561,7 +1588,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>42.71</v>
+        <v>38.9</v>
       </c>
     </row>
   </sheetData>
@@ -1722,12 +1749,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1735,904 +1797,904 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.1</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.16</v>
+      <c r="D7" s="6">
+        <v>-1.02</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.08</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>5.96</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>1.21</v>
       </c>
-      <c r="E8" s="7">
-        <v>-4.75</v>
+      <c r="D8" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.74</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-2.92</v>
       </c>
-      <c r="E9" s="6">
-        <v>1.82</v>
+      <c r="D9" s="6">
+        <v>-3.82</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>2.58</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>2.85</v>
       </c>
-      <c r="E10" s="6">
-        <v>0.27</v>
+      <c r="D10" s="6">
+        <v>5.87</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.02</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-0.6</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>2.81</v>
       </c>
-      <c r="E11" s="6">
-        <v>3.41</v>
+      <c r="D11" s="6">
+        <v>1.3</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-6.59</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.64</v>
       </c>
-      <c r="E12" s="6">
-        <v>4.95</v>
+      <c r="D12" s="6">
+        <v>-2.32</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>3.82</v>
       </c>
-      <c r="E13" s="6">
-        <v>2.79</v>
+      <c r="D13" s="6">
+        <v>1.16</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>12.45</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>9.34</v>
       </c>
-      <c r="E14" s="7">
-        <v>-3.11</v>
+      <c r="D14" s="6">
+        <v>2.05</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-7.29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>1.18</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>3.8</v>
       </c>
-      <c r="E15" s="6">
-        <v>2.62</v>
+      <c r="D15" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.04</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>3.86</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>7.77</v>
       </c>
-      <c r="E16" s="6">
-        <v>3.91</v>
+      <c r="D16" s="6">
+        <v>10.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.29</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>3.04</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>9.390000000000001</v>
       </c>
-      <c r="E17" s="6">
-        <v>6.35</v>
+      <c r="D17" s="6">
+        <v>7.17</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-2.74</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>3.14</v>
       </c>
-      <c r="E18" s="6">
-        <v>5.88</v>
+      <c r="D18" s="6">
+        <v>3.49</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-22.46</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-24.77</v>
       </c>
+      <c r="D19" s="6">
+        <v>-24.03</v>
+      </c>
       <c r="E19" s="7">
-        <v>-2.31</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>-22.35</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-29.08</v>
       </c>
+      <c r="D20" s="6">
+        <v>-29.03</v>
+      </c>
       <c r="E20" s="7">
-        <v>-6.73</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-28.75</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-28.93</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.18</v>
+      <c r="D21" s="6">
+        <v>-29.89</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>-17.02</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>-18.23</v>
       </c>
+      <c r="D22" s="6">
+        <v>-17.16</v>
+      </c>
       <c r="E22" s="7">
-        <v>-1.21</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-49.38</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>-49.08</v>
       </c>
-      <c r="E23" s="6">
-        <v>0.3</v>
+      <c r="D23" s="6">
+        <v>-48.74</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.34</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-14.35</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-11.66</v>
       </c>
-      <c r="E24" s="6">
-        <v>2.69</v>
+      <c r="D24" s="6">
+        <v>-11.51</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>-7.62</v>
       </c>
-      <c r="E25" s="6">
-        <v>1.26</v>
+      <c r="D25" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.34</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>-9.119999999999999</v>
       </c>
-      <c r="E26" s="7">
-        <v>-5.82</v>
+      <c r="D26" s="6">
+        <v>-10.04</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="5">
-        <v>-7.43</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-7.06</v>
       </c>
-      <c r="E27" s="6">
-        <v>0.37</v>
+      <c r="D27" s="6">
+        <v>-11</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>-15.09</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-14.2</v>
       </c>
-      <c r="E28" s="6">
-        <v>0.89</v>
+      <c r="D28" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="E28" s="7">
+        <v>7.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-16.62</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-11.98</v>
       </c>
-      <c r="E29" s="6">
-        <v>4.64</v>
+      <c r="D29" s="6">
+        <v>-11.8</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.18</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-9.33</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-6.29</v>
       </c>
-      <c r="E30" s="6">
-        <v>3.04</v>
+      <c r="D30" s="6">
+        <v>-8.74</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-23.87</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-24.29</v>
       </c>
+      <c r="D31" s="6">
+        <v>-22.29</v>
+      </c>
       <c r="E31" s="7">
-        <v>-0.42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="5">
-        <v>-23.66</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>-28.17</v>
       </c>
-      <c r="E32" s="7">
-        <v>-4.51</v>
+      <c r="D32" s="6">
+        <v>-28.72</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-30.45</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-31.33</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="5">
-        <v>-20.7</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>-20.94</v>
       </c>
-      <c r="E33" s="7">
+      <c r="D34" s="6">
+        <v>-12.97</v>
+      </c>
+      <c r="E34" s="7">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-48.35</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-48.78</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-23.34</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-23.58</v>
+      </c>
+      <c r="E36" s="8">
         <v>-0.24</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6">
+        <v>26.06</v>
+      </c>
+      <c r="D37" s="6">
+        <v>26.15</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.07</v>
+      </c>
+      <c r="D38" s="6">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6">
+        <v>219.01</v>
+      </c>
+      <c r="D39" s="6">
+        <v>216.25</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="6">
+        <v>680.7</v>
+      </c>
+      <c r="D40" s="6">
+        <v>713.25</v>
+      </c>
+      <c r="E40" s="7">
+        <v>32.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-49.47</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-48.35</v>
-      </c>
-      <c r="E34" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>26.68</v>
+      </c>
+      <c r="D41" s="6">
+        <v>26.46</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-25.89</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-23.34</v>
-      </c>
-      <c r="E35" s="6">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1215</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1211.2</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="6">
+        <v>34</v>
+      </c>
+      <c r="D43" s="6">
+        <v>50</v>
+      </c>
+      <c r="E43" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6">
+        <v>50</v>
+      </c>
+      <c r="D44" s="6">
+        <v>34</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="6">
+        <v>83</v>
+      </c>
+      <c r="D45" s="6">
+        <v>99</v>
+      </c>
+      <c r="E45" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="6">
+        <v>99</v>
+      </c>
+      <c r="D46" s="6">
+        <v>83</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>26.37</v>
-      </c>
-      <c r="D36" s="5">
-        <v>26.06</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6">
+        <v>47.3</v>
+      </c>
+      <c r="D47" s="6">
+        <v>48.04</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>10.84</v>
-      </c>
-      <c r="D37" s="5">
-        <v>10.07</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6">
+        <v>50.46</v>
+      </c>
+      <c r="D48" s="6">
+        <v>48.97</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>219</v>
-      </c>
-      <c r="D38" s="5">
-        <v>219.01</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>43.72</v>
+      </c>
+      <c r="D49" s="6">
+        <v>40.27</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>682.75</v>
-      </c>
-      <c r="D39" s="5">
-        <v>680.7</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>55.09</v>
+      </c>
+      <c r="D50" s="6">
+        <v>64.38</v>
+      </c>
+      <c r="E50" s="7">
+        <v>9.289999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>26.48</v>
-      </c>
-      <c r="D40" s="5">
-        <v>26.68</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>51.96</v>
+      </c>
+      <c r="D51" s="6">
+        <v>50.11</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>1174.6</v>
-      </c>
-      <c r="D41" s="5">
-        <v>1215</v>
-      </c>
-      <c r="E41" s="6">
-        <v>40.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>49.64</v>
+      </c>
+      <c r="D52" s="6">
+        <v>48.75</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" s="5">
-        <v>50</v>
-      </c>
-      <c r="D42" s="5">
-        <v>66</v>
-      </c>
-      <c r="E42" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3.16</v>
+      </c>
+      <c r="D53" s="6">
+        <v>44.88</v>
+      </c>
+      <c r="E53" s="7">
+        <v>41.72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="5">
-        <v>99</v>
-      </c>
-      <c r="D43" s="5">
-        <v>34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="6">
+        <v>105.16</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-53.55</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-158.71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="5">
-        <v>34</v>
-      </c>
-      <c r="D44" s="5">
-        <v>50</v>
-      </c>
-      <c r="E44" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="6">
+        <v>11.47</v>
+      </c>
+      <c r="D55" s="6">
+        <v>34.2</v>
+      </c>
+      <c r="E55" s="7">
+        <v>22.73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="5">
-        <v>66</v>
-      </c>
-      <c r="D45" s="5">
-        <v>83</v>
-      </c>
-      <c r="E45" s="6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="D56" s="6">
+        <v>390.31</v>
+      </c>
+      <c r="E56" s="7">
+        <v>395.65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-55.42</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-154.52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="5">
-        <v>83</v>
-      </c>
-      <c r="D46" s="5">
-        <v>99</v>
-      </c>
-      <c r="E46" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>49.57</v>
-      </c>
-      <c r="D47" s="5">
-        <v>47.3</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>61.63</v>
-      </c>
-      <c r="D48" s="5">
-        <v>50.46</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-11.17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>43.7</v>
-      </c>
-      <c r="D49" s="5">
-        <v>43.72</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>55.94</v>
-      </c>
-      <c r="D50" s="5">
-        <v>55.09</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>50.41</v>
-      </c>
-      <c r="D51" s="5">
-        <v>51.96</v>
-      </c>
-      <c r="E51" s="6">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>38.59</v>
-      </c>
-      <c r="D52" s="5">
-        <v>49.64</v>
-      </c>
-      <c r="E52" s="6">
-        <v>11.05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C53" s="5">
-        <v>37.33</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3.16</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-34.17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>207.26</v>
-      </c>
-      <c r="D54" s="5">
-        <v>105.16</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-102.1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="5">
-        <v>-5.76</v>
-      </c>
-      <c r="D55" s="5">
-        <v>11.47</v>
-      </c>
-      <c r="E55" s="6">
-        <v>17.23</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>79.79000000000001</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-85.13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>60.09</v>
-      </c>
-      <c r="D57" s="5">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="E57" s="6">
-        <v>39.01</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-16.36</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C58" s="6">
         <v>76.79000000000001</v>
       </c>
-      <c r="E58" s="6">
-        <v>93.15000000000001</v>
+      <c r="D58" s="6">
+        <v>26.33</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-50.46</v>
       </c>
     </row>
   </sheetData>
@@ -2658,60 +2720,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>41.28</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>6</v>
       </c>
-      <c r="D2" s="10">
-        <v>49.7</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>50.1</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>0</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.4</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-0.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H2" s="11">
         <v>58.2</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2813,43 +2875,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>-0.0019</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.0393</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.05690000000000001</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1344</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1762</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.2048</v>
+      <c r="A2" s="14">
+        <v>-0.0025</v>
+      </c>
+      <c r="B2" s="14">
+        <v>-0.0431</v>
+      </c>
+      <c r="C2" s="14">
+        <v>-0.048</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.1337</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.1781</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.206</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,16 +187,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.5 → 49.0</t>
+    <t>50.1 → 43.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>43.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -408,8 +408,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -781,7 +781,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,10 +922,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>26.15</v>
+        <v>25.82</v>
       </c>
       <c r="D2">
-        <v>0.35</v>
+        <v>-1.26</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -933,46 +934,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-22.29</v>
+        <v>-23.27</v>
       </c>
       <c r="H2">
-        <v>13.79</v>
+        <v>12.36</v>
       </c>
       <c r="I2">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="J2">
-        <v>-1.02</v>
+        <v>-2.38</v>
       </c>
       <c r="K2">
-        <v>-4.28</v>
+        <v>-4.41</v>
       </c>
       <c r="L2">
-        <v>-24.03</v>
+        <v>-21.62</v>
       </c>
       <c r="M2">
-        <v>-13.37</v>
+        <v>-12.93</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P2">
-        <v>26.26</v>
+        <v>26.35</v>
       </c>
       <c r="Q2">
-        <v>26.11</v>
+        <v>26.07</v>
       </c>
       <c r="R2">
-        <v>26.95</v>
+        <v>26.92</v>
       </c>
       <c r="S2">
-        <v>27.85</v>
+        <v>27.83</v>
       </c>
       <c r="T2">
-        <v>-6.12</v>
+        <v>-7.22</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -987,34 +988,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>48.04</v>
+        <v>45.5</v>
       </c>
       <c r="Z2">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="AA2">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="AB2">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="AC2">
-        <v>67.92</v>
+        <v>63.35</v>
       </c>
       <c r="AD2">
-        <v>75.26000000000001</v>
+        <v>70.06</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>44.88</v>
+        <v>-68.58</v>
       </c>
       <c r="AG2">
-        <v>27.16</v>
+        <v>27.1</v>
       </c>
       <c r="AH2">
-        <v>25.05</v>
+        <v>25.03</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1023,7 +1024,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>38.76</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1035,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.949999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="D3">
-        <v>-1.19</v>
+        <v>-2.01</v>
       </c>
       <c r="E3">
         <v>13.96</v>
@@ -1046,46 +1047,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-28.72</v>
+        <v>-30.16</v>
       </c>
       <c r="H3">
-        <v>12.18</v>
+        <v>9.92</v>
       </c>
       <c r="I3">
-        <v>2.05</v>
+        <v>0.52</v>
       </c>
       <c r="J3">
-        <v>-0.5</v>
+        <v>-2.69</v>
       </c>
       <c r="K3">
-        <v>-10.04</v>
+        <v>-12</v>
       </c>
       <c r="L3">
-        <v>-29.03</v>
+        <v>-29.35</v>
       </c>
       <c r="M3">
-        <v>-17.81</v>
+        <v>-17.46</v>
       </c>
       <c r="N3">
         <v>50</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="Q3">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
       <c r="R3">
-        <v>10.23</v>
+        <v>10.21</v>
       </c>
       <c r="S3">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
       <c r="T3">
-        <v>-7.53</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1100,34 +1101,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>48.97</v>
+        <v>46.51</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="AA3">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AB3">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC3">
-        <v>69.37</v>
+        <v>56.97</v>
       </c>
       <c r="AD3">
-        <v>82.31999999999999</v>
+        <v>69.83</v>
       </c>
       <c r="AE3">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AF3">
-        <v>-53.55</v>
+        <v>-57.82</v>
       </c>
       <c r="AG3">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
       <c r="AH3">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AI3">
         <v>9.4</v>
@@ -1136,7 +1137,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>25.63</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1148,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>216.25</v>
+        <v>214</v>
       </c>
       <c r="D4">
-        <v>-1.26</v>
+        <v>-1.04</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1159,46 +1160,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-31.33</v>
+        <v>-32.04</v>
       </c>
       <c r="H4">
-        <v>2.49</v>
+        <v>1.42</v>
       </c>
       <c r="I4">
-        <v>0.76</v>
+        <v>0.26</v>
       </c>
       <c r="J4">
-        <v>-3.82</v>
+        <v>-6.67</v>
       </c>
       <c r="K4">
-        <v>-11</v>
+        <v>-10.43</v>
       </c>
       <c r="L4">
-        <v>-29.89</v>
+        <v>-29.97</v>
       </c>
       <c r="M4">
-        <v>-4.31</v>
+        <v>-4.62</v>
       </c>
       <c r="N4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>217.1</v>
+        <v>217.21</v>
       </c>
       <c r="Q4">
-        <v>220.09</v>
+        <v>219.3</v>
       </c>
       <c r="R4">
-        <v>232.97</v>
+        <v>231.99</v>
       </c>
       <c r="S4">
-        <v>245</v>
+        <v>244.6</v>
       </c>
       <c r="T4">
-        <v>-11.73</v>
+        <v>-12.51</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1213,34 +1214,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>40.27</v>
+        <v>37.66</v>
       </c>
       <c r="Z4">
-        <v>-4.54</v>
+        <v>-4.5</v>
       </c>
       <c r="AA4">
-        <v>-5.35</v>
+        <v>-5.18</v>
       </c>
       <c r="AB4">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="AC4">
-        <v>94.52</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AD4">
-        <v>91.20999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="AE4">
-        <v>4.98</v>
+        <v>4.93</v>
       </c>
       <c r="AF4">
-        <v>34.2</v>
+        <v>-30.51</v>
       </c>
       <c r="AG4">
-        <v>233.76</v>
+        <v>232.4</v>
       </c>
       <c r="AH4">
-        <v>206.43</v>
+        <v>206.19</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1249,7 +1250,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>34.42</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,58 +1261,58 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>713.25</v>
+        <v>731.75</v>
       </c>
       <c r="D5">
-        <v>4.78</v>
+        <v>2.59</v>
       </c>
       <c r="E5">
-        <v>819.5</v>
+        <v>805.95</v>
       </c>
       <c r="F5">
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-12.97</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="H5">
-        <v>45.35</v>
+        <v>49.12</v>
       </c>
       <c r="I5">
-        <v>10.06</v>
+        <v>11.73</v>
       </c>
       <c r="J5">
-        <v>5.87</v>
+        <v>8.56</v>
       </c>
       <c r="K5">
-        <v>-7.04</v>
+        <v>-2.09</v>
       </c>
       <c r="L5">
-        <v>-17.16</v>
+        <v>-10.71</v>
       </c>
       <c r="M5">
-        <v>-4.8</v>
+        <v>-4.31</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>680.9</v>
+        <v>696.26</v>
       </c>
       <c r="Q5">
-        <v>667.95</v>
+        <v>671.09</v>
       </c>
       <c r="R5">
-        <v>674.85</v>
+        <v>675.85</v>
       </c>
       <c r="S5">
-        <v>617.45</v>
+        <v>617.53</v>
       </c>
       <c r="T5">
-        <v>15.51</v>
+        <v>18.5</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1326,43 +1327,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>64.38</v>
+        <v>68.38</v>
       </c>
       <c r="Z5">
-        <v>1.73</v>
+        <v>6.29</v>
       </c>
       <c r="AA5">
-        <v>-3.75</v>
+        <v>-1.74</v>
       </c>
       <c r="AB5">
-        <v>5.48</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AC5">
         <v>98.63</v>
       </c>
       <c r="AD5">
-        <v>90.16</v>
+        <v>96.87</v>
       </c>
       <c r="AE5">
-        <v>22.29</v>
+        <v>27.38</v>
       </c>
       <c r="AF5">
-        <v>390.31</v>
+        <v>14403.06</v>
       </c>
       <c r="AG5">
-        <v>704.5700000000001</v>
+        <v>717.52</v>
       </c>
       <c r="AH5">
-        <v>631.34</v>
+        <v>624.66</v>
       </c>
       <c r="AI5">
-        <v>633.34</v>
+        <v>673.0599999999999</v>
       </c>
       <c r="AJ5" t="s">
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>29.15</v>
+        <v>35.53</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1374,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>26.46</v>
+        <v>25.59</v>
       </c>
       <c r="D6">
-        <v>-0.82</v>
+        <v>-3.29</v>
       </c>
       <c r="E6">
         <v>51.66</v>
@@ -1385,46 +1386,46 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-48.78</v>
+        <v>-50.46</v>
       </c>
       <c r="H6">
-        <v>8.49</v>
+        <v>4.92</v>
       </c>
       <c r="I6">
-        <v>7.17</v>
+        <v>2.28</v>
       </c>
       <c r="J6">
-        <v>1.3</v>
+        <v>-3.29</v>
       </c>
       <c r="K6">
-        <v>-11.8</v>
+        <v>-14.39</v>
       </c>
       <c r="L6">
-        <v>-48.74</v>
+        <v>-49.53</v>
       </c>
       <c r="M6">
-        <v>-20.6</v>
+        <v>-20.22</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>26.17</v>
+        <v>26.29</v>
       </c>
       <c r="Q6">
-        <v>26.1</v>
+        <v>26.03</v>
       </c>
       <c r="R6">
-        <v>27.48</v>
+        <v>27.39</v>
       </c>
       <c r="S6">
-        <v>32.31</v>
+        <v>32.22</v>
       </c>
       <c r="T6">
-        <v>-18.11</v>
+        <v>-20.59</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1439,34 +1440,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>50.11</v>
+        <v>43.51</v>
       </c>
       <c r="Z6">
         <v>-0.39</v>
       </c>
       <c r="AA6">
-        <v>-0.59</v>
+        <v>-0.55</v>
       </c>
       <c r="AB6">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="AC6">
-        <v>97.09</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="AD6">
-        <v>93.31999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="AE6">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>-55.42</v>
+        <v>-37.34</v>
       </c>
       <c r="AG6">
-        <v>27.7</v>
+        <v>27.58</v>
       </c>
       <c r="AH6">
-        <v>24.51</v>
+        <v>24.48</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1475,7 +1476,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.62</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1487,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1211.2</v>
+        <v>1202</v>
       </c>
       <c r="D7">
-        <v>-0.31</v>
+        <v>-0.76</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1498,25 +1499,25 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-23.58</v>
+        <v>-24.16</v>
       </c>
       <c r="H7">
-        <v>4.51</v>
+        <v>3.72</v>
       </c>
       <c r="I7">
-        <v>3.49</v>
+        <v>3.72</v>
       </c>
       <c r="J7">
-        <v>-2.32</v>
+        <v>-3.37</v>
       </c>
       <c r="K7">
-        <v>-8.74</v>
+        <v>-9.15</v>
       </c>
       <c r="L7">
-        <v>-11.51</v>
+        <v>-12.24</v>
       </c>
       <c r="M7">
-        <v>-0.25</v>
+        <v>-0.58</v>
       </c>
       <c r="N7">
         <v>83</v>
@@ -1525,19 +1526,19 @@
         <v>45</v>
       </c>
       <c r="P7">
-        <v>1185.28</v>
+        <v>1193.9</v>
       </c>
       <c r="Q7">
-        <v>1201.42</v>
+        <v>1200.2</v>
       </c>
       <c r="R7">
-        <v>1260.51</v>
+        <v>1258.05</v>
       </c>
       <c r="S7">
-        <v>1340.75</v>
+        <v>1339.1</v>
       </c>
       <c r="T7">
-        <v>-9.66</v>
+        <v>-10.24</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1552,34 +1553,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.75</v>
+        <v>46.58</v>
       </c>
       <c r="Z7">
-        <v>-19.91</v>
+        <v>-17.86</v>
       </c>
       <c r="AA7">
-        <v>-24.62</v>
+        <v>-23.27</v>
       </c>
       <c r="AB7">
-        <v>4.71</v>
+        <v>5.41</v>
       </c>
       <c r="AC7">
-        <v>86.59</v>
+        <v>93.87</v>
       </c>
       <c r="AD7">
-        <v>68.56</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="AE7">
-        <v>24.06</v>
+        <v>24.28</v>
       </c>
       <c r="AF7">
-        <v>26.33</v>
+        <v>11.4</v>
       </c>
       <c r="AG7">
-        <v>1257.91</v>
+        <v>1255.46</v>
       </c>
       <c r="AH7">
-        <v>1144.94</v>
+        <v>1144.95</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1588,12 +1589,72 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>38.9</v>
+        <v>37.14</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK7"/>
   <conditionalFormatting sqref="AF2:AF7">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D7">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I7">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J7">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L7">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1605,8 +1666,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D7">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N7">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1615,72 +1682,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J7">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K7">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L7">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N7">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T7">
@@ -1692,26 +1693,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U7">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V7">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W7">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1729,7 +1730,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1769,7 +1770,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1821,13 +1822,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-2.1</v>
+        <v>-1.02</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.02</v>
+        <v>-2.38</v>
       </c>
       <c r="E7" s="7">
-        <v>1.08</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1838,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>1.21</v>
+        <v>-0.5</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.5</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.71</v>
+        <v>-2.69</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1855,13 +1856,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.92</v>
+        <v>-3.82</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.9</v>
+        <v>-6.67</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1872,13 +1873,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.85</v>
+        <v>5.87</v>
       </c>
       <c r="D10" s="6">
-        <v>5.87</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.02</v>
+        <v>8.56</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.69</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1889,13 +1890,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.81</v>
+        <v>1.3</v>
       </c>
       <c r="D11" s="6">
-        <v>1.3</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.51</v>
+        <v>-3.29</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1906,13 +1907,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.64</v>
+        <v>-2.32</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.68</v>
+        <v>-3.37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1923,13 +1924,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>3.82</v>
+        <v>1.16</v>
       </c>
       <c r="D13" s="6">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="E13" s="8">
-        <v>-2.66</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1940,13 +1941,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>9.34</v>
+        <v>2.05</v>
       </c>
       <c r="D14" s="6">
-        <v>2.05</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-7.29</v>
+        <v>0.52</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1957,13 +1958,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>3.8</v>
+        <v>0.76</v>
       </c>
       <c r="D15" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-3.04</v>
+        <v>0.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1974,13 +1975,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>7.77</v>
+        <v>10.06</v>
       </c>
       <c r="D16" s="6">
-        <v>10.06</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.29</v>
+        <v>11.73</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.67</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1991,13 +1992,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>9.390000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="D17" s="6">
-        <v>7.17</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.22</v>
+        <v>2.28</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-4.89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2008,13 +2009,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>3.14</v>
+        <v>3.49</v>
       </c>
       <c r="D18" s="6">
-        <v>3.49</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.35</v>
+        <v>3.72</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2025,13 +2026,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.77</v>
+        <v>-24.03</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.03</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.74</v>
+        <v>-21.62</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2042,13 +2043,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.08</v>
+        <v>-29.03</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.03</v>
+        <v>-29.35</v>
       </c>
       <c r="E20" s="7">
-        <v>0.05</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2059,13 +2060,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-28.93</v>
+        <v>-29.89</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.89</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.96</v>
+        <v>-29.97</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2076,13 +2077,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-18.23</v>
+        <v>-17.16</v>
       </c>
       <c r="D22" s="6">
-        <v>-17.16</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.07</v>
+        <v>-10.71</v>
+      </c>
+      <c r="E22" s="8">
+        <v>6.45</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2093,13 +2094,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-49.08</v>
+        <v>-48.74</v>
       </c>
       <c r="D23" s="6">
-        <v>-48.74</v>
+        <v>-49.53</v>
       </c>
       <c r="E23" s="7">
-        <v>0.34</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2110,13 +2111,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-11.66</v>
+        <v>-11.51</v>
       </c>
       <c r="D24" s="6">
-        <v>-11.51</v>
+        <v>-12.24</v>
       </c>
       <c r="E24" s="7">
-        <v>0.15</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2127,13 +2128,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-7.62</v>
+        <v>-4.28</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.28</v>
+        <v>-4.41</v>
       </c>
       <c r="E25" s="7">
-        <v>3.34</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2144,13 +2145,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-9.119999999999999</v>
+        <v>-10.04</v>
       </c>
       <c r="D26" s="6">
-        <v>-10.04</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.92</v>
+        <v>-12</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2161,13 +2162,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-7.06</v>
+        <v>-11</v>
       </c>
       <c r="D27" s="6">
-        <v>-11</v>
+        <v>-10.43</v>
       </c>
       <c r="E27" s="8">
-        <v>-3.94</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2178,13 +2179,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-14.2</v>
+        <v>-7.04</v>
       </c>
       <c r="D28" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E28" s="7">
-        <v>7.16</v>
+        <v>-2.09</v>
+      </c>
+      <c r="E28" s="8">
+        <v>4.95</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2195,13 +2196,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-11.98</v>
+        <v>-11.8</v>
       </c>
       <c r="D29" s="6">
-        <v>-11.8</v>
+        <v>-14.39</v>
       </c>
       <c r="E29" s="7">
-        <v>0.18</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2212,13 +2213,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-6.29</v>
+        <v>-8.74</v>
       </c>
       <c r="D30" s="6">
-        <v>-8.74</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.45</v>
+        <v>-9.15</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2229,13 +2230,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-24.29</v>
+        <v>-22.29</v>
       </c>
       <c r="D31" s="6">
-        <v>-22.29</v>
+        <v>-23.27</v>
       </c>
       <c r="E31" s="7">
-        <v>2</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2246,13 +2247,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.17</v>
+        <v>-28.72</v>
       </c>
       <c r="D32" s="6">
-        <v>-28.72</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.55</v>
+        <v>-30.16</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2263,13 +2264,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-30.45</v>
+        <v>-31.33</v>
       </c>
       <c r="D33" s="6">
-        <v>-31.33</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.88</v>
+        <v>-32.04</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2280,13 +2281,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-20.94</v>
+        <v>-12.97</v>
       </c>
       <c r="D34" s="6">
-        <v>-12.97</v>
-      </c>
-      <c r="E34" s="7">
-        <v>7.97</v>
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.76</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2297,13 +2298,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-48.35</v>
+        <v>-48.78</v>
       </c>
       <c r="D35" s="6">
-        <v>-48.78</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.43</v>
+        <v>-50.46</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2314,13 +2315,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-23.34</v>
+        <v>-23.58</v>
       </c>
       <c r="D36" s="6">
-        <v>-23.58</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.24</v>
+        <v>-24.16</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2331,13 +2332,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>26.06</v>
+        <v>26.15</v>
       </c>
       <c r="D37" s="6">
-        <v>26.15</v>
+        <v>25.82</v>
       </c>
       <c r="E37" s="7">
-        <v>0.09</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2348,13 +2349,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>10.07</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D38" s="6">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.12</v>
+        <v>9.75</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2365,13 +2366,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>219.01</v>
+        <v>216.25</v>
       </c>
       <c r="D39" s="6">
-        <v>216.25</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.76</v>
+        <v>214</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2382,13 +2383,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>680.7</v>
+        <v>713.25</v>
       </c>
       <c r="D40" s="6">
-        <v>713.25</v>
-      </c>
-      <c r="E40" s="7">
-        <v>32.55</v>
+        <v>731.75</v>
+      </c>
+      <c r="E40" s="8">
+        <v>18.5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2399,13 +2400,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>26.68</v>
+        <v>26.46</v>
       </c>
       <c r="D41" s="6">
-        <v>26.46</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.22</v>
+        <v>25.59</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2416,18 +2417,18 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1215</v>
+        <v>1211.2</v>
       </c>
       <c r="D42" s="6">
-        <v>1211.2</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-3.8</v>
+        <v>1202</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>13</v>
@@ -2436,265 +2437,214 @@
         <v>34</v>
       </c>
       <c r="D43" s="6">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E43" s="7">
-        <v>16</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>50</v>
+        <v>48.04</v>
       </c>
       <c r="D44" s="6">
-        <v>34</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-16</v>
+        <v>45.5</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>83</v>
+        <v>48.97</v>
       </c>
       <c r="D45" s="6">
-        <v>99</v>
+        <v>46.51</v>
       </c>
       <c r="E45" s="7">
-        <v>16</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>99</v>
+        <v>40.27</v>
       </c>
       <c r="D46" s="6">
-        <v>83</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-16</v>
+        <v>37.66</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>47.3</v>
+        <v>64.38</v>
       </c>
       <c r="D47" s="6">
-        <v>48.04</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.74</v>
+        <v>68.38</v>
+      </c>
+      <c r="E47" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>50.46</v>
+        <v>50.11</v>
       </c>
       <c r="D48" s="6">
-        <v>48.97</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.49</v>
+        <v>43.51</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>43.72</v>
+        <v>48.75</v>
       </c>
       <c r="D49" s="6">
-        <v>40.27</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-3.45</v>
+        <v>46.58</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>55.09</v>
+        <v>44.88</v>
       </c>
       <c r="D50" s="6">
-        <v>64.38</v>
+        <v>-68.58</v>
       </c>
       <c r="E50" s="7">
-        <v>9.289999999999999</v>
+        <v>-113.46</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>51.96</v>
+        <v>-53.55</v>
       </c>
       <c r="D51" s="6">
-        <v>50.11</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-1.85</v>
+        <v>-57.82</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>49.64</v>
+        <v>34.2</v>
       </c>
       <c r="D52" s="6">
-        <v>48.75</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.89</v>
+        <v>-30.51</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-64.70999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>3.16</v>
+        <v>390.31</v>
       </c>
       <c r="D53" s="6">
-        <v>44.88</v>
-      </c>
-      <c r="E53" s="7">
-        <v>41.72</v>
+        <v>14403.06</v>
+      </c>
+      <c r="E53" s="8">
+        <v>14012.75</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>105.16</v>
+        <v>-55.42</v>
       </c>
       <c r="D54" s="6">
-        <v>-53.55</v>
+        <v>-37.34</v>
       </c>
       <c r="E54" s="8">
-        <v>-158.71</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>11.47</v>
+        <v>26.33</v>
       </c>
       <c r="D55" s="6">
-        <v>34.2</v>
+        <v>11.4</v>
       </c>
       <c r="E55" s="7">
-        <v>22.73</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="D56" s="6">
-        <v>390.31</v>
-      </c>
-      <c r="E56" s="7">
-        <v>395.65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-55.42</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-154.52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="D58" s="6">
-        <v>26.33</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-50.46</v>
+        <v>-14.93</v>
       </c>
     </row>
   </sheetData>
@@ -2753,25 +2703,25 @@
         <v>43</v>
       </c>
       <c r="B2" s="11">
-        <v>41.28</v>
+        <v>39.88</v>
       </c>
       <c r="C2" s="12">
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>50.1</v>
+        <v>48</v>
       </c>
       <c r="E2" s="11">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.800000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H2" s="11">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="I2" s="11">
         <v>0</v>
@@ -2879,10 +2829,10 @@
         <v>42</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>37</v>
@@ -2896,22 +2846,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>-0.0025</v>
+        <v>-0.0058</v>
       </c>
       <c r="B2" s="14">
         <v>-0.0431</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.048</v>
+        <v>-0.0462</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1337</v>
+        <v>-0.1293</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1781</v>
+        <v>-0.1746</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.206</v>
+        <v>-0.2022</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,19 +184,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 43.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>43.5</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>68.4 → 74.3</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>68.4</t>
+  </si>
+  <si>
+    <t>74.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -248,7 +248,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,6 +282,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -295,7 +302,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +324,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,12 +421,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -422,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -781,8 +794,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -922,10 +934,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.82</v>
+        <v>25.01</v>
       </c>
       <c r="D2">
-        <v>-1.26</v>
+        <v>-3.14</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -934,46 +946,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-23.27</v>
+        <v>-25.68</v>
       </c>
       <c r="H2">
-        <v>12.36</v>
+        <v>8.83</v>
       </c>
       <c r="I2">
-        <v>1.89</v>
+        <v>-8.59</v>
       </c>
       <c r="J2">
-        <v>-2.38</v>
+        <v>-6.05</v>
       </c>
       <c r="K2">
-        <v>-4.41</v>
+        <v>-7.92</v>
       </c>
       <c r="L2">
-        <v>-21.62</v>
+        <v>-24.49</v>
       </c>
       <c r="M2">
-        <v>-12.93</v>
+        <v>-12.52</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>26.35</v>
+        <v>25.88</v>
       </c>
       <c r="Q2">
-        <v>26.07</v>
+        <v>26</v>
       </c>
       <c r="R2">
-        <v>26.92</v>
+        <v>26.87</v>
       </c>
       <c r="S2">
-        <v>27.83</v>
+        <v>27.8</v>
       </c>
       <c r="T2">
-        <v>-7.22</v>
+        <v>-10.03</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -988,34 +1000,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>45.5</v>
+        <v>39.92</v>
       </c>
       <c r="Z2">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="AA2">
         <v>-0.32</v>
       </c>
       <c r="AB2">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>63.35</v>
+        <v>55.06</v>
       </c>
       <c r="AD2">
-        <v>70.06</v>
+        <v>62.11</v>
       </c>
       <c r="AE2">
         <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>-68.58</v>
+        <v>-39.35</v>
       </c>
       <c r="AG2">
-        <v>27.1</v>
+        <v>27.12</v>
       </c>
       <c r="AH2">
-        <v>25.03</v>
+        <v>24.87</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1024,7 +1036,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>39.4</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1035,58 +1047,58 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.75</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D3">
-        <v>-2.01</v>
+        <v>-4</v>
       </c>
       <c r="E3">
-        <v>13.96</v>
+        <v>13.84</v>
       </c>
       <c r="F3">
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-30.16</v>
+        <v>-32.37</v>
       </c>
       <c r="H3">
-        <v>9.92</v>
+        <v>5.52</v>
       </c>
       <c r="I3">
-        <v>0.52</v>
+        <v>-16.05</v>
       </c>
       <c r="J3">
-        <v>-2.69</v>
+        <v>-6.21</v>
       </c>
       <c r="K3">
-        <v>-12</v>
+        <v>-15.06</v>
       </c>
       <c r="L3">
-        <v>-29.35</v>
+        <v>-32.95</v>
       </c>
       <c r="M3">
-        <v>-17.46</v>
+        <v>-17.1</v>
       </c>
       <c r="N3">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O3">
         <v>26</v>
       </c>
       <c r="P3">
-        <v>10.35</v>
+        <v>9.99</v>
       </c>
       <c r="Q3">
-        <v>9.84</v>
+        <v>9.81</v>
       </c>
       <c r="R3">
-        <v>10.21</v>
+        <v>10.18</v>
       </c>
       <c r="S3">
-        <v>10.75</v>
+        <v>10.73</v>
       </c>
       <c r="T3">
-        <v>-9.279999999999999</v>
+        <v>-12.78</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1101,43 +1113,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>46.51</v>
+        <v>42.06</v>
       </c>
       <c r="Z3">
-        <v>-0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AA3">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AB3">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>56.97</v>
+        <v>49.44</v>
       </c>
       <c r="AD3">
-        <v>69.83</v>
+        <v>58.59</v>
       </c>
       <c r="AE3">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AF3">
-        <v>-57.82</v>
+        <v>-55.94</v>
       </c>
       <c r="AG3">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
       <c r="AH3">
-        <v>8.890000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="AI3">
-        <v>9.4</v>
+        <v>11.11</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>23.08</v>
+        <v>21.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1148,10 +1160,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>214</v>
+        <v>211.39</v>
       </c>
       <c r="D4">
-        <v>-1.04</v>
+        <v>-1.22</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1160,46 +1172,46 @@
         <v>211</v>
       </c>
       <c r="G4">
-        <v>-32.04</v>
+        <v>-32.87</v>
       </c>
       <c r="H4">
-        <v>1.42</v>
+        <v>0.18</v>
       </c>
       <c r="I4">
-        <v>0.26</v>
+        <v>-2.94</v>
       </c>
       <c r="J4">
-        <v>-6.67</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="K4">
-        <v>-10.43</v>
+        <v>-11.93</v>
       </c>
       <c r="L4">
-        <v>-29.97</v>
+        <v>-32.39</v>
       </c>
       <c r="M4">
-        <v>-4.62</v>
+        <v>-4.98</v>
       </c>
       <c r="N4">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>217.21</v>
+        <v>215.93</v>
       </c>
       <c r="Q4">
-        <v>219.3</v>
+        <v>218.37</v>
       </c>
       <c r="R4">
-        <v>231.99</v>
+        <v>231.08</v>
       </c>
       <c r="S4">
-        <v>244.6</v>
+        <v>244.19</v>
       </c>
       <c r="T4">
-        <v>-12.51</v>
+        <v>-13.43</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1214,34 +1226,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.66</v>
+        <v>34.84</v>
       </c>
       <c r="Z4">
-        <v>-4.5</v>
+        <v>-4.62</v>
       </c>
       <c r="AA4">
-        <v>-5.18</v>
+        <v>-5.07</v>
       </c>
       <c r="AB4">
-        <v>0.68</v>
+        <v>0.45</v>
       </c>
       <c r="AC4">
-        <v>84.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="AD4">
-        <v>92.11</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AE4">
-        <v>4.93</v>
+        <v>5.1</v>
       </c>
       <c r="AF4">
-        <v>-30.51</v>
+        <v>-0.7</v>
       </c>
       <c r="AG4">
-        <v>232.4</v>
+        <v>230.91</v>
       </c>
       <c r="AH4">
-        <v>206.19</v>
+        <v>205.83</v>
       </c>
       <c r="AI4">
         <v>226.22</v>
@@ -1250,7 +1262,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>33.74</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1261,58 +1273,58 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>731.75</v>
+        <v>767.25</v>
       </c>
       <c r="D5">
-        <v>2.59</v>
+        <v>4.85</v>
       </c>
       <c r="E5">
-        <v>805.95</v>
+        <v>804.05</v>
       </c>
       <c r="F5">
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-9.210000000000001</v>
+        <v>-4.58</v>
       </c>
       <c r="H5">
-        <v>49.12</v>
+        <v>56.36</v>
       </c>
       <c r="I5">
-        <v>11.73</v>
+        <v>14.03</v>
       </c>
       <c r="J5">
-        <v>8.56</v>
+        <v>14.69</v>
       </c>
       <c r="K5">
-        <v>-2.09</v>
+        <v>3.21</v>
       </c>
       <c r="L5">
-        <v>-10.71</v>
+        <v>-4.8</v>
       </c>
       <c r="M5">
-        <v>-4.31</v>
+        <v>-2.41</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>696.26</v>
+        <v>715.14</v>
       </c>
       <c r="Q5">
-        <v>671.09</v>
+        <v>675.3200000000001</v>
       </c>
       <c r="R5">
-        <v>675.85</v>
+        <v>677.53</v>
       </c>
       <c r="S5">
-        <v>617.53</v>
+        <v>617.74</v>
       </c>
       <c r="T5">
-        <v>18.5</v>
+        <v>24.2</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1327,34 +1339,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>68.38</v>
+        <v>74.34</v>
       </c>
       <c r="Z5">
-        <v>6.29</v>
+        <v>12.63</v>
       </c>
       <c r="AA5">
-        <v>-1.74</v>
+        <v>1.13</v>
       </c>
       <c r="AB5">
-        <v>8.029999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>98.63</v>
+        <v>100</v>
       </c>
       <c r="AD5">
-        <v>96.87</v>
+        <v>99.09</v>
       </c>
       <c r="AE5">
-        <v>27.38</v>
+        <v>32.67</v>
       </c>
       <c r="AF5">
-        <v>14403.06</v>
+        <v>652.42</v>
       </c>
       <c r="AG5">
-        <v>717.52</v>
+        <v>738.5599999999999</v>
       </c>
       <c r="AH5">
-        <v>624.66</v>
+        <v>612.08</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1363,7 +1375,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>35.53</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1374,10 +1386,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>25.59</v>
+        <v>24.56</v>
       </c>
       <c r="D6">
-        <v>-3.29</v>
+        <v>-4.03</v>
       </c>
       <c r="E6">
         <v>51.66</v>
@@ -1386,46 +1398,46 @@
         <v>24.39</v>
       </c>
       <c r="G6">
-        <v>-50.46</v>
+        <v>-52.46</v>
       </c>
       <c r="H6">
-        <v>4.92</v>
+        <v>0.7</v>
       </c>
       <c r="I6">
-        <v>2.28</v>
+        <v>-6.37</v>
       </c>
       <c r="J6">
-        <v>-3.29</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="K6">
-        <v>-14.39</v>
+        <v>-16.91</v>
       </c>
       <c r="L6">
-        <v>-49.53</v>
+        <v>-52.45</v>
       </c>
       <c r="M6">
-        <v>-20.22</v>
+        <v>-21.49</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>26.29</v>
+        <v>25.95</v>
       </c>
       <c r="Q6">
-        <v>26.03</v>
+        <v>25.92</v>
       </c>
       <c r="R6">
-        <v>27.39</v>
+        <v>27.29</v>
       </c>
       <c r="S6">
-        <v>32.22</v>
+        <v>32.13</v>
       </c>
       <c r="T6">
-        <v>-20.59</v>
+        <v>-23.56</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1440,34 +1452,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.51</v>
+        <v>37.25</v>
       </c>
       <c r="Z6">
-        <v>-0.39</v>
+        <v>-0.47</v>
       </c>
       <c r="AA6">
-        <v>-0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="AB6">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>83.79000000000001</v>
+        <v>60.64</v>
       </c>
       <c r="AD6">
-        <v>93.62</v>
+        <v>80.5</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>-37.34</v>
+        <v>-4.17</v>
       </c>
       <c r="AG6">
-        <v>27.58</v>
+        <v>27.56</v>
       </c>
       <c r="AH6">
-        <v>24.48</v>
+        <v>24.28</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1476,7 +1488,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>29.45</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1487,10 +1499,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="D7">
-        <v>-0.76</v>
+        <v>0.58</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1499,46 +1511,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-24.16</v>
+        <v>-23.72</v>
       </c>
       <c r="H7">
-        <v>3.72</v>
+        <v>4.32</v>
       </c>
       <c r="I7">
-        <v>3.72</v>
+        <v>3.63</v>
       </c>
       <c r="J7">
-        <v>-3.37</v>
+        <v>-1.42</v>
       </c>
       <c r="K7">
-        <v>-9.15</v>
+        <v>-7.26</v>
       </c>
       <c r="L7">
-        <v>-12.24</v>
+        <v>-11.62</v>
       </c>
       <c r="M7">
-        <v>-0.58</v>
+        <v>0.35</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="P7">
-        <v>1193.9</v>
+        <v>1202.36</v>
       </c>
       <c r="Q7">
-        <v>1200.2</v>
+        <v>1198.28</v>
       </c>
       <c r="R7">
-        <v>1258.05</v>
+        <v>1255.53</v>
       </c>
       <c r="S7">
-        <v>1339.1</v>
+        <v>1337.33</v>
       </c>
       <c r="T7">
-        <v>-10.24</v>
+        <v>-9.6</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1553,34 +1565,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>46.58</v>
+        <v>48.46</v>
       </c>
       <c r="Z7">
-        <v>-17.86</v>
+        <v>-15.49</v>
       </c>
       <c r="AA7">
-        <v>-23.27</v>
+        <v>-21.71</v>
       </c>
       <c r="AB7">
-        <v>5.41</v>
+        <v>6.22</v>
       </c>
       <c r="AC7">
-        <v>93.87</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="AD7">
-        <v>83.73999999999999</v>
+        <v>90.84</v>
       </c>
       <c r="AE7">
-        <v>24.28</v>
+        <v>25.05</v>
       </c>
       <c r="AF7">
-        <v>11.4</v>
+        <v>22.66</v>
       </c>
       <c r="AG7">
-        <v>1255.46</v>
+        <v>1249.12</v>
       </c>
       <c r="AH7">
-        <v>1144.95</v>
+        <v>1147.45</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1589,7 +1601,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>37.14</v>
+        <v>36.3</v>
       </c>
     </row>
   </sheetData>
@@ -1730,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1770,7 +1782,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1822,13 +1834,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-1.02</v>
+        <v>-2.38</v>
       </c>
       <c r="D7" s="6">
-        <v>-2.38</v>
+        <v>-6.05</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.36</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1839,13 +1851,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.5</v>
+        <v>-2.69</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.69</v>
+        <v>-6.21</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.19</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1856,13 +1868,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.82</v>
+        <v>-6.67</v>
       </c>
       <c r="D9" s="6">
-        <v>-6.67</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.85</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1873,13 +1885,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>5.87</v>
+        <v>8.56</v>
       </c>
       <c r="D10" s="6">
-        <v>8.56</v>
+        <v>14.69</v>
       </c>
       <c r="E10" s="8">
-        <v>2.69</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1890,13 +1902,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>1.3</v>
+        <v>-3.29</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.29</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="E11" s="7">
-        <v>-4.59</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1907,13 +1919,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.32</v>
+        <v>-3.37</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.37</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.05</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1924,13 +1936,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>1.16</v>
+        <v>1.89</v>
       </c>
       <c r="D13" s="6">
-        <v>1.89</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.73</v>
+        <v>-8.59</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-10.48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1941,13 +1953,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>2.05</v>
+        <v>0.52</v>
       </c>
       <c r="D14" s="6">
-        <v>0.52</v>
+        <v>-16.05</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.53</v>
+        <v>-16.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1958,13 +1970,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.76</v>
+        <v>0.26</v>
       </c>
       <c r="D15" s="6">
-        <v>0.26</v>
+        <v>-2.94</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.5</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1975,13 +1987,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>10.06</v>
+        <v>11.73</v>
       </c>
       <c r="D16" s="6">
-        <v>11.73</v>
+        <v>14.03</v>
       </c>
       <c r="E16" s="8">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1992,13 +2004,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>7.17</v>
+        <v>2.28</v>
       </c>
       <c r="D17" s="6">
-        <v>2.28</v>
+        <v>-6.37</v>
       </c>
       <c r="E17" s="7">
-        <v>-4.89</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2009,13 +2021,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>3.49</v>
+        <v>3.72</v>
       </c>
       <c r="D18" s="6">
-        <v>3.72</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.23</v>
+        <v>3.63</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2026,13 +2038,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.03</v>
+        <v>-21.62</v>
       </c>
       <c r="D19" s="6">
-        <v>-21.62</v>
-      </c>
-      <c r="E19" s="8">
-        <v>2.41</v>
+        <v>-24.49</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.87</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2043,13 +2055,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.03</v>
+        <v>-29.35</v>
       </c>
       <c r="D20" s="6">
-        <v>-29.35</v>
+        <v>-32.95</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.32</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2060,13 +2072,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-29.89</v>
+        <v>-29.97</v>
       </c>
       <c r="D21" s="6">
-        <v>-29.97</v>
+        <v>-32.39</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.08</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2077,13 +2089,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-17.16</v>
+        <v>-10.71</v>
       </c>
       <c r="D22" s="6">
-        <v>-10.71</v>
+        <v>-4.8</v>
       </c>
       <c r="E22" s="8">
-        <v>6.45</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2094,13 +2106,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-48.74</v>
+        <v>-49.53</v>
       </c>
       <c r="D23" s="6">
-        <v>-49.53</v>
+        <v>-52.45</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.79</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2111,13 +2123,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-11.51</v>
+        <v>-12.24</v>
       </c>
       <c r="D24" s="6">
-        <v>-12.24</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.73</v>
+        <v>-11.62</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.62</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2128,13 +2140,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-4.28</v>
+        <v>-4.41</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.41</v>
+        <v>-7.92</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.13</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2145,13 +2157,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-10.04</v>
+        <v>-12</v>
       </c>
       <c r="D26" s="6">
-        <v>-12</v>
+        <v>-15.06</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.96</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2162,13 +2174,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-11</v>
+        <v>-10.43</v>
       </c>
       <c r="D27" s="6">
-        <v>-10.43</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.57</v>
+        <v>-11.93</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2179,13 +2191,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-7.04</v>
+        <v>-2.09</v>
       </c>
       <c r="D28" s="6">
-        <v>-2.09</v>
+        <v>3.21</v>
       </c>
       <c r="E28" s="8">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2196,13 +2208,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-11.8</v>
+        <v>-14.39</v>
       </c>
       <c r="D29" s="6">
-        <v>-14.39</v>
+        <v>-16.91</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.59</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2213,13 +2225,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.74</v>
+        <v>-9.15</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.15</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.41</v>
+        <v>-7.26</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2230,13 +2242,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-22.29</v>
+        <v>-23.27</v>
       </c>
       <c r="D31" s="6">
-        <v>-23.27</v>
+        <v>-25.68</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.98</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2247,13 +2259,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.72</v>
+        <v>-30.16</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.16</v>
+        <v>-32.37</v>
       </c>
       <c r="E32" s="7">
-        <v>-1.44</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2264,13 +2276,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-31.33</v>
+        <v>-32.04</v>
       </c>
       <c r="D33" s="6">
-        <v>-32.04</v>
+        <v>-32.87</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.71</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2281,13 +2293,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-12.97</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D34" s="6">
-        <v>-9.210000000000001</v>
+        <v>-4.58</v>
       </c>
       <c r="E34" s="8">
-        <v>3.76</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2298,13 +2310,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-48.78</v>
+        <v>-50.46</v>
       </c>
       <c r="D35" s="6">
-        <v>-50.46</v>
+        <v>-52.46</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.68</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2315,13 +2327,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-23.58</v>
+        <v>-24.16</v>
       </c>
       <c r="D36" s="6">
-        <v>-24.16</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.58</v>
+        <v>-23.72</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.44</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2332,13 +2344,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>26.15</v>
+        <v>25.82</v>
       </c>
       <c r="D37" s="6">
-        <v>25.82</v>
+        <v>25.01</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.33</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2349,13 +2361,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>9.949999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="D38" s="6">
-        <v>9.75</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.2</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2366,13 +2378,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>216.25</v>
+        <v>214</v>
       </c>
       <c r="D39" s="6">
-        <v>214</v>
+        <v>211.39</v>
       </c>
       <c r="E39" s="7">
-        <v>-2.25</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2383,13 +2395,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>713.25</v>
+        <v>731.75</v>
       </c>
       <c r="D40" s="6">
-        <v>731.75</v>
+        <v>767.25</v>
       </c>
       <c r="E40" s="8">
-        <v>18.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2400,13 +2412,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>26.46</v>
+        <v>25.59</v>
       </c>
       <c r="D41" s="6">
-        <v>25.59</v>
+        <v>24.56</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.87</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2417,234 +2429,251 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1211.2</v>
+        <v>1202</v>
       </c>
       <c r="D42" s="6">
-        <v>1202</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-9.199999999999999</v>
+        <v>1209</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C43" s="6">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
         <v>33</v>
       </c>
       <c r="E43" s="7">
-        <v>-1</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6">
-        <v>48.04</v>
+        <v>33</v>
       </c>
       <c r="D44" s="6">
-        <v>45.5</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.54</v>
+        <v>50</v>
+      </c>
+      <c r="E44" s="8">
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>48.97</v>
+        <v>45.5</v>
       </c>
       <c r="D45" s="6">
-        <v>46.51</v>
+        <v>39.92</v>
       </c>
       <c r="E45" s="7">
-        <v>-2.46</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>40.27</v>
+        <v>46.51</v>
       </c>
       <c r="D46" s="6">
-        <v>37.66</v>
+        <v>42.06</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.61</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>64.38</v>
+        <v>37.66</v>
       </c>
       <c r="D47" s="6">
-        <v>68.38</v>
-      </c>
-      <c r="E47" s="8">
-        <v>4</v>
+        <v>34.84</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.82</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>50.11</v>
+        <v>68.38</v>
       </c>
       <c r="D48" s="6">
-        <v>43.51</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-6.6</v>
+        <v>74.34</v>
+      </c>
+      <c r="E48" s="8">
+        <v>5.96</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>48.75</v>
+        <v>43.51</v>
       </c>
       <c r="D49" s="6">
-        <v>46.58</v>
+        <v>37.25</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.17</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>44.88</v>
+        <v>46.58</v>
       </c>
       <c r="D50" s="6">
-        <v>-68.58</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-113.46</v>
+        <v>48.46</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.88</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-53.55</v>
+        <v>-68.58</v>
       </c>
       <c r="D51" s="6">
-        <v>-57.82</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-4.27</v>
+        <v>-39.35</v>
+      </c>
+      <c r="E51" s="8">
+        <v>29.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>34.2</v>
+        <v>-57.82</v>
       </c>
       <c r="D52" s="6">
-        <v>-30.51</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-64.70999999999999</v>
+        <v>-55.94</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.88</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>390.31</v>
+        <v>-30.51</v>
       </c>
       <c r="D53" s="6">
-        <v>14403.06</v>
+        <v>-0.7</v>
       </c>
       <c r="E53" s="8">
-        <v>14012.75</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-55.42</v>
+        <v>14403.06</v>
       </c>
       <c r="D54" s="6">
-        <v>-37.34</v>
-      </c>
-      <c r="E54" s="8">
-        <v>18.08</v>
+        <v>652.42</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-13750.64</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>26.33</v>
+        <v>-37.34</v>
       </c>
       <c r="D55" s="6">
+        <v>-4.17</v>
+      </c>
+      <c r="E55" s="8">
+        <v>33.17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
         <v>11.4</v>
       </c>
-      <c r="E55" s="7">
-        <v>-14.93</v>
+      <c r="D56" s="6">
+        <v>22.66</v>
+      </c>
+      <c r="E56" s="8">
+        <v>11.26</v>
       </c>
     </row>
   </sheetData>
@@ -2709,16 +2738,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>48</v>
+        <v>46.1</v>
       </c>
       <c r="E2" s="11">
         <v>16.7</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.6</v>
+        <v>-2.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.699999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>58</v>
@@ -2846,22 +2875,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>-0.0058</v>
+        <v>0.0035</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0431</v>
+        <v>-0.0241</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0462</v>
+        <v>-0.0498</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1293</v>
+        <v>-0.1252</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1746</v>
+        <v>-0.171</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.2022</v>
+        <v>-0.2149</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="70">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,19 +184,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>68.4 → 74.3</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>68.4</t>
-  </si>
-  <si>
-    <t>74.3</t>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -248,7 +242,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,7 +276,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -294,15 +288,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,19 +316,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,12 +402,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -435,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -934,10 +915,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>25.01</v>
+        <v>24.88</v>
       </c>
       <c r="D2">
-        <v>-3.14</v>
+        <v>-0.52</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -946,25 +927,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.68</v>
+        <v>-26.06</v>
       </c>
       <c r="H2">
-        <v>8.83</v>
+        <v>8.27</v>
       </c>
       <c r="I2">
-        <v>-8.59</v>
+        <v>-5.65</v>
       </c>
       <c r="J2">
-        <v>-6.05</v>
+        <v>-5.83</v>
       </c>
       <c r="K2">
-        <v>-7.92</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L2">
-        <v>-24.49</v>
+        <v>-24.81</v>
       </c>
       <c r="M2">
-        <v>-12.52</v>
+        <v>-12.24</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -973,19 +954,19 @@
         <v>38</v>
       </c>
       <c r="P2">
-        <v>25.88</v>
+        <v>25.58</v>
       </c>
       <c r="Q2">
-        <v>26</v>
+        <v>25.93</v>
       </c>
       <c r="R2">
-        <v>26.87</v>
+        <v>26.83</v>
       </c>
       <c r="S2">
-        <v>27.8</v>
+        <v>27.77</v>
       </c>
       <c r="T2">
-        <v>-10.03</v>
+        <v>-10.39</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1000,34 +981,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.92</v>
+        <v>39.09</v>
       </c>
       <c r="Z2">
-        <v>-0.31</v>
+        <v>-0.37</v>
       </c>
       <c r="AA2">
-        <v>-0.32</v>
+        <v>-0.33</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="AC2">
-        <v>55.06</v>
+        <v>45</v>
       </c>
       <c r="AD2">
-        <v>62.11</v>
+        <v>54.47</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>-39.35</v>
+        <v>-44.93</v>
       </c>
       <c r="AG2">
-        <v>27.12</v>
+        <v>27.15</v>
       </c>
       <c r="AH2">
-        <v>24.87</v>
+        <v>24.71</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1036,7 +1017,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>41.63</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1047,10 +1028,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.359999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="D3">
-        <v>-4</v>
+        <v>-1.18</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1059,46 +1040,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-32.37</v>
+        <v>-33.16</v>
       </c>
       <c r="H3">
-        <v>5.52</v>
+        <v>4.28</v>
       </c>
       <c r="I3">
-        <v>-16.05</v>
+        <v>-14.67</v>
       </c>
       <c r="J3">
-        <v>-6.21</v>
+        <v>-7.22</v>
       </c>
       <c r="K3">
-        <v>-15.06</v>
+        <v>-14.51</v>
       </c>
       <c r="L3">
-        <v>-32.95</v>
+        <v>-32.33</v>
       </c>
       <c r="M3">
-        <v>-17.1</v>
+        <v>-17.29</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P3">
-        <v>9.99</v>
+        <v>9.68</v>
       </c>
       <c r="Q3">
-        <v>9.81</v>
+        <v>9.77</v>
       </c>
       <c r="R3">
-        <v>10.18</v>
+        <v>10.15</v>
       </c>
       <c r="S3">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
       <c r="T3">
-        <v>-12.78</v>
+        <v>-13.68</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1113,43 +1094,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.06</v>
+        <v>40.88</v>
       </c>
       <c r="Z3">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="AA3">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="AC3">
-        <v>49.44</v>
+        <v>42.09</v>
       </c>
       <c r="AD3">
-        <v>58.59</v>
+        <v>49.5</v>
       </c>
       <c r="AE3">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="AF3">
-        <v>-55.94</v>
+        <v>-61.36</v>
       </c>
       <c r="AG3">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
       <c r="AH3">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="AI3">
-        <v>11.11</v>
+        <v>10.8</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>21.76</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1160,58 +1141,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>211.39</v>
+        <v>210.8</v>
       </c>
       <c r="D4">
-        <v>-1.22</v>
+        <v>-0.28</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>211</v>
+        <v>210.8</v>
       </c>
       <c r="G4">
-        <v>-32.87</v>
+        <v>-33.06</v>
       </c>
       <c r="H4">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-2.94</v>
+        <v>-3.74</v>
       </c>
       <c r="J4">
-        <v>-8.050000000000001</v>
+        <v>-8.34</v>
       </c>
       <c r="K4">
-        <v>-11.93</v>
+        <v>-10.22</v>
       </c>
       <c r="L4">
-        <v>-32.39</v>
+        <v>-32.46</v>
       </c>
       <c r="M4">
-        <v>-4.98</v>
+        <v>-5.06</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>215.93</v>
+        <v>214.29</v>
       </c>
       <c r="Q4">
-        <v>218.37</v>
+        <v>217.37</v>
       </c>
       <c r="R4">
-        <v>231.08</v>
+        <v>230.22</v>
       </c>
       <c r="S4">
-        <v>244.19</v>
+        <v>243.76</v>
       </c>
       <c r="T4">
-        <v>-13.43</v>
+        <v>-13.52</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1226,43 +1207,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.84</v>
+        <v>34.21</v>
       </c>
       <c r="Z4">
-        <v>-4.62</v>
+        <v>-4.71</v>
       </c>
       <c r="AA4">
-        <v>-5.07</v>
+        <v>-5</v>
       </c>
       <c r="AB4">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
       <c r="AC4">
-        <v>70.8</v>
+        <v>61.18</v>
       </c>
       <c r="AD4">
-        <v>83.40000000000001</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="AE4">
-        <v>5.1</v>
+        <v>4.99</v>
       </c>
       <c r="AF4">
-        <v>-0.7</v>
+        <v>-16.18</v>
       </c>
       <c r="AG4">
-        <v>230.91</v>
+        <v>228.91</v>
       </c>
       <c r="AH4">
-        <v>205.83</v>
+        <v>205.84</v>
       </c>
       <c r="AI4">
-        <v>226.22</v>
+        <v>225.42</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>34.91</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1273,10 +1254,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>767.25</v>
+        <v>759.55</v>
       </c>
       <c r="D5">
-        <v>4.85</v>
+        <v>-1</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1285,88 +1266,88 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-4.58</v>
+        <v>-5.53</v>
       </c>
       <c r="H5">
-        <v>56.36</v>
+        <v>54.79</v>
       </c>
       <c r="I5">
-        <v>14.03</v>
+        <v>11.25</v>
       </c>
       <c r="J5">
-        <v>14.69</v>
+        <v>11.26</v>
       </c>
       <c r="K5">
-        <v>3.21</v>
+        <v>5.06</v>
       </c>
       <c r="L5">
-        <v>-4.8</v>
+        <v>-5.43</v>
       </c>
       <c r="M5">
-        <v>-2.41</v>
+        <v>-1.55</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>715.14</v>
+        <v>730.5</v>
       </c>
       <c r="Q5">
-        <v>675.3200000000001</v>
+        <v>679.17</v>
       </c>
       <c r="R5">
-        <v>677.53</v>
+        <v>678.97</v>
       </c>
       <c r="S5">
-        <v>617.74</v>
+        <v>617.9</v>
       </c>
       <c r="T5">
-        <v>24.2</v>
+        <v>22.92</v>
       </c>
       <c r="U5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V5" t="s">
         <v>45</v>
       </c>
       <c r="W5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>74.34</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="Z5">
-        <v>12.63</v>
+        <v>16.83</v>
       </c>
       <c r="AA5">
-        <v>1.13</v>
+        <v>4.27</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>12.56</v>
       </c>
       <c r="AC5">
-        <v>100</v>
+        <v>97.33</v>
       </c>
       <c r="AD5">
-        <v>99.09</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="AE5">
-        <v>32.67</v>
+        <v>33.23</v>
       </c>
       <c r="AF5">
-        <v>652.42</v>
+        <v>47.54</v>
       </c>
       <c r="AG5">
-        <v>738.5599999999999</v>
+        <v>752.78</v>
       </c>
       <c r="AH5">
-        <v>612.08</v>
+        <v>605.55</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1375,7 +1356,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>38.01</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1386,58 +1367,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.56</v>
+        <v>24.27</v>
       </c>
       <c r="D6">
-        <v>-4.03</v>
+        <v>-1.18</v>
       </c>
       <c r="E6">
-        <v>51.66</v>
+        <v>50.22</v>
       </c>
       <c r="F6">
-        <v>24.39</v>
+        <v>24.27</v>
       </c>
       <c r="G6">
-        <v>-52.46</v>
+        <v>-51.67</v>
       </c>
       <c r="H6">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-6.37</v>
+        <v>-8.35</v>
       </c>
       <c r="J6">
-        <v>-9.039999999999999</v>
+        <v>-9.41</v>
       </c>
       <c r="K6">
-        <v>-16.91</v>
+        <v>-15.61</v>
       </c>
       <c r="L6">
-        <v>-52.45</v>
+        <v>-53.02</v>
       </c>
       <c r="M6">
-        <v>-21.49</v>
+        <v>-20.71</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>25.95</v>
+        <v>25.51</v>
       </c>
       <c r="Q6">
-        <v>25.92</v>
+        <v>25.79</v>
       </c>
       <c r="R6">
-        <v>27.29</v>
+        <v>27.19</v>
       </c>
       <c r="S6">
-        <v>32.13</v>
+        <v>32.04</v>
       </c>
       <c r="T6">
-        <v>-23.56</v>
+        <v>-24.24</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1452,34 +1433,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.25</v>
+        <v>35.7</v>
       </c>
       <c r="Z6">
-        <v>-0.47</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA6">
         <v>-0.54</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>60.64</v>
+        <v>37.95</v>
       </c>
       <c r="AD6">
-        <v>80.5</v>
+        <v>60.79</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>-4.17</v>
+        <v>-12.66</v>
       </c>
       <c r="AG6">
-        <v>27.56</v>
+        <v>27.51</v>
       </c>
       <c r="AH6">
-        <v>24.28</v>
+        <v>24.06</v>
       </c>
       <c r="AI6">
         <v>27.21</v>
@@ -1488,7 +1469,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>28.16</v>
+        <v>27.97</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1499,10 +1480,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1209</v>
+        <v>1184.5</v>
       </c>
       <c r="D7">
-        <v>0.58</v>
+        <v>-2.03</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1511,46 +1492,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-23.72</v>
+        <v>-25.27</v>
       </c>
       <c r="H7">
-        <v>4.32</v>
+        <v>2.21</v>
       </c>
       <c r="I7">
-        <v>3.63</v>
+        <v>0.84</v>
       </c>
       <c r="J7">
-        <v>-1.42</v>
+        <v>-5.04</v>
       </c>
       <c r="K7">
-        <v>-7.26</v>
+        <v>-8.08</v>
       </c>
       <c r="L7">
-        <v>-11.62</v>
+        <v>-14.9</v>
       </c>
       <c r="M7">
-        <v>0.35</v>
+        <v>-0.09</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="P7">
-        <v>1202.36</v>
+        <v>1204.34</v>
       </c>
       <c r="Q7">
-        <v>1198.28</v>
+        <v>1195.49</v>
       </c>
       <c r="R7">
-        <v>1255.53</v>
+        <v>1252.68</v>
       </c>
       <c r="S7">
-        <v>1337.33</v>
+        <v>1335.41</v>
       </c>
       <c r="T7">
-        <v>-9.6</v>
+        <v>-11.3</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1565,34 +1546,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>48.46</v>
+        <v>42.78</v>
       </c>
       <c r="Z7">
-        <v>-15.49</v>
+        <v>-15.41</v>
       </c>
       <c r="AA7">
-        <v>-21.71</v>
+        <v>-20.45</v>
       </c>
       <c r="AB7">
-        <v>6.22</v>
+        <v>5.04</v>
       </c>
       <c r="AC7">
-        <v>92.04000000000001</v>
+        <v>82.78</v>
       </c>
       <c r="AD7">
-        <v>90.84</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="AE7">
-        <v>25.05</v>
+        <v>25.01</v>
       </c>
       <c r="AF7">
-        <v>22.66</v>
+        <v>3.2</v>
       </c>
       <c r="AG7">
-        <v>1249.12</v>
+        <v>1242.59</v>
       </c>
       <c r="AH7">
-        <v>1147.45</v>
+        <v>1148.39</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1601,7 +1582,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>36.3</v>
+        <v>32.75</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1785,901 +1766,887 @@
         <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-6.05</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-3.67</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.69</v>
+        <v>-6.05</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.21</v>
+        <v>-5.83</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.52</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.67</v>
+        <v>-6.21</v>
       </c>
       <c r="D9" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.38</v>
+        <v>-7.22</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>8.56</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>14.69</v>
+        <v>-8.34</v>
       </c>
       <c r="E10" s="8">
-        <v>6.13</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.29</v>
+        <v>14.69</v>
       </c>
       <c r="D11" s="6">
-        <v>-9.039999999999999</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-5.75</v>
+        <v>11.26</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.43</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.37</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.42</v>
+        <v>-9.41</v>
       </c>
       <c r="E12" s="8">
-        <v>1.95</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.89</v>
+        <v>-1.42</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.59</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-10.48</v>
+        <v>-5.04</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.52</v>
+        <v>-8.59</v>
       </c>
       <c r="D14" s="6">
-        <v>-16.05</v>
+        <v>-5.65</v>
       </c>
       <c r="E14" s="7">
-        <v>-16.57</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>0.26</v>
+        <v>-16.05</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.94</v>
+        <v>-14.67</v>
       </c>
       <c r="E15" s="7">
-        <v>-3.2</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>11.73</v>
+        <v>-2.94</v>
       </c>
       <c r="D16" s="6">
-        <v>14.03</v>
+        <v>-3.74</v>
       </c>
       <c r="E16" s="8">
-        <v>2.3</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>2.28</v>
+        <v>14.03</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-8.65</v>
+        <v>11.25</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.78</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>3.72</v>
+        <v>-6.37</v>
       </c>
       <c r="D18" s="6">
-        <v>3.63</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.09</v>
+        <v>-8.35</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-21.62</v>
+        <v>3.63</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.49</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.87</v>
+        <v>0.84</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.35</v>
+        <v>-24.49</v>
       </c>
       <c r="D20" s="6">
-        <v>-32.95</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.6</v>
+        <v>-24.81</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-29.97</v>
+        <v>-32.95</v>
       </c>
       <c r="D21" s="6">
-        <v>-32.39</v>
+        <v>-32.33</v>
       </c>
       <c r="E21" s="7">
-        <v>-2.42</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-10.71</v>
+        <v>-32.39</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.8</v>
+        <v>-32.46</v>
       </c>
       <c r="E22" s="8">
-        <v>5.91</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-49.53</v>
+        <v>-4.8</v>
       </c>
       <c r="D23" s="6">
-        <v>-52.45</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.92</v>
+        <v>-5.43</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-12.24</v>
+        <v>-52.45</v>
       </c>
       <c r="D24" s="6">
-        <v>-11.62</v>
+        <v>-53.02</v>
       </c>
       <c r="E24" s="8">
-        <v>0.62</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-4.41</v>
+        <v>-11.62</v>
       </c>
       <c r="D25" s="6">
-        <v>-7.92</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.51</v>
+        <v>-14.9</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-12</v>
+        <v>-7.92</v>
       </c>
       <c r="D26" s="6">
-        <v>-15.06</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-3.06</v>
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-10.43</v>
+        <v>-15.06</v>
       </c>
       <c r="D27" s="6">
-        <v>-11.93</v>
+        <v>-14.51</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.09</v>
+        <v>-11.93</v>
       </c>
       <c r="D28" s="6">
-        <v>3.21</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.3</v>
+        <v>-10.22</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-14.39</v>
+        <v>3.21</v>
       </c>
       <c r="D29" s="6">
-        <v>-16.91</v>
+        <v>5.06</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.52</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-9.15</v>
+        <v>-16.91</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.89</v>
+        <v>-15.61</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-23.27</v>
+        <v>-7.26</v>
       </c>
       <c r="D31" s="6">
-        <v>-25.68</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.41</v>
+        <v>-8.08</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-30.16</v>
+        <v>-25.68</v>
       </c>
       <c r="D32" s="6">
-        <v>-32.37</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.21</v>
+        <v>-26.06</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-32.04</v>
+        <v>-32.37</v>
       </c>
       <c r="D33" s="6">
-        <v>-32.87</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.83</v>
+        <v>-33.16</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-9.210000000000001</v>
+        <v>-32.87</v>
       </c>
       <c r="D34" s="6">
-        <v>-4.58</v>
+        <v>-33.06</v>
       </c>
       <c r="E34" s="8">
-        <v>4.63</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-50.46</v>
+        <v>-4.58</v>
       </c>
       <c r="D35" s="6">
-        <v>-52.46</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2</v>
+        <v>-5.53</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-24.16</v>
+        <v>-52.46</v>
       </c>
       <c r="D36" s="6">
-        <v>-23.72</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.44</v>
+        <v>-51.67</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>25.82</v>
+        <v>-23.72</v>
       </c>
       <c r="D37" s="6">
-        <v>25.01</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-25.27</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>9.75</v>
+        <v>25.01</v>
       </c>
       <c r="D38" s="6">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.39</v>
+        <v>24.88</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>214</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D39" s="6">
-        <v>211.39</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.61</v>
+        <v>9.25</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>731.75</v>
+        <v>211.39</v>
       </c>
       <c r="D40" s="6">
-        <v>767.25</v>
+        <v>210.8</v>
       </c>
       <c r="E40" s="8">
-        <v>35.5</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>25.59</v>
+        <v>767.25</v>
       </c>
       <c r="D41" s="6">
-        <v>24.56</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.03</v>
+        <v>759.55</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-7.7</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1202</v>
+        <v>24.56</v>
       </c>
       <c r="D42" s="6">
-        <v>1209</v>
+        <v>24.27</v>
       </c>
       <c r="E42" s="8">
-        <v>7</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>50</v>
+        <v>1209</v>
       </c>
       <c r="D43" s="6">
-        <v>33</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-17</v>
+        <v>1184.5</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-24.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>33</v>
+        <v>39.92</v>
       </c>
       <c r="D44" s="6">
-        <v>50</v>
+        <v>39.09</v>
       </c>
       <c r="E44" s="8">
-        <v>17</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>45.5</v>
+        <v>42.06</v>
       </c>
       <c r="D45" s="6">
-        <v>39.92</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-5.58</v>
+        <v>40.88</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>46.51</v>
+        <v>34.84</v>
       </c>
       <c r="D46" s="6">
-        <v>42.06</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-4.45</v>
+        <v>34.21</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>37.66</v>
+        <v>74.34</v>
       </c>
       <c r="D47" s="6">
-        <v>34.84</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.82</v>
+        <v>71.20999999999999</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-3.13</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>68.38</v>
+        <v>37.25</v>
       </c>
       <c r="D48" s="6">
-        <v>74.34</v>
+        <v>35.7</v>
       </c>
       <c r="E48" s="8">
-        <v>5.96</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>43.51</v>
+        <v>48.46</v>
       </c>
       <c r="D49" s="6">
-        <v>37.25</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-6.26</v>
+        <v>42.78</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-5.68</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>46.58</v>
+        <v>-39.35</v>
       </c>
       <c r="D50" s="6">
-        <v>48.46</v>
+        <v>-44.93</v>
       </c>
       <c r="E50" s="8">
-        <v>1.88</v>
+        <v>-5.58</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-68.58</v>
+        <v>-55.94</v>
       </c>
       <c r="D51" s="6">
-        <v>-39.35</v>
+        <v>-61.36</v>
       </c>
       <c r="E51" s="8">
-        <v>29.23</v>
+        <v>-5.42</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-57.82</v>
+        <v>-0.7</v>
       </c>
       <c r="D52" s="6">
-        <v>-55.94</v>
+        <v>-16.18</v>
       </c>
       <c r="E52" s="8">
-        <v>1.88</v>
+        <v>-15.48</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>-30.51</v>
+        <v>652.42</v>
       </c>
       <c r="D53" s="6">
-        <v>-0.7</v>
+        <v>47.54</v>
       </c>
       <c r="E53" s="8">
-        <v>29.81</v>
+        <v>-604.88</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>14403.06</v>
+        <v>-4.17</v>
       </c>
       <c r="D54" s="6">
-        <v>652.42</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-13750.64</v>
+        <v>-12.66</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-8.49</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C55" s="6">
-        <v>-37.34</v>
+        <v>22.66</v>
       </c>
       <c r="D55" s="6">
-        <v>-4.17</v>
+        <v>3.2</v>
       </c>
       <c r="E55" s="8">
-        <v>33.17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="6">
-        <v>11.4</v>
-      </c>
-      <c r="D56" s="6">
-        <v>22.66</v>
-      </c>
-      <c r="E56" s="8">
-        <v>11.26</v>
+        <v>-19.46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2703,28 +2670,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2738,22 +2705,22 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>46.1</v>
+        <v>44</v>
       </c>
       <c r="E2" s="11">
         <v>16.7</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.7</v>
+        <v>-4.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.300000000000001</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>58</v>
       </c>
       <c r="I2" s="11">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>
@@ -2875,22 +2842,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>0.0035</v>
+        <v>-0.0009</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0241</v>
+        <v>-0.0155</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0498</v>
+        <v>-0.0506</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1252</v>
+        <v>-0.1224</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.171</v>
+        <v>-0.1729</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.2149</v>
+        <v>-0.2071</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,13 +184,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>71.2 → 54.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>71.2</t>
+  </si>
+  <si>
+    <t>54.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -242,7 +248,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,7 +282,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -288,8 +294,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -316,13 +329,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,12 +421,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -416,7 +435,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -775,7 +794,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -915,10 +936,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.88</v>
+        <v>24.07</v>
       </c>
       <c r="D2">
-        <v>-0.52</v>
+        <v>-3.26</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -927,25 +948,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.06</v>
+        <v>-28.47</v>
       </c>
       <c r="H2">
-        <v>8.27</v>
+        <v>4.74</v>
       </c>
       <c r="I2">
-        <v>-5.65</v>
+        <v>-7.64</v>
       </c>
       <c r="J2">
-        <v>-5.83</v>
+        <v>-8.34</v>
       </c>
       <c r="K2">
-        <v>-9.199999999999999</v>
+        <v>-10.75</v>
       </c>
       <c r="L2">
-        <v>-24.81</v>
+        <v>-27.35</v>
       </c>
       <c r="M2">
-        <v>-12.24</v>
+        <v>-12.28</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -954,19 +975,19 @@
         <v>38</v>
       </c>
       <c r="P2">
-        <v>25.58</v>
+        <v>25.19</v>
       </c>
       <c r="Q2">
-        <v>25.93</v>
+        <v>25.79</v>
       </c>
       <c r="R2">
-        <v>26.83</v>
+        <v>26.76</v>
       </c>
       <c r="S2">
-        <v>27.77</v>
+        <v>27.73</v>
       </c>
       <c r="T2">
-        <v>-10.39</v>
+        <v>-13.2</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -981,34 +1002,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.09</v>
+        <v>34.31</v>
       </c>
       <c r="Z2">
-        <v>-0.37</v>
+        <v>-0.48</v>
       </c>
       <c r="AA2">
-        <v>-0.33</v>
+        <v>-0.36</v>
       </c>
       <c r="AB2">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>45</v>
+        <v>28.75</v>
       </c>
       <c r="AD2">
-        <v>54.47</v>
+        <v>42.94</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>-44.93</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AG2">
-        <v>27.15</v>
+        <v>27.19</v>
       </c>
       <c r="AH2">
-        <v>24.71</v>
+        <v>24.39</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1017,7 +1038,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>43.88</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1028,10 +1049,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.25</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="D3">
-        <v>-1.18</v>
+        <v>-2.38</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1040,46 +1061,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.16</v>
+        <v>-34.75</v>
       </c>
       <c r="H3">
-        <v>4.28</v>
+        <v>1.8</v>
       </c>
       <c r="I3">
-        <v>-14.67</v>
+        <v>-10.33</v>
       </c>
       <c r="J3">
-        <v>-7.22</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K3">
-        <v>-14.51</v>
+        <v>-15.13</v>
       </c>
       <c r="L3">
-        <v>-32.33</v>
+        <v>-33.21</v>
       </c>
       <c r="M3">
-        <v>-17.29</v>
+        <v>-17.25</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>9.68</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="Q3">
-        <v>9.77</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="R3">
-        <v>10.15</v>
+        <v>10.11</v>
       </c>
       <c r="S3">
-        <v>10.72</v>
+        <v>10.7</v>
       </c>
       <c r="T3">
-        <v>-13.68</v>
+        <v>-15.59</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1094,43 +1115,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>40.88</v>
+        <v>38.54</v>
       </c>
       <c r="Z3">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="AA3">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="AB3">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="AC3">
-        <v>42.09</v>
+        <v>33.35</v>
       </c>
       <c r="AD3">
-        <v>49.5</v>
+        <v>41.63</v>
       </c>
       <c r="AE3">
         <v>0.49</v>
       </c>
       <c r="AF3">
-        <v>-61.36</v>
+        <v>-52.68</v>
       </c>
       <c r="AG3">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
       <c r="AH3">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="AI3">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>20.61</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1141,37 +1162,37 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>210.8</v>
+        <v>205.03</v>
       </c>
       <c r="D4">
-        <v>-0.28</v>
+        <v>-2.74</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>210.8</v>
+        <v>205.03</v>
       </c>
       <c r="G4">
-        <v>-33.06</v>
+        <v>-34.89</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-3.74</v>
+        <v>-6.38</v>
       </c>
       <c r="J4">
-        <v>-8.34</v>
+        <v>-11.13</v>
       </c>
       <c r="K4">
-        <v>-10.22</v>
+        <v>-12.06</v>
       </c>
       <c r="L4">
-        <v>-32.46</v>
+        <v>-33.71</v>
       </c>
       <c r="M4">
-        <v>-5.06</v>
+        <v>-5.88</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1180,19 +1201,19 @@
         <v>28</v>
       </c>
       <c r="P4">
-        <v>214.29</v>
+        <v>211.49</v>
       </c>
       <c r="Q4">
-        <v>217.37</v>
+        <v>216.02</v>
       </c>
       <c r="R4">
-        <v>230.22</v>
+        <v>229.26</v>
       </c>
       <c r="S4">
-        <v>243.76</v>
+        <v>243.28</v>
       </c>
       <c r="T4">
-        <v>-13.52</v>
+        <v>-15.72</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1207,43 +1228,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>34.21</v>
+        <v>28.79</v>
       </c>
       <c r="Z4">
-        <v>-4.71</v>
+        <v>-5.19</v>
       </c>
       <c r="AA4">
-        <v>-5</v>
+        <v>-5.04</v>
       </c>
       <c r="AB4">
-        <v>0.28</v>
+        <v>-0.16</v>
       </c>
       <c r="AC4">
-        <v>61.18</v>
+        <v>47.09</v>
       </c>
       <c r="AD4">
-        <v>72.29000000000001</v>
+        <v>59.69</v>
       </c>
       <c r="AE4">
-        <v>4.99</v>
+        <v>5.28</v>
       </c>
       <c r="AF4">
-        <v>-16.18</v>
+        <v>42.72</v>
       </c>
       <c r="AG4">
-        <v>228.91</v>
+        <v>226.57</v>
       </c>
       <c r="AH4">
-        <v>205.84</v>
+        <v>205.46</v>
       </c>
       <c r="AI4">
-        <v>225.42</v>
+        <v>222.84</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>36.62</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1254,10 +1275,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>759.55</v>
+        <v>705.95</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>-7.06</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1266,46 +1287,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-5.53</v>
+        <v>-12.2</v>
       </c>
       <c r="H5">
-        <v>54.79</v>
+        <v>43.87</v>
       </c>
       <c r="I5">
-        <v>11.25</v>
+        <v>3.71</v>
       </c>
       <c r="J5">
-        <v>11.26</v>
+        <v>3.42</v>
       </c>
       <c r="K5">
-        <v>5.06</v>
+        <v>-2.55</v>
       </c>
       <c r="L5">
-        <v>-5.43</v>
+        <v>-10.69</v>
       </c>
       <c r="M5">
-        <v>-1.55</v>
+        <v>-2.54</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>730.5</v>
+        <v>735.55</v>
       </c>
       <c r="Q5">
-        <v>679.17</v>
+        <v>679.79</v>
       </c>
       <c r="R5">
-        <v>678.97</v>
+        <v>679.1900000000001</v>
       </c>
       <c r="S5">
-        <v>617.9</v>
+        <v>617.76</v>
       </c>
       <c r="T5">
-        <v>22.92</v>
+        <v>14.28</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1320,34 +1341,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>71.20999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="Z5">
-        <v>16.83</v>
+        <v>15.66</v>
       </c>
       <c r="AA5">
-        <v>4.27</v>
+        <v>6.55</v>
       </c>
       <c r="AB5">
-        <v>12.56</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AC5">
-        <v>97.33</v>
+        <v>80.09</v>
       </c>
       <c r="AD5">
-        <v>98.65000000000001</v>
+        <v>92.47</v>
       </c>
       <c r="AE5">
-        <v>33.23</v>
+        <v>35.25</v>
       </c>
       <c r="AF5">
-        <v>47.54</v>
+        <v>-34.69</v>
       </c>
       <c r="AG5">
-        <v>752.78</v>
+        <v>754.12</v>
       </c>
       <c r="AH5">
-        <v>605.55</v>
+        <v>605.45</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1356,7 +1377,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>40.16</v>
+        <v>36.46</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1367,58 +1388,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.27</v>
+        <v>23.5</v>
       </c>
       <c r="D6">
-        <v>-1.18</v>
+        <v>-3.17</v>
       </c>
       <c r="E6">
-        <v>50.22</v>
+        <v>48.99</v>
       </c>
       <c r="F6">
-        <v>24.27</v>
+        <v>23.5</v>
       </c>
       <c r="G6">
-        <v>-51.67</v>
+        <v>-52.03</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-8.35</v>
+        <v>-11.92</v>
       </c>
       <c r="J6">
-        <v>-9.41</v>
+        <v>-12.67</v>
       </c>
       <c r="K6">
-        <v>-15.61</v>
+        <v>-16.46</v>
       </c>
       <c r="L6">
-        <v>-53.02</v>
+        <v>-53.21</v>
       </c>
       <c r="M6">
-        <v>-20.71</v>
+        <v>-21.04</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>25.51</v>
+        <v>24.88</v>
       </c>
       <c r="Q6">
-        <v>25.79</v>
+        <v>25.61</v>
       </c>
       <c r="R6">
-        <v>27.19</v>
+        <v>27.08</v>
       </c>
       <c r="S6">
-        <v>32.04</v>
+        <v>31.93</v>
       </c>
       <c r="T6">
-        <v>-24.24</v>
+        <v>-26.41</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1433,43 +1454,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.7</v>
+        <v>31.89</v>
       </c>
       <c r="Z6">
-        <v>-0.5600000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="AA6">
-        <v>-0.54</v>
+        <v>-0.57</v>
       </c>
       <c r="AB6">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>37.95</v>
+        <v>19.66</v>
       </c>
       <c r="AD6">
-        <v>60.79</v>
+        <v>39.42</v>
       </c>
       <c r="AE6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>-12.66</v>
+        <v>-2.79</v>
       </c>
       <c r="AG6">
-        <v>27.51</v>
+        <v>27.49</v>
       </c>
       <c r="AH6">
-        <v>24.06</v>
+        <v>23.72</v>
       </c>
       <c r="AI6">
-        <v>27.21</v>
+        <v>26.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>27.97</v>
+        <v>29.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1480,10 +1501,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1184.5</v>
+        <v>1190</v>
       </c>
       <c r="D7">
-        <v>-2.03</v>
+        <v>0.46</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1492,46 +1513,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-25.27</v>
+        <v>-24.92</v>
       </c>
       <c r="H7">
-        <v>2.21</v>
+        <v>2.68</v>
       </c>
       <c r="I7">
-        <v>0.84</v>
+        <v>-2.06</v>
       </c>
       <c r="J7">
-        <v>-5.04</v>
+        <v>-4.06</v>
       </c>
       <c r="K7">
-        <v>-8.08</v>
+        <v>-6.46</v>
       </c>
       <c r="L7">
-        <v>-14.9</v>
+        <v>-15.62</v>
       </c>
       <c r="M7">
-        <v>-0.09</v>
+        <v>0.2</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="P7">
-        <v>1204.34</v>
+        <v>1199.34</v>
       </c>
       <c r="Q7">
-        <v>1195.49</v>
+        <v>1192.59</v>
       </c>
       <c r="R7">
-        <v>1252.68</v>
+        <v>1250</v>
       </c>
       <c r="S7">
-        <v>1335.41</v>
+        <v>1333.43</v>
       </c>
       <c r="T7">
-        <v>-11.3</v>
+        <v>-10.76</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1546,34 +1567,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.78</v>
+        <v>44.35</v>
       </c>
       <c r="Z7">
-        <v>-15.41</v>
+        <v>-14.74</v>
       </c>
       <c r="AA7">
-        <v>-20.45</v>
+        <v>-19.31</v>
       </c>
       <c r="AB7">
-        <v>5.04</v>
+        <v>4.57</v>
       </c>
       <c r="AC7">
-        <v>82.78</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="AD7">
-        <v>89.56999999999999</v>
+        <v>83.81</v>
       </c>
       <c r="AE7">
-        <v>25.01</v>
+        <v>26</v>
       </c>
       <c r="AF7">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="AG7">
-        <v>1242.59</v>
+        <v>1232.7</v>
       </c>
       <c r="AH7">
-        <v>1148.39</v>
+        <v>1152.48</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1582,7 +1603,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>32.75</v>
+        <v>30.21</v>
       </c>
     </row>
   </sheetData>
@@ -1723,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1766,887 +1787,867 @@
         <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>61</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.83</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-8.34</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.05</v>
+        <v>-7.22</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.83</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="E8" s="7">
-        <v>0.22</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.21</v>
+        <v>-8.34</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.01</v>
+        <v>-11.13</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-8.050000000000001</v>
+        <v>11.26</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.34</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.29</v>
+        <v>3.42</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>14.69</v>
+        <v>-9.41</v>
       </c>
       <c r="D11" s="6">
-        <v>11.26</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-3.43</v>
+        <v>-12.67</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.039999999999999</v>
+        <v>-5.04</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.41</v>
+        <v>-4.06</v>
       </c>
       <c r="E12" s="8">
-        <v>-0.37</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.42</v>
+        <v>-5.65</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-3.62</v>
+        <v>-7.64</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.59</v>
+        <v>-14.67</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.65</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.94</v>
+        <v>-10.33</v>
+      </c>
+      <c r="E14" s="8">
+        <v>4.34</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-16.05</v>
+        <v>-3.74</v>
       </c>
       <c r="D15" s="6">
-        <v>-14.67</v>
+        <v>-6.38</v>
       </c>
       <c r="E15" s="7">
-        <v>1.38</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.94</v>
+        <v>11.25</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.8</v>
+        <v>3.71</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-7.54</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>14.03</v>
+        <v>-8.35</v>
       </c>
       <c r="D17" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.78</v>
+        <v>-11.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-6.37</v>
+        <v>0.84</v>
       </c>
       <c r="D18" s="6">
-        <v>-8.35</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.98</v>
+        <v>-2.06</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>3.63</v>
+        <v>-24.81</v>
       </c>
       <c r="D19" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.79</v>
+        <v>-27.35</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.54</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-24.49</v>
+        <v>-32.33</v>
       </c>
       <c r="D20" s="6">
-        <v>-24.81</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.32</v>
+        <v>-33.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-32.95</v>
+        <v>-32.46</v>
       </c>
       <c r="D21" s="6">
-        <v>-32.33</v>
+        <v>-33.71</v>
       </c>
       <c r="E21" s="7">
-        <v>0.62</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>-32.39</v>
+        <v>-5.43</v>
       </c>
       <c r="D22" s="6">
-        <v>-32.46</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-10.69</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.8</v>
+        <v>-53.02</v>
       </c>
       <c r="D23" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.63</v>
+        <v>-53.21</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-52.45</v>
+        <v>-14.9</v>
       </c>
       <c r="D24" s="6">
-        <v>-53.02</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.57</v>
+        <v>-15.62</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-11.62</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D25" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-3.28</v>
+        <v>-10.75</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-7.92</v>
+        <v>-14.51</v>
       </c>
       <c r="D26" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.28</v>
+        <v>-15.13</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-15.06</v>
+        <v>-10.22</v>
       </c>
       <c r="D27" s="6">
-        <v>-14.51</v>
+        <v>-12.06</v>
       </c>
       <c r="E27" s="7">
-        <v>0.55</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-11.93</v>
+        <v>5.06</v>
       </c>
       <c r="D28" s="6">
-        <v>-10.22</v>
+        <v>-2.55</v>
       </c>
       <c r="E28" s="7">
-        <v>1.71</v>
+        <v>-7.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>3.21</v>
+        <v>-15.61</v>
       </c>
       <c r="D29" s="6">
-        <v>5.06</v>
+        <v>-16.46</v>
       </c>
       <c r="E29" s="7">
-        <v>1.85</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-16.91</v>
+        <v>-8.08</v>
       </c>
       <c r="D30" s="6">
-        <v>-15.61</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.3</v>
+        <v>-6.46</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-7.26</v>
+        <v>-26.06</v>
       </c>
       <c r="D31" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.82</v>
+        <v>-28.47</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>-25.68</v>
+        <v>-33.16</v>
       </c>
       <c r="D32" s="6">
-        <v>-26.06</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.38</v>
+        <v>-34.75</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="6">
-        <v>-32.37</v>
+        <v>-33.06</v>
       </c>
       <c r="D33" s="6">
-        <v>-33.16</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.79</v>
+        <v>-34.89</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.83</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="6">
-        <v>-32.87</v>
+        <v>-5.53</v>
       </c>
       <c r="D34" s="6">
-        <v>-33.06</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.19</v>
+        <v>-12.2</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.67</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.58</v>
+        <v>-51.67</v>
       </c>
       <c r="D35" s="6">
-        <v>-5.53</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.95</v>
+        <v>-52.03</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-52.46</v>
+        <v>-25.27</v>
       </c>
       <c r="D36" s="6">
-        <v>-51.67</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.79</v>
+        <v>-24.92</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.35</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>-23.72</v>
+        <v>24.88</v>
       </c>
       <c r="D37" s="6">
-        <v>-25.27</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.55</v>
+        <v>24.07</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="6">
-        <v>25.01</v>
+        <v>9.25</v>
       </c>
       <c r="D38" s="6">
-        <v>24.88</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.13</v>
+        <v>9.029999999999999</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C39" s="6">
-        <v>9.359999999999999</v>
+        <v>210.8</v>
       </c>
       <c r="D39" s="6">
-        <v>9.25</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.11</v>
+        <v>205.03</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-5.77</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C40" s="6">
-        <v>211.39</v>
+        <v>759.55</v>
       </c>
       <c r="D40" s="6">
-        <v>210.8</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.59</v>
+        <v>705.95</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-53.6</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C41" s="6">
-        <v>767.25</v>
+        <v>24.27</v>
       </c>
       <c r="D41" s="6">
-        <v>759.55</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-7.7</v>
+        <v>23.5</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>24.56</v>
+        <v>1184.5</v>
       </c>
       <c r="D42" s="6">
-        <v>24.27</v>
+        <v>1190</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.29</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>1209</v>
+        <v>39.09</v>
       </c>
       <c r="D43" s="6">
-        <v>1184.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-24.5</v>
+        <v>34.31</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-4.78</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6">
-        <v>39.92</v>
+        <v>40.88</v>
       </c>
       <c r="D44" s="6">
-        <v>39.09</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.83</v>
+        <v>38.54</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6">
-        <v>42.06</v>
+        <v>34.21</v>
       </c>
       <c r="D45" s="6">
-        <v>40.88</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.18</v>
+        <v>28.79</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-5.42</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6">
-        <v>34.84</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="D46" s="6">
-        <v>34.21</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.63</v>
+        <v>54.1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-17.11</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="6">
-        <v>74.34</v>
+        <v>35.7</v>
       </c>
       <c r="D47" s="6">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-3.13</v>
+        <v>31.89</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.81</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="6">
-        <v>37.25</v>
+        <v>42.78</v>
       </c>
       <c r="D48" s="6">
-        <v>35.7</v>
+        <v>44.35</v>
       </c>
       <c r="E48" s="8">
-        <v>-1.55</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C49" s="6">
-        <v>48.46</v>
+        <v>-44.93</v>
       </c>
       <c r="D49" s="6">
-        <v>42.78</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E49" s="8">
-        <v>-5.68</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C50" s="6">
-        <v>-39.35</v>
+        <v>-61.36</v>
       </c>
       <c r="D50" s="6">
-        <v>-44.93</v>
+        <v>-52.68</v>
       </c>
       <c r="E50" s="8">
-        <v>-5.58</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="6">
-        <v>-55.94</v>
+        <v>-16.18</v>
       </c>
       <c r="D51" s="6">
-        <v>-61.36</v>
+        <v>42.72</v>
       </c>
       <c r="E51" s="8">
-        <v>-5.42</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="6">
-        <v>-0.7</v>
+        <v>47.54</v>
       </c>
       <c r="D52" s="6">
-        <v>-16.18</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-15.48</v>
+        <v>-34.69</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-82.23</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="6">
-        <v>652.42</v>
+        <v>-12.66</v>
       </c>
       <c r="D53" s="6">
-        <v>47.54</v>
+        <v>-2.79</v>
       </c>
       <c r="E53" s="8">
-        <v>-604.88</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="6">
-        <v>-4.17</v>
+        <v>3.2</v>
       </c>
       <c r="D54" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-8.49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="6">
-        <v>22.66</v>
-      </c>
-      <c r="D55" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-19.46</v>
+        <v>1.33</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2670,28 +2671,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2705,16 +2706,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="11">
-        <v>44</v>
+        <v>38.7</v>
       </c>
       <c r="E2" s="11">
         <v>16.7</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.1</v>
+        <v>-7.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.800000000000001</v>
+        <v>-10.6</v>
       </c>
       <c r="H2" s="11">
         <v>58</v>
@@ -2842,22 +2843,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="14">
-        <v>-0.0009</v>
+        <v>0.002</v>
       </c>
       <c r="B2" s="14">
-        <v>-0.0155</v>
+        <v>-0.0254</v>
       </c>
       <c r="C2" s="14">
-        <v>-0.0506</v>
+        <v>-0.0588</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.1224</v>
+        <v>-0.1228</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.1729</v>
+        <v>-0.1725</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.2071</v>
+        <v>-0.2104</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>71.2 → 54.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>71.2</t>
-  </si>
-  <si>
-    <t>54.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -248,7 +221,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,7 +255,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -294,15 +267,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,19 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,22 +371,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -435,7 +394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -794,16 +753,13 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="25" max="26" width="7.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -936,10 +892,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.07</v>
+        <v>24.62</v>
       </c>
       <c r="D2">
-        <v>-3.26</v>
+        <v>2.29</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -948,46 +904,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-28.47</v>
+        <v>-26.84</v>
       </c>
       <c r="H2">
-        <v>4.74</v>
+        <v>7.14</v>
       </c>
       <c r="I2">
-        <v>-7.64</v>
+        <v>-5.85</v>
       </c>
       <c r="J2">
-        <v>-8.34</v>
+        <v>-8.27</v>
       </c>
       <c r="K2">
-        <v>-10.75</v>
+        <v>-9.35</v>
       </c>
       <c r="L2">
-        <v>-27.35</v>
+        <v>-25.44</v>
       </c>
       <c r="M2">
-        <v>-12.28</v>
+        <v>-12.34</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P2">
-        <v>25.19</v>
+        <v>24.88</v>
       </c>
       <c r="Q2">
-        <v>25.79</v>
+        <v>25.69</v>
       </c>
       <c r="R2">
-        <v>26.76</v>
+        <v>26.72</v>
       </c>
       <c r="S2">
-        <v>27.73</v>
+        <v>27.69</v>
       </c>
       <c r="T2">
-        <v>-13.2</v>
+        <v>-11.1</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1002,34 +958,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>34.31</v>
+        <v>39.7</v>
       </c>
       <c r="Z2">
-        <v>-0.48</v>
+        <v>-0.51</v>
       </c>
       <c r="AA2">
-        <v>-0.36</v>
+        <v>-0.39</v>
       </c>
       <c r="AB2">
         <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>28.75</v>
+        <v>25.67</v>
       </c>
       <c r="AD2">
-        <v>42.94</v>
+        <v>33.14</v>
       </c>
       <c r="AE2">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>9.960000000000001</v>
+        <v>-5.15</v>
       </c>
       <c r="AG2">
-        <v>27.19</v>
+        <v>27.14</v>
       </c>
       <c r="AH2">
-        <v>24.39</v>
+        <v>24.25</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1038,7 +994,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>47.08</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1005,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.029999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="D3">
-        <v>-2.38</v>
+        <v>-0.44</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1061,46 +1017,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-34.75</v>
+        <v>-35.04</v>
       </c>
       <c r="H3">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="I3">
-        <v>-10.33</v>
+        <v>-9.65</v>
       </c>
       <c r="J3">
-        <v>-9.609999999999999</v>
+        <v>-10.99</v>
       </c>
       <c r="K3">
-        <v>-15.13</v>
+        <v>-16.45</v>
       </c>
       <c r="L3">
-        <v>-33.21</v>
+        <v>-33.01</v>
       </c>
       <c r="M3">
-        <v>-17.25</v>
+        <v>-17.7</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P3">
-        <v>9.470000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="Q3">
-        <v>9.720000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="R3">
-        <v>10.11</v>
+        <v>10.08</v>
       </c>
       <c r="S3">
-        <v>10.7</v>
+        <v>10.68</v>
       </c>
       <c r="T3">
-        <v>-15.59</v>
+        <v>-15.83</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1115,43 +1071,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.54</v>
+        <v>38.11</v>
       </c>
       <c r="Z3">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="AA3">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AB3">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="AC3">
-        <v>33.35</v>
+        <v>25.31</v>
       </c>
       <c r="AD3">
-        <v>41.63</v>
+        <v>33.58</v>
       </c>
       <c r="AE3">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AF3">
-        <v>-52.68</v>
+        <v>-71.55</v>
       </c>
       <c r="AG3">
-        <v>10.77</v>
+        <v>10.76</v>
       </c>
       <c r="AH3">
-        <v>8.68</v>
+        <v>8.58</v>
       </c>
       <c r="AI3">
-        <v>10.6</v>
+        <v>10.36</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>21.39</v>
+        <v>22.13</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1118,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>205.03</v>
+        <v>205.23</v>
       </c>
       <c r="D4">
-        <v>-2.74</v>
+        <v>0.1</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1174,46 +1130,46 @@
         <v>205.03</v>
       </c>
       <c r="G4">
-        <v>-34.89</v>
+        <v>-34.83</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I4">
-        <v>-6.38</v>
+        <v>-5.1</v>
       </c>
       <c r="J4">
-        <v>-11.13</v>
+        <v>-11.6</v>
       </c>
       <c r="K4">
-        <v>-12.06</v>
+        <v>-12.56</v>
       </c>
       <c r="L4">
-        <v>-33.71</v>
+        <v>-33.95</v>
       </c>
       <c r="M4">
-        <v>-5.88</v>
+        <v>-5.84</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>211.49</v>
+        <v>209.29</v>
       </c>
       <c r="Q4">
-        <v>216.02</v>
+        <v>214.92</v>
       </c>
       <c r="R4">
-        <v>229.26</v>
+        <v>228.25</v>
       </c>
       <c r="S4">
-        <v>243.28</v>
+        <v>242.8</v>
       </c>
       <c r="T4">
-        <v>-15.72</v>
+        <v>-15.47</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1228,43 +1184,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>28.79</v>
+        <v>29.21</v>
       </c>
       <c r="Z4">
-        <v>-5.19</v>
+        <v>-5.49</v>
       </c>
       <c r="AA4">
-        <v>-5.04</v>
+        <v>-5.13</v>
       </c>
       <c r="AB4">
-        <v>-0.16</v>
+        <v>-0.37</v>
       </c>
       <c r="AC4">
-        <v>47.09</v>
+        <v>28.8</v>
       </c>
       <c r="AD4">
-        <v>59.69</v>
+        <v>45.69</v>
       </c>
       <c r="AE4">
-        <v>5.28</v>
+        <v>5.15</v>
       </c>
       <c r="AF4">
-        <v>42.72</v>
+        <v>-17.95</v>
       </c>
       <c r="AG4">
-        <v>226.57</v>
+        <v>225.14</v>
       </c>
       <c r="AH4">
-        <v>205.46</v>
+        <v>204.69</v>
       </c>
       <c r="AI4">
-        <v>222.84</v>
+        <v>219.84</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>40.31</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1231,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>705.95</v>
+        <v>698.8</v>
       </c>
       <c r="D5">
-        <v>-7.06</v>
+        <v>-1.01</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1287,46 +1243,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-12.2</v>
+        <v>-13.09</v>
       </c>
       <c r="H5">
-        <v>43.87</v>
+        <v>42.41</v>
       </c>
       <c r="I5">
-        <v>3.71</v>
+        <v>-2.03</v>
       </c>
       <c r="J5">
-        <v>3.42</v>
+        <v>0.76</v>
       </c>
       <c r="K5">
-        <v>-2.55</v>
+        <v>-4.14</v>
       </c>
       <c r="L5">
-        <v>-10.69</v>
+        <v>-11.01</v>
       </c>
       <c r="M5">
-        <v>-2.54</v>
+        <v>-3.6</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P5">
-        <v>735.55</v>
+        <v>732.66</v>
       </c>
       <c r="Q5">
-        <v>679.79</v>
+        <v>681.11</v>
       </c>
       <c r="R5">
-        <v>679.1900000000001</v>
+        <v>679.42</v>
       </c>
       <c r="S5">
-        <v>617.76</v>
+        <v>617.59</v>
       </c>
       <c r="T5">
-        <v>14.28</v>
+        <v>13.15</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1341,34 +1297,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.1</v>
+        <v>52.3</v>
       </c>
       <c r="Z5">
-        <v>15.66</v>
+        <v>13.99</v>
       </c>
       <c r="AA5">
-        <v>6.55</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AB5">
-        <v>9.109999999999999</v>
+        <v>5.95</v>
       </c>
       <c r="AC5">
-        <v>80.09</v>
+        <v>61.32</v>
       </c>
       <c r="AD5">
-        <v>92.47</v>
+        <v>79.58</v>
       </c>
       <c r="AE5">
-        <v>35.25</v>
+        <v>34.32</v>
       </c>
       <c r="AF5">
-        <v>-34.69</v>
+        <v>-72.37</v>
       </c>
       <c r="AG5">
-        <v>754.12</v>
+        <v>755.8200000000001</v>
       </c>
       <c r="AH5">
-        <v>605.45</v>
+        <v>606.39</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1377,7 +1333,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>36.46</v>
+        <v>32.66</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,58 +1344,58 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>23.5</v>
+        <v>23.19</v>
       </c>
       <c r="D6">
-        <v>-3.17</v>
+        <v>-1.32</v>
       </c>
       <c r="E6">
         <v>48.99</v>
       </c>
       <c r="F6">
-        <v>23.5</v>
+        <v>23.19</v>
       </c>
       <c r="G6">
-        <v>-52.03</v>
+        <v>-52.66</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-11.92</v>
+        <v>-12.36</v>
       </c>
       <c r="J6">
-        <v>-12.67</v>
+        <v>-14.55</v>
       </c>
       <c r="K6">
-        <v>-16.46</v>
+        <v>-18.97</v>
       </c>
       <c r="L6">
-        <v>-53.21</v>
+        <v>-52.31</v>
       </c>
       <c r="M6">
-        <v>-21.04</v>
+        <v>-22.23</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>24.88</v>
+        <v>24.22</v>
       </c>
       <c r="Q6">
-        <v>25.61</v>
+        <v>25.42</v>
       </c>
       <c r="R6">
-        <v>27.08</v>
+        <v>26.97</v>
       </c>
       <c r="S6">
-        <v>31.93</v>
+        <v>31.83</v>
       </c>
       <c r="T6">
-        <v>-26.41</v>
+        <v>-27.15</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1454,43 +1410,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>31.89</v>
+        <v>30.48</v>
       </c>
       <c r="Z6">
-        <v>-0.68</v>
+        <v>-0.79</v>
       </c>
       <c r="AA6">
-        <v>-0.57</v>
+        <v>-0.61</v>
       </c>
       <c r="AB6">
-        <v>-0.11</v>
+        <v>-0.17</v>
       </c>
       <c r="AC6">
-        <v>19.66</v>
+        <v>9.48</v>
       </c>
       <c r="AD6">
-        <v>39.42</v>
+        <v>22.36</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>-2.79</v>
+        <v>28.26</v>
       </c>
       <c r="AG6">
-        <v>27.49</v>
+        <v>27.48</v>
       </c>
       <c r="AH6">
-        <v>23.72</v>
+        <v>23.36</v>
       </c>
       <c r="AI6">
-        <v>26.98</v>
+        <v>26.4</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>29.84</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1457,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1190</v>
+        <v>1201.8</v>
       </c>
       <c r="D7">
-        <v>0.46</v>
+        <v>0.99</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1513,46 +1469,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-24.92</v>
+        <v>-24.18</v>
       </c>
       <c r="H7">
-        <v>2.68</v>
+        <v>3.7</v>
       </c>
       <c r="I7">
-        <v>-2.06</v>
+        <v>-0.78</v>
       </c>
       <c r="J7">
-        <v>-4.06</v>
+        <v>-3.7</v>
       </c>
       <c r="K7">
-        <v>-6.46</v>
+        <v>-5.96</v>
       </c>
       <c r="L7">
-        <v>-15.62</v>
+        <v>-17.69</v>
       </c>
       <c r="M7">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P7">
-        <v>1199.34</v>
+        <v>1197.46</v>
       </c>
       <c r="Q7">
-        <v>1192.59</v>
+        <v>1191.72</v>
       </c>
       <c r="R7">
-        <v>1250</v>
+        <v>1247.45</v>
       </c>
       <c r="S7">
-        <v>1333.43</v>
+        <v>1331.59</v>
       </c>
       <c r="T7">
-        <v>-10.76</v>
+        <v>-9.75</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1567,34 +1523,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>44.35</v>
+        <v>47.69</v>
       </c>
       <c r="Z7">
-        <v>-14.74</v>
+        <v>-13.1</v>
       </c>
       <c r="AA7">
-        <v>-19.31</v>
+        <v>-18.07</v>
       </c>
       <c r="AB7">
-        <v>4.57</v>
+        <v>4.97</v>
       </c>
       <c r="AC7">
-        <v>76.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="AD7">
-        <v>83.81</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="AE7">
-        <v>26</v>
+        <v>26.28</v>
       </c>
       <c r="AF7">
-        <v>1.33</v>
+        <v>-49.76</v>
       </c>
       <c r="AG7">
-        <v>1232.7</v>
+        <v>1230.12</v>
       </c>
       <c r="AH7">
-        <v>1152.48</v>
+        <v>1153.32</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1603,7 +1559,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>30.21</v>
+        <v>27.56</v>
       </c>
     </row>
   </sheetData>
@@ -1764,47 +1720,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1812,836 +1733,836 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-8.34</v>
       </c>
-      <c r="E7" s="7">
+      <c r="D7" s="5">
+        <v>-8.27</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-10.99</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-11.13</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-11.6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3.42</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-12.67</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-14.55</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.06</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.7</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-7.64</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-5.85</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-10.33</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-9.65</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.38</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3.71</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-11.92</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-12.36</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.06</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-0.78</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-27.35</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-25.44</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-33.21</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-33.01</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-33.71</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-33.95</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-10.69</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-11.01</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-53.21</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-52.31</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-15.62</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-17.69</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-10.75</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-9.35</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-15.13</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-16.45</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-12.06</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-12.56</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-2.55</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-4.14</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-16.46</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-18.97</v>
+      </c>
+      <c r="E29" s="7">
         <v>-2.51</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.46</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-28.47</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-26.84</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-34.75</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-35.04</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-8.34</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-11.13</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-34.89</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-34.83</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-12.2</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-13.09</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-52.03</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-52.66</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-24.92</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-24.18</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>24.07</v>
+      </c>
+      <c r="D37" s="5">
+        <v>24.62</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.029999999999999</v>
+      </c>
+      <c r="D38" s="5">
+        <v>8.99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>205.03</v>
+      </c>
+      <c r="D39" s="5">
+        <v>205.23</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>705.95</v>
+      </c>
+      <c r="D40" s="5">
+        <v>698.8</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-7.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>23.5</v>
+      </c>
+      <c r="D41" s="5">
+        <v>23.19</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1190</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1201.8</v>
+      </c>
+      <c r="E42" s="6">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="5">
+        <v>34.31</v>
+      </c>
+      <c r="D43" s="5">
+        <v>39.7</v>
+      </c>
+      <c r="E43" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="5">
+        <v>38.54</v>
+      </c>
+      <c r="D44" s="5">
+        <v>38.11</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>28.79</v>
+      </c>
+      <c r="D45" s="5">
+        <v>29.21</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>54.1</v>
+      </c>
+      <c r="D46" s="5">
+        <v>52.3</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>31.89</v>
+      </c>
+      <c r="D47" s="5">
+        <v>30.48</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>44.35</v>
+      </c>
+      <c r="D48" s="5">
+        <v>47.69</v>
+      </c>
+      <c r="E48" s="6">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="5">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-5.15</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-15.11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-52.68</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-71.55</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-18.87</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>42.72</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-17.95</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-60.67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-34.69</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-72.37</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-37.68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
         <v>-2.79</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>11.26</v>
-      </c>
-      <c r="D10" s="6">
-        <v>3.42</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-7.84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-9.41</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-12.67</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D53" s="5">
+        <v>28.26</v>
+      </c>
+      <c r="E53" s="6">
+        <v>31.05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.06</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.65</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-7.64</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-10.33</v>
-      </c>
-      <c r="E14" s="8">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D16" s="6">
-        <v>3.71</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-7.54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-8.35</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-11.92</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-24.81</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-27.35</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-32.33</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-33.21</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-32.46</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-33.71</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-10.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-5.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-53.02</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-53.21</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.9</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-15.62</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-10.75</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-14.51</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-15.13</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-10.22</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-12.06</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>5.06</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-2.55</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-7.61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-15.61</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.46</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-26.06</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-28.47</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-33.16</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-34.75</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-33.06</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-34.89</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-5.53</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-12.2</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-51.67</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-52.03</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-25.27</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-24.92</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>24.88</v>
-      </c>
-      <c r="D37" s="6">
-        <v>24.07</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="6">
-        <v>9.25</v>
-      </c>
-      <c r="D38" s="6">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="6">
-        <v>210.8</v>
-      </c>
-      <c r="D39" s="6">
-        <v>205.03</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-5.77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="6">
-        <v>759.55</v>
-      </c>
-      <c r="D40" s="6">
-        <v>705.95</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-53.6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>24.27</v>
-      </c>
-      <c r="D41" s="6">
-        <v>23.5</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1184.5</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1190</v>
-      </c>
-      <c r="E42" s="8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="6">
-        <v>39.09</v>
-      </c>
-      <c r="D43" s="6">
-        <v>34.31</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="6">
-        <v>40.88</v>
-      </c>
-      <c r="D44" s="6">
-        <v>38.54</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="6">
-        <v>34.21</v>
-      </c>
-      <c r="D45" s="6">
-        <v>28.79</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-5.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6">
-        <v>71.20999999999999</v>
-      </c>
-      <c r="D46" s="6">
-        <v>54.1</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-17.11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6">
-        <v>35.7</v>
-      </c>
-      <c r="D47" s="6">
-        <v>31.89</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6">
-        <v>42.78</v>
-      </c>
-      <c r="D48" s="6">
-        <v>44.35</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="6">
-        <v>-44.93</v>
-      </c>
-      <c r="D49" s="6">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E49" s="8">
-        <v>54.89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-61.36</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-52.68</v>
-      </c>
-      <c r="E50" s="8">
-        <v>8.68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-16.18</v>
-      </c>
-      <c r="D51" s="6">
-        <v>42.72</v>
-      </c>
-      <c r="E51" s="8">
-        <v>58.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="6">
-        <v>47.54</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-34.69</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-82.23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-12.66</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="E53" s="8">
-        <v>9.869999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>1.33</v>
       </c>
+      <c r="D54" s="5">
+        <v>-49.76</v>
+      </c>
       <c r="E54" s="7">
-        <v>-1.87</v>
+        <v>-51.09</v>
       </c>
     </row>
   </sheetData>
@@ -2667,60 +2588,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>39.88</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>16.7</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-10.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-11.2</v>
+      </c>
+      <c r="H2" s="10">
         <v>58</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>16.7</v>
       </c>
     </row>
@@ -2822,43 +2743,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14">
-        <v>0.002</v>
-      </c>
-      <c r="B2" s="14">
-        <v>-0.0254</v>
-      </c>
-      <c r="C2" s="14">
-        <v>-0.0588</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.1228</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.1725</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.2104</v>
+      <c r="A2" s="13">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.036</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0584</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1234</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.177</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.2223</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.2 → 33.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>33.5</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.3 → 49.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>49.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,14 +413,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -753,13 +797,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
-    <col min="25" max="26" width="7.7109375" customWidth="1"/>
+    <col min="25" max="25" width="7.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -892,10 +938,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.62</v>
+        <v>24.47</v>
       </c>
       <c r="D2">
-        <v>2.29</v>
+        <v>-0.61</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -904,46 +950,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-26.84</v>
+        <v>-27.28</v>
       </c>
       <c r="H2">
-        <v>7.14</v>
+        <v>6.48</v>
       </c>
       <c r="I2">
-        <v>-5.85</v>
+        <v>-5.23</v>
       </c>
       <c r="J2">
-        <v>-8.27</v>
+        <v>-7.73</v>
       </c>
       <c r="K2">
-        <v>-9.35</v>
+        <v>-10.6</v>
       </c>
       <c r="L2">
-        <v>-25.44</v>
+        <v>-26.93</v>
       </c>
       <c r="M2">
-        <v>-12.34</v>
+        <v>-12.42</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="P2">
-        <v>24.88</v>
+        <v>24.61</v>
       </c>
       <c r="Q2">
-        <v>25.69</v>
+        <v>25.6</v>
       </c>
       <c r="R2">
-        <v>26.72</v>
+        <v>26.65</v>
       </c>
       <c r="S2">
-        <v>27.69</v>
+        <v>27.66</v>
       </c>
       <c r="T2">
-        <v>-11.1</v>
+        <v>-11.53</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -958,34 +1004,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>39.7</v>
+        <v>38.77</v>
       </c>
       <c r="Z2">
-        <v>-0.51</v>
+        <v>-0.55</v>
       </c>
       <c r="AA2">
-        <v>-0.39</v>
+        <v>-0.42</v>
       </c>
       <c r="AB2">
         <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>25.67</v>
+        <v>22.33</v>
       </c>
       <c r="AD2">
-        <v>33.14</v>
+        <v>25.58</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>-5.15</v>
+        <v>-59.72</v>
       </c>
       <c r="AG2">
-        <v>27.14</v>
+        <v>27.1</v>
       </c>
       <c r="AH2">
-        <v>24.25</v>
+        <v>24.09</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -994,7 +1040,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>47.56</v>
+        <v>47.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1051,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>8.99</v>
+        <v>9.17</v>
       </c>
       <c r="D3">
-        <v>-0.44</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1017,46 +1063,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-35.04</v>
+        <v>-33.74</v>
       </c>
       <c r="H3">
-        <v>1.35</v>
+        <v>3.38</v>
       </c>
       <c r="I3">
-        <v>-9.65</v>
+        <v>-5.95</v>
       </c>
       <c r="J3">
-        <v>-10.99</v>
+        <v>-7.93</v>
       </c>
       <c r="K3">
-        <v>-16.45</v>
+        <v>-15.72</v>
       </c>
       <c r="L3">
-        <v>-33.01</v>
+        <v>-32.57</v>
       </c>
       <c r="M3">
-        <v>-17.7</v>
+        <v>-17.12</v>
       </c>
       <c r="N3">
         <v>33</v>
       </c>
       <c r="O3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P3">
-        <v>9.279999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="Q3">
-        <v>9.67</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="R3">
-        <v>10.08</v>
+        <v>10.05</v>
       </c>
       <c r="S3">
-        <v>10.68</v>
+        <v>10.66</v>
       </c>
       <c r="T3">
-        <v>-15.83</v>
+        <v>-14.01</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1071,34 +1117,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>38.11</v>
+        <v>41.27</v>
       </c>
       <c r="Z3">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
       <c r="AA3">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="AB3">
         <v>-0.08</v>
       </c>
       <c r="AC3">
-        <v>25.31</v>
+        <v>21.29</v>
       </c>
       <c r="AD3">
-        <v>33.58</v>
+        <v>26.65</v>
       </c>
       <c r="AE3">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AF3">
-        <v>-71.55</v>
+        <v>-58.78</v>
       </c>
       <c r="AG3">
-        <v>10.76</v>
+        <v>10.74</v>
       </c>
       <c r="AH3">
-        <v>8.58</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="AI3">
         <v>10.36</v>
@@ -1107,7 +1153,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>22.13</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1164,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>205.23</v>
+        <v>207.24</v>
       </c>
       <c r="D4">
-        <v>0.1</v>
+        <v>0.98</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1130,46 +1176,46 @@
         <v>205.03</v>
       </c>
       <c r="G4">
-        <v>-34.83</v>
+        <v>-34.19</v>
       </c>
       <c r="H4">
-        <v>0.1</v>
+        <v>1.08</v>
       </c>
       <c r="I4">
-        <v>-5.1</v>
+        <v>-3.16</v>
       </c>
       <c r="J4">
-        <v>-11.6</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K4">
-        <v>-12.56</v>
+        <v>-12.25</v>
       </c>
       <c r="L4">
-        <v>-33.95</v>
+        <v>-33.53</v>
       </c>
       <c r="M4">
-        <v>-5.84</v>
+        <v>-5.54</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>209.29</v>
+        <v>207.94</v>
       </c>
       <c r="Q4">
-        <v>214.92</v>
+        <v>213.93</v>
       </c>
       <c r="R4">
-        <v>228.25</v>
+        <v>227.28</v>
       </c>
       <c r="S4">
-        <v>242.8</v>
+        <v>242.35</v>
       </c>
       <c r="T4">
-        <v>-15.47</v>
+        <v>-14.49</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,34 +1230,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.21</v>
+        <v>33.45</v>
       </c>
       <c r="Z4">
-        <v>-5.49</v>
+        <v>-5.51</v>
       </c>
       <c r="AA4">
-        <v>-5.13</v>
+        <v>-5.2</v>
       </c>
       <c r="AB4">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="AC4">
-        <v>28.8</v>
+        <v>20.96</v>
       </c>
       <c r="AD4">
-        <v>45.69</v>
+        <v>32.28</v>
       </c>
       <c r="AE4">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AF4">
-        <v>-17.95</v>
+        <v>4.83</v>
       </c>
       <c r="AG4">
-        <v>225.14</v>
+        <v>222.99</v>
       </c>
       <c r="AH4">
-        <v>204.69</v>
+        <v>204.87</v>
       </c>
       <c r="AI4">
         <v>219.84</v>
@@ -1220,7 +1266,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>43.51</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1277,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>698.8</v>
+        <v>687.1</v>
       </c>
       <c r="D5">
-        <v>-1.01</v>
+        <v>-1.67</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1243,46 +1289,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-13.09</v>
+        <v>-14.55</v>
       </c>
       <c r="H5">
-        <v>42.41</v>
+        <v>40.02</v>
       </c>
       <c r="I5">
-        <v>-2.03</v>
+        <v>-6.1</v>
       </c>
       <c r="J5">
-        <v>0.76</v>
+        <v>2.19</v>
       </c>
       <c r="K5">
-        <v>-4.14</v>
+        <v>-4.4</v>
       </c>
       <c r="L5">
-        <v>-11.01</v>
+        <v>-13.5</v>
       </c>
       <c r="M5">
-        <v>-3.6</v>
+        <v>-3.51</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P5">
-        <v>732.66</v>
+        <v>723.73</v>
       </c>
       <c r="Q5">
-        <v>681.11</v>
+        <v>681.85</v>
       </c>
       <c r="R5">
-        <v>679.42</v>
+        <v>679.6</v>
       </c>
       <c r="S5">
-        <v>617.59</v>
+        <v>617.39</v>
       </c>
       <c r="T5">
-        <v>13.15</v>
+        <v>11.29</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1297,34 +1343,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>52.3</v>
+        <v>49.39</v>
       </c>
       <c r="Z5">
-        <v>13.99</v>
+        <v>11.59</v>
       </c>
       <c r="AA5">
-        <v>8.039999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="AB5">
-        <v>5.95</v>
+        <v>2.84</v>
       </c>
       <c r="AC5">
-        <v>61.32</v>
+        <v>42.74</v>
       </c>
       <c r="AD5">
-        <v>79.58</v>
+        <v>61.38</v>
       </c>
       <c r="AE5">
-        <v>34.32</v>
+        <v>33.45</v>
       </c>
       <c r="AF5">
-        <v>-72.37</v>
+        <v>-81.94</v>
       </c>
       <c r="AG5">
-        <v>755.8200000000001</v>
+        <v>756.49</v>
       </c>
       <c r="AH5">
-        <v>606.39</v>
+        <v>607.22</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1333,7 +1379,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>32.66</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1390,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>23.19</v>
+        <v>23.85</v>
       </c>
       <c r="D6">
-        <v>-1.32</v>
+        <v>2.85</v>
       </c>
       <c r="E6">
         <v>48.99</v>
@@ -1356,46 +1402,46 @@
         <v>23.19</v>
       </c>
       <c r="G6">
-        <v>-52.66</v>
+        <v>-51.32</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="I6">
-        <v>-12.36</v>
+        <v>-6.8</v>
       </c>
       <c r="J6">
-        <v>-14.55</v>
+        <v>-11.57</v>
       </c>
       <c r="K6">
-        <v>-18.97</v>
+        <v>-17.33</v>
       </c>
       <c r="L6">
-        <v>-52.31</v>
+        <v>-51.16</v>
       </c>
       <c r="M6">
-        <v>-22.23</v>
+        <v>-21.28</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>24.22</v>
+        <v>23.87</v>
       </c>
       <c r="Q6">
-        <v>25.42</v>
+        <v>25.27</v>
       </c>
       <c r="R6">
-        <v>26.97</v>
+        <v>26.87</v>
       </c>
       <c r="S6">
-        <v>31.83</v>
+        <v>31.73</v>
       </c>
       <c r="T6">
-        <v>-27.15</v>
+        <v>-24.84</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,34 +1456,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>30.48</v>
+        <v>36.88</v>
       </c>
       <c r="Z6">
-        <v>-0.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA6">
-        <v>-0.61</v>
+        <v>-0.65</v>
       </c>
       <c r="AB6">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="AC6">
-        <v>9.48</v>
+        <v>11.67</v>
       </c>
       <c r="AD6">
-        <v>22.36</v>
+        <v>13.6</v>
       </c>
       <c r="AE6">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>28.26</v>
+        <v>50.35</v>
       </c>
       <c r="AG6">
-        <v>27.48</v>
+        <v>27.35</v>
       </c>
       <c r="AH6">
-        <v>23.36</v>
+        <v>23.2</v>
       </c>
       <c r="AI6">
         <v>26.4</v>
@@ -1446,7 +1492,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>32.02</v>
+        <v>29.59</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1457,10 +1503,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1201.8</v>
+        <v>1196.2</v>
       </c>
       <c r="D7">
-        <v>0.99</v>
+        <v>-0.47</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1469,46 +1515,46 @@
         <v>1158.9</v>
       </c>
       <c r="G7">
-        <v>-24.18</v>
+        <v>-24.53</v>
       </c>
       <c r="H7">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="I7">
-        <v>-0.78</v>
+        <v>-0.48</v>
       </c>
       <c r="J7">
-        <v>-3.7</v>
+        <v>-1.89</v>
       </c>
       <c r="K7">
-        <v>-5.96</v>
+        <v>-6.55</v>
       </c>
       <c r="L7">
-        <v>-17.69</v>
+        <v>-17.98</v>
       </c>
       <c r="M7">
-        <v>-0.06</v>
+        <v>0.1</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P7">
-        <v>1197.46</v>
+        <v>1196.3</v>
       </c>
       <c r="Q7">
-        <v>1191.72</v>
+        <v>1190.23</v>
       </c>
       <c r="R7">
-        <v>1247.45</v>
+        <v>1245.04</v>
       </c>
       <c r="S7">
-        <v>1331.59</v>
+        <v>1330.06</v>
       </c>
       <c r="T7">
-        <v>-9.75</v>
+        <v>-10.06</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1523,34 +1569,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>47.69</v>
+        <v>46.27</v>
       </c>
       <c r="Z7">
-        <v>-13.1</v>
+        <v>-12.12</v>
       </c>
       <c r="AA7">
-        <v>-18.07</v>
+        <v>-16.88</v>
       </c>
       <c r="AB7">
-        <v>4.97</v>
+        <v>4.76</v>
       </c>
       <c r="AC7">
-        <v>74.40000000000001</v>
+        <v>78.08</v>
       </c>
       <c r="AD7">
-        <v>77.93000000000001</v>
+        <v>76.36</v>
       </c>
       <c r="AE7">
-        <v>26.28</v>
+        <v>25.73</v>
       </c>
       <c r="AF7">
-        <v>-49.76</v>
+        <v>-12.1</v>
       </c>
       <c r="AG7">
-        <v>1230.12</v>
+        <v>1225.19</v>
       </c>
       <c r="AH7">
-        <v>1153.32</v>
+        <v>1155.27</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1559,7 +1605,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>27.56</v>
+        <v>25.27</v>
       </c>
     </row>
   </sheetData>
@@ -1700,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1720,855 +1766,910 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-8.34</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>-8.27</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>-7.73</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>-10.99</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>-7.93</v>
+      </c>
+      <c r="E9" s="8">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-11.13</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-11.6</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>3.42</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="7">
         <v>0.76</v>
       </c>
-      <c r="E10" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-12.67</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="7">
         <v>-14.55</v>
       </c>
-      <c r="E11" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-11.57</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-4.06</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="7">
         <v>-3.7</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-1.89</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-7.64</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="7">
         <v>-5.85</v>
       </c>
-      <c r="E13" s="6">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="7">
+        <v>-5.23</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-10.33</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="7">
         <v>-9.65</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="7">
+        <v>-5.95</v>
+      </c>
+      <c r="E15" s="8">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-6.38</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="7">
         <v>-5.1</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>3.71</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="7">
         <v>-2.03</v>
       </c>
-      <c r="E16" s="7">
-        <v>-5.74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-6.1</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-11.92</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="7">
         <v>-12.36</v>
       </c>
-      <c r="E17" s="7">
+      <c r="D18" s="7">
+        <v>-6.8</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.78</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.48</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-25.44</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-26.93</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-33.01</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-32.57</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-33.95</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-33.53</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-11.01</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-13.5</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-2.49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-52.31</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-51.16</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-17.69</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-17.98</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-9.35</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-10.6</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-16.45</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-15.72</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-12.56</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-12.25</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-4.14</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-4.4</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-18.97</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-17.33</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-5.96</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-6.55</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-26.84</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-27.28</v>
+      </c>
+      <c r="E32" s="9">
         <v>-0.44</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-35.04</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-33.74</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-34.83</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-34.19</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-13.09</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-14.55</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-52.66</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-51.32</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.06</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-0.78</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-24.18</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-24.53</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-27.35</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-25.44</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="7">
+        <v>24.62</v>
+      </c>
+      <c r="D38" s="7">
+        <v>24.47</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-33.21</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-33.01</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="7">
+        <v>8.99</v>
+      </c>
+      <c r="D39" s="7">
+        <v>9.17</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-33.71</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-33.95</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="7">
+        <v>205.23</v>
+      </c>
+      <c r="D40" s="7">
+        <v>207.24</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-10.69</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-11.01</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B41" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7">
+        <v>698.8</v>
+      </c>
+      <c r="D41" s="7">
+        <v>687.1</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-11.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-53.21</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-52.31</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="7">
+        <v>23.19</v>
+      </c>
+      <c r="D42" s="7">
+        <v>23.85</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-15.62</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-17.69</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1201.8</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1196.2</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-10.75</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="7">
+        <v>39.7</v>
+      </c>
+      <c r="D44" s="7">
+        <v>38.77</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-15.13</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-16.45</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="7">
+        <v>38.11</v>
+      </c>
+      <c r="D45" s="7">
+        <v>41.27</v>
+      </c>
+      <c r="E45" s="8">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-12.06</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-12.56</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="7">
+        <v>29.21</v>
+      </c>
+      <c r="D46" s="7">
+        <v>33.45</v>
+      </c>
+      <c r="E46" s="8">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-2.55</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-4.14</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="7">
+        <v>52.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>49.39</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-16.46</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-18.97</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="7">
+        <v>30.48</v>
+      </c>
+      <c r="D48" s="7">
+        <v>36.88</v>
+      </c>
+      <c r="E48" s="8">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-6.46</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-5.96</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="7">
+        <v>47.69</v>
+      </c>
+      <c r="D49" s="7">
+        <v>46.27</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-28.47</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-26.84</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-5.15</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-59.72</v>
+      </c>
+      <c r="E50" s="9">
+        <v>-54.57</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-34.75</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-35.04</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-71.55</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-58.78</v>
+      </c>
+      <c r="E51" s="8">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-34.89</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-34.83</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-17.95</v>
+      </c>
+      <c r="D52" s="7">
+        <v>4.83</v>
+      </c>
+      <c r="E52" s="8">
+        <v>22.78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-12.2</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-13.09</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7">
+        <v>-72.37</v>
+      </c>
+      <c r="D53" s="7">
+        <v>-81.94</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-9.57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-52.03</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-52.66</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7">
+        <v>28.26</v>
+      </c>
+      <c r="D54" s="7">
+        <v>50.35</v>
+      </c>
+      <c r="E54" s="8">
+        <v>22.09</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-24.92</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-24.18</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="5">
-        <v>24.07</v>
-      </c>
-      <c r="D37" s="5">
-        <v>24.62</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="5">
-        <v>9.029999999999999</v>
-      </c>
-      <c r="D38" s="5">
-        <v>8.99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="5">
-        <v>205.03</v>
-      </c>
-      <c r="D39" s="5">
-        <v>205.23</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="5">
-        <v>705.95</v>
-      </c>
-      <c r="D40" s="5">
-        <v>698.8</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-7.15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>23.5</v>
-      </c>
-      <c r="D41" s="5">
-        <v>23.19</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1190</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1201.8</v>
-      </c>
-      <c r="E42" s="6">
-        <v>11.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>34.31</v>
-      </c>
-      <c r="D43" s="5">
-        <v>39.7</v>
-      </c>
-      <c r="E43" s="6">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="5">
-        <v>38.54</v>
-      </c>
-      <c r="D44" s="5">
-        <v>38.11</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="5">
-        <v>28.79</v>
-      </c>
-      <c r="D45" s="5">
-        <v>29.21</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="5">
-        <v>54.1</v>
-      </c>
-      <c r="D46" s="5">
-        <v>52.3</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="5">
-        <v>31.89</v>
-      </c>
-      <c r="D47" s="5">
-        <v>30.48</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="5">
-        <v>44.35</v>
-      </c>
-      <c r="D48" s="5">
-        <v>47.69</v>
-      </c>
-      <c r="E48" s="6">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="B55" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C49" s="5">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-5.15</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-15.11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-52.68</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-71.55</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-18.87</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="5">
-        <v>42.72</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-17.95</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-60.67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="5">
-        <v>-34.69</v>
-      </c>
-      <c r="D52" s="5">
-        <v>-72.37</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-37.68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="D53" s="5">
-        <v>28.26</v>
-      </c>
-      <c r="E53" s="6">
-        <v>31.05</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1.33</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C55" s="7">
         <v>-49.76</v>
       </c>
-      <c r="E54" s="7">
-        <v>-51.09</v>
+      <c r="D55" s="7">
+        <v>-12.1</v>
+      </c>
+      <c r="E55" s="8">
+        <v>37.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2588,60 +2689,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="12">
+        <v>39.88</v>
+      </c>
+      <c r="C2" s="13">
+        <v>6</v>
+      </c>
+      <c r="D2" s="12">
+        <v>41</v>
+      </c>
+      <c r="E2" s="12">
+        <v>16.7</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-11.1</v>
+      </c>
+      <c r="H2" s="12">
         <v>58</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="10">
-        <v>39.88</v>
-      </c>
-      <c r="C2" s="11">
-        <v>6</v>
-      </c>
-      <c r="D2" s="10">
-        <v>39.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>16.7</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-8.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-11.2</v>
-      </c>
-      <c r="H2" s="10">
-        <v>58</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>16.7</v>
       </c>
     </row>
@@ -2743,43 +2844,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="13">
-        <v>-0.0005999999999999999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>-0.036</v>
-      </c>
-      <c r="C2" s="13">
-        <v>-0.0584</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.1234</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.177</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.2223</v>
+      <c r="A2" s="15">
+        <v>0.001</v>
+      </c>
+      <c r="B2" s="15">
+        <v>-0.0351</v>
+      </c>
+      <c r="C2" s="15">
+        <v>-0.0554</v>
+      </c>
+      <c r="D2" s="15">
+        <v>-0.1242</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.1712</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.2128</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,49 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 33.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>33.5</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.3 → 49.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.3</t>
-  </si>
-  <si>
-    <t>49.4</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -413,16 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -798,7 +754,9 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -938,10 +896,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.47</v>
+        <v>24.44</v>
       </c>
       <c r="D2">
-        <v>-0.61</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -950,25 +908,25 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.28</v>
+        <v>-27.37</v>
       </c>
       <c r="H2">
-        <v>6.48</v>
+        <v>6.35</v>
       </c>
       <c r="I2">
-        <v>-5.23</v>
+        <v>-2.28</v>
       </c>
       <c r="J2">
-        <v>-7.73</v>
+        <v>-7.35</v>
       </c>
       <c r="K2">
-        <v>-10.6</v>
+        <v>-10.25</v>
       </c>
       <c r="L2">
-        <v>-26.93</v>
+        <v>-26.96</v>
       </c>
       <c r="M2">
-        <v>-12.42</v>
+        <v>-11.98</v>
       </c>
       <c r="N2">
         <v>66</v>
@@ -977,19 +935,19 @@
         <v>36</v>
       </c>
       <c r="P2">
-        <v>24.61</v>
+        <v>24.5</v>
       </c>
       <c r="Q2">
-        <v>25.6</v>
+        <v>25.52</v>
       </c>
       <c r="R2">
-        <v>26.65</v>
+        <v>26.59</v>
       </c>
       <c r="S2">
-        <v>27.66</v>
+        <v>27.62</v>
       </c>
       <c r="T2">
-        <v>-11.53</v>
+        <v>-11.51</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -1004,34 +962,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.77</v>
+        <v>38.57</v>
       </c>
       <c r="Z2">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="AA2">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="AB2">
         <v>-0.12</v>
       </c>
       <c r="AC2">
-        <v>22.33</v>
+        <v>27.79</v>
       </c>
       <c r="AD2">
-        <v>25.58</v>
+        <v>25.26</v>
       </c>
       <c r="AE2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>-59.72</v>
+        <v>-15.67</v>
       </c>
       <c r="AG2">
         <v>27.1</v>
       </c>
       <c r="AH2">
-        <v>24.09</v>
+        <v>23.94</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -1040,7 +998,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>47.97</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1051,10 +1009,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.17</v>
+        <v>9.25</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0.87</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1063,46 +1021,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.74</v>
+        <v>-33.16</v>
       </c>
       <c r="H3">
-        <v>3.38</v>
+        <v>4.28</v>
       </c>
       <c r="I3">
-        <v>-5.95</v>
+        <v>-1.18</v>
       </c>
       <c r="J3">
-        <v>-7.93</v>
+        <v>-6.85</v>
       </c>
       <c r="K3">
-        <v>-15.72</v>
+        <v>-14.43</v>
       </c>
       <c r="L3">
-        <v>-32.57</v>
+        <v>-32.87</v>
       </c>
       <c r="M3">
-        <v>-17.12</v>
+        <v>-16.76</v>
       </c>
       <c r="N3">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="O3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P3">
-        <v>9.16</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Q3">
         <v>9.630000000000001</v>
       </c>
       <c r="R3">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="S3">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
       <c r="T3">
-        <v>-14.01</v>
+        <v>-13.13</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1117,34 +1075,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>41.27</v>
+        <v>42.67</v>
       </c>
       <c r="Z3">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="AA3">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="AB3">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC3">
-        <v>21.29</v>
+        <v>22.83</v>
       </c>
       <c r="AD3">
-        <v>26.65</v>
+        <v>23.14</v>
       </c>
       <c r="AE3">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AF3">
-        <v>-58.78</v>
+        <v>-72.81999999999999</v>
       </c>
       <c r="AG3">
         <v>10.74</v>
       </c>
       <c r="AH3">
-        <v>8.529999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="AI3">
         <v>10.36</v>
@@ -1153,7 +1111,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>20.87</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1164,10 +1122,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>207.24</v>
+        <v>205.15</v>
       </c>
       <c r="D4">
-        <v>0.98</v>
+        <v>-1.01</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1176,46 +1134,46 @@
         <v>205.03</v>
       </c>
       <c r="G4">
-        <v>-34.19</v>
+        <v>-34.85</v>
       </c>
       <c r="H4">
-        <v>1.08</v>
+        <v>0.06</v>
       </c>
       <c r="I4">
-        <v>-3.16</v>
+        <v>-2.95</v>
       </c>
       <c r="J4">
-        <v>-8.789999999999999</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K4">
-        <v>-12.25</v>
+        <v>-13.47</v>
       </c>
       <c r="L4">
-        <v>-33.53</v>
+        <v>-33.62</v>
       </c>
       <c r="M4">
-        <v>-5.54</v>
+        <v>-5.84</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>207.94</v>
+        <v>206.69</v>
       </c>
       <c r="Q4">
-        <v>213.93</v>
+        <v>213.16</v>
       </c>
       <c r="R4">
-        <v>227.28</v>
+        <v>226.4</v>
       </c>
       <c r="S4">
-        <v>242.35</v>
+        <v>241.85</v>
       </c>
       <c r="T4">
-        <v>-14.49</v>
+        <v>-15.18</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1230,34 +1188,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>33.45</v>
+        <v>31.34</v>
       </c>
       <c r="Z4">
-        <v>-5.51</v>
+        <v>-5.62</v>
       </c>
       <c r="AA4">
-        <v>-5.2</v>
+        <v>-5.29</v>
       </c>
       <c r="AB4">
-        <v>-0.3</v>
+        <v>-0.33</v>
       </c>
       <c r="AC4">
-        <v>20.96</v>
+        <v>17.05</v>
       </c>
       <c r="AD4">
-        <v>32.28</v>
+        <v>22.27</v>
       </c>
       <c r="AE4">
-        <v>5.05</v>
+        <v>5.02</v>
       </c>
       <c r="AF4">
-        <v>4.83</v>
+        <v>-10.89</v>
       </c>
       <c r="AG4">
-        <v>222.99</v>
+        <v>222.48</v>
       </c>
       <c r="AH4">
-        <v>204.87</v>
+        <v>203.85</v>
       </c>
       <c r="AI4">
         <v>219.84</v>
@@ -1266,7 +1224,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>43.82</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1277,10 +1235,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>687.1</v>
+        <v>682.95</v>
       </c>
       <c r="D5">
-        <v>-1.67</v>
+        <v>-0.6</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1289,46 +1247,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-14.55</v>
+        <v>-15.06</v>
       </c>
       <c r="H5">
-        <v>40.02</v>
+        <v>39.18</v>
       </c>
       <c r="I5">
-        <v>-6.1</v>
+        <v>-10.99</v>
       </c>
       <c r="J5">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="K5">
-        <v>-4.4</v>
+        <v>-6.23</v>
       </c>
       <c r="L5">
-        <v>-13.5</v>
+        <v>-12.16</v>
       </c>
       <c r="M5">
-        <v>-3.51</v>
+        <v>-3.22</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P5">
-        <v>723.73</v>
+        <v>706.87</v>
       </c>
       <c r="Q5">
-        <v>681.85</v>
+        <v>683.05</v>
       </c>
       <c r="R5">
-        <v>679.6</v>
+        <v>679.64</v>
       </c>
       <c r="S5">
-        <v>617.39</v>
+        <v>617.09</v>
       </c>
       <c r="T5">
-        <v>11.29</v>
+        <v>10.67</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1343,34 +1301,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.39</v>
+        <v>48.37</v>
       </c>
       <c r="Z5">
-        <v>11.59</v>
+        <v>9.25</v>
       </c>
       <c r="AA5">
-        <v>8.75</v>
+        <v>8.85</v>
       </c>
       <c r="AB5">
-        <v>2.84</v>
+        <v>0.4</v>
       </c>
       <c r="AC5">
-        <v>42.74</v>
+        <v>37.86</v>
       </c>
       <c r="AD5">
-        <v>61.38</v>
+        <v>47.3</v>
       </c>
       <c r="AE5">
-        <v>33.45</v>
+        <v>32.78</v>
       </c>
       <c r="AF5">
-        <v>-81.94</v>
+        <v>-88.48999999999999</v>
       </c>
       <c r="AG5">
-        <v>756.49</v>
+        <v>756.91</v>
       </c>
       <c r="AH5">
-        <v>607.22</v>
+        <v>609.2</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1379,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>28.52</v>
+        <v>25.72</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1390,10 +1348,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>23.85</v>
+        <v>24.18</v>
       </c>
       <c r="D6">
-        <v>2.85</v>
+        <v>1.38</v>
       </c>
       <c r="E6">
         <v>48.99</v>
@@ -1402,46 +1360,46 @@
         <v>23.19</v>
       </c>
       <c r="G6">
-        <v>-51.32</v>
+        <v>-50.64</v>
       </c>
       <c r="H6">
-        <v>2.85</v>
+        <v>4.27</v>
       </c>
       <c r="I6">
-        <v>-6.8</v>
+        <v>-1.55</v>
       </c>
       <c r="J6">
-        <v>-11.57</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K6">
-        <v>-17.33</v>
+        <v>-16.22</v>
       </c>
       <c r="L6">
-        <v>-51.16</v>
+        <v>-50.36</v>
       </c>
       <c r="M6">
-        <v>-21.28</v>
+        <v>-20.55</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6">
-        <v>23.87</v>
+        <v>23.8</v>
       </c>
       <c r="Q6">
-        <v>25.27</v>
+        <v>25.18</v>
       </c>
       <c r="R6">
-        <v>26.87</v>
+        <v>26.77</v>
       </c>
       <c r="S6">
-        <v>31.73</v>
+        <v>31.63</v>
       </c>
       <c r="T6">
-        <v>-24.84</v>
+        <v>-23.56</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1456,34 +1414,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.88</v>
+        <v>39.86</v>
       </c>
       <c r="Z6">
-        <v>-0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="AA6">
-        <v>-0.65</v>
+        <v>-0.68</v>
       </c>
       <c r="AB6">
-        <v>-0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="AC6">
-        <v>11.67</v>
+        <v>24.49</v>
       </c>
       <c r="AD6">
-        <v>13.6</v>
+        <v>15.21</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF6">
-        <v>50.35</v>
+        <v>-16.85</v>
       </c>
       <c r="AG6">
-        <v>27.35</v>
+        <v>27.28</v>
       </c>
       <c r="AH6">
-        <v>23.2</v>
+        <v>23.08</v>
       </c>
       <c r="AI6">
         <v>26.4</v>
@@ -1492,7 +1450,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>29.59</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1503,58 +1461,58 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1196.2</v>
+        <v>1158</v>
       </c>
       <c r="D7">
-        <v>-0.47</v>
+        <v>-3.19</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
       </c>
       <c r="F7">
-        <v>1158.9</v>
+        <v>1158</v>
       </c>
       <c r="G7">
-        <v>-24.53</v>
+        <v>-26.94</v>
       </c>
       <c r="H7">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-0.48</v>
+        <v>-4.22</v>
       </c>
       <c r="J7">
-        <v>-1.89</v>
+        <v>-5.55</v>
       </c>
       <c r="K7">
-        <v>-6.55</v>
+        <v>-8.65</v>
       </c>
       <c r="L7">
-        <v>-17.98</v>
+        <v>-19.68</v>
       </c>
       <c r="M7">
-        <v>0.1</v>
+        <v>-0.32</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="P7">
-        <v>1196.3</v>
+        <v>1186.1</v>
       </c>
       <c r="Q7">
-        <v>1190.23</v>
+        <v>1188.25</v>
       </c>
       <c r="R7">
-        <v>1245.04</v>
+        <v>1242</v>
       </c>
       <c r="S7">
-        <v>1330.06</v>
+        <v>1328.37</v>
       </c>
       <c r="T7">
-        <v>-10.06</v>
+        <v>-12.83</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1569,34 +1527,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>46.27</v>
+        <v>37.98</v>
       </c>
       <c r="Z7">
-        <v>-12.12</v>
+        <v>-14.25</v>
       </c>
       <c r="AA7">
-        <v>-16.88</v>
+        <v>-16.35</v>
       </c>
       <c r="AB7">
-        <v>4.76</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>78.08</v>
+        <v>64.91</v>
       </c>
       <c r="AD7">
-        <v>76.36</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="AE7">
-        <v>25.73</v>
+        <v>27.32</v>
       </c>
       <c r="AF7">
-        <v>-12.1</v>
+        <v>47.43</v>
       </c>
       <c r="AG7">
-        <v>1225.19</v>
+        <v>1225.84</v>
       </c>
       <c r="AH7">
-        <v>1155.27</v>
+        <v>1150.66</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1605,7 +1563,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>25.27</v>
+        <v>26.75</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1766,910 +1724,889 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.73</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.35</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-7.93</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-6.85</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-11.57</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-1.89</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-5.55</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-8.27</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-7.73</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.28</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-5.95</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3.16</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-2.95</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.1</v>
+      </c>
+      <c r="D16" s="5">
         <v>-10.99</v>
       </c>
-      <c r="D9" s="7">
-        <v>-7.93</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="E16" s="7">
+        <v>-4.89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-6.8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.55</v>
+      </c>
+      <c r="E17" s="6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.48</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.22</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.93</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.96</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-32.57</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-32.87</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-11.6</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-33.53</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-33.62</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.76</v>
-      </c>
-      <c r="D11" s="7">
-        <v>2.19</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-13.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-12.16</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-51.16</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-50.36</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-17.98</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-19.68</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-10.6</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-10.25</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-15.72</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-14.43</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-12.25</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-13.47</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-4.4</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-6.23</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-17.33</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-16.22</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.55</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-8.65</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-27.28</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-27.37</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-33.74</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-33.16</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-34.19</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-34.85</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
         <v>-14.55</v>
       </c>
-      <c r="D12" s="7">
-        <v>-11.57</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="D34" s="5">
+        <v>-15.06</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-51.32</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-50.64</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-24.53</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-26.94</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="5">
+        <v>24.47</v>
+      </c>
+      <c r="D37" s="5">
+        <v>24.44</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.17</v>
+      </c>
+      <c r="D38" s="5">
+        <v>9.25</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="5">
+        <v>207.24</v>
+      </c>
+      <c r="D39" s="5">
+        <v>205.15</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="5">
+        <v>687.1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>682.95</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>23.85</v>
+      </c>
+      <c r="D41" s="5">
+        <v>24.18</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1196.2</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1158</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-38.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="5">
+        <v>33</v>
+      </c>
+      <c r="D43" s="5">
+        <v>50</v>
+      </c>
+      <c r="E43" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="5">
+        <v>50</v>
+      </c>
+      <c r="D44" s="5">
+        <v>33</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="5">
+        <v>38.77</v>
+      </c>
+      <c r="D45" s="5">
+        <v>38.57</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="5">
+        <v>41.27</v>
+      </c>
+      <c r="D46" s="5">
+        <v>42.67</v>
+      </c>
+      <c r="E46" s="6">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="5">
+        <v>33.45</v>
+      </c>
+      <c r="D47" s="5">
+        <v>31.34</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="5">
+        <v>49.39</v>
+      </c>
+      <c r="D48" s="5">
+        <v>48.37</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>36.88</v>
+      </c>
+      <c r="D49" s="5">
+        <v>39.86</v>
+      </c>
+      <c r="E49" s="6">
         <v>2.98</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-3.7</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-1.89</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>46.27</v>
+      </c>
+      <c r="D50" s="5">
+        <v>37.98</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-8.289999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-5.85</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-5.23</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B51" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-59.72</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-15.67</v>
+      </c>
+      <c r="E51" s="6">
+        <v>44.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-9.65</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-5.95</v>
-      </c>
-      <c r="E15" s="8">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="5">
+        <v>-58.78</v>
+      </c>
+      <c r="D52" s="5">
+        <v>-72.81999999999999</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-14.04</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-5.1</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-3.16</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4.83</v>
+      </c>
+      <c r="D53" s="5">
+        <v>-10.89</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-15.72</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.03</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-6.1</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="5">
+        <v>-81.94</v>
+      </c>
+      <c r="D54" s="5">
+        <v>-88.48999999999999</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-12.36</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-6.8</v>
-      </c>
-      <c r="E18" s="8">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>50.35</v>
+      </c>
+      <c r="D55" s="5">
+        <v>-16.85</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-67.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.78</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.48</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-25.44</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-26.93</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-33.01</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-32.57</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-33.95</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-33.53</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-11.01</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-13.5</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-52.31</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-51.16</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-17.69</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-17.98</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-10.6</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-16.45</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-15.72</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-12.56</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-12.25</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-4.14</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-4.4</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-18.97</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-17.33</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-5.96</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-6.55</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-26.84</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-27.28</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-35.04</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-33.74</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-34.83</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-34.19</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-13.09</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-14.55</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-52.66</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-51.32</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-24.18</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-24.53</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>24.62</v>
-      </c>
-      <c r="D38" s="7">
-        <v>24.47</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="7">
-        <v>8.99</v>
-      </c>
-      <c r="D39" s="7">
-        <v>9.17</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="7">
-        <v>205.23</v>
-      </c>
-      <c r="D40" s="7">
-        <v>207.24</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="7">
-        <v>698.8</v>
-      </c>
-      <c r="D41" s="7">
-        <v>687.1</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-11.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="7">
-        <v>23.19</v>
-      </c>
-      <c r="D42" s="7">
-        <v>23.85</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1201.8</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1196.2</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="7">
-        <v>39.7</v>
-      </c>
-      <c r="D44" s="7">
-        <v>38.77</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="7">
-        <v>38.11</v>
-      </c>
-      <c r="D45" s="7">
-        <v>41.27</v>
-      </c>
-      <c r="E45" s="8">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="7">
-        <v>29.21</v>
-      </c>
-      <c r="D46" s="7">
-        <v>33.45</v>
-      </c>
-      <c r="E46" s="8">
-        <v>4.24</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="7">
-        <v>52.3</v>
-      </c>
-      <c r="D47" s="7">
-        <v>49.39</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="7">
-        <v>30.48</v>
-      </c>
-      <c r="D48" s="7">
-        <v>36.88</v>
-      </c>
-      <c r="E48" s="8">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="7">
-        <v>47.69</v>
-      </c>
-      <c r="D49" s="7">
-        <v>46.27</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="B56" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="7">
-        <v>-5.15</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-59.72</v>
-      </c>
-      <c r="E50" s="9">
-        <v>-54.57</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-71.55</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-58.78</v>
-      </c>
-      <c r="E51" s="8">
-        <v>12.77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-17.95</v>
-      </c>
-      <c r="D52" s="7">
-        <v>4.83</v>
-      </c>
-      <c r="E52" s="8">
-        <v>22.78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7">
-        <v>-72.37</v>
-      </c>
-      <c r="D53" s="7">
-        <v>-81.94</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-9.57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C54" s="7">
-        <v>28.26</v>
-      </c>
-      <c r="D54" s="7">
-        <v>50.35</v>
-      </c>
-      <c r="E54" s="8">
-        <v>22.09</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="7">
-        <v>-49.76</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="C56" s="5">
         <v>-12.1</v>
       </c>
-      <c r="E55" s="8">
-        <v>37.66</v>
+      <c r="D56" s="5">
+        <v>47.43</v>
+      </c>
+      <c r="E56" s="6">
+        <v>59.53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2689,60 +2626,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>76</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>39.88</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>6</v>
       </c>
-      <c r="D2" s="12">
-        <v>41</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>39.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>16.7</v>
       </c>
-      <c r="F2" s="12">
-        <v>-6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-11.1</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-6.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-11.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>58</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>16.7</v>
       </c>
     </row>
@@ -2844,43 +2781,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="15">
-        <v>0.001</v>
-      </c>
-      <c r="B2" s="15">
-        <v>-0.0351</v>
-      </c>
-      <c r="C2" s="15">
-        <v>-0.0554</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.1242</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.1712</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.2128</v>
+      <c r="A2" s="13">
+        <v>-0.0032</v>
+      </c>
+      <c r="B2" s="13">
+        <v>-0.0322</v>
+      </c>
+      <c r="C2" s="13">
+        <v>-0.0584</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.1198</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.1676</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.2055</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -753,10 +753,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +893,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.44</v>
+        <v>24.94</v>
       </c>
       <c r="D2">
-        <v>-0.12</v>
+        <v>2.05</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -908,46 +905,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-27.37</v>
+        <v>-25.88</v>
       </c>
       <c r="H2">
-        <v>6.35</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="I2">
-        <v>-2.28</v>
+        <v>0.24</v>
       </c>
       <c r="J2">
-        <v>-7.35</v>
+        <v>-4.08</v>
       </c>
       <c r="K2">
-        <v>-10.25</v>
+        <v>-9.57</v>
       </c>
       <c r="L2">
-        <v>-26.96</v>
+        <v>-25.17</v>
       </c>
       <c r="M2">
-        <v>-11.98</v>
+        <v>-11</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="P2">
-        <v>24.5</v>
+        <v>24.51</v>
       </c>
       <c r="Q2">
-        <v>25.52</v>
+        <v>25.47</v>
       </c>
       <c r="R2">
-        <v>26.59</v>
+        <v>26.54</v>
       </c>
       <c r="S2">
-        <v>27.62</v>
+        <v>27.59</v>
       </c>
       <c r="T2">
-        <v>-11.51</v>
+        <v>-9.6</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -962,34 +959,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.57</v>
+        <v>43.67</v>
       </c>
       <c r="Z2">
-        <v>-0.57</v>
+        <v>-0.54</v>
       </c>
       <c r="AA2">
-        <v>-0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="AB2">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>27.79</v>
+        <v>30.92</v>
       </c>
       <c r="AD2">
-        <v>25.26</v>
+        <v>27.01</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF2">
-        <v>-15.67</v>
+        <v>-48.54</v>
       </c>
       <c r="AG2">
-        <v>27.1</v>
+        <v>27.06</v>
       </c>
       <c r="AH2">
-        <v>23.94</v>
+        <v>23.88</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -998,7 +995,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>48.95</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1006,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="D3">
-        <v>0.87</v>
+        <v>-0.11</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1021,46 +1018,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.16</v>
+        <v>-33.24</v>
       </c>
       <c r="H3">
-        <v>4.28</v>
+        <v>4.17</v>
       </c>
       <c r="I3">
-        <v>-1.18</v>
+        <v>-0.11</v>
       </c>
       <c r="J3">
-        <v>-6.85</v>
+        <v>-1.39</v>
       </c>
       <c r="K3">
-        <v>-14.43</v>
+        <v>-14.44</v>
       </c>
       <c r="L3">
-        <v>-32.87</v>
+        <v>-32.9</v>
       </c>
       <c r="M3">
-        <v>-16.76</v>
+        <v>-15.78</v>
       </c>
       <c r="N3">
         <v>50</v>
       </c>
       <c r="O3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P3">
         <v>9.140000000000001</v>
       </c>
       <c r="Q3">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R3">
-        <v>10.02</v>
+        <v>9.99</v>
       </c>
       <c r="S3">
-        <v>10.65</v>
+        <v>10.63</v>
       </c>
       <c r="T3">
-        <v>-13.13</v>
+        <v>-13.1</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1075,34 +1072,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.67</v>
+        <v>42.53</v>
       </c>
       <c r="Z3">
         <v>-0.23</v>
       </c>
       <c r="AA3">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="AB3">
-        <v>-0.07000000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>22.83</v>
+        <v>22.78</v>
       </c>
       <c r="AD3">
-        <v>23.14</v>
+        <v>22.3</v>
       </c>
       <c r="AE3">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AF3">
-        <v>-72.81999999999999</v>
+        <v>-82.77</v>
       </c>
       <c r="AG3">
         <v>10.74</v>
       </c>
       <c r="AH3">
-        <v>8.52</v>
+        <v>8.49</v>
       </c>
       <c r="AI3">
         <v>10.36</v>
@@ -1111,7 +1108,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>19.25</v>
+        <v>17.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1119,10 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>205.15</v>
+        <v>207</v>
       </c>
       <c r="D4">
-        <v>-1.01</v>
+        <v>0.9</v>
       </c>
       <c r="E4">
         <v>314.9</v>
@@ -1134,46 +1131,46 @@
         <v>205.03</v>
       </c>
       <c r="G4">
-        <v>-34.85</v>
+        <v>-34.26</v>
       </c>
       <c r="H4">
-        <v>0.06</v>
+        <v>0.96</v>
       </c>
       <c r="I4">
-        <v>-2.95</v>
+        <v>-1.8</v>
       </c>
       <c r="J4">
-        <v>-9.630000000000001</v>
+        <v>-6.12</v>
       </c>
       <c r="K4">
-        <v>-13.47</v>
+        <v>-17.03</v>
       </c>
       <c r="L4">
-        <v>-33.62</v>
+        <v>-32.34</v>
       </c>
       <c r="M4">
-        <v>-5.84</v>
+        <v>-5.57</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P4">
-        <v>206.69</v>
+        <v>205.93</v>
       </c>
       <c r="Q4">
-        <v>213.16</v>
+        <v>212.63</v>
       </c>
       <c r="R4">
-        <v>226.4</v>
+        <v>225.55</v>
       </c>
       <c r="S4">
-        <v>241.85</v>
+        <v>241.42</v>
       </c>
       <c r="T4">
-        <v>-15.18</v>
+        <v>-14.26</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1188,34 +1185,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.34</v>
+        <v>35.22</v>
       </c>
       <c r="Z4">
-        <v>-5.62</v>
+        <v>-5.5</v>
       </c>
       <c r="AA4">
-        <v>-5.29</v>
+        <v>-5.33</v>
       </c>
       <c r="AB4">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="AC4">
-        <v>17.05</v>
+        <v>30.49</v>
       </c>
       <c r="AD4">
-        <v>22.27</v>
+        <v>22.83</v>
       </c>
       <c r="AE4">
-        <v>5.02</v>
+        <v>4.89</v>
       </c>
       <c r="AF4">
-        <v>-10.89</v>
+        <v>-11.06</v>
       </c>
       <c r="AG4">
-        <v>222.48</v>
+        <v>222.1</v>
       </c>
       <c r="AH4">
-        <v>203.85</v>
+        <v>203.17</v>
       </c>
       <c r="AI4">
         <v>219.84</v>
@@ -1224,7 +1221,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>43.12</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1232,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>682.95</v>
+        <v>678.35</v>
       </c>
       <c r="D5">
-        <v>-0.6</v>
+        <v>-0.67</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1247,46 +1244,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-15.06</v>
+        <v>-15.63</v>
       </c>
       <c r="H5">
-        <v>39.18</v>
+        <v>38.24</v>
       </c>
       <c r="I5">
-        <v>-10.99</v>
+        <v>-10.69</v>
       </c>
       <c r="J5">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="K5">
-        <v>-6.23</v>
+        <v>-10</v>
       </c>
       <c r="L5">
-        <v>-12.16</v>
+        <v>-12.5</v>
       </c>
       <c r="M5">
-        <v>-3.22</v>
+        <v>-3.19</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="P5">
-        <v>706.87</v>
+        <v>690.63</v>
       </c>
       <c r="Q5">
-        <v>683.05</v>
+        <v>684.15</v>
       </c>
       <c r="R5">
-        <v>679.64</v>
+        <v>679.59</v>
       </c>
       <c r="S5">
-        <v>617.09</v>
+        <v>616.8099999999999</v>
       </c>
       <c r="T5">
-        <v>10.67</v>
+        <v>9.98</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1301,34 +1298,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>48.37</v>
+        <v>47.2</v>
       </c>
       <c r="Z5">
-        <v>9.25</v>
+        <v>6.94</v>
       </c>
       <c r="AA5">
-        <v>8.85</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AB5">
-        <v>0.4</v>
+        <v>-1.53</v>
       </c>
       <c r="AC5">
-        <v>37.86</v>
+        <v>27.82</v>
       </c>
       <c r="AD5">
-        <v>47.3</v>
+        <v>36.14</v>
       </c>
       <c r="AE5">
-        <v>32.78</v>
+        <v>31.74</v>
       </c>
       <c r="AF5">
-        <v>-88.48999999999999</v>
+        <v>-92.16</v>
       </c>
       <c r="AG5">
-        <v>756.91</v>
+        <v>756.99</v>
       </c>
       <c r="AH5">
-        <v>609.2</v>
+        <v>611.3</v>
       </c>
       <c r="AI5">
         <v>673.0599999999999</v>
@@ -1337,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>25.72</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1345,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.18</v>
+        <v>24.13</v>
       </c>
       <c r="D6">
-        <v>1.38</v>
+        <v>-0.21</v>
       </c>
       <c r="E6">
         <v>48.99</v>
@@ -1360,46 +1357,46 @@
         <v>23.19</v>
       </c>
       <c r="G6">
-        <v>-50.64</v>
+        <v>-50.75</v>
       </c>
       <c r="H6">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="I6">
-        <v>-1.55</v>
+        <v>-0.58</v>
       </c>
       <c r="J6">
-        <v>-9.609999999999999</v>
+        <v>-7.12</v>
       </c>
       <c r="K6">
-        <v>-16.22</v>
+        <v>-17.48</v>
       </c>
       <c r="L6">
-        <v>-50.36</v>
+        <v>-50.01</v>
       </c>
       <c r="M6">
-        <v>-20.55</v>
+        <v>-20.75</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>23.8</v>
+        <v>23.77</v>
       </c>
       <c r="Q6">
-        <v>25.18</v>
+        <v>25.09</v>
       </c>
       <c r="R6">
-        <v>26.77</v>
+        <v>26.67</v>
       </c>
       <c r="S6">
-        <v>31.63</v>
+        <v>31.54</v>
       </c>
       <c r="T6">
-        <v>-23.56</v>
+        <v>-23.5</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1414,34 +1411,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>39.86</v>
+        <v>39.55</v>
       </c>
       <c r="Z6">
-        <v>-0.8</v>
+        <v>-0.78</v>
       </c>
       <c r="AA6">
-        <v>-0.68</v>
+        <v>-0.7</v>
       </c>
       <c r="AB6">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="AC6">
-        <v>24.49</v>
+        <v>38.57</v>
       </c>
       <c r="AD6">
-        <v>15.21</v>
+        <v>24.91</v>
       </c>
       <c r="AE6">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>-16.85</v>
+        <v>-11.15</v>
       </c>
       <c r="AG6">
-        <v>27.28</v>
+        <v>27.22</v>
       </c>
       <c r="AH6">
-        <v>23.08</v>
+        <v>22.97</v>
       </c>
       <c r="AI6">
         <v>26.4</v>
@@ -1450,7 +1447,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>27.49</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1458,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1158</v>
+        <v>1167.4</v>
       </c>
       <c r="D7">
-        <v>-3.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1473,46 +1470,46 @@
         <v>1158</v>
       </c>
       <c r="G7">
-        <v>-26.94</v>
+        <v>-26.35</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I7">
-        <v>-4.22</v>
+        <v>-1.44</v>
       </c>
       <c r="J7">
-        <v>-5.55</v>
+        <v>-2.52</v>
       </c>
       <c r="K7">
-        <v>-8.65</v>
+        <v>-8.5</v>
       </c>
       <c r="L7">
-        <v>-19.68</v>
+        <v>-19.21</v>
       </c>
       <c r="M7">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="N7">
         <v>83</v>
       </c>
       <c r="O7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P7">
-        <v>1186.1</v>
+        <v>1182.68</v>
       </c>
       <c r="Q7">
-        <v>1188.25</v>
+        <v>1187.52</v>
       </c>
       <c r="R7">
-        <v>1242</v>
+        <v>1239.03</v>
       </c>
       <c r="S7">
-        <v>1328.37</v>
+        <v>1326.89</v>
       </c>
       <c r="T7">
-        <v>-12.83</v>
+        <v>-12.02</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1527,34 +1524,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>37.98</v>
+        <v>40.79</v>
       </c>
       <c r="Z7">
-        <v>-14.25</v>
+        <v>-15.02</v>
       </c>
       <c r="AA7">
-        <v>-16.35</v>
+        <v>-16.09</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="AC7">
-        <v>64.91</v>
+        <v>50.66</v>
       </c>
       <c r="AD7">
-        <v>72.45999999999999</v>
+        <v>64.55</v>
       </c>
       <c r="AE7">
-        <v>27.32</v>
+        <v>27.26</v>
       </c>
       <c r="AF7">
-        <v>47.43</v>
+        <v>36.16</v>
       </c>
       <c r="AG7">
-        <v>1225.84</v>
+        <v>1226.17</v>
       </c>
       <c r="AH7">
-        <v>1150.66</v>
+        <v>1148.87</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1563,7 +1560,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>26.75</v>
+        <v>28.12</v>
       </c>
     </row>
   </sheetData>
@@ -1704,7 +1701,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1761,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.73</v>
+        <v>-7.35</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.35</v>
+        <v>-4.08</v>
       </c>
       <c r="E7" s="6">
-        <v>0.38</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1778,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-7.93</v>
+        <v>-6.85</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.85</v>
+        <v>-1.39</v>
       </c>
       <c r="E8" s="6">
-        <v>1.08</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1795,13 +1792,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.789999999999999</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.84</v>
+        <v>-6.12</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1812,13 +1809,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>2.19</v>
+        <v>1.6</v>
       </c>
       <c r="D10" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.59</v>
+        <v>2.94</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.34</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1829,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-11.57</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.609999999999999</v>
+        <v>-7.12</v>
       </c>
       <c r="E11" s="6">
-        <v>1.96</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1846,13 +1843,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-1.89</v>
+        <v>-5.55</v>
       </c>
       <c r="D12" s="5">
-        <v>-5.55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.66</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3.03</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1863,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-5.23</v>
+        <v>-2.28</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.28</v>
+        <v>0.24</v>
       </c>
       <c r="E13" s="6">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1880,13 +1877,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-5.95</v>
+        <v>-1.18</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.18</v>
+        <v>-0.11</v>
       </c>
       <c r="E14" s="6">
-        <v>4.77</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1897,13 +1894,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-3.16</v>
+        <v>-2.95</v>
       </c>
       <c r="D15" s="5">
-        <v>-2.95</v>
+        <v>-1.8</v>
       </c>
       <c r="E15" s="6">
-        <v>0.21</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1914,13 +1911,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.1</v>
+        <v>-10.99</v>
       </c>
       <c r="D16" s="5">
-        <v>-10.99</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-4.89</v>
+        <v>-10.69</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1931,13 +1928,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-6.8</v>
+        <v>-1.55</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.55</v>
+        <v>-0.58</v>
       </c>
       <c r="E17" s="6">
-        <v>5.25</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1948,13 +1945,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-0.48</v>
+        <v>-4.22</v>
       </c>
       <c r="D18" s="5">
-        <v>-4.22</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.74</v>
+        <v>-1.44</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.78</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1965,13 +1962,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.93</v>
+        <v>-26.96</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.03</v>
+        <v>-25.17</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1982,13 +1979,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.57</v>
+        <v>-32.87</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.87</v>
+        <v>-32.9</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1999,13 +1996,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.53</v>
+        <v>-33.62</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.62</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.09</v>
+        <v>-32.34</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.28</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2016,13 +2013,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-13.5</v>
+        <v>-12.16</v>
       </c>
       <c r="D22" s="5">
-        <v>-12.16</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1.34</v>
+        <v>-12.5</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2033,13 +2030,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-51.16</v>
+        <v>-50.36</v>
       </c>
       <c r="D23" s="5">
-        <v>-50.36</v>
+        <v>-50.01</v>
       </c>
       <c r="E23" s="6">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2050,13 +2047,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-17.98</v>
+        <v>-19.68</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.68</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.7</v>
+        <v>-19.21</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.47</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2067,13 +2064,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.6</v>
+        <v>-10.25</v>
       </c>
       <c r="D25" s="5">
-        <v>-10.25</v>
+        <v>-9.57</v>
       </c>
       <c r="E25" s="6">
-        <v>0.35</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2084,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-15.72</v>
+        <v>-14.43</v>
       </c>
       <c r="D26" s="5">
-        <v>-14.43</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.29</v>
+        <v>-14.44</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2101,13 +2098,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-12.25</v>
+        <v>-13.47</v>
       </c>
       <c r="D27" s="5">
-        <v>-13.47</v>
+        <v>-17.03</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.22</v>
+        <v>-3.56</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2118,13 +2115,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>-4.4</v>
+        <v>-6.23</v>
       </c>
       <c r="D28" s="5">
-        <v>-6.23</v>
+        <v>-10</v>
       </c>
       <c r="E28" s="7">
-        <v>-1.83</v>
+        <v>-3.77</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2135,13 +2132,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-17.33</v>
+        <v>-16.22</v>
       </c>
       <c r="D29" s="5">
-        <v>-16.22</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.11</v>
+        <v>-17.48</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2152,13 +2149,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.55</v>
+        <v>-8.65</v>
       </c>
       <c r="D30" s="5">
-        <v>-8.65</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.1</v>
+        <v>-8.5</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2169,13 +2166,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.28</v>
+        <v>-27.37</v>
       </c>
       <c r="D31" s="5">
-        <v>-27.37</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.09</v>
+        <v>-25.88</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.49</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2186,13 +2183,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-33.74</v>
+        <v>-33.16</v>
       </c>
       <c r="D32" s="5">
-        <v>-33.16</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.58</v>
+        <v>-33.24</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2203,13 +2200,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-34.19</v>
+        <v>-34.85</v>
       </c>
       <c r="D33" s="5">
-        <v>-34.85</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.66</v>
+        <v>-34.26</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2220,13 +2217,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-14.55</v>
+        <v>-15.06</v>
       </c>
       <c r="D34" s="5">
-        <v>-15.06</v>
+        <v>-15.63</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.51</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2237,13 +2234,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-51.32</v>
+        <v>-50.64</v>
       </c>
       <c r="D35" s="5">
-        <v>-50.64</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.68</v>
+        <v>-50.75</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2254,13 +2251,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-24.53</v>
+        <v>-26.94</v>
       </c>
       <c r="D36" s="5">
-        <v>-26.94</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.41</v>
+        <v>-26.35</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.59</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2271,13 +2268,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>24.47</v>
+        <v>24.44</v>
       </c>
       <c r="D37" s="5">
-        <v>24.44</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.03</v>
+        <v>24.94</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2288,13 +2285,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.17</v>
+        <v>9.25</v>
       </c>
       <c r="D38" s="5">
-        <v>9.25</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.08</v>
+        <v>9.24</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2305,13 +2302,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>207.24</v>
+        <v>205.15</v>
       </c>
       <c r="D39" s="5">
-        <v>205.15</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.09</v>
+        <v>207</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1.85</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2322,13 +2319,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>687.1</v>
+        <v>682.95</v>
       </c>
       <c r="D40" s="5">
-        <v>682.95</v>
+        <v>678.35</v>
       </c>
       <c r="E40" s="7">
-        <v>-4.15</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2339,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>23.85</v>
+        <v>24.18</v>
       </c>
       <c r="D41" s="5">
-        <v>24.18</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.33</v>
+        <v>24.13</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2356,251 +2353,217 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1196.2</v>
+        <v>1158</v>
       </c>
       <c r="D42" s="5">
-        <v>1158</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-38.2</v>
+        <v>1167.4</v>
+      </c>
+      <c r="E42" s="6">
+        <v>9.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>33</v>
+        <v>38.57</v>
       </c>
       <c r="D43" s="5">
-        <v>50</v>
+        <v>43.67</v>
       </c>
       <c r="E43" s="6">
-        <v>17</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C44" s="5">
-        <v>50</v>
+        <v>42.67</v>
       </c>
       <c r="D44" s="5">
-        <v>33</v>
+        <v>42.53</v>
       </c>
       <c r="E44" s="7">
-        <v>-17</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>38.77</v>
+        <v>31.34</v>
       </c>
       <c r="D45" s="5">
-        <v>38.57</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.2</v>
+        <v>35.22</v>
+      </c>
+      <c r="E45" s="6">
+        <v>3.88</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>41.27</v>
+        <v>48.37</v>
       </c>
       <c r="D46" s="5">
-        <v>42.67</v>
-      </c>
-      <c r="E46" s="6">
-        <v>1.4</v>
+        <v>47.2</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>33.45</v>
+        <v>39.86</v>
       </c>
       <c r="D47" s="5">
-        <v>31.34</v>
+        <v>39.55</v>
       </c>
       <c r="E47" s="7">
-        <v>-2.11</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>49.39</v>
+        <v>37.98</v>
       </c>
       <c r="D48" s="5">
-        <v>48.37</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-1.02</v>
+        <v>40.79</v>
+      </c>
+      <c r="E48" s="6">
+        <v>2.81</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C49" s="5">
-        <v>36.88</v>
+        <v>-15.67</v>
       </c>
       <c r="D49" s="5">
-        <v>39.86</v>
-      </c>
-      <c r="E49" s="6">
-        <v>2.98</v>
+        <v>-48.54</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-32.87</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C50" s="5">
-        <v>46.27</v>
+        <v>-72.81999999999999</v>
       </c>
       <c r="D50" s="5">
-        <v>37.98</v>
+        <v>-82.77</v>
       </c>
       <c r="E50" s="7">
-        <v>-8.289999999999999</v>
+        <v>-9.949999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>-59.72</v>
+        <v>-10.89</v>
       </c>
       <c r="D51" s="5">
-        <v>-15.67</v>
-      </c>
-      <c r="E51" s="6">
-        <v>44.05</v>
+        <v>-11.06</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-58.78</v>
+        <v>-88.48999999999999</v>
       </c>
       <c r="D52" s="5">
-        <v>-72.81999999999999</v>
+        <v>-92.16</v>
       </c>
       <c r="E52" s="7">
-        <v>-14.04</v>
+        <v>-3.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>4.83</v>
+        <v>-16.85</v>
       </c>
       <c r="D53" s="5">
-        <v>-10.89</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-15.72</v>
+        <v>-11.15</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5.7</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>-81.94</v>
+        <v>47.43</v>
       </c>
       <c r="D54" s="5">
-        <v>-88.48999999999999</v>
+        <v>36.16</v>
       </c>
       <c r="E54" s="7">
-        <v>-6.55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C55" s="5">
-        <v>50.35</v>
-      </c>
-      <c r="D55" s="5">
-        <v>-16.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-67.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-12.1</v>
-      </c>
-      <c r="D56" s="5">
-        <v>47.43</v>
-      </c>
-      <c r="E56" s="6">
-        <v>59.53</v>
+        <v>-11.27</v>
       </c>
     </row>
   </sheetData>
@@ -2665,16 +2628,16 @@
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="E2" s="10">
         <v>16.7</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.2</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="10">
-        <v>-11.5</v>
+        <v>-12.8</v>
       </c>
       <c r="H2" s="10">
         <v>58</v>
@@ -2802,22 +2765,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>-0.0032</v>
+        <v>0.0032</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0322</v>
+        <v>-0.0319</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0584</v>
+        <v>-0.0557</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.1198</v>
+        <v>-0.11</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1676</v>
+        <v>-0.1578</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.2055</v>
+        <v>-0.2075</v>
       </c>
     </row>
   </sheetData>

--- a/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
+++ b/MUKESH_AMBANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>DOWN</t>
-  </si>
-  <si>
-    <t>UP</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -255,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -893,10 +890,10 @@
         <v>43</v>
       </c>
       <c r="C2">
-        <v>24.94</v>
+        <v>24.38</v>
       </c>
       <c r="D2">
-        <v>2.05</v>
+        <v>-2.25</v>
       </c>
       <c r="E2">
         <v>33.65</v>
@@ -905,46 +902,46 @@
         <v>22.98</v>
       </c>
       <c r="G2">
-        <v>-25.88</v>
+        <v>-27.55</v>
       </c>
       <c r="H2">
-        <v>8.529999999999999</v>
+        <v>6.09</v>
       </c>
       <c r="I2">
-        <v>0.24</v>
+        <v>1.29</v>
       </c>
       <c r="J2">
-        <v>-4.08</v>
+        <v>-5.91</v>
       </c>
       <c r="K2">
-        <v>-9.57</v>
+        <v>-11.09</v>
       </c>
       <c r="L2">
-        <v>-25.17</v>
+        <v>-26.72</v>
       </c>
       <c r="M2">
-        <v>-11</v>
+        <v>-11.43</v>
       </c>
       <c r="N2">
         <v>66</v>
       </c>
       <c r="O2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P2">
-        <v>24.51</v>
+        <v>24.57</v>
       </c>
       <c r="Q2">
-        <v>25.47</v>
+        <v>25.39</v>
       </c>
       <c r="R2">
-        <v>26.54</v>
+        <v>26.48</v>
       </c>
       <c r="S2">
-        <v>27.59</v>
+        <v>27.55</v>
       </c>
       <c r="T2">
-        <v>-9.6</v>
+        <v>-11.52</v>
       </c>
       <c r="U2" t="s">
         <v>44</v>
@@ -959,34 +956,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>43.67</v>
+        <v>39.7</v>
       </c>
       <c r="Z2">
-        <v>-0.54</v>
+        <v>-0.55</v>
       </c>
       <c r="AA2">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="AB2">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>30.92</v>
+        <v>29.61</v>
       </c>
       <c r="AD2">
-        <v>27.01</v>
+        <v>29.44</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>-48.54</v>
+        <v>-49.4</v>
       </c>
       <c r="AG2">
-        <v>27.06</v>
+        <v>27.04</v>
       </c>
       <c r="AH2">
-        <v>23.88</v>
+        <v>23.75</v>
       </c>
       <c r="AI2">
         <v>27.51</v>
@@ -995,7 +992,7 @@
         <v>46</v>
       </c>
       <c r="AK2">
-        <v>48.6</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1003,10 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>9.24</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D3">
-        <v>-0.11</v>
+        <v>-2.06</v>
       </c>
       <c r="E3">
         <v>13.84</v>
@@ -1018,46 +1015,46 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G3">
-        <v>-33.24</v>
+        <v>-34.61</v>
       </c>
       <c r="H3">
-        <v>4.17</v>
+        <v>2.03</v>
       </c>
       <c r="I3">
-        <v>-0.11</v>
+        <v>0.22</v>
       </c>
       <c r="J3">
-        <v>-1.39</v>
+        <v>-4.64</v>
       </c>
       <c r="K3">
-        <v>-14.44</v>
+        <v>-15.81</v>
       </c>
       <c r="L3">
-        <v>-32.9</v>
+        <v>-34.42</v>
       </c>
       <c r="M3">
-        <v>-15.78</v>
+        <v>-16.1</v>
       </c>
       <c r="N3">
         <v>50</v>
       </c>
       <c r="O3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3">
         <v>9.140000000000001</v>
       </c>
       <c r="Q3">
-        <v>9.619999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R3">
-        <v>9.99</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="S3">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
       <c r="T3">
-        <v>-13.1</v>
+        <v>-14.77</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1072,43 +1069,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>42.53</v>
+        <v>39.92</v>
       </c>
       <c r="Z3">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="AA3">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AB3">
         <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>22.78</v>
+        <v>16.68</v>
       </c>
       <c r="AD3">
-        <v>22.3</v>
+        <v>20.76</v>
       </c>
       <c r="AE3">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="AF3">
-        <v>-82.77</v>
+        <v>-49.27</v>
       </c>
       <c r="AG3">
         <v>10.74</v>
       </c>
       <c r="AH3">
-        <v>8.49</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AI3">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>17.84</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,58 +1116,58 @@
         <v>43</v>
       </c>
       <c r="C4">
-        <v>207</v>
+        <v>204.5</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>-1.21</v>
       </c>
       <c r="E4">
         <v>314.9</v>
       </c>
       <c r="F4">
-        <v>205.03</v>
+        <v>204.5</v>
       </c>
       <c r="G4">
-        <v>-34.26</v>
+        <v>-35.06</v>
       </c>
       <c r="H4">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.8</v>
+        <v>-0.26</v>
       </c>
       <c r="J4">
-        <v>-6.12</v>
+        <v>-6</v>
       </c>
       <c r="K4">
-        <v>-17.03</v>
+        <v>-17.19</v>
       </c>
       <c r="L4">
-        <v>-32.34</v>
+        <v>-33.07</v>
       </c>
       <c r="M4">
-        <v>-5.57</v>
+        <v>-5.92</v>
       </c>
       <c r="N4">
         <v>33</v>
       </c>
       <c r="O4">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>205.93</v>
+        <v>205.82</v>
       </c>
       <c r="Q4">
-        <v>212.63</v>
+        <v>212.02</v>
       </c>
       <c r="R4">
-        <v>225.55</v>
+        <v>224.72</v>
       </c>
       <c r="S4">
-        <v>241.42</v>
+        <v>241.01</v>
       </c>
       <c r="T4">
-        <v>-14.26</v>
+        <v>-15.15</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1185,34 +1182,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>35.22</v>
+        <v>32.55</v>
       </c>
       <c r="Z4">
-        <v>-5.5</v>
+        <v>-5.54</v>
       </c>
       <c r="AA4">
-        <v>-5.33</v>
+        <v>-5.37</v>
       </c>
       <c r="AB4">
         <v>-0.17</v>
       </c>
       <c r="AC4">
-        <v>30.49</v>
+        <v>28.48</v>
       </c>
       <c r="AD4">
-        <v>22.83</v>
+        <v>25.34</v>
       </c>
       <c r="AE4">
-        <v>4.89</v>
+        <v>4.72</v>
       </c>
       <c r="AF4">
-        <v>-11.06</v>
+        <v>-35.33</v>
       </c>
       <c r="AG4">
-        <v>222.1</v>
+        <v>221.92</v>
       </c>
       <c r="AH4">
-        <v>203.17</v>
+        <v>202.11</v>
       </c>
       <c r="AI4">
         <v>219.84</v>
@@ -1221,7 +1218,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>42.5</v>
+        <v>42.03</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1229,10 @@
         <v>43</v>
       </c>
       <c r="C5">
-        <v>678.35</v>
+        <v>644.5</v>
       </c>
       <c r="D5">
-        <v>-0.67</v>
+        <v>-4.99</v>
       </c>
       <c r="E5">
         <v>804.05</v>
@@ -1244,46 +1241,46 @@
         <v>490.7</v>
       </c>
       <c r="G5">
-        <v>-15.63</v>
+        <v>-19.84</v>
       </c>
       <c r="H5">
-        <v>38.24</v>
+        <v>31.34</v>
       </c>
       <c r="I5">
-        <v>-10.69</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>-1.83</v>
       </c>
       <c r="K5">
-        <v>-10</v>
+        <v>-13.1</v>
       </c>
       <c r="L5">
-        <v>-12.5</v>
+        <v>-18.56</v>
       </c>
       <c r="M5">
-        <v>-3.19</v>
+        <v>-3.94</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="O5">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P5">
-        <v>690.63</v>
+        <v>678.34</v>
       </c>
       <c r="Q5">
-        <v>684.15</v>
+        <v>683.0599999999999</v>
       </c>
       <c r="R5">
-        <v>679.59</v>
+        <v>679.26</v>
       </c>
       <c r="S5">
-        <v>616.8099999999999</v>
+        <v>616.45</v>
       </c>
       <c r="T5">
-        <v>9.98</v>
+        <v>4.55</v>
       </c>
       <c r="U5" t="s">
         <v>45</v>
@@ -1298,43 +1295,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>47.2</v>
+        <v>39.61</v>
       </c>
       <c r="Z5">
-        <v>6.94</v>
+        <v>2.35</v>
       </c>
       <c r="AA5">
-        <v>8.470000000000001</v>
+        <v>7.24</v>
       </c>
       <c r="AB5">
-        <v>-1.53</v>
+        <v>-4.89</v>
       </c>
       <c r="AC5">
-        <v>27.82</v>
+        <v>15.74</v>
       </c>
       <c r="AD5">
-        <v>36.14</v>
+        <v>27.14</v>
       </c>
       <c r="AE5">
-        <v>31.74</v>
+        <v>32.32</v>
       </c>
       <c r="AF5">
-        <v>-92.16</v>
+        <v>-84.2</v>
       </c>
       <c r="AG5">
-        <v>756.99</v>
+        <v>757.65</v>
       </c>
       <c r="AH5">
-        <v>611.3</v>
+        <v>608.47</v>
       </c>
       <c r="AI5">
-        <v>673.0599999999999</v>
+        <v>756.88</v>
       </c>
       <c r="AJ5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AK5">
-        <v>23.3</v>
+        <v>24.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1342,10 @@
         <v>43</v>
       </c>
       <c r="C6">
-        <v>24.13</v>
+        <v>23.75</v>
       </c>
       <c r="D6">
-        <v>-0.21</v>
+        <v>-1.57</v>
       </c>
       <c r="E6">
         <v>48.99</v>
@@ -1357,46 +1354,46 @@
         <v>23.19</v>
       </c>
       <c r="G6">
-        <v>-50.75</v>
+        <v>-51.52</v>
       </c>
       <c r="H6">
-        <v>4.05</v>
+        <v>2.41</v>
       </c>
       <c r="I6">
-        <v>-0.58</v>
+        <v>1.06</v>
       </c>
       <c r="J6">
-        <v>-7.12</v>
+        <v>-8.23</v>
       </c>
       <c r="K6">
-        <v>-17.48</v>
+        <v>-18.91</v>
       </c>
       <c r="L6">
-        <v>-50.01</v>
+        <v>-50.26</v>
       </c>
       <c r="M6">
-        <v>-20.75</v>
+        <v>-22.02</v>
       </c>
       <c r="N6">
         <v>17</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6">
-        <v>23.77</v>
+        <v>23.82</v>
       </c>
       <c r="Q6">
-        <v>25.09</v>
+        <v>24.99</v>
       </c>
       <c r="R6">
-        <v>26.67</v>
+        <v>26.58</v>
       </c>
       <c r="S6">
-        <v>31.54</v>
+        <v>31.45</v>
       </c>
       <c r="T6">
-        <v>-23.5</v>
+        <v>-24.49</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1411,34 +1408,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>39.55</v>
+        <v>37.22</v>
       </c>
       <c r="Z6">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="AA6">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="AB6">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC6">
-        <v>38.57</v>
+        <v>39.11</v>
       </c>
       <c r="AD6">
-        <v>24.91</v>
+        <v>34.06</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AF6">
-        <v>-11.15</v>
+        <v>630.0700000000001</v>
       </c>
       <c r="AG6">
-        <v>27.22</v>
+        <v>27.16</v>
       </c>
       <c r="AH6">
-        <v>22.97</v>
+        <v>22.82</v>
       </c>
       <c r="AI6">
         <v>26.4</v>
@@ -1447,7 +1444,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>25.66</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1455,10 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>1167.4</v>
+        <v>1164.9</v>
       </c>
       <c r="D7">
-        <v>0.8100000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="E7">
         <v>1584.97</v>
@@ -1470,46 +1467,46 @@
         <v>1158</v>
       </c>
       <c r="G7">
-        <v>-26.35</v>
+        <v>-26.5</v>
       </c>
       <c r="H7">
-        <v>0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I7">
-        <v>-1.44</v>
+        <v>-2.11</v>
       </c>
       <c r="J7">
-        <v>-2.52</v>
+        <v>-1.45</v>
       </c>
       <c r="K7">
-        <v>-8.5</v>
+        <v>-9.9</v>
       </c>
       <c r="L7">
-        <v>-19.21</v>
+        <v>-21.15</v>
       </c>
       <c r="M7">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="N7">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O7">
         <v>47</v>
       </c>
       <c r="P7">
-        <v>1182.68</v>
+        <v>1177.66</v>
       </c>
       <c r="Q7">
-        <v>1187.52</v>
+        <v>1186.41</v>
       </c>
       <c r="R7">
-        <v>1239.03</v>
+        <v>1235.88</v>
       </c>
       <c r="S7">
-        <v>1326.89</v>
+        <v>1325.37</v>
       </c>
       <c r="T7">
-        <v>-12.02</v>
+        <v>-12.11</v>
       </c>
       <c r="U7" t="s">
         <v>44</v>
@@ -1524,34 +1521,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>40.79</v>
+        <v>40.27</v>
       </c>
       <c r="Z7">
-        <v>-15.02</v>
+        <v>-15.64</v>
       </c>
       <c r="AA7">
-        <v>-16.09</v>
+        <v>-16</v>
       </c>
       <c r="AB7">
-        <v>1.07</v>
+        <v>0.36</v>
       </c>
       <c r="AC7">
-        <v>50.66</v>
+        <v>38.25</v>
       </c>
       <c r="AD7">
-        <v>64.55</v>
+        <v>51.27</v>
       </c>
       <c r="AE7">
-        <v>27.26</v>
+        <v>26.89</v>
       </c>
       <c r="AF7">
-        <v>36.16</v>
+        <v>-5.51</v>
       </c>
       <c r="AG7">
-        <v>1226.17</v>
+        <v>1226.37</v>
       </c>
       <c r="AH7">
-        <v>1148.87</v>
+        <v>1146.46</v>
       </c>
       <c r="AI7">
         <v>1227.59</v>
@@ -1560,7 +1557,7 @@
         <v>46</v>
       </c>
       <c r="AK7">
-        <v>28.12</v>
+        <v>29.65</v>
       </c>
     </row>
   </sheetData>
@@ -1664,27 +1661,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U7">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V7">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W7">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y7">
@@ -1701,7 +1698,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1711,7 +1708,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1721,12 +1718,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1738,16 +1735,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1758,13 +1755,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.35</v>
+        <v>-4.08</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.08</v>
+        <v>-5.91</v>
       </c>
       <c r="E7" s="6">
-        <v>3.27</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1775,13 +1772,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-6.85</v>
+        <v>-1.39</v>
       </c>
       <c r="D8" s="5">
-        <v>-1.39</v>
+        <v>-4.64</v>
       </c>
       <c r="E8" s="6">
-        <v>5.46</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1792,13 +1789,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-9.630000000000001</v>
+        <v>-6.12</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.12</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.51</v>
+        <v>-6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1809,13 +1806,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="D10" s="5">
-        <v>2.94</v>
+        <v>-1.83</v>
       </c>
       <c r="E10" s="6">
-        <v>1.34</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1826,13 +1823,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-9.609999999999999</v>
+        <v>-7.12</v>
       </c>
       <c r="D11" s="5">
-        <v>-7.12</v>
+        <v>-8.23</v>
       </c>
       <c r="E11" s="6">
-        <v>2.49</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1843,13 +1840,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-5.55</v>
+        <v>-2.52</v>
       </c>
       <c r="D12" s="5">
-        <v>-2.52</v>
-      </c>
-      <c r="E12" s="6">
-        <v>3.03</v>
+        <v>-1.45</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1860,13 +1857,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.28</v>
+        <v>0.24</v>
       </c>
       <c r="D13" s="5">
-        <v>0.24</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2.52</v>
+        <v>1.29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1877,13 +1874,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.18</v>
+        <v>-0.11</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.11</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1.07</v>
+        <v>0.22</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1894,13 +1891,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-2.95</v>
+        <v>-1.8</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.8</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.15</v>
+        <v>-0.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1911,13 +1908,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-10.99</v>
+        <v>-10.69</v>
       </c>
       <c r="D16" s="5">
-        <v>-10.69</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.3</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1928,13 +1925,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.55</v>
+        <v>-0.58</v>
       </c>
       <c r="D17" s="5">
-        <v>-0.58</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.97</v>
+        <v>1.06</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1945,13 +1942,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.22</v>
+        <v>-1.44</v>
       </c>
       <c r="D18" s="5">
-        <v>-1.44</v>
+        <v>-2.11</v>
       </c>
       <c r="E18" s="6">
-        <v>2.78</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1962,13 +1959,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.96</v>
+        <v>-25.17</v>
       </c>
       <c r="D19" s="5">
-        <v>-25.17</v>
+        <v>-26.72</v>
       </c>
       <c r="E19" s="6">
-        <v>1.79</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1979,13 +1976,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.87</v>
+        <v>-32.9</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.9</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.03</v>
+        <v>-34.42</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1996,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-33.62</v>
+        <v>-32.34</v>
       </c>
       <c r="D21" s="5">
-        <v>-32.34</v>
+        <v>-33.07</v>
       </c>
       <c r="E21" s="6">
-        <v>1.28</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2013,13 +2010,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>-12.16</v>
+        <v>-12.5</v>
       </c>
       <c r="D22" s="5">
-        <v>-12.5</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.34</v>
+        <v>-18.56</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-6.06</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2030,13 +2027,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-50.36</v>
+        <v>-50.01</v>
       </c>
       <c r="D23" s="5">
-        <v>-50.01</v>
+        <v>-50.26</v>
       </c>
       <c r="E23" s="6">
-        <v>0.35</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2047,13 +2044,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-19.68</v>
+        <v>-19.21</v>
       </c>
       <c r="D24" s="5">
-        <v>-19.21</v>
+        <v>-21.15</v>
       </c>
       <c r="E24" s="6">
-        <v>0.47</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2064,13 +2061,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-10.25</v>
+        <v>-9.57</v>
       </c>
       <c r="D25" s="5">
-        <v>-9.57</v>
+        <v>-11.09</v>
       </c>
       <c r="E25" s="6">
-        <v>0.68</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2081,13 +2078,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-14.43</v>
+        <v>-14.44</v>
       </c>
       <c r="D26" s="5">
-        <v>-14.44</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.01</v>
+        <v>-15.81</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2098,13 +2095,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="5">
-        <v>-13.47</v>
+        <v>-17.03</v>
       </c>
       <c r="D27" s="5">
-        <v>-17.03</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.56</v>
+        <v>-17.19</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2115,13 +2112,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>-6.23</v>
+        <v>-10</v>
       </c>
       <c r="D28" s="5">
-        <v>-10</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.77</v>
+        <v>-13.1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2132,13 +2129,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-16.22</v>
+        <v>-17.48</v>
       </c>
       <c r="D29" s="5">
-        <v>-17.48</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.26</v>
+        <v>-18.91</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2149,13 +2146,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-8.65</v>
+        <v>-8.5</v>
       </c>
       <c r="D30" s="5">
-        <v>-8.5</v>
+        <v>-9.9</v>
       </c>
       <c r="E30" s="6">
-        <v>0.15</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2166,13 +2163,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-27.37</v>
+        <v>-25.88</v>
       </c>
       <c r="D31" s="5">
-        <v>-25.88</v>
+        <v>-27.55</v>
       </c>
       <c r="E31" s="6">
-        <v>1.49</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2183,13 +2180,13 @@
         <v>6</v>
       </c>
       <c r="C32" s="5">
-        <v>-33.16</v>
+        <v>-33.24</v>
       </c>
       <c r="D32" s="5">
-        <v>-33.24</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.08</v>
+        <v>-34.61</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2200,13 +2197,13 @@
         <v>6</v>
       </c>
       <c r="C33" s="5">
-        <v>-34.85</v>
+        <v>-34.26</v>
       </c>
       <c r="D33" s="5">
-        <v>-34.26</v>
+        <v>-35.06</v>
       </c>
       <c r="E33" s="6">
-        <v>0.59</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2217,13 +2214,13 @@
         <v>6</v>
       </c>
       <c r="C34" s="5">
-        <v>-15.06</v>
+        <v>-15.63</v>
       </c>
       <c r="D34" s="5">
-        <v>-15.63</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.57</v>
+        <v>-19.84</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-4.21</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2234,13 +2231,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-50.64</v>
+        <v>-50.75</v>
       </c>
       <c r="D35" s="5">
-        <v>-50.75</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.11</v>
+        <v>-51.52</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2251,13 +2248,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-26.94</v>
+        <v>-26.35</v>
       </c>
       <c r="D36" s="5">
-        <v>-26.35</v>
+        <v>-26.5</v>
       </c>
       <c r="E36" s="6">
-        <v>0.59</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2268,13 +2265,13 @@
         <v>2</v>
       </c>
       <c r="C37" s="5">
-        <v>24.44</v>
+        <v>24.94</v>
       </c>
       <c r="D37" s="5">
-        <v>24.94</v>
+        <v>24.38</v>
       </c>
       <c r="E37" s="6">
-        <v>0.5</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2285,13 +2282,13 @@
         <v>2</v>
       </c>
       <c r="C38" s="5">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="D38" s="5">
-        <v>9.24</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.01</v>
+        <v>9.050000000000001</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2302,13 +2299,13 @@
         <v>2</v>
       </c>
       <c r="C39" s="5">
-        <v>205.15</v>
+        <v>207</v>
       </c>
       <c r="D39" s="5">
-        <v>207</v>
+        <v>204.5</v>
       </c>
       <c r="E39" s="6">
-        <v>1.85</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2319,13 +2316,13 @@
         <v>2</v>
       </c>
       <c r="C40" s="5">
-        <v>682.95</v>
+        <v>678.35</v>
       </c>
       <c r="D40" s="5">
-        <v>678.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-4.6</v>
+        <v>644.5</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-33.85</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2336,13 +2333,13 @@
         <v>2</v>
       </c>
       <c r="C41" s="5">
-        <v>24.18</v>
+        <v>24.13</v>
       </c>
       <c r="D41" s="5">
-        <v>24.13</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.05</v>
+        <v>23.75</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2353,217 +2350,251 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1158</v>
+        <v>1167.4</v>
       </c>
       <c r="D42" s="5">
-        <v>1167.4</v>
+        <v>1164.9</v>
       </c>
       <c r="E42" s="6">
-        <v>9.4</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C43" s="5">
-        <v>38.57</v>
+        <v>99</v>
       </c>
       <c r="D43" s="5">
-        <v>43.67</v>
+        <v>83</v>
       </c>
       <c r="E43" s="6">
-        <v>5.1</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C44" s="5">
-        <v>42.67</v>
+        <v>83</v>
       </c>
       <c r="D44" s="5">
-        <v>42.53</v>
+        <v>99</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="5">
-        <v>31.34</v>
+        <v>43.67</v>
       </c>
       <c r="D45" s="5">
-        <v>35.22</v>
+        <v>39.7</v>
       </c>
       <c r="E45" s="6">
-        <v>3.88</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="5">
-        <v>48.37</v>
+        <v>42.53</v>
       </c>
       <c r="D46" s="5">
-        <v>47.2</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.17</v>
+        <v>39.92</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="5">
-        <v>39.86</v>
+        <v>35.22</v>
       </c>
       <c r="D47" s="5">
-        <v>39.55</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.31</v>
+        <v>32.55</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C48" s="5">
-        <v>37.98</v>
+        <v>47.2</v>
       </c>
       <c r="D48" s="5">
-        <v>40.79</v>
+        <v>39.61</v>
       </c>
       <c r="E48" s="6">
-        <v>2.81</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>-15.67</v>
+        <v>39.55</v>
       </c>
       <c r="D49" s="5">
-        <v>-48.54</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-32.87</v>
+        <v>37.22</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-2.33</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>-72.81999999999999</v>
+        <v>40.79</v>
       </c>
       <c r="D50" s="5">
-        <v>-82.77</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-9.949999999999999</v>
+        <v>40.27</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C51" s="5">
-        <v>-10.89</v>
+        <v>-48.54</v>
       </c>
       <c r="D51" s="5">
-        <v>-11.06</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.17</v>
+        <v>-49.4</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C52" s="5">
-        <v>-88.48999999999999</v>
+        <v>-82.77</v>
       </c>
       <c r="D52" s="5">
-        <v>-92.16</v>
+        <v>-49.27</v>
       </c>
       <c r="E52" s="7">
-        <v>-3.67</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C53" s="5">
-        <v>-16.85</v>
+        <v>-11.06</v>
       </c>
       <c r="D53" s="5">
-        <v>-11.15</v>
+        <v>-35.33</v>
       </c>
       <c r="E53" s="6">
-        <v>5.7</v>
+        <v>-24.27</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C54" s="5">
-        <v>47.43</v>
+        <v>-92.16</v>
       </c>
       <c r="D54" s="5">
+        <v>-84.2</v>
+      </c>
+      <c r="E54" s="7">
+        <v>7.96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-11.15</v>
+      </c>
+      <c r="D55" s="5">
+        <v>630.0700000000001</v>
+      </c>
+      <c r="E55" s="7">
+        <v>641.22</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
         <v>36.16</v>
       </c>
-      <c r="E54" s="7">
-        <v>-11.27</v>
+      <c r="D56" s="5">
+        <v>-5.51</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-41.67</v>
       </c>
     </row>
   </sheetData>
@@ -2593,28 +2624,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2622,22 +2653,22 @@
         <v>43</v>
       </c>
       <c r="B2" s="10">
-        <v>39.88</v>
+        <v>39.9</v>
       </c>
       <c r="C2" s="11">
         <v>6</v>
       </c>
       <c r="D2" s="10">
-        <v>41.5</v>
+        <v>38.2</v>
       </c>
       <c r="E2" s="10">
         <v>16.7</v>
       </c>
       <c r="F2" s="10">
-        <v>-3</v>
+        <v>-4.7</v>
       </c>
       <c r="G2" s="10">
-        <v>-12.8</v>
+        <v>-14.3</v>
       </c>
       <c r="H2" s="10">
         <v>58</v>
@@ -2765,22 +2796,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="13">
-        <v>0.0032</v>
+        <v>0.0027</v>
       </c>
       <c r="B2" s="13">
-        <v>-0.0319</v>
+        <v>-0.0394</v>
       </c>
       <c r="C2" s="13">
-        <v>-0.0557</v>
+        <v>-0.0592</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.11</v>
+        <v>-0.1143</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.1578</v>
+        <v>-0.161</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.2075</v>
+        <v>-0.2202</v>
       </c>
     </row>
   </sheetData>
